--- a/results/cluster_ga/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
@@ -672,31 +672,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.5759275485993</v>
+        <v>28.69129801235542</v>
       </c>
       <c r="C2" t="n">
-        <v>24.33238424813723</v>
+        <v>41.72556510633359</v>
       </c>
       <c r="D2" t="n">
-        <v>27.5111441538676</v>
+        <v>30.89476832700868</v>
       </c>
       <c r="E2" t="n">
-        <v>36.16312711349127</v>
+        <v>26.11306329430092</v>
       </c>
       <c r="F2" t="n">
-        <v>33.40517238520574</v>
+        <v>31.05914109135398</v>
       </c>
       <c r="G2" t="n">
-        <v>35.83513574189546</v>
+        <v>43.99024550258977</v>
       </c>
       <c r="H2" t="n">
-        <v>35.63060529500967</v>
+        <v>58.10445935612326</v>
       </c>
       <c r="I2" t="n">
-        <v>34.89319692150355</v>
+        <v>33.46674495411732</v>
       </c>
       <c r="J2" t="n">
-        <v>37.0084478095403</v>
+        <v>49.80966224685074</v>
       </c>
     </row>
   </sheetData>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.68026366912186</v>
+        <v>31.35319382345633</v>
       </c>
       <c r="C2" t="n">
-        <v>33.78197327280043</v>
+        <v>41.62324811871258</v>
       </c>
       <c r="D2" t="n">
-        <v>35.28022348609876</v>
+        <v>45.72411569920189</v>
       </c>
       <c r="E2" t="n">
-        <v>34.43240159762122</v>
+        <v>28.60179658692508</v>
       </c>
       <c r="F2" t="n">
-        <v>33.56256974920839</v>
+        <v>47.58226902434697</v>
       </c>
       <c r="G2" t="n">
-        <v>33.13816188378904</v>
+        <v>45.73172145751793</v>
       </c>
       <c r="H2" t="n">
-        <v>37.24782200500629</v>
+        <v>43.71857499395353</v>
       </c>
       <c r="I2" t="n">
-        <v>36.05573158202624</v>
+        <v>41.65382843780496</v>
       </c>
       <c r="J2" t="n">
-        <v>50.19878479983086</v>
+        <v>60.54739188628798</v>
       </c>
     </row>
   </sheetData>
@@ -868,31 +868,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.74388311614847</v>
+        <v>40.48050345642972</v>
       </c>
       <c r="C2" t="n">
-        <v>41.50097599602959</v>
+        <v>41.47990192373307</v>
       </c>
       <c r="D2" t="n">
-        <v>37.4101865599285</v>
+        <v>46.0635621214688</v>
       </c>
       <c r="E2" t="n">
-        <v>33.05050860182975</v>
+        <v>31.7468036390663</v>
       </c>
       <c r="F2" t="n">
-        <v>34.37620591237392</v>
+        <v>38.36751136909455</v>
       </c>
       <c r="G2" t="n">
-        <v>36.88364023666157</v>
+        <v>37.43876463179905</v>
       </c>
       <c r="H2" t="n">
-        <v>47.59628679247933</v>
+        <v>48.76167257886615</v>
       </c>
       <c r="I2" t="n">
-        <v>46.5028960506896</v>
+        <v>36.54156351307486</v>
       </c>
       <c r="J2" t="n">
-        <v>40.24966231307283</v>
+        <v>46.34764269789114</v>
       </c>
     </row>
   </sheetData>
@@ -966,31 +966,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.4651919111357</v>
+        <v>33.52881107506214</v>
       </c>
       <c r="C2" t="n">
-        <v>26.22494381078687</v>
+        <v>26.93408792543321</v>
       </c>
       <c r="D2" t="n">
-        <v>25.46271738792039</v>
+        <v>47.32381236780249</v>
       </c>
       <c r="E2" t="n">
-        <v>38.15457242108481</v>
+        <v>32.38823419172655</v>
       </c>
       <c r="F2" t="n">
-        <v>28.39417243977422</v>
+        <v>32.70473607303069</v>
       </c>
       <c r="G2" t="n">
-        <v>35.48825781055756</v>
+        <v>34.61454054347676</v>
       </c>
       <c r="H2" t="n">
-        <v>40.72922900492827</v>
+        <v>46.15947403785714</v>
       </c>
       <c r="I2" t="n">
-        <v>31.52591622689421</v>
+        <v>46.42411938610034</v>
       </c>
       <c r="J2" t="n">
-        <v>29.91008645980616</v>
+        <v>34.53498010129823</v>
       </c>
     </row>
   </sheetData>
@@ -1064,31 +1064,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.40308790606967</v>
+        <v>30.46100516995968</v>
       </c>
       <c r="C2" t="n">
-        <v>39.97472272002304</v>
+        <v>42.06537849224643</v>
       </c>
       <c r="D2" t="n">
-        <v>37.41872423682295</v>
+        <v>43.22468196584116</v>
       </c>
       <c r="E2" t="n">
+        <v>35.41268828680094</v>
+      </c>
+      <c r="F2" t="n">
+        <v>29.21757054321095</v>
+      </c>
+      <c r="G2" t="n">
+        <v>37.61743016924664</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.47662702629052</v>
+      </c>
+      <c r="I2" t="n">
         <v>46.5688901665752</v>
       </c>
-      <c r="F2" t="n">
-        <v>49.24050130353001</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.08916118824942</v>
-      </c>
-      <c r="H2" t="n">
-        <v>31.36484678649562</v>
-      </c>
-      <c r="I2" t="n">
-        <v>36.23235128986576</v>
-      </c>
       <c r="J2" t="n">
-        <v>36.36769965243668</v>
+        <v>40.87212880245769</v>
       </c>
     </row>
   </sheetData>
@@ -1162,31 +1162,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.90618008575722</v>
+        <v>40.10076791220516</v>
       </c>
       <c r="C2" t="n">
-        <v>50.60924693530757</v>
+        <v>35.40868195306519</v>
       </c>
       <c r="D2" t="n">
-        <v>39.91461824082468</v>
+        <v>48.39259785541164</v>
       </c>
       <c r="E2" t="n">
-        <v>21.04383996795858</v>
+        <v>39.64407447899148</v>
       </c>
       <c r="F2" t="n">
-        <v>37.31126483204461</v>
+        <v>41.22692326139941</v>
       </c>
       <c r="G2" t="n">
-        <v>41.33942166277971</v>
+        <v>42.20625657602751</v>
       </c>
       <c r="H2" t="n">
-        <v>34.8418903960363</v>
+        <v>37.17746183381674</v>
       </c>
       <c r="I2" t="n">
-        <v>43.54832872124854</v>
+        <v>50.19794233334264</v>
       </c>
       <c r="J2" t="n">
-        <v>36.31322156703233</v>
+        <v>54.09001493132165</v>
       </c>
     </row>
   </sheetData>
@@ -1260,31 +1260,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.25883201207149</v>
+        <v>33.19995914765622</v>
       </c>
       <c r="C2" t="n">
-        <v>40.46497178128516</v>
+        <v>49.31411233857364</v>
       </c>
       <c r="D2" t="n">
-        <v>25.19841439053034</v>
+        <v>32.38021193273439</v>
       </c>
       <c r="E2" t="n">
-        <v>41.19424250693245</v>
+        <v>27.58619012779657</v>
       </c>
       <c r="F2" t="n">
-        <v>30.76036190773628</v>
+        <v>35.11034824874898</v>
       </c>
       <c r="G2" t="n">
-        <v>52.2151881856616</v>
+        <v>55.51152464792543</v>
       </c>
       <c r="H2" t="n">
-        <v>33.68535022286764</v>
+        <v>33.06055472507566</v>
       </c>
       <c r="I2" t="n">
-        <v>29.56381781123031</v>
+        <v>37.54658991751047</v>
       </c>
       <c r="J2" t="n">
-        <v>25.35952750490565</v>
+        <v>40.64884726222676</v>
       </c>
     </row>
   </sheetData>
@@ -1358,31 +1358,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.61562546424897</v>
+        <v>42.19923855882721</v>
       </c>
       <c r="C2" t="n">
-        <v>36.89102461256798</v>
+        <v>48.42339104085832</v>
       </c>
       <c r="D2" t="n">
-        <v>31.6765528681054</v>
+        <v>40.01793183492877</v>
       </c>
       <c r="E2" t="n">
-        <v>45.77695918233846</v>
+        <v>37.48677088044374</v>
       </c>
       <c r="F2" t="n">
-        <v>39.47054336306896</v>
+        <v>42.37709137076293</v>
       </c>
       <c r="G2" t="n">
-        <v>52.8913956175364</v>
+        <v>43.43188697159024</v>
       </c>
       <c r="H2" t="n">
-        <v>48.13354903860455</v>
+        <v>28.9791906253258</v>
       </c>
       <c r="I2" t="n">
-        <v>29.67013588544607</v>
+        <v>35.91241513787045</v>
       </c>
       <c r="J2" t="n">
-        <v>21.49768343210168</v>
+        <v>52.59779024731688</v>
       </c>
     </row>
   </sheetData>
@@ -1456,31 +1456,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.9666980651365</v>
+        <v>24.71516984137358</v>
       </c>
       <c r="C2" t="n">
-        <v>40.09950293657695</v>
+        <v>45.7260688948633</v>
       </c>
       <c r="D2" t="n">
-        <v>32.20928608925302</v>
+        <v>45.0010238550098</v>
       </c>
       <c r="E2" t="n">
-        <v>41.57931766589292</v>
+        <v>28.63177175297437</v>
       </c>
       <c r="F2" t="n">
-        <v>38.06814683901759</v>
+        <v>40.15553856741342</v>
       </c>
       <c r="G2" t="n">
-        <v>28.39535719742201</v>
+        <v>49.4971391333893</v>
       </c>
       <c r="H2" t="n">
-        <v>41.25301842178343</v>
+        <v>35.27271873756037</v>
       </c>
       <c r="I2" t="n">
-        <v>34.16447267641087</v>
+        <v>43.78151380034631</v>
       </c>
       <c r="J2" t="n">
-        <v>27.09232107750533</v>
+        <v>38.6595292691327</v>
       </c>
     </row>
   </sheetData>
@@ -1554,31 +1554,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.01195229903422</v>
+        <v>28.03136883495579</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6060212896948</v>
+        <v>42.19090883629073</v>
       </c>
       <c r="D2" t="n">
-        <v>26.61920300552683</v>
+        <v>37.40199857172991</v>
       </c>
       <c r="E2" t="n">
-        <v>50.54554814773183</v>
+        <v>27.5985491410315</v>
       </c>
       <c r="F2" t="n">
-        <v>26.58748886105921</v>
+        <v>36.21895376028461</v>
       </c>
       <c r="G2" t="n">
-        <v>41.60159135777315</v>
+        <v>28.40670828467011</v>
       </c>
       <c r="H2" t="n">
-        <v>30.19433776257609</v>
+        <v>37.20983367356916</v>
       </c>
       <c r="I2" t="n">
-        <v>21.56005346040521</v>
+        <v>59.15844491872449</v>
       </c>
       <c r="J2" t="n">
-        <v>35.89865020284216</v>
+        <v>37.68636012245775</v>
       </c>
     </row>
   </sheetData>
@@ -1652,31 +1652,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.20749796822741</v>
+        <v>41.41471829979307</v>
       </c>
       <c r="C2" t="n">
-        <v>31.56301157973932</v>
+        <v>43.92034106243117</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4637701081905</v>
+        <v>59.68274878075805</v>
       </c>
       <c r="E2" t="n">
-        <v>42.36280227833093</v>
+        <v>35.45646632731006</v>
       </c>
       <c r="F2" t="n">
-        <v>50.2923403924665</v>
+        <v>51.11880086875968</v>
       </c>
       <c r="G2" t="n">
-        <v>34.92476446862002</v>
+        <v>26.36685417281074</v>
       </c>
       <c r="H2" t="n">
-        <v>32.61990379422476</v>
+        <v>43.01089255262244</v>
       </c>
       <c r="I2" t="n">
-        <v>35.4652453957472</v>
+        <v>43.61495330370686</v>
       </c>
       <c r="J2" t="n">
-        <v>29.79532755524464</v>
+        <v>41.75282033312715</v>
       </c>
     </row>
   </sheetData>
@@ -1750,31 +1750,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.47260416528901</v>
+        <v>29.8541413347068</v>
       </c>
       <c r="C2" t="n">
-        <v>37.40461919052767</v>
+        <v>42.43297368622365</v>
       </c>
       <c r="D2" t="n">
-        <v>28.51124880557877</v>
+        <v>38.5586388590326</v>
       </c>
       <c r="E2" t="n">
-        <v>28.59363942832145</v>
+        <v>38.49417147016621</v>
       </c>
       <c r="F2" t="n">
-        <v>40.68325187340076</v>
+        <v>50.28051213654314</v>
       </c>
       <c r="G2" t="n">
-        <v>37.84548395025425</v>
+        <v>43.11685309140387</v>
       </c>
       <c r="H2" t="n">
-        <v>37.44171347390069</v>
+        <v>41.35173293915548</v>
       </c>
       <c r="I2" t="n">
-        <v>41.04643028822775</v>
+        <v>44.34566150088659</v>
       </c>
       <c r="J2" t="n">
-        <v>44.03886433394005</v>
+        <v>39.58266069305766</v>
       </c>
     </row>
   </sheetData>
@@ -1848,31 +1848,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.04134700466518</v>
+        <v>36.4067367691213</v>
       </c>
       <c r="C2" t="n">
-        <v>35.38081410628876</v>
+        <v>30.92517187740832</v>
       </c>
       <c r="D2" t="n">
-        <v>39.20191201081821</v>
+        <v>35.98347426723101</v>
       </c>
       <c r="E2" t="n">
-        <v>27.0925622810891</v>
+        <v>45.941875635023</v>
       </c>
       <c r="F2" t="n">
-        <v>46.24207730760988</v>
+        <v>42.0968705691418</v>
       </c>
       <c r="G2" t="n">
-        <v>39.47364799237889</v>
+        <v>46.26393712262565</v>
       </c>
       <c r="H2" t="n">
-        <v>39.23673223571671</v>
+        <v>37.47651521260529</v>
       </c>
       <c r="I2" t="n">
-        <v>36.49175314211575</v>
+        <v>40.02580354490414</v>
       </c>
       <c r="J2" t="n">
-        <v>34.21914040813275</v>
+        <v>52.64349386148013</v>
       </c>
     </row>
   </sheetData>
@@ -1946,31 +1946,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.43055981652979</v>
+        <v>32.73691776008177</v>
       </c>
       <c r="C2" t="n">
-        <v>38.32656737195837</v>
+        <v>49.29613526005254</v>
       </c>
       <c r="D2" t="n">
-        <v>45.72988240096372</v>
+        <v>42.59737097341799</v>
       </c>
       <c r="E2" t="n">
-        <v>47.94809408427645</v>
+        <v>34.8477772560128</v>
       </c>
       <c r="F2" t="n">
-        <v>37.96273737100319</v>
+        <v>41.26999053707455</v>
       </c>
       <c r="G2" t="n">
-        <v>28.61469986042515</v>
+        <v>42.11679517522072</v>
       </c>
       <c r="H2" t="n">
-        <v>13.79806692976676</v>
+        <v>36.80758049276486</v>
       </c>
       <c r="I2" t="n">
-        <v>39.66714074011987</v>
+        <v>44.32743306478221</v>
       </c>
       <c r="J2" t="n">
-        <v>35.15266060390954</v>
+        <v>35.9504773978917</v>
       </c>
     </row>
   </sheetData>
@@ -2044,31 +2044,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.80351028085306</v>
+        <v>32.46484645393207</v>
       </c>
       <c r="C2" t="n">
-        <v>54.66144243260851</v>
+        <v>38.26929393815428</v>
       </c>
       <c r="D2" t="n">
-        <v>41.66426856523997</v>
+        <v>38.10145256656755</v>
       </c>
       <c r="E2" t="n">
-        <v>40.19246606308892</v>
+        <v>30.14462050272892</v>
       </c>
       <c r="F2" t="n">
-        <v>27.33677383202376</v>
+        <v>30.17079723184112</v>
       </c>
       <c r="G2" t="n">
-        <v>60.69046733965282</v>
+        <v>38.24952215710075</v>
       </c>
       <c r="H2" t="n">
-        <v>35.7726499133182</v>
+        <v>68.37134300852337</v>
       </c>
       <c r="I2" t="n">
-        <v>37.44954026525463</v>
+        <v>40.28851697475802</v>
       </c>
       <c r="J2" t="n">
-        <v>21.1638037468436</v>
+        <v>38.90299767779575</v>
       </c>
     </row>
   </sheetData>
@@ -2142,31 +2142,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.33123189486566</v>
+        <v>39.22677645875252</v>
       </c>
       <c r="C2" t="n">
-        <v>42.72650311516274</v>
+        <v>30.71131169621209</v>
       </c>
       <c r="D2" t="n">
-        <v>25.69202519142398</v>
+        <v>36.03560483248351</v>
       </c>
       <c r="E2" t="n">
-        <v>31.99734062523108</v>
+        <v>35.13412891289613</v>
       </c>
       <c r="F2" t="n">
-        <v>24.63516226711207</v>
+        <v>34.06307768495812</v>
       </c>
       <c r="G2" t="n">
-        <v>41.98772616912974</v>
+        <v>34.59243038399026</v>
       </c>
       <c r="H2" t="n">
-        <v>42.21794414693647</v>
+        <v>55.38063714228797</v>
       </c>
       <c r="I2" t="n">
-        <v>35.27318394904436</v>
+        <v>27.60549091882253</v>
       </c>
       <c r="J2" t="n">
-        <v>38.46968877393871</v>
+        <v>32.09477682831024</v>
       </c>
     </row>
   </sheetData>
@@ -2240,31 +2240,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.45893007379522</v>
+        <v>31.95234954461181</v>
       </c>
       <c r="C2" t="n">
-        <v>38.62572544393522</v>
+        <v>38.30724370695803</v>
       </c>
       <c r="D2" t="n">
-        <v>34.02132657941073</v>
+        <v>63.89941210882294</v>
       </c>
       <c r="E2" t="n">
-        <v>36.0634583049324</v>
+        <v>34.43181157939578</v>
       </c>
       <c r="F2" t="n">
-        <v>33.23387574952545</v>
+        <v>44.48629775112433</v>
       </c>
       <c r="G2" t="n">
-        <v>73.92968784164569</v>
+        <v>37.30763788326239</v>
       </c>
       <c r="H2" t="n">
-        <v>35.5844182845747</v>
+        <v>44.46999864898968</v>
       </c>
       <c r="I2" t="n">
-        <v>24.92813166170961</v>
+        <v>35.58648931836431</v>
       </c>
       <c r="J2" t="n">
-        <v>42.68791233782751</v>
+        <v>53.07494211616775</v>
       </c>
     </row>
   </sheetData>
@@ -2338,31 +2338,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.31254844865011</v>
+        <v>34.84378518211428</v>
       </c>
       <c r="C2" t="n">
-        <v>35.81579687298146</v>
+        <v>38.95426649803407</v>
       </c>
       <c r="D2" t="n">
-        <v>36.63171765541372</v>
+        <v>40.47361221905489</v>
       </c>
       <c r="E2" t="n">
-        <v>33.94989770592961</v>
+        <v>44.69976220306939</v>
       </c>
       <c r="F2" t="n">
-        <v>35.624817202118</v>
+        <v>32.09118079217689</v>
       </c>
       <c r="G2" t="n">
-        <v>27.39408818749127</v>
+        <v>38.736822813354</v>
       </c>
       <c r="H2" t="n">
-        <v>51.61563181349487</v>
+        <v>39.28075812016605</v>
       </c>
       <c r="I2" t="n">
-        <v>31.16220643084219</v>
+        <v>57.40570982825643</v>
       </c>
       <c r="J2" t="n">
-        <v>60.90468641164433</v>
+        <v>40.82023351035281</v>
       </c>
     </row>
   </sheetData>
@@ -2436,31 +2436,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.76588264030136</v>
+        <v>26.8028157779817</v>
       </c>
       <c r="C2" t="n">
-        <v>40.37319974303328</v>
+        <v>26.57434195519482</v>
       </c>
       <c r="D2" t="n">
-        <v>42.2753082992423</v>
+        <v>48.74349414478029</v>
       </c>
       <c r="E2" t="n">
-        <v>52.28216775199803</v>
+        <v>34.75348486771652</v>
       </c>
       <c r="F2" t="n">
-        <v>42.60642968690673</v>
+        <v>46.12404252517982</v>
       </c>
       <c r="G2" t="n">
-        <v>25.14697035782991</v>
+        <v>44.0321085974536</v>
       </c>
       <c r="H2" t="n">
-        <v>36.95211590431062</v>
+        <v>45.54933356171681</v>
       </c>
       <c r="I2" t="n">
-        <v>40.16195679080894</v>
+        <v>45.48686913758396</v>
       </c>
       <c r="J2" t="n">
-        <v>32.50855922685553</v>
+        <v>37.00002014188239</v>
       </c>
     </row>
   </sheetData>
@@ -2534,31 +2534,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.78491772459087</v>
+        <v>37.05823662253427</v>
       </c>
       <c r="C2" t="n">
-        <v>36.31256045768644</v>
+        <v>37.22557522123852</v>
       </c>
       <c r="D2" t="n">
-        <v>26.94593891750309</v>
+        <v>33.18615523986774</v>
       </c>
       <c r="E2" t="n">
-        <v>36.21732843021185</v>
+        <v>28.6505113760099</v>
       </c>
       <c r="F2" t="n">
-        <v>26.034604735061</v>
+        <v>39.75577412996692</v>
       </c>
       <c r="G2" t="n">
-        <v>38.42077810207535</v>
+        <v>32.59211202888294</v>
       </c>
       <c r="H2" t="n">
-        <v>31.55479928305982</v>
+        <v>38.34713419500879</v>
       </c>
       <c r="I2" t="n">
-        <v>35.89622475488493</v>
+        <v>42.8958487072687</v>
       </c>
       <c r="J2" t="n">
-        <v>36.99536928569193</v>
+        <v>47.54572146463155</v>
       </c>
     </row>
   </sheetData>
@@ -2632,31 +2632,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.8776010689484</v>
+        <v>33.54942244784043</v>
       </c>
       <c r="C2" t="n">
-        <v>27.36767389698857</v>
+        <v>51.71121630962773</v>
       </c>
       <c r="D2" t="n">
-        <v>30.55611446909568</v>
+        <v>37.6430351653844</v>
       </c>
       <c r="E2" t="n">
-        <v>25.40366534090416</v>
+        <v>32.98367987132269</v>
       </c>
       <c r="F2" t="n">
-        <v>36.50344120062971</v>
+        <v>29.07935940337013</v>
       </c>
       <c r="G2" t="n">
-        <v>40.59503712856336</v>
+        <v>31.70907810887898</v>
       </c>
       <c r="H2" t="n">
-        <v>33.16394011963742</v>
+        <v>29.2093091742228</v>
       </c>
       <c r="I2" t="n">
-        <v>37.66261691167043</v>
+        <v>35.07948680272801</v>
       </c>
       <c r="J2" t="n">
-        <v>36.38039657988853</v>
+        <v>35.62315044837526</v>
       </c>
     </row>
   </sheetData>
@@ -2730,31 +2730,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.87985126062701</v>
+        <v>40.14837380880321</v>
       </c>
       <c r="C2" t="n">
-        <v>30.4381305144057</v>
+        <v>43.2237961641931</v>
       </c>
       <c r="D2" t="n">
-        <v>36.43720814328922</v>
+        <v>46.8137995560487</v>
       </c>
       <c r="E2" t="n">
-        <v>38.69034966512577</v>
+        <v>38.35980880555366</v>
       </c>
       <c r="F2" t="n">
-        <v>33.82709620352575</v>
+        <v>43.76341552338776</v>
       </c>
       <c r="G2" t="n">
-        <v>78.16673624144866</v>
+        <v>36.501723116839</v>
       </c>
       <c r="H2" t="n">
-        <v>36.60637334627729</v>
+        <v>45.05325681768022</v>
       </c>
       <c r="I2" t="n">
-        <v>31.02410493204441</v>
+        <v>51.29600082278006</v>
       </c>
       <c r="J2" t="n">
-        <v>58.38503851884034</v>
+        <v>30.99327800601064</v>
       </c>
     </row>
   </sheetData>
@@ -2828,31 +2828,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.83013551764475</v>
+        <v>32.667240777441</v>
       </c>
       <c r="C2" t="n">
-        <v>34.47310772452902</v>
+        <v>45.18626880185687</v>
       </c>
       <c r="D2" t="n">
-        <v>24.23592841142888</v>
+        <v>55.27072677603702</v>
       </c>
       <c r="E2" t="n">
-        <v>41.21734541663026</v>
+        <v>27.38351146077256</v>
       </c>
       <c r="F2" t="n">
-        <v>38.64278441423346</v>
+        <v>32.62594596760746</v>
       </c>
       <c r="G2" t="n">
-        <v>36.52085683832014</v>
+        <v>31.37583138420469</v>
       </c>
       <c r="H2" t="n">
-        <v>36.03422317834325</v>
+        <v>27.25189012413374</v>
       </c>
       <c r="I2" t="n">
-        <v>30.72809324389204</v>
+        <v>40.46631679953585</v>
       </c>
       <c r="J2" t="n">
-        <v>32.74899153123988</v>
+        <v>42.10428683288404</v>
       </c>
     </row>
   </sheetData>
@@ -2926,31 +2926,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.80935310393686</v>
+        <v>24.62171837771139</v>
       </c>
       <c r="C2" t="n">
-        <v>24.46558912342995</v>
+        <v>33.97094305301903</v>
       </c>
       <c r="D2" t="n">
-        <v>29.45736355619304</v>
+        <v>40.38671373885034</v>
       </c>
       <c r="E2" t="n">
-        <v>45.77368701771675</v>
+        <v>27.84934758105544</v>
       </c>
       <c r="F2" t="n">
-        <v>37.84906146198359</v>
+        <v>43.23608517267669</v>
       </c>
       <c r="G2" t="n">
-        <v>64.15945079839675</v>
+        <v>34.80533447000408</v>
       </c>
       <c r="H2" t="n">
-        <v>35.0771166481882</v>
+        <v>31.88254856759419</v>
       </c>
       <c r="I2" t="n">
-        <v>31.98602689246345</v>
+        <v>64.79315566998817</v>
       </c>
       <c r="J2" t="n">
-        <v>34.20525520966869</v>
+        <v>39.57220775745108</v>
       </c>
     </row>
   </sheetData>
@@ -3024,31 +3024,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.03804923618183</v>
+        <v>29.43161501288023</v>
       </c>
       <c r="C2" t="n">
-        <v>24.79802843230723</v>
+        <v>33.8496498820063</v>
       </c>
       <c r="D2" t="n">
-        <v>36.85850038048735</v>
+        <v>53.43263946539157</v>
       </c>
       <c r="E2" t="n">
-        <v>46.05036740248574</v>
+        <v>41.54787503178428</v>
       </c>
       <c r="F2" t="n">
-        <v>44.88064008038892</v>
+        <v>43.1321253449903</v>
       </c>
       <c r="G2" t="n">
-        <v>36.97670999582222</v>
+        <v>45.60647049246208</v>
       </c>
       <c r="H2" t="n">
-        <v>49.95355996056177</v>
+        <v>36.3356455245756</v>
       </c>
       <c r="I2" t="n">
-        <v>28.50062569438791</v>
+        <v>46.65252606220243</v>
       </c>
       <c r="J2" t="n">
-        <v>35.36671459249261</v>
+        <v>46.74381902619493</v>
       </c>
     </row>
   </sheetData>
@@ -3122,31 +3122,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.32194821859513</v>
+        <v>21.93607999386793</v>
       </c>
       <c r="C2" t="n">
-        <v>21.10818746127174</v>
+        <v>24.84862113253838</v>
       </c>
       <c r="D2" t="n">
-        <v>27.25114088642941</v>
+        <v>40.66686708302818</v>
       </c>
       <c r="E2" t="n">
-        <v>49.53504072184892</v>
+        <v>28.78772650029489</v>
       </c>
       <c r="F2" t="n">
-        <v>34.29818962063388</v>
+        <v>40.96483871819225</v>
       </c>
       <c r="G2" t="n">
-        <v>29.93176575919205</v>
+        <v>49.3013071043428</v>
       </c>
       <c r="H2" t="n">
-        <v>28.38402420359748</v>
+        <v>50.07641400805874</v>
       </c>
       <c r="I2" t="n">
-        <v>39.89425551516432</v>
+        <v>39.45008044009375</v>
       </c>
       <c r="J2" t="n">
-        <v>44.00928527606199</v>
+        <v>34.75285777405747</v>
       </c>
     </row>
   </sheetData>
@@ -3220,31 +3220,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.63077721878248</v>
+        <v>44.33719210032627</v>
       </c>
       <c r="C2" t="n">
-        <v>40.4652572786177</v>
+        <v>41.69100373562902</v>
       </c>
       <c r="D2" t="n">
-        <v>31.2190342318522</v>
+        <v>36.71764533626795</v>
       </c>
       <c r="E2" t="n">
-        <v>34.441646000959</v>
+        <v>38.79473085599896</v>
       </c>
       <c r="F2" t="n">
-        <v>29.27491623735711</v>
+        <v>42.77259704644244</v>
       </c>
       <c r="G2" t="n">
-        <v>43.382956061759</v>
+        <v>40.48479396895411</v>
       </c>
       <c r="H2" t="n">
-        <v>39.21495486948218</v>
+        <v>46.52982807494229</v>
       </c>
       <c r="I2" t="n">
-        <v>41.34124533312253</v>
+        <v>28.60273238234328</v>
       </c>
       <c r="J2" t="n">
-        <v>40.78844447564916</v>
+        <v>59.44419421797414</v>
       </c>
     </row>
   </sheetData>
@@ -3318,31 +3318,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.61505243013238</v>
+        <v>33.78717858523296</v>
       </c>
       <c r="C2" t="n">
-        <v>37.07040905833806</v>
+        <v>43.9153657715057</v>
       </c>
       <c r="D2" t="n">
-        <v>45.45744476831832</v>
+        <v>37.3989184228806</v>
       </c>
       <c r="E2" t="n">
-        <v>30.06748002543216</v>
+        <v>35.45767391189519</v>
       </c>
       <c r="F2" t="n">
-        <v>31.9888430885597</v>
+        <v>35.63806568599209</v>
       </c>
       <c r="G2" t="n">
-        <v>35.23559976098154</v>
+        <v>34.91469437858259</v>
       </c>
       <c r="H2" t="n">
-        <v>27.23565202142949</v>
+        <v>49.91908312852672</v>
       </c>
       <c r="I2" t="n">
-        <v>29.24906077332345</v>
+        <v>48.58690251400408</v>
       </c>
       <c r="J2" t="n">
-        <v>45.87357814937366</v>
+        <v>35.95107480511042</v>
       </c>
     </row>
   </sheetData>
@@ -3416,31 +3416,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.93279685276209</v>
+        <v>39.80811018620588</v>
       </c>
       <c r="C2" t="n">
-        <v>64.19620217484855</v>
+        <v>55.70421933438183</v>
       </c>
       <c r="D2" t="n">
-        <v>24.77219964662626</v>
+        <v>48.67602762117096</v>
       </c>
       <c r="E2" t="n">
-        <v>32.22660530477031</v>
+        <v>36.79338797612766</v>
       </c>
       <c r="F2" t="n">
-        <v>33.94038358739123</v>
+        <v>42.8128720114946</v>
       </c>
       <c r="G2" t="n">
-        <v>36.39178252210743</v>
+        <v>31.26385866099676</v>
       </c>
       <c r="H2" t="n">
-        <v>29.27658044545601</v>
+        <v>45.24950605569077</v>
       </c>
       <c r="I2" t="n">
-        <v>43.08486776459048</v>
+        <v>31.54183145189589</v>
       </c>
       <c r="J2" t="n">
-        <v>44.2317219443657</v>
+        <v>37.19493196788586</v>
       </c>
     </row>
   </sheetData>
@@ -3514,31 +3514,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.21194881004949</v>
+        <v>36.49437681695932</v>
       </c>
       <c r="C2" t="n">
-        <v>34.60866925142404</v>
+        <v>41.41180861969016</v>
       </c>
       <c r="D2" t="n">
-        <v>22.83697536692149</v>
+        <v>37.54804444960037</v>
       </c>
       <c r="E2" t="n">
-        <v>38.56332980972967</v>
+        <v>28.8662096919513</v>
       </c>
       <c r="F2" t="n">
-        <v>36.62925737165205</v>
+        <v>30.20869844255792</v>
       </c>
       <c r="G2" t="n">
-        <v>47.7838684370081</v>
+        <v>43.09849267834051</v>
       </c>
       <c r="H2" t="n">
-        <v>21.62422847224547</v>
+        <v>41.78990505862818</v>
       </c>
       <c r="I2" t="n">
-        <v>35.18421652099607</v>
+        <v>37.95278024635412</v>
       </c>
       <c r="J2" t="n">
-        <v>35.78140943314146</v>
+        <v>40.47638939510023</v>
       </c>
     </row>
   </sheetData>
@@ -3612,31 +3612,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.8770822395316</v>
+        <v>30.7753772722445</v>
       </c>
       <c r="C2" t="n">
-        <v>51.93093233310662</v>
+        <v>25.56140653589319</v>
       </c>
       <c r="D2" t="n">
-        <v>42.43312151534391</v>
+        <v>36.40763771550455</v>
       </c>
       <c r="E2" t="n">
-        <v>32.61733500544953</v>
+        <v>45.8459631111736</v>
       </c>
       <c r="F2" t="n">
-        <v>44.228764138647</v>
+        <v>36.60908414269655</v>
       </c>
       <c r="G2" t="n">
-        <v>34.78115010747712</v>
+        <v>44.59894201372272</v>
       </c>
       <c r="H2" t="n">
-        <v>39.82422681250042</v>
+        <v>53.52380688209839</v>
       </c>
       <c r="I2" t="n">
-        <v>33.21875576568102</v>
+        <v>43.59339420969123</v>
       </c>
       <c r="J2" t="n">
-        <v>34.21993194096135</v>
+        <v>33.2575504722754</v>
       </c>
     </row>
   </sheetData>
@@ -3710,31 +3710,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.4859673956903</v>
+        <v>40.04097975460691</v>
       </c>
       <c r="C2" t="n">
-        <v>25.47556219987792</v>
+        <v>45.45619873840622</v>
       </c>
       <c r="D2" t="n">
-        <v>35.75901795343291</v>
+        <v>33.0771139281985</v>
       </c>
       <c r="E2" t="n">
-        <v>39.24218250938983</v>
+        <v>38.32224106479834</v>
       </c>
       <c r="F2" t="n">
-        <v>30.33697929284469</v>
+        <v>37.9260036258578</v>
       </c>
       <c r="G2" t="n">
-        <v>44.25191261453089</v>
+        <v>44.54147443296369</v>
       </c>
       <c r="H2" t="n">
-        <v>28.85236154259572</v>
+        <v>42.54061361128965</v>
       </c>
       <c r="I2" t="n">
-        <v>38.72238969127432</v>
+        <v>41.25918402593918</v>
       </c>
       <c r="J2" t="n">
-        <v>45.16146761248793</v>
+        <v>29.50612899588394</v>
       </c>
     </row>
   </sheetData>
@@ -3808,31 +3808,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.6073467026179</v>
+        <v>33.21484541022535</v>
       </c>
       <c r="C2" t="n">
-        <v>28.59676748955471</v>
+        <v>46.19778125534253</v>
       </c>
       <c r="D2" t="n">
-        <v>36.52153352847522</v>
+        <v>61.05766351996888</v>
       </c>
       <c r="E2" t="n">
-        <v>43.71099398073399</v>
+        <v>38.65450238348752</v>
       </c>
       <c r="F2" t="n">
-        <v>41.29978673550622</v>
+        <v>35.25357096036107</v>
       </c>
       <c r="G2" t="n">
-        <v>41.30474319252802</v>
+        <v>36.61796019145353</v>
       </c>
       <c r="H2" t="n">
-        <v>26.26502457468394</v>
+        <v>39.86987885030459</v>
       </c>
       <c r="I2" t="n">
-        <v>31.92702500378143</v>
+        <v>35.41671342257799</v>
       </c>
       <c r="J2" t="n">
-        <v>24.70632311163781</v>
+        <v>37.36119314341906</v>
       </c>
     </row>
   </sheetData>
@@ -3906,31 +3906,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.84363332942031</v>
+        <v>31.80123613610603</v>
       </c>
       <c r="C2" t="n">
-        <v>38.37586664240498</v>
+        <v>38.7257142373747</v>
       </c>
       <c r="D2" t="n">
-        <v>23.72350379256457</v>
+        <v>41.02124861266001</v>
       </c>
       <c r="E2" t="n">
-        <v>34.06281776793078</v>
+        <v>27.21464353820082</v>
       </c>
       <c r="F2" t="n">
-        <v>31.14631761720448</v>
+        <v>37.42208472299806</v>
       </c>
       <c r="G2" t="n">
-        <v>43.33120204922468</v>
+        <v>36.40848817490798</v>
       </c>
       <c r="H2" t="n">
-        <v>48.24617558757559</v>
+        <v>44.76688883025918</v>
       </c>
       <c r="I2" t="n">
-        <v>36.12735263304692</v>
+        <v>51.43818253125096</v>
       </c>
       <c r="J2" t="n">
-        <v>35.09652627664256</v>
+        <v>44.11097889775676</v>
       </c>
     </row>
   </sheetData>
@@ -4004,31 +4004,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>20.78469383861114</v>
+        <v>39.91136937672216</v>
       </c>
       <c r="C2" t="n">
-        <v>37.82689269569527</v>
+        <v>43.11238464702846</v>
       </c>
       <c r="D2" t="n">
-        <v>36.67060873681563</v>
+        <v>34.27383716494216</v>
       </c>
       <c r="E2" t="n">
-        <v>40.65033770243697</v>
+        <v>30.20971110468276</v>
       </c>
       <c r="F2" t="n">
-        <v>27.27652253961297</v>
+        <v>53.00266546514386</v>
       </c>
       <c r="G2" t="n">
-        <v>47.2565143123233</v>
+        <v>41.40253041100949</v>
       </c>
       <c r="H2" t="n">
-        <v>43.44569055523221</v>
+        <v>36.53481392324134</v>
       </c>
       <c r="I2" t="n">
-        <v>31.34773089102846</v>
+        <v>38.45494106466679</v>
       </c>
       <c r="J2" t="n">
-        <v>38.11321813149452</v>
+        <v>52.14771570811113</v>
       </c>
     </row>
   </sheetData>
@@ -4102,31 +4102,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.25497988023194</v>
+        <v>29.50836390779991</v>
       </c>
       <c r="C2" t="n">
-        <v>32.67518891338107</v>
+        <v>43.19947175454884</v>
       </c>
       <c r="D2" t="n">
-        <v>37.1091248218554</v>
+        <v>32.02069455274974</v>
       </c>
       <c r="E2" t="n">
-        <v>35.45415751422237</v>
+        <v>41.84262922598575</v>
       </c>
       <c r="F2" t="n">
-        <v>46.24773476199946</v>
+        <v>28.71995108931697</v>
       </c>
       <c r="G2" t="n">
-        <v>47.62145806508058</v>
+        <v>36.83839640960487</v>
       </c>
       <c r="H2" t="n">
-        <v>33.80998898186702</v>
+        <v>39.93895893311682</v>
       </c>
       <c r="I2" t="n">
-        <v>23.46422230535325</v>
+        <v>54.44619695157956</v>
       </c>
       <c r="J2" t="n">
-        <v>34.7824947128682</v>
+        <v>42.10995138115279</v>
       </c>
     </row>
   </sheetData>
@@ -4200,31 +4200,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.72407611180385</v>
+        <v>34.48295746928797</v>
       </c>
       <c r="C2" t="n">
-        <v>37.26286096078943</v>
+        <v>42.99985672208966</v>
       </c>
       <c r="D2" t="n">
-        <v>31.79960858232158</v>
+        <v>49.05732625898384</v>
       </c>
       <c r="E2" t="n">
-        <v>32.13529232983279</v>
+        <v>32.60340019627131</v>
       </c>
       <c r="F2" t="n">
-        <v>43.06404277281498</v>
+        <v>40.63477329916049</v>
       </c>
       <c r="G2" t="n">
-        <v>43.83994280128307</v>
+        <v>39.12860925406809</v>
       </c>
       <c r="H2" t="n">
-        <v>45.15549998692042</v>
+        <v>48.33821266692475</v>
       </c>
       <c r="I2" t="n">
-        <v>38.33535891089281</v>
+        <v>51.65659136669579</v>
       </c>
       <c r="J2" t="n">
-        <v>46.58170574839099</v>
+        <v>39.10728388166558</v>
       </c>
     </row>
   </sheetData>
@@ -4298,31 +4298,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.51069523341483</v>
+        <v>28.85939292049749</v>
       </c>
       <c r="C2" t="n">
-        <v>38.51296889964221</v>
+        <v>38.59507819654371</v>
       </c>
       <c r="D2" t="n">
-        <v>33.65407446038897</v>
+        <v>43.37677978855267</v>
       </c>
       <c r="E2" t="n">
-        <v>39.73845168668539</v>
+        <v>31.52266648798739</v>
       </c>
       <c r="F2" t="n">
-        <v>33.06653871657218</v>
+        <v>46.51151799880513</v>
       </c>
       <c r="G2" t="n">
-        <v>42.80506713564417</v>
+        <v>37.99732752047375</v>
       </c>
       <c r="H2" t="n">
-        <v>37.18275809779934</v>
+        <v>44.59213900390329</v>
       </c>
       <c r="I2" t="n">
-        <v>55.38835403812489</v>
+        <v>50.70962536598678</v>
       </c>
       <c r="J2" t="n">
-        <v>24.25469682021205</v>
+        <v>50.63623679550923</v>
       </c>
     </row>
   </sheetData>
@@ -4396,31 +4396,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.90429576451427</v>
+        <v>25.04448666042192</v>
       </c>
       <c r="C2" t="n">
-        <v>41.87470455515651</v>
+        <v>40.08139894521247</v>
       </c>
       <c r="D2" t="n">
-        <v>25.04283974503399</v>
+        <v>32.51787872765044</v>
       </c>
       <c r="E2" t="n">
-        <v>40.46173327806795</v>
+        <v>28.79451797664942</v>
       </c>
       <c r="F2" t="n">
-        <v>25.59953149265739</v>
+        <v>49.07008897521567</v>
       </c>
       <c r="G2" t="n">
-        <v>36.29748207678215</v>
+        <v>35.17809550082776</v>
       </c>
       <c r="H2" t="n">
-        <v>41.27883404158588</v>
+        <v>41.35613383469461</v>
       </c>
       <c r="I2" t="n">
-        <v>36.7259834403955</v>
+        <v>52.96234159603147</v>
       </c>
       <c r="J2" t="n">
-        <v>33.45280725528484</v>
+        <v>35.82510586689799</v>
       </c>
     </row>
   </sheetData>
@@ -4494,31 +4494,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.62442111824635</v>
+        <v>45.85830698855668</v>
       </c>
       <c r="C2" t="n">
-        <v>26.29601200849336</v>
+        <v>23.47071460950983</v>
       </c>
       <c r="D2" t="n">
-        <v>30.38921630208092</v>
+        <v>40.91521346575011</v>
       </c>
       <c r="E2" t="n">
-        <v>43.9870875861363</v>
+        <v>32.78415072287432</v>
       </c>
       <c r="F2" t="n">
-        <v>45.50693605898703</v>
+        <v>34.35775525898011</v>
       </c>
       <c r="G2" t="n">
-        <v>42.56186412570157</v>
+        <v>29.17409765115641</v>
       </c>
       <c r="H2" t="n">
-        <v>47.29568529480378</v>
+        <v>46.28427023902551</v>
       </c>
       <c r="I2" t="n">
-        <v>35.6281877811043</v>
+        <v>44.05618099279799</v>
       </c>
       <c r="J2" t="n">
-        <v>31.01799735341283</v>
+        <v>51.44281261872213</v>
       </c>
     </row>
   </sheetData>
@@ -4592,31 +4592,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.22223245124676</v>
+        <v>32.49535479874496</v>
       </c>
       <c r="C2" t="n">
-        <v>36.43562132892596</v>
+        <v>45.76481823228914</v>
       </c>
       <c r="D2" t="n">
-        <v>36.24163061579868</v>
+        <v>30.87334387776957</v>
       </c>
       <c r="E2" t="n">
-        <v>20.43998097291386</v>
+        <v>29.30561805378533</v>
       </c>
       <c r="F2" t="n">
-        <v>30.34218591027532</v>
+        <v>46.5274963112311</v>
       </c>
       <c r="G2" t="n">
-        <v>39.40134678122353</v>
+        <v>49.38928693088891</v>
       </c>
       <c r="H2" t="n">
-        <v>37.98651419694591</v>
+        <v>30.58235220051913</v>
       </c>
       <c r="I2" t="n">
-        <v>37.67137666963625</v>
+        <v>45.64062525828559</v>
       </c>
       <c r="J2" t="n">
-        <v>53.85829987556645</v>
+        <v>32.97018352898615</v>
       </c>
     </row>
   </sheetData>
@@ -4690,31 +4690,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.37100347362067</v>
+        <v>29.83721981887997</v>
       </c>
       <c r="C2" t="n">
-        <v>45.58774075163267</v>
+        <v>33.96316731210241</v>
       </c>
       <c r="D2" t="n">
-        <v>38.96692403866704</v>
+        <v>40.2076901553263</v>
       </c>
       <c r="E2" t="n">
-        <v>37.2530049830855</v>
+        <v>31.33718866340778</v>
       </c>
       <c r="F2" t="n">
-        <v>28.57077457050588</v>
+        <v>38.12045766484317</v>
       </c>
       <c r="G2" t="n">
-        <v>38.83189219071287</v>
+        <v>43.96662998855363</v>
       </c>
       <c r="H2" t="n">
-        <v>35.58621916673338</v>
+        <v>43.80097724170994</v>
       </c>
       <c r="I2" t="n">
-        <v>55.58735581984831</v>
+        <v>43.58170959799962</v>
       </c>
       <c r="J2" t="n">
-        <v>45.92991698877087</v>
+        <v>49.73566276878405</v>
       </c>
     </row>
   </sheetData>
@@ -4788,31 +4788,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.89215255987311</v>
+        <v>32.878731409487</v>
       </c>
       <c r="C2" t="n">
-        <v>22.14070964385979</v>
+        <v>56.05926992893282</v>
       </c>
       <c r="D2" t="n">
-        <v>29.10973216585474</v>
+        <v>54.19852557319138</v>
       </c>
       <c r="E2" t="n">
-        <v>43.23648173611517</v>
+        <v>29.84814784016237</v>
       </c>
       <c r="F2" t="n">
-        <v>45.59917908320081</v>
+        <v>54.27458766931039</v>
       </c>
       <c r="G2" t="n">
-        <v>38.2954466686508</v>
+        <v>52.11805675214714</v>
       </c>
       <c r="H2" t="n">
-        <v>32.16703926505536</v>
+        <v>41.26804319843006</v>
       </c>
       <c r="I2" t="n">
-        <v>47.39860250311565</v>
+        <v>53.74844419970165</v>
       </c>
       <c r="J2" t="n">
-        <v>34.65533425506283</v>
+        <v>27.05899841620186</v>
       </c>
     </row>
   </sheetData>
@@ -4886,31 +4886,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.81653398790906</v>
+        <v>29.92485187653438</v>
       </c>
       <c r="C2" t="n">
-        <v>37.71158443495838</v>
+        <v>43.79412827692465</v>
       </c>
       <c r="D2" t="n">
-        <v>31.74883417506227</v>
+        <v>34.22460138804702</v>
       </c>
       <c r="E2" t="n">
-        <v>45.75874765259283</v>
+        <v>31.86612592823591</v>
       </c>
       <c r="F2" t="n">
-        <v>35.89498671465382</v>
+        <v>50.90553691700425</v>
       </c>
       <c r="G2" t="n">
-        <v>32.31073243029841</v>
+        <v>39.55683899821663</v>
       </c>
       <c r="H2" t="n">
-        <v>34.20693813441017</v>
+        <v>36.4449306716967</v>
       </c>
       <c r="I2" t="n">
-        <v>29.79484039072254</v>
+        <v>46.41693178499447</v>
       </c>
       <c r="J2" t="n">
-        <v>39.16199317132624</v>
+        <v>47.04410591210485</v>
       </c>
     </row>
   </sheetData>
@@ -4984,31 +4984,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.83114548603186</v>
+        <v>44.01134980558857</v>
       </c>
       <c r="C2" t="n">
-        <v>46.02829344993981</v>
+        <v>41.84309188103682</v>
       </c>
       <c r="D2" t="n">
-        <v>36.92788359354479</v>
+        <v>48.43151990194294</v>
       </c>
       <c r="E2" t="n">
-        <v>29.27792125364033</v>
+        <v>35.64693291853079</v>
       </c>
       <c r="F2" t="n">
-        <v>40.25376211578347</v>
+        <v>31.30831562638745</v>
       </c>
       <c r="G2" t="n">
-        <v>35.87826649481487</v>
+        <v>38.56257352331381</v>
       </c>
       <c r="H2" t="n">
-        <v>42.9751727525586</v>
+        <v>37.78791270017622</v>
       </c>
       <c r="I2" t="n">
-        <v>35.49478151563573</v>
+        <v>45.44171351538792</v>
       </c>
       <c r="J2" t="n">
-        <v>32.19058133059788</v>
+        <v>32.14198073773235</v>
       </c>
     </row>
   </sheetData>
@@ -5082,31 +5082,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.04572472744354</v>
+        <v>30.1491949519713</v>
       </c>
       <c r="C2" t="n">
-        <v>32.11003244584737</v>
+        <v>39.03286042842225</v>
       </c>
       <c r="D2" t="n">
-        <v>34.74078535100029</v>
+        <v>38.36851776648138</v>
       </c>
       <c r="E2" t="n">
-        <v>44.69955588015996</v>
+        <v>31.86474591222676</v>
       </c>
       <c r="F2" t="n">
-        <v>26.99926659044963</v>
+        <v>30.24936415219033</v>
       </c>
       <c r="G2" t="n">
-        <v>37.06041310315232</v>
+        <v>46.65546783549189</v>
       </c>
       <c r="H2" t="n">
-        <v>29.85259859698774</v>
+        <v>47.5252105359639</v>
       </c>
       <c r="I2" t="n">
-        <v>41.73272531559148</v>
+        <v>35.50190751414411</v>
       </c>
       <c r="J2" t="n">
-        <v>30.48732061168072</v>
+        <v>42.8375191676022</v>
       </c>
     </row>
   </sheetData>
@@ -5180,31 +5180,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.68881991466603</v>
+        <v>37.73001131593698</v>
       </c>
       <c r="C2" t="n">
-        <v>35.79205361604053</v>
+        <v>39.12507387664088</v>
       </c>
       <c r="D2" t="n">
-        <v>47.44834773070362</v>
+        <v>38.45304297280331</v>
       </c>
       <c r="E2" t="n">
-        <v>29.74275976170922</v>
+        <v>35.56346992709531</v>
       </c>
       <c r="F2" t="n">
-        <v>44.06148233905173</v>
+        <v>36.31413225822384</v>
       </c>
       <c r="G2" t="n">
-        <v>47.98274640543798</v>
+        <v>29.91530048444214</v>
       </c>
       <c r="H2" t="n">
-        <v>42.6974600849929</v>
+        <v>42.18333123127182</v>
       </c>
       <c r="I2" t="n">
-        <v>28.09346971289688</v>
+        <v>41.46616170354575</v>
       </c>
       <c r="J2" t="n">
-        <v>31.23919928467646</v>
+        <v>36.72598148754447</v>
       </c>
     </row>
   </sheetData>
@@ -5278,31 +5278,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.11673515917381</v>
+        <v>37.27350538805951</v>
       </c>
       <c r="C2" t="n">
-        <v>37.86405046436962</v>
+        <v>27.1393984705589</v>
       </c>
       <c r="D2" t="n">
-        <v>33.88646378745352</v>
+        <v>41.99827096035759</v>
       </c>
       <c r="E2" t="n">
-        <v>34.84814597870893</v>
+        <v>27.77281056353472</v>
       </c>
       <c r="F2" t="n">
-        <v>34.47330460828921</v>
+        <v>37.35644115231381</v>
       </c>
       <c r="G2" t="n">
-        <v>22.0896836652315</v>
+        <v>40.1935412240972</v>
       </c>
       <c r="H2" t="n">
-        <v>28.70169274913151</v>
+        <v>42.05722380236808</v>
       </c>
       <c r="I2" t="n">
-        <v>34.89087531615818</v>
+        <v>37.00937422358763</v>
       </c>
       <c r="J2" t="n">
-        <v>28.14379191443661</v>
+        <v>37.26126504974896</v>
       </c>
     </row>
   </sheetData>
@@ -5376,31 +5376,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.86898193514539</v>
+        <v>31.0795094727487</v>
       </c>
       <c r="C2" t="n">
-        <v>43.10186261216327</v>
+        <v>53.42256238779951</v>
       </c>
       <c r="D2" t="n">
-        <v>31.56958058854667</v>
+        <v>46.67037844126257</v>
       </c>
       <c r="E2" t="n">
-        <v>40.50667333759973</v>
+        <v>32.62418817071929</v>
       </c>
       <c r="F2" t="n">
-        <v>45.29909192092728</v>
+        <v>39.42939989989358</v>
       </c>
       <c r="G2" t="n">
-        <v>52.19208184074879</v>
+        <v>35.84859686532749</v>
       </c>
       <c r="H2" t="n">
-        <v>34.56664586360766</v>
+        <v>42.58962388546112</v>
       </c>
       <c r="I2" t="n">
-        <v>25.40238601997468</v>
+        <v>43.09909886509781</v>
       </c>
       <c r="J2" t="n">
-        <v>30.40162644365575</v>
+        <v>46.2384924593809</v>
       </c>
     </row>
   </sheetData>
@@ -5474,31 +5474,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.11847132222976</v>
+        <v>29.67210076449411</v>
       </c>
       <c r="C2" t="n">
-        <v>26.08174820732846</v>
+        <v>25.04799592837143</v>
       </c>
       <c r="D2" t="n">
-        <v>33.10808033172373</v>
+        <v>53.1190465905711</v>
       </c>
       <c r="E2" t="n">
-        <v>35.67444021197912</v>
+        <v>30.20282903891719</v>
       </c>
       <c r="F2" t="n">
-        <v>31.3816060350247</v>
+        <v>40.41850516164353</v>
       </c>
       <c r="G2" t="n">
-        <v>37.84333702724137</v>
+        <v>37.56340831148523</v>
       </c>
       <c r="H2" t="n">
-        <v>30.282089469704</v>
+        <v>41.37549298757249</v>
       </c>
       <c r="I2" t="n">
-        <v>34.81140033739361</v>
+        <v>33.08911434019052</v>
       </c>
       <c r="J2" t="n">
-        <v>46.630181155111</v>
+        <v>45.54541856499309</v>
       </c>
     </row>
   </sheetData>
@@ -5572,31 +5572,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.8613280692121</v>
+        <v>31.38911128796357</v>
       </c>
       <c r="C2" t="n">
-        <v>39.81094571715613</v>
+        <v>35.13618866808125</v>
       </c>
       <c r="D2" t="n">
-        <v>36.81418524017812</v>
+        <v>48.64489970090057</v>
       </c>
       <c r="E2" t="n">
-        <v>41.07792002260022</v>
+        <v>37.36557465248157</v>
       </c>
       <c r="F2" t="n">
-        <v>43.07102585516438</v>
+        <v>37.07925088038933</v>
       </c>
       <c r="G2" t="n">
-        <v>35.37602595777729</v>
+        <v>45.83806767215177</v>
       </c>
       <c r="H2" t="n">
-        <v>37.30466574463372</v>
+        <v>52.59652676038849</v>
       </c>
       <c r="I2" t="n">
-        <v>44.75474932843261</v>
+        <v>61.65678431317322</v>
       </c>
       <c r="J2" t="n">
-        <v>29.22671558577764</v>
+        <v>46.0940843322322</v>
       </c>
     </row>
   </sheetData>
@@ -5670,31 +5670,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.05603594744082</v>
+        <v>42.48746464167787</v>
       </c>
       <c r="C2" t="n">
-        <v>50.83525505030011</v>
+        <v>41.40925371848645</v>
       </c>
       <c r="D2" t="n">
-        <v>35.32997602810629</v>
+        <v>38.40148665710482</v>
       </c>
       <c r="E2" t="n">
-        <v>38.97474891853652</v>
+        <v>36.26730155227834</v>
       </c>
       <c r="F2" t="n">
-        <v>35.36962248986851</v>
+        <v>43.36345037890836</v>
       </c>
       <c r="G2" t="n">
-        <v>42.02593588417529</v>
+        <v>42.45808098503245</v>
       </c>
       <c r="H2" t="n">
-        <v>33.1813679905838</v>
+        <v>33.57927507920353</v>
       </c>
       <c r="I2" t="n">
-        <v>28.722710090959</v>
+        <v>53.51102056372133</v>
       </c>
       <c r="J2" t="n">
-        <v>31.80724642680741</v>
+        <v>55.27520941862584</v>
       </c>
     </row>
   </sheetData>
@@ -5768,31 +5768,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.36289787128065</v>
+        <v>37.7032211366889</v>
       </c>
       <c r="C2" t="n">
-        <v>38.50590440776038</v>
+        <v>56.01128331415059</v>
       </c>
       <c r="D2" t="n">
-        <v>44.131326124561</v>
+        <v>31.21602035296804</v>
       </c>
       <c r="E2" t="n">
-        <v>46.54879852071092</v>
+        <v>37.01747809404844</v>
       </c>
       <c r="F2" t="n">
-        <v>30.12629349989678</v>
+        <v>39.25273271204517</v>
       </c>
       <c r="G2" t="n">
-        <v>40.14092175487013</v>
+        <v>41.71162766519811</v>
       </c>
       <c r="H2" t="n">
-        <v>30.70075275477191</v>
+        <v>33.55736101232346</v>
       </c>
       <c r="I2" t="n">
-        <v>45.38872757600753</v>
+        <v>48.77650165594473</v>
       </c>
       <c r="J2" t="n">
-        <v>24.69766195400102</v>
+        <v>47.3343790072167</v>
       </c>
     </row>
   </sheetData>
@@ -5866,31 +5866,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.53126316439599</v>
+        <v>31.6187952150399</v>
       </c>
       <c r="C2" t="n">
-        <v>31.70798443759007</v>
+        <v>46.00168173062237</v>
       </c>
       <c r="D2" t="n">
-        <v>23.94509679724715</v>
+        <v>38.53340939323173</v>
       </c>
       <c r="E2" t="n">
-        <v>49.55311838996074</v>
+        <v>24.26659983395137</v>
       </c>
       <c r="F2" t="n">
-        <v>35.91981514097228</v>
+        <v>41.85458887240108</v>
       </c>
       <c r="G2" t="n">
-        <v>38.6739693733596</v>
+        <v>34.03063455060407</v>
       </c>
       <c r="H2" t="n">
-        <v>24.31480490728041</v>
+        <v>35.51882491203666</v>
       </c>
       <c r="I2" t="n">
-        <v>44.12327188417923</v>
+        <v>46.76449011670181</v>
       </c>
       <c r="J2" t="n">
-        <v>36.02696135948545</v>
+        <v>25.46415049541892</v>
       </c>
     </row>
   </sheetData>
@@ -5964,31 +5964,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.00828009582358</v>
+        <v>32.60993627711669</v>
       </c>
       <c r="C2" t="n">
-        <v>40.43044776531291</v>
+        <v>41.75256288247564</v>
       </c>
       <c r="D2" t="n">
-        <v>40.38451064443588</v>
+        <v>47.69861840111147</v>
       </c>
       <c r="E2" t="n">
-        <v>20.75255474723778</v>
+        <v>32.34211694077875</v>
       </c>
       <c r="F2" t="n">
-        <v>55.97458933662448</v>
+        <v>33.42990224316042</v>
       </c>
       <c r="G2" t="n">
-        <v>23.86321300648272</v>
+        <v>20.51767894607903</v>
       </c>
       <c r="H2" t="n">
-        <v>32.95689299635277</v>
+        <v>44.3145764273787</v>
       </c>
       <c r="I2" t="n">
-        <v>37.97406129395738</v>
+        <v>56.44613826294831</v>
       </c>
       <c r="J2" t="n">
-        <v>30.01827281187564</v>
+        <v>20.78368738834571</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.96434941117291</v>
+        <v>43.05216881725627</v>
       </c>
       <c r="C2" t="n">
-        <v>37.90057566855116</v>
+        <v>30.04926667292741</v>
       </c>
       <c r="D2" t="n">
-        <v>29.27586077394585</v>
+        <v>37.72893817275848</v>
       </c>
       <c r="E2" t="n">
-        <v>37.26658159369864</v>
+        <v>35.91231214789197</v>
       </c>
       <c r="F2" t="n">
-        <v>33.34568341467623</v>
+        <v>28.01614124919016</v>
       </c>
       <c r="G2" t="n">
-        <v>28.16088371125333</v>
+        <v>28.22819744884106</v>
       </c>
       <c r="H2" t="n">
-        <v>28.17210917050277</v>
+        <v>42.9401888142816</v>
       </c>
       <c r="I2" t="n">
-        <v>23.84053841592232</v>
+        <v>34.29227923943357</v>
       </c>
       <c r="J2" t="n">
-        <v>57.40053510615463</v>
+        <v>33.48824679361343</v>
       </c>
     </row>
   </sheetData>
@@ -6160,31 +6160,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.81943921278173</v>
+        <v>33.59569602668072</v>
       </c>
       <c r="C2" t="n">
-        <v>33.44883154871168</v>
+        <v>44.85962954409549</v>
       </c>
       <c r="D2" t="n">
-        <v>37.6828953629884</v>
+        <v>23.83230780520802</v>
       </c>
       <c r="E2" t="n">
-        <v>35.25306694024516</v>
+        <v>26.13665432335064</v>
       </c>
       <c r="F2" t="n">
-        <v>31.8109082070741</v>
+        <v>34.51831419218973</v>
       </c>
       <c r="G2" t="n">
-        <v>41.30679322247485</v>
+        <v>38.909943081069</v>
       </c>
       <c r="H2" t="n">
-        <v>22.11133047443345</v>
+        <v>40.11143013186368</v>
       </c>
       <c r="I2" t="n">
-        <v>39.28176490648367</v>
+        <v>52.1522983975097</v>
       </c>
       <c r="J2" t="n">
-        <v>27.52330683614237</v>
+        <v>51.24269591869628</v>
       </c>
     </row>
   </sheetData>
@@ -6258,31 +6258,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.6226200870946</v>
+        <v>33.74496121575465</v>
       </c>
       <c r="C2" t="n">
-        <v>33.33386712582913</v>
+        <v>38.92559590569908</v>
       </c>
       <c r="D2" t="n">
-        <v>30.84883233806009</v>
+        <v>52.2196826281374</v>
       </c>
       <c r="E2" t="n">
-        <v>45.48608338842706</v>
+        <v>30.12769312774783</v>
       </c>
       <c r="F2" t="n">
-        <v>46.1606495793701</v>
+        <v>42.58339527543784</v>
       </c>
       <c r="G2" t="n">
-        <v>36.05858503134112</v>
+        <v>42.47714289356094</v>
       </c>
       <c r="H2" t="n">
-        <v>45.61988277174543</v>
+        <v>37.48720840055997</v>
       </c>
       <c r="I2" t="n">
-        <v>25.13490299383125</v>
+        <v>42.71526232337662</v>
       </c>
       <c r="J2" t="n">
-        <v>32.58507765544195</v>
+        <v>40.04039459951469</v>
       </c>
     </row>
   </sheetData>
@@ -6356,31 +6356,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.71864489007289</v>
+        <v>22.93317683345457</v>
       </c>
       <c r="C2" t="n">
-        <v>33.03984560494074</v>
+        <v>31.48072587660169</v>
       </c>
       <c r="D2" t="n">
-        <v>37.9201821961265</v>
+        <v>47.65006125263304</v>
       </c>
       <c r="E2" t="n">
-        <v>34.37225600312696</v>
+        <v>39.91007921226749</v>
       </c>
       <c r="F2" t="n">
-        <v>45.94469574307606</v>
+        <v>42.17268615824759</v>
       </c>
       <c r="G2" t="n">
-        <v>36.1428579209315</v>
+        <v>32.22563074510575</v>
       </c>
       <c r="H2" t="n">
-        <v>31.93669894263827</v>
+        <v>41.25887334332889</v>
       </c>
       <c r="I2" t="n">
-        <v>26.80652287743668</v>
+        <v>45.35064144010723</v>
       </c>
       <c r="J2" t="n">
-        <v>30.19131946681818</v>
+        <v>37.8710556810484</v>
       </c>
     </row>
   </sheetData>
@@ -6454,31 +6454,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.52467625707069</v>
+        <v>38.54174352785417</v>
       </c>
       <c r="C2" t="n">
-        <v>37.92890896882974</v>
+        <v>58.28438434475243</v>
       </c>
       <c r="D2" t="n">
-        <v>37.44778791677494</v>
+        <v>41.1322671910449</v>
       </c>
       <c r="E2" t="n">
-        <v>29.67901232176737</v>
+        <v>33.91389638427361</v>
       </c>
       <c r="F2" t="n">
-        <v>37.21885161535712</v>
+        <v>35.61189300215473</v>
       </c>
       <c r="G2" t="n">
-        <v>29.97994262835119</v>
+        <v>47.32773759280258</v>
       </c>
       <c r="H2" t="n">
-        <v>31.3506088764898</v>
+        <v>37.54744802301435</v>
       </c>
       <c r="I2" t="n">
-        <v>39.77144377307945</v>
+        <v>30.93750548452154</v>
       </c>
       <c r="J2" t="n">
-        <v>39.09641257431781</v>
+        <v>31.24708610819341</v>
       </c>
     </row>
   </sheetData>
@@ -6552,31 +6552,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.27265454325444</v>
+        <v>24.89778036776197</v>
       </c>
       <c r="C2" t="n">
-        <v>18.23190160138005</v>
+        <v>46.64381185632803</v>
       </c>
       <c r="D2" t="n">
-        <v>31.02459547532612</v>
+        <v>33.08200734909907</v>
       </c>
       <c r="E2" t="n">
-        <v>1710.435383552177</v>
+        <v>31.54149279453784</v>
       </c>
       <c r="F2" t="n">
-        <v>35.39493813658117</v>
+        <v>42.96880055390665</v>
       </c>
       <c r="G2" t="n">
-        <v>54.12920888433361</v>
+        <v>38.75068076370842</v>
       </c>
       <c r="H2" t="n">
-        <v>17.73343069030603</v>
+        <v>51.20451425989114</v>
       </c>
       <c r="I2" t="n">
-        <v>42.8759518319352</v>
+        <v>44.24319287515893</v>
       </c>
       <c r="J2" t="n">
-        <v>43.26174737169403</v>
+        <v>39.47183695263826</v>
       </c>
     </row>
   </sheetData>
@@ -6650,31 +6650,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.68579900901788</v>
+        <v>27.45295021123692</v>
       </c>
       <c r="C2" t="n">
-        <v>58.12531365517209</v>
+        <v>49.23738928420465</v>
       </c>
       <c r="D2" t="n">
-        <v>27.03041128821961</v>
+        <v>49.08380209885699</v>
       </c>
       <c r="E2" t="n">
-        <v>27.02809278734593</v>
+        <v>31.42790368129342</v>
       </c>
       <c r="F2" t="n">
-        <v>53.02656120905988</v>
+        <v>30.56518736828512</v>
       </c>
       <c r="G2" t="n">
-        <v>44.10996876627254</v>
+        <v>26.77642924295497</v>
       </c>
       <c r="H2" t="n">
-        <v>27.65235090148692</v>
+        <v>48.40494057407253</v>
       </c>
       <c r="I2" t="n">
-        <v>40.13058562777936</v>
+        <v>42.33647814653461</v>
       </c>
       <c r="J2" t="n">
-        <v>36.17930608772466</v>
+        <v>50.57148461529727</v>
       </c>
     </row>
   </sheetData>
@@ -6748,31 +6748,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.81173217288047</v>
+        <v>36.15432137208386</v>
       </c>
       <c r="C2" t="n">
-        <v>55.99815216322117</v>
+        <v>37.8280999042723</v>
       </c>
       <c r="D2" t="n">
-        <v>37.97895692850207</v>
+        <v>37.40455555285877</v>
       </c>
       <c r="E2" t="n">
-        <v>31.29024382126468</v>
+        <v>34.34880045479926</v>
       </c>
       <c r="F2" t="n">
-        <v>27.20774252152923</v>
+        <v>37.88586795152371</v>
       </c>
       <c r="G2" t="n">
-        <v>49.67599240352283</v>
+        <v>35.70469025731659</v>
       </c>
       <c r="H2" t="n">
-        <v>30.648106487326</v>
+        <v>42.37060259071025</v>
       </c>
       <c r="I2" t="n">
-        <v>30.41444555510676</v>
+        <v>35.77434268456354</v>
       </c>
       <c r="J2" t="n">
-        <v>36.01315175694212</v>
+        <v>51.37231723456615</v>
       </c>
     </row>
   </sheetData>
@@ -6846,31 +6846,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.85758952712619</v>
+        <v>29.62266975655254</v>
       </c>
       <c r="C2" t="n">
-        <v>59.31762765031461</v>
+        <v>42.89397766902082</v>
       </c>
       <c r="D2" t="n">
-        <v>23.14568070169222</v>
+        <v>35.6594700762341</v>
       </c>
       <c r="E2" t="n">
-        <v>51.46259772905439</v>
+        <v>34.11436503649102</v>
       </c>
       <c r="F2" t="n">
-        <v>32.77908397259612</v>
+        <v>38.85274646779835</v>
       </c>
       <c r="G2" t="n">
-        <v>17.64397418637492</v>
+        <v>33.15272284898351</v>
       </c>
       <c r="H2" t="n">
-        <v>34.56485081247232</v>
+        <v>38.70388910835693</v>
       </c>
       <c r="I2" t="n">
-        <v>44.91295848141272</v>
+        <v>37.59991542516732</v>
       </c>
       <c r="J2" t="n">
-        <v>25.128267633044</v>
+        <v>56.00929083262253</v>
       </c>
     </row>
   </sheetData>
@@ -6944,31 +6944,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.19750649881865</v>
+        <v>37.4036010699164</v>
       </c>
       <c r="C2" t="n">
-        <v>46.66098829837859</v>
+        <v>61.174117074687</v>
       </c>
       <c r="D2" t="n">
-        <v>43.04549632036554</v>
+        <v>56.30448138091793</v>
       </c>
       <c r="E2" t="n">
-        <v>34.70623187847951</v>
+        <v>29.62204385521795</v>
       </c>
       <c r="F2" t="n">
-        <v>47.13386879261843</v>
+        <v>40.74159328210646</v>
       </c>
       <c r="G2" t="n">
-        <v>39.87441659651144</v>
+        <v>37.67940543779872</v>
       </c>
       <c r="H2" t="n">
-        <v>29.95556040988419</v>
+        <v>38.26610657904303</v>
       </c>
       <c r="I2" t="n">
-        <v>39.08373610660362</v>
+        <v>39.58643824979596</v>
       </c>
       <c r="J2" t="n">
-        <v>43.86182680433801</v>
+        <v>46.01984490536503</v>
       </c>
     </row>
   </sheetData>
@@ -7042,31 +7042,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.96699013908335</v>
+        <v>36.85406619470765</v>
       </c>
       <c r="C2" t="n">
-        <v>33.76082682013969</v>
+        <v>41.81137748667754</v>
       </c>
       <c r="D2" t="n">
-        <v>37.69303496721996</v>
+        <v>43.06484074640486</v>
       </c>
       <c r="E2" t="n">
-        <v>32.28119519815215</v>
+        <v>32.44774285737381</v>
       </c>
       <c r="F2" t="n">
-        <v>32.0289964024054</v>
+        <v>40.87812798443665</v>
       </c>
       <c r="G2" t="n">
-        <v>33.13950433511076</v>
+        <v>36.91485329148549</v>
       </c>
       <c r="H2" t="n">
-        <v>32.11322167376628</v>
+        <v>44.39920767852214</v>
       </c>
       <c r="I2" t="n">
-        <v>46.26180461986691</v>
+        <v>33.15052984691904</v>
       </c>
       <c r="J2" t="n">
-        <v>40.91229472571602</v>
+        <v>40.84463557012261</v>
       </c>
     </row>
   </sheetData>
@@ -7140,31 +7140,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.11798060905605</v>
+        <v>34.31138519898142</v>
       </c>
       <c r="C2" t="n">
-        <v>27.74678529968515</v>
+        <v>41.77975544337978</v>
       </c>
       <c r="D2" t="n">
-        <v>46.02721621944176</v>
+        <v>45.53582326534423</v>
       </c>
       <c r="E2" t="n">
-        <v>38.32079731763452</v>
+        <v>35.63676182524042</v>
       </c>
       <c r="F2" t="n">
-        <v>43.96793534888375</v>
+        <v>41.44514321463383</v>
       </c>
       <c r="G2" t="n">
-        <v>42.40898271963385</v>
+        <v>46.89945906036674</v>
       </c>
       <c r="H2" t="n">
-        <v>28.96323251396492</v>
+        <v>42.78304136527355</v>
       </c>
       <c r="I2" t="n">
-        <v>37.1306498585277</v>
+        <v>45.60630890792556</v>
       </c>
       <c r="J2" t="n">
-        <v>56.89686651652859</v>
+        <v>28.79851332880295</v>
       </c>
     </row>
   </sheetData>
@@ -7238,31 +7238,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.98230691159862</v>
+        <v>37.73560554311052</v>
       </c>
       <c r="C2" t="n">
-        <v>33.32420284119893</v>
+        <v>43.2618563802142</v>
       </c>
       <c r="D2" t="n">
-        <v>25.05360357190641</v>
+        <v>32.44129984503563</v>
       </c>
       <c r="E2" t="n">
-        <v>54.39734822346026</v>
+        <v>37.22312540854823</v>
       </c>
       <c r="F2" t="n">
-        <v>44.14710114159005</v>
+        <v>36.87911656066144</v>
       </c>
       <c r="G2" t="n">
-        <v>34.05472858398856</v>
+        <v>41.00096568328712</v>
       </c>
       <c r="H2" t="n">
-        <v>53.16616052939913</v>
+        <v>45.77385342056947</v>
       </c>
       <c r="I2" t="n">
-        <v>36.47923120313845</v>
+        <v>60.95914448471792</v>
       </c>
       <c r="J2" t="n">
-        <v>36.41997734001527</v>
+        <v>48.81374778599088</v>
       </c>
     </row>
   </sheetData>
@@ -7336,31 +7336,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.10282355456185</v>
+        <v>44.22260972592706</v>
       </c>
       <c r="C2" t="n">
-        <v>41.9504128149001</v>
+        <v>44.48564115288806</v>
       </c>
       <c r="D2" t="n">
-        <v>26.73360948460965</v>
+        <v>42.43597888313234</v>
       </c>
       <c r="E2" t="n">
-        <v>34.29224075071406</v>
+        <v>34.29505227532075</v>
       </c>
       <c r="F2" t="n">
-        <v>46.72481877965974</v>
+        <v>42.47168675261062</v>
       </c>
       <c r="G2" t="n">
-        <v>33.91894614677398</v>
+        <v>28.25462843660228</v>
       </c>
       <c r="H2" t="n">
-        <v>45.9062985818236</v>
+        <v>39.27518201811337</v>
       </c>
       <c r="I2" t="n">
-        <v>25.88413876479505</v>
+        <v>47.61575929409493</v>
       </c>
       <c r="J2" t="n">
-        <v>55.16255428430043</v>
+        <v>61.68234613312993</v>
       </c>
     </row>
   </sheetData>
@@ -7434,31 +7434,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.64269360623667</v>
+        <v>28.7484883207772</v>
       </c>
       <c r="C2" t="n">
-        <v>42.4824599783171</v>
+        <v>41.57195911621769</v>
       </c>
       <c r="D2" t="n">
-        <v>23.58110249192825</v>
+        <v>47.65316695486101</v>
       </c>
       <c r="E2" t="n">
-        <v>42.21267280040697</v>
+        <v>44.49605907591378</v>
       </c>
       <c r="F2" t="n">
-        <v>41.4041712167765</v>
+        <v>33.30607226129098</v>
       </c>
       <c r="G2" t="n">
-        <v>39.78979212179625</v>
+        <v>45.50907302550596</v>
       </c>
       <c r="H2" t="n">
-        <v>33.21703814527986</v>
+        <v>28.74002308155081</v>
       </c>
       <c r="I2" t="n">
-        <v>31.71430569260115</v>
+        <v>61.89323136157762</v>
       </c>
       <c r="J2" t="n">
-        <v>46.84352666784332</v>
+        <v>38.16900935376687</v>
       </c>
     </row>
   </sheetData>
@@ -7532,31 +7532,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.82740666940399</v>
+        <v>32.41894767128341</v>
       </c>
       <c r="C2" t="n">
-        <v>32.69757579219906</v>
+        <v>36.60027657236033</v>
       </c>
       <c r="D2" t="n">
-        <v>40.0256131140418</v>
+        <v>35.61870072797061</v>
       </c>
       <c r="E2" t="n">
-        <v>44.12297997237184</v>
+        <v>32.76019032935437</v>
       </c>
       <c r="F2" t="n">
-        <v>26.96647024061767</v>
+        <v>36.18874503304168</v>
       </c>
       <c r="G2" t="n">
-        <v>37.56404417087712</v>
+        <v>34.46665946726061</v>
       </c>
       <c r="H2" t="n">
-        <v>30.79302254083178</v>
+        <v>38.17794209082246</v>
       </c>
       <c r="I2" t="n">
-        <v>26.20063057483559</v>
+        <v>43.97050203966985</v>
       </c>
       <c r="J2" t="n">
-        <v>33.20532474539937</v>
+        <v>32.33724718114509</v>
       </c>
     </row>
   </sheetData>
@@ -7630,31 +7630,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.08219073268805</v>
+        <v>28.83772402774586</v>
       </c>
       <c r="C2" t="n">
-        <v>39.28932891857686</v>
+        <v>30.73799947359387</v>
       </c>
       <c r="D2" t="n">
-        <v>32.81813399929725</v>
+        <v>46.164045641858</v>
       </c>
       <c r="E2" t="n">
-        <v>18.11508266918422</v>
+        <v>33.10006852132931</v>
       </c>
       <c r="F2" t="n">
-        <v>40.81269939059481</v>
+        <v>35.11508516597205</v>
       </c>
       <c r="G2" t="n">
-        <v>54.21178218686272</v>
+        <v>40.60526866537604</v>
       </c>
       <c r="H2" t="n">
-        <v>30.4401434033983</v>
+        <v>44.75390369903536</v>
       </c>
       <c r="I2" t="n">
-        <v>40.71827519317534</v>
+        <v>48.61504959145336</v>
       </c>
       <c r="J2" t="n">
-        <v>47.15362333284219</v>
+        <v>45.00815080808893</v>
       </c>
     </row>
   </sheetData>
@@ -7728,31 +7728,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.95592522681093</v>
+        <v>30.58441280909216</v>
       </c>
       <c r="C2" t="n">
-        <v>33.87129453018448</v>
+        <v>38.47438735956195</v>
       </c>
       <c r="D2" t="n">
-        <v>31.10373028052723</v>
+        <v>38.39706449439273</v>
       </c>
       <c r="E2" t="n">
-        <v>32.79897965970111</v>
+        <v>31.74537746752971</v>
       </c>
       <c r="F2" t="n">
-        <v>52.39366438898684</v>
+        <v>41.20419066874022</v>
       </c>
       <c r="G2" t="n">
-        <v>38.40409355379604</v>
+        <v>37.70177623311709</v>
       </c>
       <c r="H2" t="n">
-        <v>42.40773818970758</v>
+        <v>53.2866511732224</v>
       </c>
       <c r="I2" t="n">
-        <v>36.27733341744131</v>
+        <v>44.86150398983548</v>
       </c>
       <c r="J2" t="n">
-        <v>52.08880318233508</v>
+        <v>58.1972981529897</v>
       </c>
     </row>
   </sheetData>
@@ -7826,31 +7826,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.76425072034683</v>
+        <v>30.49535083595393</v>
       </c>
       <c r="C2" t="n">
-        <v>34.99116884028577</v>
+        <v>52.8631138037162</v>
       </c>
       <c r="D2" t="n">
-        <v>25.14623044809532</v>
+        <v>46.46578642967751</v>
       </c>
       <c r="E2" t="n">
-        <v>23.58125374297794</v>
+        <v>31.48086368717747</v>
       </c>
       <c r="F2" t="n">
-        <v>27.19924173587224</v>
+        <v>33.03775363277319</v>
       </c>
       <c r="G2" t="n">
-        <v>44.99392202664639</v>
+        <v>36.53971794938013</v>
       </c>
       <c r="H2" t="n">
-        <v>37.22123008031323</v>
+        <v>34.95182533942322</v>
       </c>
       <c r="I2" t="n">
-        <v>33.9644788709824</v>
+        <v>34.63697129574491</v>
       </c>
       <c r="J2" t="n">
-        <v>61.58768309769334</v>
+        <v>42.03770719624125</v>
       </c>
     </row>
   </sheetData>
@@ -7924,31 +7924,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.07545524308384</v>
+        <v>34.34347354377102</v>
       </c>
       <c r="C2" t="n">
-        <v>26.49434888665121</v>
+        <v>47.65028801604439</v>
       </c>
       <c r="D2" t="n">
-        <v>48.52014965408171</v>
+        <v>49.05422436890254</v>
       </c>
       <c r="E2" t="n">
-        <v>48.29596095548484</v>
+        <v>39.21818115671925</v>
       </c>
       <c r="F2" t="n">
-        <v>54.27947459682903</v>
+        <v>30.75783320133931</v>
       </c>
       <c r="G2" t="n">
-        <v>37.60877482661945</v>
+        <v>30.38181465318678</v>
       </c>
       <c r="H2" t="n">
-        <v>30.67198878739122</v>
+        <v>43.31363612758464</v>
       </c>
       <c r="I2" t="n">
-        <v>24.83976050137586</v>
+        <v>36.8281361423053</v>
       </c>
       <c r="J2" t="n">
-        <v>29.75900106260385</v>
+        <v>40.48777151167292</v>
       </c>
     </row>
   </sheetData>
@@ -8022,31 +8022,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.63552086031969</v>
+        <v>34.3407640480975</v>
       </c>
       <c r="C2" t="n">
-        <v>48.17299163559152</v>
+        <v>51.07010221896373</v>
       </c>
       <c r="D2" t="n">
-        <v>33.53698204056644</v>
+        <v>50.96993433852938</v>
       </c>
       <c r="E2" t="n">
-        <v>20.95474041886987</v>
+        <v>36.12031981925319</v>
       </c>
       <c r="F2" t="n">
-        <v>32.99395910036646</v>
+        <v>29.98837761134963</v>
       </c>
       <c r="G2" t="n">
-        <v>39.52933797616341</v>
+        <v>56.11034298020468</v>
       </c>
       <c r="H2" t="n">
-        <v>53.59953473880937</v>
+        <v>44.64544966544253</v>
       </c>
       <c r="I2" t="n">
-        <v>35.62955928386471</v>
+        <v>26.45936667602497</v>
       </c>
       <c r="J2" t="n">
-        <v>27.3782290389175</v>
+        <v>33.95637680819508</v>
       </c>
     </row>
   </sheetData>
@@ -8120,31 +8120,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.4346553755643</v>
+        <v>38.02488124423183</v>
       </c>
       <c r="C2" t="n">
-        <v>21.48013436451985</v>
+        <v>48.16365766122921</v>
       </c>
       <c r="D2" t="n">
-        <v>15.84927821788206</v>
+        <v>32.99808289869161</v>
       </c>
       <c r="E2" t="n">
-        <v>43.28973756227919</v>
+        <v>28.94206465777996</v>
       </c>
       <c r="F2" t="n">
-        <v>41.3535881366543</v>
+        <v>29.54856946700651</v>
       </c>
       <c r="G2" t="n">
-        <v>44.86744883960343</v>
+        <v>53.47974835071876</v>
       </c>
       <c r="H2" t="n">
-        <v>32.59562212386761</v>
+        <v>35.70716101813636</v>
       </c>
       <c r="I2" t="n">
-        <v>48.23482480810253</v>
+        <v>44.48930164974913</v>
       </c>
       <c r="J2" t="n">
-        <v>40.54006103174788</v>
+        <v>40.44776105224816</v>
       </c>
     </row>
   </sheetData>
@@ -8218,31 +8218,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.72582763696872</v>
+        <v>36.53519912501255</v>
       </c>
       <c r="C2" t="n">
-        <v>35.90333035057258</v>
+        <v>48.33611488146229</v>
       </c>
       <c r="D2" t="n">
-        <v>38.49045096309729</v>
+        <v>38.89674664250671</v>
       </c>
       <c r="E2" t="n">
-        <v>47.36813876933508</v>
+        <v>31.77389363236348</v>
       </c>
       <c r="F2" t="n">
-        <v>38.61448926078307</v>
+        <v>44.461968780314</v>
       </c>
       <c r="G2" t="n">
-        <v>32.35595619267761</v>
+        <v>26.15080675306413</v>
       </c>
       <c r="H2" t="n">
-        <v>37.72186061217413</v>
+        <v>36.30064314680875</v>
       </c>
       <c r="I2" t="n">
-        <v>35.6584236451383</v>
+        <v>65.35067653167884</v>
       </c>
       <c r="J2" t="n">
-        <v>34.67074941320797</v>
+        <v>46.43911581660265</v>
       </c>
     </row>
   </sheetData>
@@ -8316,31 +8316,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>14.44523469387096</v>
+        <v>31.51612086990797</v>
       </c>
       <c r="C2" t="n">
-        <v>44.51817706141047</v>
+        <v>49.99603619524415</v>
       </c>
       <c r="D2" t="n">
-        <v>32.43278794823623</v>
+        <v>22.99221912438695</v>
       </c>
       <c r="E2" t="n">
-        <v>35.61910219964787</v>
+        <v>42.49743686320823</v>
       </c>
       <c r="F2" t="n">
-        <v>35.8555470325874</v>
+        <v>32.98460608421814</v>
       </c>
       <c r="G2" t="n">
-        <v>49.07888928358899</v>
+        <v>37.67917408780153</v>
       </c>
       <c r="H2" t="n">
-        <v>47.93421027373986</v>
+        <v>36.99027219077468</v>
       </c>
       <c r="I2" t="n">
-        <v>40.95677136866068</v>
+        <v>39.73079305378414</v>
       </c>
       <c r="J2" t="n">
-        <v>32.64359921612211</v>
+        <v>56.740532036378</v>
       </c>
     </row>
   </sheetData>
@@ -8414,31 +8414,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.63119163268639</v>
+        <v>36.92794537038954</v>
       </c>
       <c r="C2" t="n">
-        <v>41.4391155472284</v>
+        <v>38.67338555249943</v>
       </c>
       <c r="D2" t="n">
-        <v>45.45656416997537</v>
+        <v>34.69502736827733</v>
       </c>
       <c r="E2" t="n">
-        <v>32.89785494544898</v>
+        <v>39.38626157813499</v>
       </c>
       <c r="F2" t="n">
-        <v>27.66369552189044</v>
+        <v>35.0080884429814</v>
       </c>
       <c r="G2" t="n">
-        <v>46.47145576890718</v>
+        <v>35.83479542760721</v>
       </c>
       <c r="H2" t="n">
-        <v>34.90960505439307</v>
+        <v>39.49442234019099</v>
       </c>
       <c r="I2" t="n">
-        <v>36.99132402434304</v>
+        <v>38.37427496262826</v>
       </c>
       <c r="J2" t="n">
-        <v>35.35547474159598</v>
+        <v>36.11057491762245</v>
       </c>
     </row>
   </sheetData>
@@ -8512,31 +8512,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.16412001805789</v>
+        <v>30.81455877116376</v>
       </c>
       <c r="C2" t="n">
-        <v>53.19608746939446</v>
+        <v>22.92451538033249</v>
       </c>
       <c r="D2" t="n">
-        <v>28.93286260521552</v>
+        <v>35.79670130890917</v>
       </c>
       <c r="E2" t="n">
-        <v>21.852240632299</v>
+        <v>37.42870295981471</v>
       </c>
       <c r="F2" t="n">
-        <v>42.06222517670879</v>
+        <v>31.38595013045222</v>
       </c>
       <c r="G2" t="n">
-        <v>27.68679462502528</v>
+        <v>40.30720776658394</v>
       </c>
       <c r="H2" t="n">
-        <v>36.63600519085627</v>
+        <v>37.36038953319719</v>
       </c>
       <c r="I2" t="n">
-        <v>38.06140310544701</v>
+        <v>38.87565665477977</v>
       </c>
       <c r="J2" t="n">
-        <v>25.46735597214693</v>
+        <v>40.29022108746623</v>
       </c>
     </row>
   </sheetData>
@@ -8610,31 +8610,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.20182463061408</v>
+        <v>31.13343099759375</v>
       </c>
       <c r="C2" t="n">
-        <v>35.20264624646517</v>
+        <v>42.98833924545806</v>
       </c>
       <c r="D2" t="n">
-        <v>20.65606064221413</v>
+        <v>33.33264313344097</v>
       </c>
       <c r="E2" t="n">
-        <v>37.68457058718457</v>
+        <v>19.190440464479</v>
       </c>
       <c r="F2" t="n">
-        <v>30.53065147062696</v>
+        <v>37.12311142397331</v>
       </c>
       <c r="G2" t="n">
-        <v>45.65180660995826</v>
+        <v>42.44687797056082</v>
       </c>
       <c r="H2" t="n">
-        <v>20.34711849850162</v>
+        <v>36.48588301104306</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12437852356049</v>
+        <v>37.77567638837535</v>
       </c>
       <c r="J2" t="n">
-        <v>36.96057246906995</v>
+        <v>36.96454154766724</v>
       </c>
     </row>
   </sheetData>
@@ -8708,31 +8708,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.35808419307641</v>
+        <v>41.0952455715126</v>
       </c>
       <c r="C2" t="n">
-        <v>41.20950076527714</v>
+        <v>41.65244761661972</v>
       </c>
       <c r="D2" t="n">
-        <v>30.04787406191832</v>
+        <v>48.69546448912782</v>
       </c>
       <c r="E2" t="n">
-        <v>33.99556635243968</v>
+        <v>35.63116408557293</v>
       </c>
       <c r="F2" t="n">
-        <v>30.67358593363909</v>
+        <v>29.46724982464909</v>
       </c>
       <c r="G2" t="n">
-        <v>54.95689238389145</v>
+        <v>26.15350771193466</v>
       </c>
       <c r="H2" t="n">
-        <v>22.93071396653806</v>
+        <v>48.35845816397156</v>
       </c>
       <c r="I2" t="n">
-        <v>46.92286861860877</v>
+        <v>35.02939183421395</v>
       </c>
       <c r="J2" t="n">
-        <v>42.69307340316462</v>
+        <v>46.23209430308491</v>
       </c>
     </row>
   </sheetData>
@@ -8806,31 +8806,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.87283053283355</v>
+        <v>27.08650110790089</v>
       </c>
       <c r="C2" t="n">
-        <v>46.80503375061251</v>
+        <v>54.77146202055039</v>
       </c>
       <c r="D2" t="n">
-        <v>47.554511752841</v>
+        <v>38.25718192916144</v>
       </c>
       <c r="E2" t="n">
-        <v>33.2253168674019</v>
+        <v>47.3719313252032</v>
       </c>
       <c r="F2" t="n">
-        <v>46.93512871356491</v>
+        <v>41.59799650304888</v>
       </c>
       <c r="G2" t="n">
-        <v>33.80567003564909</v>
+        <v>39.15282499866093</v>
       </c>
       <c r="H2" t="n">
-        <v>35.65108066419804</v>
+        <v>43.39736250725615</v>
       </c>
       <c r="I2" t="n">
-        <v>37.73143003840867</v>
+        <v>50.70539582585416</v>
       </c>
       <c r="J2" t="n">
-        <v>39.16979008945383</v>
+        <v>43.15103372139293</v>
       </c>
     </row>
   </sheetData>
@@ -8904,31 +8904,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.06808417852609</v>
+        <v>36.66658710780847</v>
       </c>
       <c r="C2" t="n">
-        <v>44.19323859420904</v>
+        <v>36.44603520020548</v>
       </c>
       <c r="D2" t="n">
-        <v>38.45667214154382</v>
+        <v>31.22626132077709</v>
       </c>
       <c r="E2" t="n">
-        <v>31.64787578164229</v>
+        <v>64.93914559784375</v>
       </c>
       <c r="F2" t="n">
-        <v>36.29873286157339</v>
+        <v>47.8890171930046</v>
       </c>
       <c r="G2" t="n">
-        <v>30.77956572398948</v>
+        <v>36.80245593151528</v>
       </c>
       <c r="H2" t="n">
-        <v>48.98302648372701</v>
+        <v>25.82679626127884</v>
       </c>
       <c r="I2" t="n">
-        <v>32.38931417990585</v>
+        <v>35.3083571597705</v>
       </c>
       <c r="J2" t="n">
-        <v>36.33331856986488</v>
+        <v>40.69641018960023</v>
       </c>
     </row>
   </sheetData>
@@ -9002,31 +9002,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.58367859244498</v>
+        <v>28.75126010562716</v>
       </c>
       <c r="C2" t="n">
-        <v>35.37387013221109</v>
+        <v>38.30163025086148</v>
       </c>
       <c r="D2" t="n">
-        <v>27.32812849498213</v>
+        <v>51.99834494531</v>
       </c>
       <c r="E2" t="n">
-        <v>29.35861245528244</v>
+        <v>24.51924912685853</v>
       </c>
       <c r="F2" t="n">
-        <v>52.22205236686504</v>
+        <v>37.02814173673011</v>
       </c>
       <c r="G2" t="n">
-        <v>31.24219837198841</v>
+        <v>45.84986597722957</v>
       </c>
       <c r="H2" t="n">
-        <v>37.88364195332643</v>
+        <v>40.96697132066213</v>
       </c>
       <c r="I2" t="n">
-        <v>44.14793524603679</v>
+        <v>49.47952952269954</v>
       </c>
       <c r="J2" t="n">
-        <v>36.47608356293284</v>
+        <v>43.11388478270717</v>
       </c>
     </row>
   </sheetData>
@@ -9100,31 +9100,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.01170785572681</v>
+        <v>40.25885264215</v>
       </c>
       <c r="C2" t="n">
-        <v>27.13746685389296</v>
+        <v>44.31688101529563</v>
       </c>
       <c r="D2" t="n">
-        <v>25.99735990567943</v>
+        <v>47.47218429448117</v>
       </c>
       <c r="E2" t="n">
-        <v>35.50450802451173</v>
+        <v>30.90768224651791</v>
       </c>
       <c r="F2" t="n">
-        <v>39.2130818930064</v>
+        <v>38.38958432631708</v>
       </c>
       <c r="G2" t="n">
-        <v>29.79166526282292</v>
+        <v>27.36843012509327</v>
       </c>
       <c r="H2" t="n">
-        <v>36.24010707930668</v>
+        <v>31.53501415218712</v>
       </c>
       <c r="I2" t="n">
-        <v>23.57225451400734</v>
+        <v>37.88016337089846</v>
       </c>
       <c r="J2" t="n">
-        <v>45.92779106298708</v>
+        <v>44.9917808938869</v>
       </c>
     </row>
   </sheetData>
@@ -9198,31 +9198,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.9050268281239</v>
+        <v>32.35041697006638</v>
       </c>
       <c r="C2" t="n">
-        <v>39.98214964295895</v>
+        <v>45.10353201291951</v>
       </c>
       <c r="D2" t="n">
-        <v>29.40211688196736</v>
+        <v>44.39896464399638</v>
       </c>
       <c r="E2" t="n">
-        <v>47.98485396973414</v>
+        <v>28.06171146450519</v>
       </c>
       <c r="F2" t="n">
-        <v>44.62648885766519</v>
+        <v>39.25686267624836</v>
       </c>
       <c r="G2" t="n">
-        <v>31.14798935128344</v>
+        <v>46.75483341690743</v>
       </c>
       <c r="H2" t="n">
-        <v>34.81112650036562</v>
+        <v>41.59427419335068</v>
       </c>
       <c r="I2" t="n">
-        <v>37.38384948493597</v>
+        <v>46.51707038396744</v>
       </c>
       <c r="J2" t="n">
-        <v>42.36846565139859</v>
+        <v>43.78495495760458</v>
       </c>
     </row>
   </sheetData>
@@ -9296,31 +9296,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.91785340826191</v>
+        <v>22.08572474366878</v>
       </c>
       <c r="C2" t="n">
-        <v>35.11723304496774</v>
+        <v>41.64576705345534</v>
       </c>
       <c r="D2" t="n">
-        <v>42.90069751246383</v>
+        <v>38.07586636773674</v>
       </c>
       <c r="E2" t="n">
-        <v>25.18334122368902</v>
+        <v>34.911706458556</v>
       </c>
       <c r="F2" t="n">
-        <v>26.24347131544539</v>
+        <v>32.71728810538725</v>
       </c>
       <c r="G2" t="n">
-        <v>50.92770387146834</v>
+        <v>34.97169220040217</v>
       </c>
       <c r="H2" t="n">
-        <v>32.20405840585492</v>
+        <v>34.90775243158386</v>
       </c>
       <c r="I2" t="n">
-        <v>32.7214869330521</v>
+        <v>43.67566414629911</v>
       </c>
       <c r="J2" t="n">
-        <v>39.76584555428227</v>
+        <v>38.38408120387702</v>
       </c>
     </row>
   </sheetData>
@@ -9394,31 +9394,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.86618119278756</v>
+        <v>30.54123085478627</v>
       </c>
       <c r="C2" t="n">
-        <v>35.2807001781823</v>
+        <v>39.91172614031008</v>
       </c>
       <c r="D2" t="n">
-        <v>22.96327064528981</v>
+        <v>25.56663373565013</v>
       </c>
       <c r="E2" t="n">
-        <v>34.07218050989412</v>
+        <v>29.15635642924451</v>
       </c>
       <c r="F2" t="n">
-        <v>44.46428620186924</v>
+        <v>42.17991042914127</v>
       </c>
       <c r="G2" t="n">
-        <v>37.6760723389688</v>
+        <v>37.24405122468724</v>
       </c>
       <c r="H2" t="n">
-        <v>34.56462402361576</v>
+        <v>45.92587548281202</v>
       </c>
       <c r="I2" t="n">
-        <v>45.73135215796388</v>
+        <v>45.99372957654304</v>
       </c>
       <c r="J2" t="n">
-        <v>35.86219842400823</v>
+        <v>39.52029844927709</v>
       </c>
     </row>
   </sheetData>
@@ -9492,31 +9492,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.93675430356465</v>
+        <v>38.4373867666866</v>
       </c>
       <c r="C2" t="n">
-        <v>32.3096781630804</v>
+        <v>54.92463586339689</v>
       </c>
       <c r="D2" t="n">
-        <v>46.89017212822471</v>
+        <v>64.32515189209423</v>
       </c>
       <c r="E2" t="n">
-        <v>41.24714182073537</v>
+        <v>40.96209680041591</v>
       </c>
       <c r="F2" t="n">
-        <v>30.27130305449711</v>
+        <v>38.38411841553605</v>
       </c>
       <c r="G2" t="n">
-        <v>51.49366178483984</v>
+        <v>31.92130172417154</v>
       </c>
       <c r="H2" t="n">
-        <v>40.06694087216085</v>
+        <v>35.99448762051751</v>
       </c>
       <c r="I2" t="n">
-        <v>29.49321603494501</v>
+        <v>46.01468277847735</v>
       </c>
       <c r="J2" t="n">
-        <v>34.07535340529416</v>
+        <v>31.48998768956766</v>
       </c>
     </row>
   </sheetData>
@@ -9590,31 +9590,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.10277179441934</v>
+        <v>30.72482875975701</v>
       </c>
       <c r="C2" t="n">
-        <v>31.30247782819986</v>
+        <v>28.98671270441668</v>
       </c>
       <c r="D2" t="n">
-        <v>31.60298271921447</v>
+        <v>30.59006040445936</v>
       </c>
       <c r="E2" t="n">
-        <v>27.30535077448634</v>
+        <v>45.83148262704837</v>
       </c>
       <c r="F2" t="n">
-        <v>37.87927020423814</v>
+        <v>32.06683307365419</v>
       </c>
       <c r="G2" t="n">
-        <v>43.00779739829546</v>
+        <v>25.99398230166549</v>
       </c>
       <c r="H2" t="n">
-        <v>44.76903316019526</v>
+        <v>40.55810203296313</v>
       </c>
       <c r="I2" t="n">
-        <v>29.38937607292807</v>
+        <v>37.84994311320799</v>
       </c>
       <c r="J2" t="n">
-        <v>27.80060237116642</v>
+        <v>37.25267798821143</v>
       </c>
     </row>
   </sheetData>
@@ -9688,31 +9688,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.27007353274976</v>
+        <v>40.63331246042956</v>
       </c>
       <c r="C2" t="n">
-        <v>47.00105608994247</v>
+        <v>49.79475487327638</v>
       </c>
       <c r="D2" t="n">
-        <v>40.12833253458082</v>
+        <v>40.99479608694661</v>
       </c>
       <c r="E2" t="n">
-        <v>53.04055574906315</v>
+        <v>45.23546204809858</v>
       </c>
       <c r="F2" t="n">
-        <v>31.30913127187285</v>
+        <v>48.91168124592528</v>
       </c>
       <c r="G2" t="n">
-        <v>37.94270652896468</v>
+        <v>32.58022466274244</v>
       </c>
       <c r="H2" t="n">
-        <v>25.61524478216555</v>
+        <v>29.8945144078654</v>
       </c>
       <c r="I2" t="n">
-        <v>19.21058413138045</v>
+        <v>33.42035517561729</v>
       </c>
       <c r="J2" t="n">
-        <v>39.25033758072153</v>
+        <v>28.61614148376232</v>
       </c>
     </row>
   </sheetData>
@@ -9786,31 +9786,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.49871489456314</v>
+        <v>38.88826988584783</v>
       </c>
       <c r="C2" t="n">
-        <v>40.29442106767804</v>
+        <v>34.35505780899832</v>
       </c>
       <c r="D2" t="n">
-        <v>28.79851197631576</v>
+        <v>31.6060259541558</v>
       </c>
       <c r="E2" t="n">
-        <v>29.48173691713738</v>
+        <v>33.25431443789868</v>
       </c>
       <c r="F2" t="n">
-        <v>30.96726822410579</v>
+        <v>36.7801756053632</v>
       </c>
       <c r="G2" t="n">
-        <v>34.41390834164178</v>
+        <v>38.14615078237259</v>
       </c>
       <c r="H2" t="n">
-        <v>49.06596880892769</v>
+        <v>54.0162004094977</v>
       </c>
       <c r="I2" t="n">
-        <v>35.55925492529019</v>
+        <v>35.88254830574998</v>
       </c>
       <c r="J2" t="n">
-        <v>29.54102665266438</v>
+        <v>37.53933802084379</v>
       </c>
     </row>
   </sheetData>
@@ -9884,31 +9884,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.73972899500839</v>
+        <v>47.5419474820787</v>
       </c>
       <c r="C2" t="n">
-        <v>40.8444908581914</v>
+        <v>31.44848308415364</v>
       </c>
       <c r="D2" t="n">
-        <v>29.47671950316344</v>
+        <v>41.46713990203323</v>
       </c>
       <c r="E2" t="n">
-        <v>38.34619000439037</v>
+        <v>35.92099422474178</v>
       </c>
       <c r="F2" t="n">
-        <v>41.82574848111346</v>
+        <v>29.63977438911681</v>
       </c>
       <c r="G2" t="n">
-        <v>32.92317519553855</v>
+        <v>40.72287721281418</v>
       </c>
       <c r="H2" t="n">
-        <v>38.93290146754902</v>
+        <v>26.33238096394221</v>
       </c>
       <c r="I2" t="n">
-        <v>30.15143856473422</v>
+        <v>46.23323016544079</v>
       </c>
       <c r="J2" t="n">
-        <v>36.05435288224313</v>
+        <v>45.41141141083523</v>
       </c>
     </row>
   </sheetData>
@@ -9982,31 +9982,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.47219337731929</v>
+        <v>34.12456182833483</v>
       </c>
       <c r="C2" t="n">
-        <v>39.58208170487007</v>
+        <v>36.85285755148495</v>
       </c>
       <c r="D2" t="n">
-        <v>29.21204575819172</v>
+        <v>37.93725200964871</v>
       </c>
       <c r="E2" t="n">
-        <v>40.65580269106902</v>
+        <v>29.66612784925144</v>
       </c>
       <c r="F2" t="n">
-        <v>39.31117301853141</v>
+        <v>35.67078498585364</v>
       </c>
       <c r="G2" t="n">
-        <v>39.12528150950909</v>
+        <v>33.58058670313217</v>
       </c>
       <c r="H2" t="n">
-        <v>26.10821910321492</v>
+        <v>34.03438850136492</v>
       </c>
       <c r="I2" t="n">
-        <v>23.49898649043263</v>
+        <v>38.67820522418337</v>
       </c>
       <c r="J2" t="n">
-        <v>24.65930832636381</v>
+        <v>40.63416606345331</v>
       </c>
     </row>
   </sheetData>
@@ -10080,31 +10080,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.63850154447314</v>
+        <v>27.74077700487566</v>
       </c>
       <c r="C2" t="n">
-        <v>46.35734869195444</v>
+        <v>50.05589098951727</v>
       </c>
       <c r="D2" t="n">
-        <v>28.37873619215392</v>
+        <v>46.01614779105635</v>
       </c>
       <c r="E2" t="n">
-        <v>34.34360552122899</v>
+        <v>33.98531710914836</v>
       </c>
       <c r="F2" t="n">
-        <v>33.3135871112781</v>
+        <v>42.70369611319779</v>
       </c>
       <c r="G2" t="n">
-        <v>45.40472060243759</v>
+        <v>52.55131876147743</v>
       </c>
       <c r="H2" t="n">
-        <v>45.40364642486522</v>
+        <v>33.44847339649719</v>
       </c>
       <c r="I2" t="n">
-        <v>44.22720469990714</v>
+        <v>38.07189763978016</v>
       </c>
       <c r="J2" t="n">
-        <v>35.55767234153537</v>
+        <v>43.49603211550068</v>
       </c>
     </row>
   </sheetData>
@@ -10178,31 +10178,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.91962786047667</v>
+        <v>32.47123770408634</v>
       </c>
       <c r="C2" t="n">
-        <v>30.56098879958116</v>
+        <v>35.84905801044288</v>
       </c>
       <c r="D2" t="n">
-        <v>29.28136166213952</v>
+        <v>42.939018210725</v>
       </c>
       <c r="E2" t="n">
-        <v>34.2485789087478</v>
+        <v>30.14303461531438</v>
       </c>
       <c r="F2" t="n">
-        <v>43.34237942182762</v>
+        <v>35.81917826445756</v>
       </c>
       <c r="G2" t="n">
-        <v>41.65769854096175</v>
+        <v>46.68088738711363</v>
       </c>
       <c r="H2" t="n">
-        <v>32.65445915708234</v>
+        <v>37.71354631694783</v>
       </c>
       <c r="I2" t="n">
-        <v>45.99681198706642</v>
+        <v>37.24433761270111</v>
       </c>
       <c r="J2" t="n">
-        <v>36.08752113509583</v>
+        <v>56.59918596930849</v>
       </c>
     </row>
   </sheetData>
@@ -10276,31 +10276,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.05719362252641</v>
+        <v>32.56610572054766</v>
       </c>
       <c r="C2" t="n">
-        <v>37.71036051140179</v>
+        <v>32.48883894912959</v>
       </c>
       <c r="D2" t="n">
-        <v>33.76877751151602</v>
+        <v>38.30020868031664</v>
       </c>
       <c r="E2" t="n">
-        <v>27.60372338837054</v>
+        <v>29.37974863020761</v>
       </c>
       <c r="F2" t="n">
-        <v>30.90222844765427</v>
+        <v>36.16052540679778</v>
       </c>
       <c r="G2" t="n">
-        <v>53.34879200536533</v>
+        <v>35.52036047342052</v>
       </c>
       <c r="H2" t="n">
-        <v>30.58257677506034</v>
+        <v>50.57224685347197</v>
       </c>
       <c r="I2" t="n">
-        <v>36.32137538485264</v>
+        <v>37.51737829967092</v>
       </c>
       <c r="J2" t="n">
-        <v>29.01537696829883</v>
+        <v>49.45487164799093</v>
       </c>
     </row>
   </sheetData>
@@ -10374,31 +10374,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.33889364432225</v>
+        <v>38.11709026800217</v>
       </c>
       <c r="C2" t="n">
-        <v>41.75322747548527</v>
+        <v>43.69531684361355</v>
       </c>
       <c r="D2" t="n">
-        <v>58.26110674740811</v>
+        <v>36.72029701656959</v>
       </c>
       <c r="E2" t="n">
-        <v>25.36720429925931</v>
+        <v>28.76538076085821</v>
       </c>
       <c r="F2" t="n">
-        <v>24.98603268985078</v>
+        <v>34.98178731073273</v>
       </c>
       <c r="G2" t="n">
-        <v>35.52313622870648</v>
+        <v>37.01972346562368</v>
       </c>
       <c r="H2" t="n">
-        <v>27.50827135083596</v>
+        <v>41.55763367426365</v>
       </c>
       <c r="I2" t="n">
-        <v>36.85844202264891</v>
+        <v>29.29869321136971</v>
       </c>
       <c r="J2" t="n">
-        <v>27.05448006561035</v>
+        <v>40.19558555746423</v>
       </c>
     </row>
   </sheetData>
@@ -10472,31 +10472,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.30047461571912</v>
+        <v>24.54355732875267</v>
       </c>
       <c r="C2" t="n">
-        <v>30.54034329333589</v>
+        <v>48.7562946987666</v>
       </c>
       <c r="D2" t="n">
-        <v>32.08231031359907</v>
+        <v>35.90685841207765</v>
       </c>
       <c r="E2" t="n">
-        <v>38.2378903463924</v>
+        <v>27.63942001084954</v>
       </c>
       <c r="F2" t="n">
-        <v>42.94172364139043</v>
+        <v>35.93728042442933</v>
       </c>
       <c r="G2" t="n">
-        <v>34.05125638278939</v>
+        <v>37.54109667493673</v>
       </c>
       <c r="H2" t="n">
-        <v>33.50804907604893</v>
+        <v>33.9254192369546</v>
       </c>
       <c r="I2" t="n">
-        <v>25.48209124900387</v>
+        <v>43.7384390823283</v>
       </c>
       <c r="J2" t="n">
-        <v>34.14374444471637</v>
+        <v>54.78262327323097</v>
       </c>
     </row>
   </sheetData>
@@ -10570,31 +10570,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.4618096100741</v>
+        <v>27.33738125721516</v>
       </c>
       <c r="C2" t="n">
-        <v>50.4562520659898</v>
+        <v>27.66141611843057</v>
       </c>
       <c r="D2" t="n">
-        <v>39.67458728266026</v>
+        <v>48.18799305734927</v>
       </c>
       <c r="E2" t="n">
-        <v>30.58290533093125</v>
+        <v>46.36581538488582</v>
       </c>
       <c r="F2" t="n">
-        <v>42.18745003237196</v>
+        <v>40.82449333090664</v>
       </c>
       <c r="G2" t="n">
-        <v>22.10917403849577</v>
+        <v>37.49840784024178</v>
       </c>
       <c r="H2" t="n">
-        <v>34.47556793885603</v>
+        <v>40.80919819431578</v>
       </c>
       <c r="I2" t="n">
-        <v>30.85097679042545</v>
+        <v>35.56268938671899</v>
       </c>
       <c r="J2" t="n">
-        <v>37.61091591694334</v>
+        <v>51.94935250389901</v>
       </c>
     </row>
   </sheetData>
@@ -10668,31 +10668,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.52354989996262</v>
+        <v>50.73654867761504</v>
       </c>
       <c r="C2" t="n">
-        <v>35.37344090418167</v>
+        <v>49.81750198854631</v>
       </c>
       <c r="D2" t="n">
-        <v>45.38627236017233</v>
+        <v>47.04146047493789</v>
       </c>
       <c r="E2" t="n">
-        <v>31.98799357316033</v>
+        <v>35.19990246745022</v>
       </c>
       <c r="F2" t="n">
-        <v>38.07790414933786</v>
+        <v>40.47985366555904</v>
       </c>
       <c r="G2" t="n">
-        <v>42.75247708609166</v>
+        <v>40.98141457074963</v>
       </c>
       <c r="H2" t="n">
-        <v>64.14150094596447</v>
+        <v>35.70249352158983</v>
       </c>
       <c r="I2" t="n">
-        <v>31.43388786504306</v>
+        <v>50.7811763060439</v>
       </c>
       <c r="J2" t="n">
-        <v>37.71063080690483</v>
+        <v>42.48307223489603</v>
       </c>
     </row>
   </sheetData>
@@ -10766,31 +10766,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.51284302373474</v>
+        <v>32.92351354876077</v>
       </c>
       <c r="C2" t="n">
-        <v>49.09792700534966</v>
+        <v>35.52883207749991</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47357172883034</v>
+        <v>46.88362050355783</v>
       </c>
       <c r="E2" t="n">
-        <v>33.33596131885353</v>
+        <v>27.13251123064445</v>
       </c>
       <c r="F2" t="n">
-        <v>29.8936519630847</v>
+        <v>28.0682382292948</v>
       </c>
       <c r="G2" t="n">
-        <v>30.07426316638958</v>
+        <v>39.5144877380895</v>
       </c>
       <c r="H2" t="n">
-        <v>27.92881184324955</v>
+        <v>36.82128984680624</v>
       </c>
       <c r="I2" t="n">
-        <v>21.21478247515329</v>
+        <v>33.85544486367287</v>
       </c>
       <c r="J2" t="n">
-        <v>34.30652070715928</v>
+        <v>33.96884961142644</v>
       </c>
     </row>
   </sheetData>
@@ -10864,31 +10864,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.43314065924083</v>
+        <v>41.94995683447998</v>
       </c>
       <c r="C2" t="n">
-        <v>35.8928757875419</v>
+        <v>43.57832377171413</v>
       </c>
       <c r="D2" t="n">
-        <v>25.23346030504002</v>
+        <v>40.02965866699503</v>
       </c>
       <c r="E2" t="n">
-        <v>36.43296893505349</v>
+        <v>32.62931096912003</v>
       </c>
       <c r="F2" t="n">
-        <v>27.68067276810511</v>
+        <v>35.89313628601901</v>
       </c>
       <c r="G2" t="n">
-        <v>44.94437861014421</v>
+        <v>30.55018145169432</v>
       </c>
       <c r="H2" t="n">
-        <v>48.13605242278383</v>
+        <v>22.56033288723687</v>
       </c>
       <c r="I2" t="n">
-        <v>32.8841298407139</v>
+        <v>32.80184353779788</v>
       </c>
       <c r="J2" t="n">
-        <v>26.83251126651856</v>
+        <v>39.44426429684906</v>
       </c>
     </row>
   </sheetData>
@@ -10962,31 +10962,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.75218024026951</v>
+        <v>35.18421077312617</v>
       </c>
       <c r="C2" t="n">
-        <v>46.40431631054972</v>
+        <v>53.08958353945789</v>
       </c>
       <c r="D2" t="n">
-        <v>73.11868435468335</v>
+        <v>42.53465403890101</v>
       </c>
       <c r="E2" t="n">
-        <v>43.05121616578766</v>
+        <v>21.97403482565366</v>
       </c>
       <c r="F2" t="n">
-        <v>39.74968041550962</v>
+        <v>51.56767598923325</v>
       </c>
       <c r="G2" t="n">
-        <v>39.89795848979163</v>
+        <v>33.4814462076617</v>
       </c>
       <c r="H2" t="n">
-        <v>39.34403590876833</v>
+        <v>53.51197335392486</v>
       </c>
       <c r="I2" t="n">
-        <v>35.02312772249013</v>
+        <v>37.92014668426754</v>
       </c>
       <c r="J2" t="n">
-        <v>34.9858401036514</v>
+        <v>55.94668004794175</v>
       </c>
     </row>
   </sheetData>
@@ -11060,31 +11060,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.34818636763976</v>
+        <v>35.87297746786067</v>
       </c>
       <c r="C2" t="n">
-        <v>3221.3199723566</v>
+        <v>44.78168426004299</v>
       </c>
       <c r="D2" t="n">
-        <v>17.71317669702425</v>
+        <v>44.74023062258476</v>
       </c>
       <c r="E2" t="n">
-        <v>25.31405207471857</v>
+        <v>30.33648666488289</v>
       </c>
       <c r="F2" t="n">
-        <v>54.43221506747631</v>
+        <v>45.4530960516061</v>
       </c>
       <c r="G2" t="n">
-        <v>26.95967541913545</v>
+        <v>41.88548351579973</v>
       </c>
       <c r="H2" t="n">
-        <v>28.13488913236173</v>
+        <v>27.60504664245588</v>
       </c>
       <c r="I2" t="n">
-        <v>13.24056084681712</v>
+        <v>24.38375175472018</v>
       </c>
       <c r="J2" t="n">
-        <v>56.60847075653813</v>
+        <v>45.04708580744758</v>
       </c>
     </row>
   </sheetData>
@@ -11158,31 +11158,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.56966030227746</v>
+        <v>36.83810349947691</v>
       </c>
       <c r="C2" t="n">
-        <v>40.97299889479529</v>
+        <v>40.54741478018603</v>
       </c>
       <c r="D2" t="n">
-        <v>35.40279819996602</v>
+        <v>30.80597212645095</v>
       </c>
       <c r="E2" t="n">
-        <v>35.3850652619086</v>
+        <v>26.83729375231882</v>
       </c>
       <c r="F2" t="n">
-        <v>30.66747938278274</v>
+        <v>44.91112773617568</v>
       </c>
       <c r="G2" t="n">
-        <v>30.07333812457965</v>
+        <v>33.47685590099892</v>
       </c>
       <c r="H2" t="n">
-        <v>35.81207656227799</v>
+        <v>38.11248666169506</v>
       </c>
       <c r="I2" t="n">
-        <v>27.74117523952026</v>
+        <v>29.67162484947596</v>
       </c>
       <c r="J2" t="n">
-        <v>26.58626437654874</v>
+        <v>49.04472435407121</v>
       </c>
     </row>
   </sheetData>
@@ -11256,31 +11256,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.35926663877076</v>
+        <v>39.58114578406385</v>
       </c>
       <c r="C2" t="n">
-        <v>25.34956625599529</v>
+        <v>33.23292967176981</v>
       </c>
       <c r="D2" t="n">
-        <v>23.2115943540775</v>
+        <v>30.35818348099832</v>
       </c>
       <c r="E2" t="n">
-        <v>29.49873035495912</v>
+        <v>28.98392435847344</v>
       </c>
       <c r="F2" t="n">
-        <v>38.31002004911129</v>
+        <v>49.62061498502309</v>
       </c>
       <c r="G2" t="n">
-        <v>53.85510663441155</v>
+        <v>30.26820642323704</v>
       </c>
       <c r="H2" t="n">
-        <v>56.20178971345632</v>
+        <v>41.62254244451323</v>
       </c>
       <c r="I2" t="n">
-        <v>38.37782542652012</v>
+        <v>50.08726184519146</v>
       </c>
       <c r="J2" t="n">
-        <v>36.9231148021646</v>
+        <v>45.85381944613433</v>
       </c>
     </row>
   </sheetData>
@@ -11354,31 +11354,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.61261719671619</v>
+        <v>33.39295553354921</v>
       </c>
       <c r="C2" t="n">
-        <v>43.57145890704345</v>
+        <v>44.26911894401515</v>
       </c>
       <c r="D2" t="n">
-        <v>26.80093624393997</v>
+        <v>46.39589818177483</v>
       </c>
       <c r="E2" t="n">
-        <v>30.29847573969614</v>
+        <v>41.50303441459395</v>
       </c>
       <c r="F2" t="n">
-        <v>45.29404004560465</v>
+        <v>30.22275774245649</v>
       </c>
       <c r="G2" t="n">
-        <v>38.94915288024874</v>
+        <v>34.70008810143054</v>
       </c>
       <c r="H2" t="n">
-        <v>27.44457398632532</v>
+        <v>39.71290120076704</v>
       </c>
       <c r="I2" t="n">
-        <v>38.14232471002754</v>
+        <v>42.03850716546322</v>
       </c>
       <c r="J2" t="n">
-        <v>26.73561362462332</v>
+        <v>27.02905907333097</v>
       </c>
     </row>
   </sheetData>
@@ -11452,31 +11452,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.7776463315378</v>
+        <v>31.22531253410007</v>
       </c>
       <c r="C2" t="n">
-        <v>42.05000644112273</v>
+        <v>44.09001241342775</v>
       </c>
       <c r="D2" t="n">
-        <v>28.4907298329155</v>
+        <v>45.87687022785766</v>
       </c>
       <c r="E2" t="n">
-        <v>36.71916498865735</v>
+        <v>23.4109444465673</v>
       </c>
       <c r="F2" t="n">
-        <v>57.41927546117971</v>
+        <v>45.79238348362828</v>
       </c>
       <c r="G2" t="n">
-        <v>36.87894323747399</v>
+        <v>40.63313867266073</v>
       </c>
       <c r="H2" t="n">
-        <v>45.48935070368628</v>
+        <v>47.06081708576981</v>
       </c>
       <c r="I2" t="n">
-        <v>38.71402444845847</v>
+        <v>42.73502200434883</v>
       </c>
       <c r="J2" t="n">
-        <v>27.41610773370273</v>
+        <v>35.4644615146906</v>
       </c>
     </row>
   </sheetData>
@@ -11550,31 +11550,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.50592123055138</v>
+        <v>36.82840720947992</v>
       </c>
       <c r="C2" t="n">
-        <v>37.09489327640312</v>
+        <v>56.33024231069633</v>
       </c>
       <c r="D2" t="n">
-        <v>42.92544296689118</v>
+        <v>52.04757500630598</v>
       </c>
       <c r="E2" t="n">
-        <v>27.04998801066556</v>
+        <v>42.09198350918652</v>
       </c>
       <c r="F2" t="n">
-        <v>44.62856965619643</v>
+        <v>29.69284137034828</v>
       </c>
       <c r="G2" t="n">
-        <v>60.44797564678489</v>
+        <v>44.9963155549942</v>
       </c>
       <c r="H2" t="n">
-        <v>30.79227996072026</v>
+        <v>31.16099331238422</v>
       </c>
       <c r="I2" t="n">
-        <v>26.89293012858459</v>
+        <v>41.05592410840912</v>
       </c>
       <c r="J2" t="n">
-        <v>41.18179505665521</v>
+        <v>33.00932271419988</v>
       </c>
     </row>
   </sheetData>
@@ -11648,31 +11648,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.90079826044557</v>
+        <v>29.90127997134904</v>
       </c>
       <c r="C2" t="n">
-        <v>23.76345908103617</v>
+        <v>29.52994964952233</v>
       </c>
       <c r="D2" t="n">
-        <v>31.55358182417514</v>
+        <v>56.07167797014998</v>
       </c>
       <c r="E2" t="n">
-        <v>42.82477288024761</v>
+        <v>32.995510935651</v>
       </c>
       <c r="F2" t="n">
-        <v>45.14369722684612</v>
+        <v>37.37212894528111</v>
       </c>
       <c r="G2" t="n">
-        <v>30.03347473478293</v>
+        <v>27.38438704571094</v>
       </c>
       <c r="H2" t="n">
-        <v>23.40417974528735</v>
+        <v>40.80302868556712</v>
       </c>
       <c r="I2" t="n">
-        <v>34.72750205299101</v>
+        <v>28.5214735195307</v>
       </c>
       <c r="J2" t="n">
-        <v>32.48536780733902</v>
+        <v>40.47620552327125</v>
       </c>
     </row>
   </sheetData>
@@ -11746,31 +11746,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.42197589291063</v>
+        <v>35.5726549916867</v>
       </c>
       <c r="C2" t="n">
-        <v>29.81170362018246</v>
+        <v>35.13310561227703</v>
       </c>
       <c r="D2" t="n">
-        <v>46.32625209518357</v>
+        <v>43.16593879076268</v>
       </c>
       <c r="E2" t="n">
-        <v>28.3214345946666</v>
+        <v>38.22154029894973</v>
       </c>
       <c r="F2" t="n">
-        <v>23.14679045741287</v>
+        <v>37.72981735154914</v>
       </c>
       <c r="G2" t="n">
-        <v>24.67606136744978</v>
+        <v>36.31992763570613</v>
       </c>
       <c r="H2" t="n">
-        <v>35.41260114182453</v>
+        <v>32.95108285384012</v>
       </c>
       <c r="I2" t="n">
-        <v>43.99884633229825</v>
+        <v>22.68546855056244</v>
       </c>
       <c r="J2" t="n">
-        <v>49.86390977307562</v>
+        <v>35.58159308262943</v>
       </c>
     </row>
   </sheetData>
@@ -11844,31 +11844,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.54416512997339</v>
+        <v>30.71905386416669</v>
       </c>
       <c r="C2" t="n">
-        <v>41.0427562338496</v>
+        <v>45.94384560353404</v>
       </c>
       <c r="D2" t="n">
-        <v>49.82751080930711</v>
+        <v>41.90172018340812</v>
       </c>
       <c r="E2" t="n">
-        <v>33.400906216893</v>
+        <v>37.05227716136557</v>
       </c>
       <c r="F2" t="n">
-        <v>29.74656976826486</v>
+        <v>27.74243714254043</v>
       </c>
       <c r="G2" t="n">
-        <v>32.1014925737937</v>
+        <v>32.19680514956635</v>
       </c>
       <c r="H2" t="n">
-        <v>47.64221926246265</v>
+        <v>37.41281431284645</v>
       </c>
       <c r="I2" t="n">
-        <v>32.72839587132762</v>
+        <v>46.53149135790883</v>
       </c>
       <c r="J2" t="n">
-        <v>27.79004917219956</v>
+        <v>36.26446747082349</v>
       </c>
     </row>
   </sheetData>
@@ -11942,31 +11942,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.57608106777955</v>
+        <v>35.89060171371737</v>
       </c>
       <c r="C2" t="n">
-        <v>32.65083024254888</v>
+        <v>47.11228937723568</v>
       </c>
       <c r="D2" t="n">
-        <v>26.39461691633988</v>
+        <v>27.65038074685243</v>
       </c>
       <c r="E2" t="n">
-        <v>32.87778832775326</v>
+        <v>40.77449509176844</v>
       </c>
       <c r="F2" t="n">
-        <v>51.31105706894522</v>
+        <v>38.60088181419534</v>
       </c>
       <c r="G2" t="n">
-        <v>39.77997687319072</v>
+        <v>34.32058790562527</v>
       </c>
       <c r="H2" t="n">
-        <v>33.23794356291201</v>
+        <v>42.46608749351973</v>
       </c>
       <c r="I2" t="n">
-        <v>34.18805824774854</v>
+        <v>51.28238787819934</v>
       </c>
       <c r="J2" t="n">
-        <v>38.31307862901177</v>
+        <v>39.48749679191989</v>
       </c>
     </row>
   </sheetData>
@@ -12040,31 +12040,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.65775869634119</v>
+        <v>35.10090010186455</v>
       </c>
       <c r="C2" t="n">
-        <v>33.14755992640632</v>
+        <v>47.20571203088418</v>
       </c>
       <c r="D2" t="n">
-        <v>50.59510348364046</v>
+        <v>35.19183763568588</v>
       </c>
       <c r="E2" t="n">
-        <v>48.1105178820843</v>
+        <v>32.79408157980053</v>
       </c>
       <c r="F2" t="n">
-        <v>41.83225215774796</v>
+        <v>33.96801129807777</v>
       </c>
       <c r="G2" t="n">
-        <v>35.10423740517923</v>
+        <v>38.60815681186187</v>
       </c>
       <c r="H2" t="n">
-        <v>33.58970651612653</v>
+        <v>45.30490265809164</v>
       </c>
       <c r="I2" t="n">
-        <v>28.64182259977364</v>
+        <v>47.62851914905819</v>
       </c>
       <c r="J2" t="n">
-        <v>27.88778488419642</v>
+        <v>32.17804960099684</v>
       </c>
     </row>
   </sheetData>
@@ -12138,31 +12138,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.09277865498656</v>
+        <v>39.72957257117906</v>
       </c>
       <c r="C2" t="n">
-        <v>34.8241249614363</v>
+        <v>39.74201280121883</v>
       </c>
       <c r="D2" t="n">
-        <v>40.15482161454933</v>
+        <v>37.92732229183811</v>
       </c>
       <c r="E2" t="n">
-        <v>37.12498990270114</v>
+        <v>27.56138304968006</v>
       </c>
       <c r="F2" t="n">
-        <v>28.92787651456247</v>
+        <v>30.45006564114752</v>
       </c>
       <c r="G2" t="n">
-        <v>44.54251690773163</v>
+        <v>41.46857296269953</v>
       </c>
       <c r="H2" t="n">
-        <v>29.49332235102385</v>
+        <v>39.00743433520599</v>
       </c>
       <c r="I2" t="n">
-        <v>31.56566232781116</v>
+        <v>43.58526168846818</v>
       </c>
       <c r="J2" t="n">
-        <v>45.98801587414943</v>
+        <v>37.41233403839784</v>
       </c>
     </row>
   </sheetData>
@@ -12236,31 +12236,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.93120059432678</v>
+        <v>39.76063541752219</v>
       </c>
       <c r="C2" t="n">
-        <v>41.03470341791642</v>
+        <v>48.54660113103795</v>
       </c>
       <c r="D2" t="n">
-        <v>30.57092481047613</v>
+        <v>26.9319650011232</v>
       </c>
       <c r="E2" t="n">
-        <v>45.12884414728304</v>
+        <v>39.96710571808319</v>
       </c>
       <c r="F2" t="n">
-        <v>48.68839340170133</v>
+        <v>44.92625348168536</v>
       </c>
       <c r="G2" t="n">
-        <v>37.79203023153986</v>
+        <v>45.88146627860492</v>
       </c>
       <c r="H2" t="n">
-        <v>48.05018841567499</v>
+        <v>46.24159979953161</v>
       </c>
       <c r="I2" t="n">
-        <v>25.60817277336353</v>
+        <v>40.98362454620361</v>
       </c>
       <c r="J2" t="n">
-        <v>41.33737508994071</v>
+        <v>39.40023571885678</v>
       </c>
     </row>
   </sheetData>
@@ -12334,31 +12334,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.06517797880585</v>
+        <v>35.56334131265682</v>
       </c>
       <c r="C2" t="n">
-        <v>28.46692681930309</v>
+        <v>53.07033334251197</v>
       </c>
       <c r="D2" t="n">
-        <v>49.93494201470607</v>
+        <v>36.09482919779981</v>
       </c>
       <c r="E2" t="n">
-        <v>36.78773255920554</v>
+        <v>40.44592552524038</v>
       </c>
       <c r="F2" t="n">
-        <v>43.67980256413867</v>
+        <v>54.83571820606598</v>
       </c>
       <c r="G2" t="n">
-        <v>33.26386408952315</v>
+        <v>42.40227579140084</v>
       </c>
       <c r="H2" t="n">
-        <v>29.5793906477997</v>
+        <v>35.16380595681611</v>
       </c>
       <c r="I2" t="n">
-        <v>39.05288584292248</v>
+        <v>44.60828471857125</v>
       </c>
       <c r="J2" t="n">
-        <v>32.71129451744402</v>
+        <v>34.04601269872518</v>
       </c>
     </row>
   </sheetData>
@@ -12432,31 +12432,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.7340656342963</v>
+        <v>30.13043340487193</v>
       </c>
       <c r="C2" t="n">
-        <v>58.88802857866101</v>
+        <v>55.46477462859256</v>
       </c>
       <c r="D2" t="n">
-        <v>31.47818758449537</v>
+        <v>54.44088410487981</v>
       </c>
       <c r="E2" t="n">
-        <v>37.27305045459546</v>
+        <v>23.39869204710016</v>
       </c>
       <c r="F2" t="n">
-        <v>32.90545664198908</v>
+        <v>37.70272105575276</v>
       </c>
       <c r="G2" t="n">
-        <v>46.26250873641189</v>
+        <v>30.44372612490623</v>
       </c>
       <c r="H2" t="n">
-        <v>35.18806724162863</v>
+        <v>44.57507026836404</v>
       </c>
       <c r="I2" t="n">
-        <v>31.69288105700105</v>
+        <v>43.42950875284534</v>
       </c>
       <c r="J2" t="n">
-        <v>29.09370107209181</v>
+        <v>44.92366999300583</v>
       </c>
     </row>
   </sheetData>
@@ -12530,31 +12530,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.81654325205601</v>
+        <v>32.71283512850223</v>
       </c>
       <c r="C2" t="n">
-        <v>37.57071372209058</v>
+        <v>40.96532440399498</v>
       </c>
       <c r="D2" t="n">
-        <v>27.96239748523011</v>
+        <v>48.26626457740466</v>
       </c>
       <c r="E2" t="n">
-        <v>32.87175462619538</v>
+        <v>37.76790763992302</v>
       </c>
       <c r="F2" t="n">
-        <v>38.45040058332663</v>
+        <v>45.13639771626802</v>
       </c>
       <c r="G2" t="n">
-        <v>39.47854166010696</v>
+        <v>33.23415811625073</v>
       </c>
       <c r="H2" t="n">
-        <v>31.20191756869131</v>
+        <v>37.1535285327497</v>
       </c>
       <c r="I2" t="n">
-        <v>43.66335419693912</v>
+        <v>39.42316210941656</v>
       </c>
       <c r="J2" t="n">
-        <v>38.79056651182781</v>
+        <v>37.91383656151285</v>
       </c>
     </row>
   </sheetData>
@@ -12628,31 +12628,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.49492386146793</v>
+        <v>27.59405600370111</v>
       </c>
       <c r="C2" t="n">
-        <v>31.57221948162142</v>
+        <v>42.58347727248456</v>
       </c>
       <c r="D2" t="n">
-        <v>35.35728837210794</v>
+        <v>52.83252283948703</v>
       </c>
       <c r="E2" t="n">
-        <v>41.87223415223125</v>
+        <v>28.42099728813059</v>
       </c>
       <c r="F2" t="n">
-        <v>37.41578610612227</v>
+        <v>30.29443872994508</v>
       </c>
       <c r="G2" t="n">
-        <v>37.92995441754621</v>
+        <v>60.61797067049148</v>
       </c>
       <c r="H2" t="n">
-        <v>32.74007000748762</v>
+        <v>35.09358754438568</v>
       </c>
       <c r="I2" t="n">
-        <v>48.25443195843788</v>
+        <v>35.14453129535773</v>
       </c>
       <c r="J2" t="n">
-        <v>24.15123808832168</v>
+        <v>46.83430132449742</v>
       </c>
     </row>
   </sheetData>
@@ -12726,31 +12726,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.31908272496638</v>
+        <v>30.15847531222924</v>
       </c>
       <c r="C2" t="n">
-        <v>31.00276329565327</v>
+        <v>49.75515744499121</v>
       </c>
       <c r="D2" t="n">
-        <v>32.02358505791302</v>
+        <v>33.73336591650334</v>
       </c>
       <c r="E2" t="n">
-        <v>41.15961514255731</v>
+        <v>39.18588067203475</v>
       </c>
       <c r="F2" t="n">
-        <v>36.6293048509723</v>
+        <v>39.08948470722528</v>
       </c>
       <c r="G2" t="n">
-        <v>23.53057020283221</v>
+        <v>34.37942508279712</v>
       </c>
       <c r="H2" t="n">
-        <v>42.23048094883729</v>
+        <v>35.8470892615716</v>
       </c>
       <c r="I2" t="n">
-        <v>50.63451303868156</v>
+        <v>44.68287547249659</v>
       </c>
       <c r="J2" t="n">
-        <v>31.48215024220642</v>
+        <v>25.75418027335452</v>
       </c>
     </row>
   </sheetData>
@@ -12824,31 +12824,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.94678347229947</v>
+        <v>34.69561036825863</v>
       </c>
       <c r="C2" t="n">
-        <v>39.01479472939451</v>
+        <v>31.40718778265666</v>
       </c>
       <c r="D2" t="n">
-        <v>42.16672677442118</v>
+        <v>43.74859926132564</v>
       </c>
       <c r="E2" t="n">
-        <v>22.50176992990975</v>
+        <v>44.06586387524026</v>
       </c>
       <c r="F2" t="n">
-        <v>32.3684995627918</v>
+        <v>38.99808854855888</v>
       </c>
       <c r="G2" t="n">
-        <v>42.86458047965493</v>
+        <v>29.89197348605143</v>
       </c>
       <c r="H2" t="n">
-        <v>51.43913433427003</v>
+        <v>51.93672750886437</v>
       </c>
       <c r="I2" t="n">
-        <v>33.51195904705083</v>
+        <v>40.11260780024229</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4464559275597</v>
+        <v>39.4060867692145</v>
       </c>
     </row>
   </sheetData>
@@ -12922,31 +12922,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.33666994585969</v>
+        <v>25.07848688173906</v>
       </c>
       <c r="C2" t="n">
-        <v>31.07411178961288</v>
+        <v>37.84443455468656</v>
       </c>
       <c r="D2" t="n">
-        <v>30.12785865568417</v>
+        <v>36.21529796137833</v>
       </c>
       <c r="E2" t="n">
-        <v>34.71307849130037</v>
+        <v>31.41664650784049</v>
       </c>
       <c r="F2" t="n">
-        <v>33.56067434775187</v>
+        <v>31.25070245637761</v>
       </c>
       <c r="G2" t="n">
-        <v>37.80497034092904</v>
+        <v>31.67526779078166</v>
       </c>
       <c r="H2" t="n">
-        <v>32.93611231567846</v>
+        <v>39.58482592291774</v>
       </c>
       <c r="I2" t="n">
-        <v>34.68415509140065</v>
+        <v>63.2929546351555</v>
       </c>
       <c r="J2" t="n">
-        <v>39.86666483391847</v>
+        <v>55.0839093312557</v>
       </c>
     </row>
   </sheetData>
@@ -13020,31 +13020,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.90338723206781</v>
+        <v>30.15737265998499</v>
       </c>
       <c r="C2" t="n">
-        <v>43.24677470906256</v>
+        <v>48.11579496771089</v>
       </c>
       <c r="D2" t="n">
-        <v>39.00584783631093</v>
+        <v>44.18873887960909</v>
       </c>
       <c r="E2" t="n">
-        <v>45.54044378552137</v>
+        <v>42.08422832858863</v>
       </c>
       <c r="F2" t="n">
-        <v>46.56428874814439</v>
+        <v>29.16149749932534</v>
       </c>
       <c r="G2" t="n">
-        <v>38.54498294230685</v>
+        <v>44.05452181262508</v>
       </c>
       <c r="H2" t="n">
-        <v>26.51588146670122</v>
+        <v>42.24171023895497</v>
       </c>
       <c r="I2" t="n">
-        <v>48.71271907305945</v>
+        <v>52.28070148978591</v>
       </c>
       <c r="J2" t="n">
-        <v>25.22235271007365</v>
+        <v>33.453336612588</v>
       </c>
     </row>
   </sheetData>
@@ -13118,31 +13118,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.32222115492817</v>
+        <v>27.48890346322728</v>
       </c>
       <c r="C2" t="n">
-        <v>35.00731908203434</v>
+        <v>46.8810023516481</v>
       </c>
       <c r="D2" t="n">
-        <v>28.99255034916341</v>
+        <v>45.82731365099036</v>
       </c>
       <c r="E2" t="n">
-        <v>37.67945917379684</v>
+        <v>30.60543363688579</v>
       </c>
       <c r="F2" t="n">
-        <v>49.2278146527276</v>
+        <v>45.32194511122425</v>
       </c>
       <c r="G2" t="n">
-        <v>48.58529014313797</v>
+        <v>43.16475620448432</v>
       </c>
       <c r="H2" t="n">
-        <v>35.60594738749906</v>
+        <v>36.26841482290244</v>
       </c>
       <c r="I2" t="n">
-        <v>53.93830638088944</v>
+        <v>45.80709770710459</v>
       </c>
       <c r="J2" t="n">
-        <v>26.92204107920615</v>
+        <v>39.31585428187338</v>
       </c>
     </row>
   </sheetData>
@@ -13216,31 +13216,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.46493107841849</v>
+        <v>32.64701427639131</v>
       </c>
       <c r="C2" t="n">
-        <v>38.61448326322455</v>
+        <v>55.5963276730935</v>
       </c>
       <c r="D2" t="n">
-        <v>25.82478512913166</v>
+        <v>34.33374388528846</v>
       </c>
       <c r="E2" t="n">
-        <v>48.14027739100133</v>
+        <v>33.65194056599105</v>
       </c>
       <c r="F2" t="n">
-        <v>22.29016468439165</v>
+        <v>42.25269130521183</v>
       </c>
       <c r="G2" t="n">
-        <v>48.87164366881908</v>
+        <v>56.21940791346515</v>
       </c>
       <c r="H2" t="n">
-        <v>48.54765052589109</v>
+        <v>47.57550790796358</v>
       </c>
       <c r="I2" t="n">
-        <v>40.39538009357425</v>
+        <v>37.19796028693453</v>
       </c>
       <c r="J2" t="n">
-        <v>35.23720667797133</v>
+        <v>34.44884809381626</v>
       </c>
     </row>
   </sheetData>
@@ -13314,31 +13314,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.85946088313118</v>
+        <v>34.29629601222289</v>
       </c>
       <c r="C2" t="n">
-        <v>35.71020489194153</v>
+        <v>43.59910790738163</v>
       </c>
       <c r="D2" t="n">
-        <v>29.32099883879071</v>
+        <v>42.64175134832512</v>
       </c>
       <c r="E2" t="n">
-        <v>29.43283893608252</v>
+        <v>28.39746800252593</v>
       </c>
       <c r="F2" t="n">
-        <v>43.0647129594114</v>
+        <v>40.12454295604651</v>
       </c>
       <c r="G2" t="n">
-        <v>46.9970123048486</v>
+        <v>31.15950519019272</v>
       </c>
       <c r="H2" t="n">
-        <v>45.21873366780083</v>
+        <v>50.2808610790356</v>
       </c>
       <c r="I2" t="n">
-        <v>26.20568063503347</v>
+        <v>61.56360847617074</v>
       </c>
       <c r="J2" t="n">
-        <v>38.67862994280558</v>
+        <v>39.35039761767561</v>
       </c>
     </row>
   </sheetData>
@@ -13412,31 +13412,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>23.02814404502979</v>
+        <v>35.50835349841697</v>
       </c>
       <c r="C2" t="n">
-        <v>41.20588336568683</v>
+        <v>40.81766755690691</v>
       </c>
       <c r="D2" t="n">
-        <v>35.25594502290534</v>
+        <v>40.03082054157797</v>
       </c>
       <c r="E2" t="n">
-        <v>36.74572523810183</v>
+        <v>39.99033585690373</v>
       </c>
       <c r="F2" t="n">
-        <v>39.37274386004873</v>
+        <v>46.09500283300553</v>
       </c>
       <c r="G2" t="n">
-        <v>29.17195729190156</v>
+        <v>34.61995651006524</v>
       </c>
       <c r="H2" t="n">
-        <v>40.45131095566434</v>
+        <v>29.61457456752644</v>
       </c>
       <c r="I2" t="n">
-        <v>35.09357280099407</v>
+        <v>35.56891006285166</v>
       </c>
       <c r="J2" t="n">
-        <v>44.18013088969038</v>
+        <v>41.73693300965699</v>
       </c>
     </row>
   </sheetData>
@@ -13510,31 +13510,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.02356649369101</v>
+        <v>31.78211705653271</v>
       </c>
       <c r="C2" t="n">
-        <v>25.67428400996036</v>
+        <v>34.95263292929236</v>
       </c>
       <c r="D2" t="n">
-        <v>41.52046895978873</v>
+        <v>51.47670711338414</v>
       </c>
       <c r="E2" t="n">
-        <v>32.4464548236161</v>
+        <v>32.74955740335786</v>
       </c>
       <c r="F2" t="n">
-        <v>45.85432027672828</v>
+        <v>36.52506241980483</v>
       </c>
       <c r="G2" t="n">
-        <v>38.4671925625066</v>
+        <v>37.91268392695289</v>
       </c>
       <c r="H2" t="n">
-        <v>44.25866157945329</v>
+        <v>45.05306502844978</v>
       </c>
       <c r="I2" t="n">
-        <v>42.78581580154415</v>
+        <v>41.43330088799004</v>
       </c>
       <c r="J2" t="n">
-        <v>30.11045193092257</v>
+        <v>59.97248789418503</v>
       </c>
     </row>
   </sheetData>
@@ -13608,31 +13608,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.09370365919872</v>
+        <v>43.28965803407371</v>
       </c>
       <c r="C2" t="n">
-        <v>40.80920847519355</v>
+        <v>36.40283220676886</v>
       </c>
       <c r="D2" t="n">
-        <v>31.43516025595101</v>
+        <v>38.76020600960967</v>
       </c>
       <c r="E2" t="n">
-        <v>40.7114580247994</v>
+        <v>35.51291921919398</v>
       </c>
       <c r="F2" t="n">
-        <v>47.57963893822775</v>
+        <v>32.69621682061677</v>
       </c>
       <c r="G2" t="n">
-        <v>29.22654541238857</v>
+        <v>31.95075531118119</v>
       </c>
       <c r="H2" t="n">
-        <v>46.91452316197805</v>
+        <v>36.52582862883867</v>
       </c>
       <c r="I2" t="n">
-        <v>27.23443652195734</v>
+        <v>47.11506797408585</v>
       </c>
       <c r="J2" t="n">
-        <v>40.84776527116377</v>
+        <v>52.59665925921327</v>
       </c>
     </row>
   </sheetData>
@@ -13706,31 +13706,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.21215757207122</v>
+        <v>33.82310109936016</v>
       </c>
       <c r="C2" t="n">
-        <v>41.31792968612299</v>
+        <v>31.13664547621954</v>
       </c>
       <c r="D2" t="n">
-        <v>25.37016227656558</v>
+        <v>40.35679294527691</v>
       </c>
       <c r="E2" t="n">
-        <v>26.14893279723161</v>
+        <v>28.48017972632914</v>
       </c>
       <c r="F2" t="n">
-        <v>36.58500281806241</v>
+        <v>41.19188398613464</v>
       </c>
       <c r="G2" t="n">
-        <v>42.38166124672806</v>
+        <v>37.12899420925197</v>
       </c>
       <c r="H2" t="n">
-        <v>31.86479918084605</v>
+        <v>46.85705888385455</v>
       </c>
       <c r="I2" t="n">
-        <v>40.80063136296675</v>
+        <v>58.8272685233741</v>
       </c>
       <c r="J2" t="n">
-        <v>34.1790855936633</v>
+        <v>31.48642832132083</v>
       </c>
     </row>
   </sheetData>
@@ -13804,31 +13804,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.98415217357142</v>
+        <v>35.9114616724227</v>
       </c>
       <c r="C2" t="n">
-        <v>52.01490695414444</v>
+        <v>48.04609195229148</v>
       </c>
       <c r="D2" t="n">
-        <v>41.75190563942228</v>
+        <v>37.36242502948266</v>
       </c>
       <c r="E2" t="n">
-        <v>42.48889276275786</v>
+        <v>31.21506249004051</v>
       </c>
       <c r="F2" t="n">
-        <v>36.42198320576259</v>
+        <v>49.49612287856652</v>
       </c>
       <c r="G2" t="n">
-        <v>29.62294599806878</v>
+        <v>38.91493190980846</v>
       </c>
       <c r="H2" t="n">
-        <v>25.87270950792748</v>
+        <v>45.79008661684759</v>
       </c>
       <c r="I2" t="n">
-        <v>40.46716787277222</v>
+        <v>48.62471458849416</v>
       </c>
       <c r="J2" t="n">
-        <v>44.49657133652142</v>
+        <v>45.46835403178432</v>
       </c>
     </row>
   </sheetData>
@@ -13902,31 +13902,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.69510842264305</v>
+        <v>51.01262710804344</v>
       </c>
       <c r="C2" t="n">
-        <v>29.57295765674599</v>
+        <v>40.72700039874542</v>
       </c>
       <c r="D2" t="n">
-        <v>50.30056873981703</v>
+        <v>47.34303740621963</v>
       </c>
       <c r="E2" t="n">
-        <v>54.54859808812844</v>
+        <v>43.19917674633928</v>
       </c>
       <c r="F2" t="n">
-        <v>43.73513627716542</v>
+        <v>38.14974200534588</v>
       </c>
       <c r="G2" t="n">
-        <v>35.11089476411023</v>
+        <v>30.52416095016967</v>
       </c>
       <c r="H2" t="n">
-        <v>35.44820366604445</v>
+        <v>52.29243437299948</v>
       </c>
       <c r="I2" t="n">
-        <v>24.35752635027142</v>
+        <v>32.94757802509053</v>
       </c>
       <c r="J2" t="n">
-        <v>32.54048120089981</v>
+        <v>43.35703599135397</v>
       </c>
     </row>
   </sheetData>
@@ -14000,31 +14000,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.83244884995121</v>
+        <v>37.47457651896413</v>
       </c>
       <c r="C2" t="n">
-        <v>29.1010947374744</v>
+        <v>42.7563635220091</v>
       </c>
       <c r="D2" t="n">
-        <v>39.60590195620403</v>
+        <v>57.03709409794535</v>
       </c>
       <c r="E2" t="n">
-        <v>40.21558562255416</v>
+        <v>34.42192604513549</v>
       </c>
       <c r="F2" t="n">
-        <v>38.72452630481003</v>
+        <v>46.59109097055699</v>
       </c>
       <c r="G2" t="n">
-        <v>40.00279649794454</v>
+        <v>45.15971769154141</v>
       </c>
       <c r="H2" t="n">
-        <v>40.72120523393006</v>
+        <v>40.57421961483621</v>
       </c>
       <c r="I2" t="n">
-        <v>44.88292521645058</v>
+        <v>28.89417118826998</v>
       </c>
       <c r="J2" t="n">
-        <v>30.52964761244653</v>
+        <v>52.17925290920123</v>
       </c>
     </row>
   </sheetData>
@@ -14098,31 +14098,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.75904537602235</v>
+        <v>32.23713159368589</v>
       </c>
       <c r="C2" t="n">
-        <v>52.22460248379996</v>
+        <v>37.47581667289957</v>
       </c>
       <c r="D2" t="n">
-        <v>36.94745299512718</v>
+        <v>47.45869759155231</v>
       </c>
       <c r="E2" t="n">
-        <v>31.32110550955223</v>
+        <v>29.25582972778069</v>
       </c>
       <c r="F2" t="n">
-        <v>42.70587973415728</v>
+        <v>43.93195219694224</v>
       </c>
       <c r="G2" t="n">
-        <v>39.44772065968787</v>
+        <v>39.14218318946426</v>
       </c>
       <c r="H2" t="n">
-        <v>38.81069644586363</v>
+        <v>39.13797791716838</v>
       </c>
       <c r="I2" t="n">
-        <v>41.73828511293041</v>
+        <v>58.1472265518813</v>
       </c>
       <c r="J2" t="n">
-        <v>43.11685162309544</v>
+        <v>39.41846044071964</v>
       </c>
     </row>
   </sheetData>
@@ -14196,31 +14196,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.10633298483836</v>
+        <v>31.04786427978851</v>
       </c>
       <c r="C2" t="n">
-        <v>33.20301500155936</v>
+        <v>43.94615687841726</v>
       </c>
       <c r="D2" t="n">
-        <v>33.23165277023405</v>
+        <v>42.56518778970728</v>
       </c>
       <c r="E2" t="n">
-        <v>31.27955997734908</v>
+        <v>25.96669986256119</v>
       </c>
       <c r="F2" t="n">
-        <v>42.97460286169862</v>
+        <v>44.20300587337483</v>
       </c>
       <c r="G2" t="n">
-        <v>41.04428263108282</v>
+        <v>42.59461910455515</v>
       </c>
       <c r="H2" t="n">
-        <v>28.95531132281927</v>
+        <v>29.94371955514769</v>
       </c>
       <c r="I2" t="n">
-        <v>40.67015648460863</v>
+        <v>31.65802772954805</v>
       </c>
       <c r="J2" t="n">
-        <v>32.62466377311826</v>
+        <v>43.45410247497241</v>
       </c>
     </row>
   </sheetData>
@@ -14294,31 +14294,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.71282883775253</v>
+        <v>30.2493378696533</v>
       </c>
       <c r="C2" t="n">
-        <v>38.88892861708923</v>
+        <v>62.05653733091682</v>
       </c>
       <c r="D2" t="n">
-        <v>25.6724057213518</v>
+        <v>37.35011965501319</v>
       </c>
       <c r="E2" t="n">
-        <v>41.31848015898275</v>
+        <v>26.4838446170847</v>
       </c>
       <c r="F2" t="n">
-        <v>45.35776106243092</v>
+        <v>31.69222589031865</v>
       </c>
       <c r="G2" t="n">
-        <v>39.69497463711292</v>
+        <v>40.93109353253086</v>
       </c>
       <c r="H2" t="n">
-        <v>38.03607862301764</v>
+        <v>52.01375412533192</v>
       </c>
       <c r="I2" t="n">
-        <v>30.14114166350847</v>
+        <v>44.58388306004062</v>
       </c>
       <c r="J2" t="n">
-        <v>36.76793127632248</v>
+        <v>47.14201072359398</v>
       </c>
     </row>
   </sheetData>
@@ -14392,31 +14392,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>46.30801717640224</v>
+        <v>33.83279170282424</v>
       </c>
       <c r="C2" t="n">
-        <v>47.86530261646809</v>
+        <v>43.88415680412544</v>
       </c>
       <c r="D2" t="n">
-        <v>48.01095334733083</v>
+        <v>54.57532526803944</v>
       </c>
       <c r="E2" t="n">
-        <v>25.86166506867552</v>
+        <v>34.4303591967447</v>
       </c>
       <c r="F2" t="n">
-        <v>40.80171029593653</v>
+        <v>52.0344656979312</v>
       </c>
       <c r="G2" t="n">
-        <v>44.48629406672599</v>
+        <v>23.3582550055195</v>
       </c>
       <c r="H2" t="n">
-        <v>35.4641211829023</v>
+        <v>43.07625067027902</v>
       </c>
       <c r="I2" t="n">
-        <v>41.17047425486525</v>
+        <v>53.48736564516992</v>
       </c>
       <c r="J2" t="n">
-        <v>34.41410080988592</v>
+        <v>52.71973167830293</v>
       </c>
     </row>
   </sheetData>
@@ -14490,31 +14490,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.20621650610114</v>
+        <v>33.38044779960575</v>
       </c>
       <c r="C2" t="n">
-        <v>37.71141339276018</v>
+        <v>32.3106621648838</v>
       </c>
       <c r="D2" t="n">
-        <v>36.89984579209538</v>
+        <v>40.51969820341996</v>
       </c>
       <c r="E2" t="n">
-        <v>39.75097248849492</v>
+        <v>37.13385806608039</v>
       </c>
       <c r="F2" t="n">
-        <v>39.90309437366761</v>
+        <v>35.79562355481367</v>
       </c>
       <c r="G2" t="n">
-        <v>18.35716555375683</v>
+        <v>28.00282727843424</v>
       </c>
       <c r="H2" t="n">
-        <v>38.53101372348702</v>
+        <v>53.03847353139626</v>
       </c>
       <c r="I2" t="n">
-        <v>44.15503271850511</v>
+        <v>52.2072162029388</v>
       </c>
       <c r="J2" t="n">
-        <v>32.06596278047974</v>
+        <v>41.32408888765523</v>
       </c>
     </row>
   </sheetData>
@@ -14588,31 +14588,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.53773071740962</v>
+        <v>29.47384169922073</v>
       </c>
       <c r="C2" t="n">
-        <v>26.43859058175244</v>
+        <v>40.8001802504058</v>
       </c>
       <c r="D2" t="n">
-        <v>37.77191136111903</v>
+        <v>35.83970737450797</v>
       </c>
       <c r="E2" t="n">
-        <v>46.46582448269383</v>
+        <v>32.27598947444564</v>
       </c>
       <c r="F2" t="n">
-        <v>50.28861202543316</v>
+        <v>42.47921348792428</v>
       </c>
       <c r="G2" t="n">
-        <v>36.56506537229663</v>
+        <v>47.31392034788489</v>
       </c>
       <c r="H2" t="n">
-        <v>20.05032089675765</v>
+        <v>64.59833005171576</v>
       </c>
       <c r="I2" t="n">
-        <v>47.91954340169472</v>
+        <v>43.70379858468031</v>
       </c>
       <c r="J2" t="n">
-        <v>46.74089058942909</v>
+        <v>50.30991220018599</v>
       </c>
     </row>
   </sheetData>
@@ -14686,31 +14686,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.16849577388364</v>
+        <v>27.18739575489785</v>
       </c>
       <c r="C2" t="n">
-        <v>36.23973369865138</v>
+        <v>31.23608929852049</v>
       </c>
       <c r="D2" t="n">
-        <v>34.2053873058748</v>
+        <v>40.46597865672474</v>
       </c>
       <c r="E2" t="n">
-        <v>45.65765344859958</v>
+        <v>29.29406978614281</v>
       </c>
       <c r="F2" t="n">
-        <v>39.57196368185095</v>
+        <v>42.89719354675477</v>
       </c>
       <c r="G2" t="n">
-        <v>46.29735281798873</v>
+        <v>42.021799810894</v>
       </c>
       <c r="H2" t="n">
-        <v>33.91107646954583</v>
+        <v>31.73335942305809</v>
       </c>
       <c r="I2" t="n">
-        <v>25.6158401971353</v>
+        <v>49.06028521371098</v>
       </c>
       <c r="J2" t="n">
-        <v>32.54349367556129</v>
+        <v>56.53802883123848</v>
       </c>
     </row>
   </sheetData>
@@ -14784,31 +14784,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.95392070579133</v>
+        <v>30.99501954243282</v>
       </c>
       <c r="C2" t="n">
-        <v>33.0379524153565</v>
+        <v>50.35324355427786</v>
       </c>
       <c r="D2" t="n">
-        <v>48.70197098681033</v>
+        <v>31.34637944343174</v>
       </c>
       <c r="E2" t="n">
-        <v>25.90290552712029</v>
+        <v>34.98903036853771</v>
       </c>
       <c r="F2" t="n">
-        <v>52.59860424444945</v>
+        <v>31.93494487151616</v>
       </c>
       <c r="G2" t="n">
-        <v>22.01410866933431</v>
+        <v>33.97221480580994</v>
       </c>
       <c r="H2" t="n">
-        <v>31.09567685521837</v>
+        <v>35.50374449673586</v>
       </c>
       <c r="I2" t="n">
-        <v>48.02546586329064</v>
+        <v>49.01277932336271</v>
       </c>
       <c r="J2" t="n">
-        <v>29.78197057244552</v>
+        <v>47.89589577919704</v>
       </c>
     </row>
   </sheetData>
@@ -14882,31 +14882,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.81294622258617</v>
+        <v>31.61602024245472</v>
       </c>
       <c r="C2" t="n">
-        <v>34.92676722759272</v>
+        <v>34.41781920733892</v>
       </c>
       <c r="D2" t="n">
-        <v>53.22499076501273</v>
+        <v>38.26201978972493</v>
       </c>
       <c r="E2" t="n">
-        <v>31.55816747979335</v>
+        <v>39.56034113548939</v>
       </c>
       <c r="F2" t="n">
-        <v>44.19207916948542</v>
+        <v>45.68043740290383</v>
       </c>
       <c r="G2" t="n">
-        <v>33.63471689625376</v>
+        <v>30.28655113994122</v>
       </c>
       <c r="H2" t="n">
-        <v>37.73714409168755</v>
+        <v>46.08052272788272</v>
       </c>
       <c r="I2" t="n">
-        <v>50.10723938858041</v>
+        <v>49.83502727183092</v>
       </c>
       <c r="J2" t="n">
-        <v>33.44467515797827</v>
+        <v>46.67939126094283</v>
       </c>
     </row>
   </sheetData>
@@ -14980,31 +14980,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.05893289065319</v>
+        <v>31.59546126696028</v>
       </c>
       <c r="C2" t="n">
-        <v>32.75615248058288</v>
+        <v>44.97897794584978</v>
       </c>
       <c r="D2" t="n">
-        <v>26.38984929486594</v>
+        <v>37.90331892690061</v>
       </c>
       <c r="E2" t="n">
-        <v>34.97695209390379</v>
+        <v>38.98014017151183</v>
       </c>
       <c r="F2" t="n">
-        <v>40.25976937880977</v>
+        <v>46.6744736380212</v>
       </c>
       <c r="G2" t="n">
-        <v>44.23592552342205</v>
+        <v>41.16733383123794</v>
       </c>
       <c r="H2" t="n">
-        <v>43.76467474186173</v>
+        <v>36.94988043631749</v>
       </c>
       <c r="I2" t="n">
-        <v>27.24334569315699</v>
+        <v>42.37109240066008</v>
       </c>
       <c r="J2" t="n">
-        <v>55.15850248267009</v>
+        <v>37.4309017469336</v>
       </c>
     </row>
   </sheetData>
@@ -15078,31 +15078,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.38121600550568</v>
+        <v>37.07655625951042</v>
       </c>
       <c r="C2" t="n">
-        <v>52.34509811907514</v>
+        <v>53.25920480358658</v>
       </c>
       <c r="D2" t="n">
-        <v>18.33346511904641</v>
+        <v>48.53599857156382</v>
       </c>
       <c r="E2" t="n">
-        <v>40.61113326999744</v>
+        <v>32.02999789662543</v>
       </c>
       <c r="F2" t="n">
-        <v>54.8346176242114</v>
+        <v>47.37657272087173</v>
       </c>
       <c r="G2" t="n">
-        <v>52.40802293110813</v>
+        <v>26.08601783342114</v>
       </c>
       <c r="H2" t="n">
-        <v>18.27986637308688</v>
+        <v>49.37339052224778</v>
       </c>
       <c r="I2" t="n">
-        <v>41.46068589442419</v>
+        <v>40.79932589892455</v>
       </c>
       <c r="J2" t="n">
-        <v>38.70883705971634</v>
+        <v>31.39350630521577</v>
       </c>
     </row>
   </sheetData>
@@ -15176,31 +15176,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.85980813925867</v>
+        <v>31.89734117612987</v>
       </c>
       <c r="C2" t="n">
-        <v>29.08003632538271</v>
+        <v>43.6441791808688</v>
       </c>
       <c r="D2" t="n">
-        <v>33.85387304362683</v>
+        <v>41.9578384419106</v>
       </c>
       <c r="E2" t="n">
-        <v>36.23712717919256</v>
+        <v>34.48531044943745</v>
       </c>
       <c r="F2" t="n">
-        <v>50.58943797429846</v>
+        <v>30.23561974979208</v>
       </c>
       <c r="G2" t="n">
-        <v>39.05145345182239</v>
+        <v>33.68449460628305</v>
       </c>
       <c r="H2" t="n">
-        <v>27.10294875579297</v>
+        <v>40.19445083593202</v>
       </c>
       <c r="I2" t="n">
-        <v>40.54903259627731</v>
+        <v>51.74510054994481</v>
       </c>
       <c r="J2" t="n">
-        <v>30.73794944566902</v>
+        <v>40.42054576756018</v>
       </c>
     </row>
   </sheetData>
@@ -15274,31 +15274,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.97677647598969</v>
+        <v>33.43433515421437</v>
       </c>
       <c r="C2" t="n">
-        <v>41.61061092860346</v>
+        <v>49.8494716706434</v>
       </c>
       <c r="D2" t="n">
-        <v>35.54149425283543</v>
+        <v>57.59393664604734</v>
       </c>
       <c r="E2" t="n">
-        <v>45.23246561269476</v>
+        <v>36.9934971418753</v>
       </c>
       <c r="F2" t="n">
-        <v>40.06814036426914</v>
+        <v>32.23975143417558</v>
       </c>
       <c r="G2" t="n">
-        <v>40.34804938064055</v>
+        <v>39.21501922923268</v>
       </c>
       <c r="H2" t="n">
-        <v>41.96306514326855</v>
+        <v>52.41443536786407</v>
       </c>
       <c r="I2" t="n">
-        <v>39.15593679347828</v>
+        <v>36.78439589001038</v>
       </c>
       <c r="J2" t="n">
-        <v>38.73306167602439</v>
+        <v>46.82141709647832</v>
       </c>
     </row>
   </sheetData>
@@ -15372,31 +15372,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.68624753430024</v>
+        <v>35.74456527244342</v>
       </c>
       <c r="C2" t="n">
-        <v>41.35128251485273</v>
+        <v>39.56169624494289</v>
       </c>
       <c r="D2" t="n">
-        <v>45.21207195459144</v>
+        <v>25.98542518028848</v>
       </c>
       <c r="E2" t="n">
-        <v>22.23003851656356</v>
+        <v>36.23662170209816</v>
       </c>
       <c r="F2" t="n">
-        <v>33.90583492519705</v>
+        <v>43.52102290091437</v>
       </c>
       <c r="G2" t="n">
-        <v>45.01431208624108</v>
+        <v>46.31724361282311</v>
       </c>
       <c r="H2" t="n">
-        <v>36.98017166995907</v>
+        <v>36.04079996495726</v>
       </c>
       <c r="I2" t="n">
-        <v>22.32463019727863</v>
+        <v>42.04584654253522</v>
       </c>
       <c r="J2" t="n">
-        <v>28.11568923954295</v>
+        <v>34.16011564664326</v>
       </c>
     </row>
   </sheetData>
@@ -15470,31 +15470,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.87994594798875</v>
+        <v>35.513372376258</v>
       </c>
       <c r="C2" t="n">
-        <v>29.08038452351795</v>
+        <v>52.72543146368076</v>
       </c>
       <c r="D2" t="n">
-        <v>23.5534336205433</v>
+        <v>19.84348554224034</v>
       </c>
       <c r="E2" t="n">
-        <v>32.93729576336183</v>
+        <v>32.01365937116081</v>
       </c>
       <c r="F2" t="n">
-        <v>44.47729231564101</v>
+        <v>38.48672152749512</v>
       </c>
       <c r="G2" t="n">
-        <v>33.74969002524695</v>
+        <v>39.99270817139762</v>
       </c>
       <c r="H2" t="n">
-        <v>35.22861278537873</v>
+        <v>45.6930315114278</v>
       </c>
       <c r="I2" t="n">
-        <v>47.24774040993621</v>
+        <v>41.98064176333175</v>
       </c>
       <c r="J2" t="n">
-        <v>29.29614271560491</v>
+        <v>35.73077438790346</v>
       </c>
     </row>
   </sheetData>
@@ -15568,31 +15568,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>52.23086130055249</v>
+        <v>41.69529485796871</v>
       </c>
       <c r="C2" t="n">
-        <v>39.39408222664968</v>
+        <v>47.2802629234153</v>
       </c>
       <c r="D2" t="n">
-        <v>35.1825494559954</v>
+        <v>44.96211830351428</v>
       </c>
       <c r="E2" t="n">
-        <v>35.75397058119469</v>
+        <v>28.26862757049929</v>
       </c>
       <c r="F2" t="n">
-        <v>34.40422464251356</v>
+        <v>28.86102473775417</v>
       </c>
       <c r="G2" t="n">
-        <v>32.5247521399715</v>
+        <v>43.91306599282976</v>
       </c>
       <c r="H2" t="n">
-        <v>28.73737520183323</v>
+        <v>28.94052714248324</v>
       </c>
       <c r="I2" t="n">
-        <v>41.80031621260725</v>
+        <v>38.16547082958817</v>
       </c>
       <c r="J2" t="n">
-        <v>33.95165023000497</v>
+        <v>41.98149408225944</v>
       </c>
     </row>
   </sheetData>
@@ -15666,31 +15666,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.87737054941354</v>
+        <v>29.92476796531155</v>
       </c>
       <c r="C2" t="n">
-        <v>22.74140991117945</v>
+        <v>36.63422186666423</v>
       </c>
       <c r="D2" t="n">
-        <v>41.44505389063801</v>
+        <v>40.88245830767441</v>
       </c>
       <c r="E2" t="n">
-        <v>33.73191472277261</v>
+        <v>45.48716440416095</v>
       </c>
       <c r="F2" t="n">
-        <v>35.58049030083212</v>
+        <v>40.25200144432439</v>
       </c>
       <c r="G2" t="n">
-        <v>29.90942716626856</v>
+        <v>45.66161437015262</v>
       </c>
       <c r="H2" t="n">
-        <v>34.95532407055326</v>
+        <v>45.82200442364118</v>
       </c>
       <c r="I2" t="n">
-        <v>66.12336391584003</v>
+        <v>30.10142803268492</v>
       </c>
       <c r="J2" t="n">
-        <v>31.94790923711814</v>
+        <v>19.83168573685139</v>
       </c>
     </row>
   </sheetData>
@@ -15764,31 +15764,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.25602992537176</v>
+        <v>30.14227904253332</v>
       </c>
       <c r="C2" t="n">
-        <v>38.93151826378542</v>
+        <v>47.81991012850276</v>
       </c>
       <c r="D2" t="n">
-        <v>47.18253346833842</v>
+        <v>54.06445879065677</v>
       </c>
       <c r="E2" t="n">
-        <v>44.02583948173194</v>
+        <v>36.58622184355838</v>
       </c>
       <c r="F2" t="n">
-        <v>38.437975234147</v>
+        <v>43.65905622726666</v>
       </c>
       <c r="G2" t="n">
-        <v>42.45860909519428</v>
+        <v>45.47263651900324</v>
       </c>
       <c r="H2" t="n">
-        <v>40.89107375041078</v>
+        <v>47.38959673391209</v>
       </c>
       <c r="I2" t="n">
-        <v>42.03306580718419</v>
+        <v>35.50064522386441</v>
       </c>
       <c r="J2" t="n">
-        <v>27.90182465158449</v>
+        <v>40.20531389764504</v>
       </c>
     </row>
   </sheetData>
@@ -15862,31 +15862,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.76708284328119</v>
+        <v>30.28517008350413</v>
       </c>
       <c r="C2" t="n">
-        <v>40.60300135833315</v>
+        <v>34.34168866744659</v>
       </c>
       <c r="D2" t="n">
-        <v>30.21517335642685</v>
+        <v>35.83025323245169</v>
       </c>
       <c r="E2" t="n">
-        <v>35.00111804543084</v>
+        <v>41.33403172920122</v>
       </c>
       <c r="F2" t="n">
-        <v>24.91013122405614</v>
+        <v>46.36604630467288</v>
       </c>
       <c r="G2" t="n">
-        <v>28.56101039288219</v>
+        <v>30.60473807198147</v>
       </c>
       <c r="H2" t="n">
-        <v>44.13306670146296</v>
+        <v>36.58121616033913</v>
       </c>
       <c r="I2" t="n">
-        <v>45.01192869039441</v>
+        <v>49.02101635819535</v>
       </c>
       <c r="J2" t="n">
-        <v>34.47719665016916</v>
+        <v>40.22333892713753</v>
       </c>
     </row>
   </sheetData>
@@ -15960,31 +15960,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.12517102082703</v>
+        <v>49.58507722500021</v>
       </c>
       <c r="C2" t="n">
-        <v>36.25880543393553</v>
+        <v>49.04565863570147</v>
       </c>
       <c r="D2" t="n">
-        <v>37.42924414037643</v>
+        <v>33.55988239106628</v>
       </c>
       <c r="E2" t="n">
-        <v>38.41132720052484</v>
+        <v>28.98121547349856</v>
       </c>
       <c r="F2" t="n">
-        <v>45.96424804337067</v>
+        <v>33.50729662452457</v>
       </c>
       <c r="G2" t="n">
-        <v>41.19764567761024</v>
+        <v>27.00209684184311</v>
       </c>
       <c r="H2" t="n">
-        <v>28.0688814894983</v>
+        <v>46.94192655207522</v>
       </c>
       <c r="I2" t="n">
-        <v>24.05500174824629</v>
+        <v>28.76767486255594</v>
       </c>
       <c r="J2" t="n">
-        <v>38.63187629371536</v>
+        <v>39.91937215224625</v>
       </c>
     </row>
   </sheetData>
@@ -16058,31 +16058,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.18672189711492</v>
+        <v>33.69064972588087</v>
       </c>
       <c r="C2" t="n">
-        <v>26.19083914664967</v>
+        <v>14.57201144096362</v>
       </c>
       <c r="D2" t="n">
-        <v>36.71068844048972</v>
+        <v>71.73090934787625</v>
       </c>
       <c r="E2" t="n">
-        <v>1629.532606961664</v>
+        <v>29.96438299833077</v>
       </c>
       <c r="F2" t="n">
-        <v>41.67939092867479</v>
+        <v>29.8969557814002</v>
       </c>
       <c r="G2" t="n">
-        <v>27.18648464408684</v>
+        <v>62.82542129675206</v>
       </c>
       <c r="H2" t="n">
-        <v>27.48355630666468</v>
+        <v>45.28675253415462</v>
       </c>
       <c r="I2" t="n">
-        <v>19.98069915581677</v>
+        <v>43.89255174995348</v>
       </c>
       <c r="J2" t="n">
-        <v>43.88530099750723</v>
+        <v>32.52667429212219</v>
       </c>
     </row>
   </sheetData>
@@ -16156,31 +16156,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.54152152782687</v>
+        <v>27.61449745479815</v>
       </c>
       <c r="C2" t="n">
-        <v>29.04148684322491</v>
+        <v>28.89105792925444</v>
       </c>
       <c r="D2" t="n">
-        <v>34.06210053411453</v>
+        <v>59.66463994255065</v>
       </c>
       <c r="E2" t="n">
-        <v>45.66980878232284</v>
+        <v>40.97017277335516</v>
       </c>
       <c r="F2" t="n">
-        <v>42.45808058410556</v>
+        <v>52.61686920396554</v>
       </c>
       <c r="G2" t="n">
-        <v>49.9314653173108</v>
+        <v>43.18444645386787</v>
       </c>
       <c r="H2" t="n">
-        <v>48.35905280774685</v>
+        <v>29.60169544355067</v>
       </c>
       <c r="I2" t="n">
-        <v>26.82871239319945</v>
+        <v>57.33854479332919</v>
       </c>
       <c r="J2" t="n">
-        <v>47.15942889286291</v>
+        <v>51.40176969618508</v>
       </c>
     </row>
   </sheetData>
@@ -16254,31 +16254,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.85623565741278</v>
+        <v>44.9393161415425</v>
       </c>
       <c r="C2" t="n">
-        <v>41.31144485032977</v>
+        <v>30.41509647292805</v>
       </c>
       <c r="D2" t="n">
-        <v>34.21267973692164</v>
+        <v>60.59605697007095</v>
       </c>
       <c r="E2" t="n">
-        <v>28.38135986949636</v>
+        <v>40.67873975487949</v>
       </c>
       <c r="F2" t="n">
-        <v>20.5910346038676</v>
+        <v>39.25931543860927</v>
       </c>
       <c r="G2" t="n">
-        <v>39.12318468653616</v>
+        <v>38.03015757761204</v>
       </c>
       <c r="H2" t="n">
-        <v>44.2292574514352</v>
+        <v>29.90249914877251</v>
       </c>
       <c r="I2" t="n">
-        <v>43.01514387976596</v>
+        <v>37.71200543594571</v>
       </c>
       <c r="J2" t="n">
-        <v>27.65397958200014</v>
+        <v>36.38866957239077</v>
       </c>
     </row>
   </sheetData>
@@ -16352,31 +16352,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.43908819975913</v>
+        <v>43.28573892891256</v>
       </c>
       <c r="C2" t="n">
-        <v>38.46088988775882</v>
+        <v>45.50057358521946</v>
       </c>
       <c r="D2" t="n">
-        <v>28.8250624434447</v>
+        <v>34.91616400165193</v>
       </c>
       <c r="E2" t="n">
-        <v>46.34924060311229</v>
+        <v>42.23276676694341</v>
       </c>
       <c r="F2" t="n">
-        <v>33.27717063519383</v>
+        <v>36.75725616148917</v>
       </c>
       <c r="G2" t="n">
-        <v>30.89192069652038</v>
+        <v>44.4266329845228</v>
       </c>
       <c r="H2" t="n">
-        <v>40.93259466203915</v>
+        <v>39.58614059151671</v>
       </c>
       <c r="I2" t="n">
-        <v>46.08698038627779</v>
+        <v>48.01651859497793</v>
       </c>
       <c r="J2" t="n">
-        <v>45.45415490923934</v>
+        <v>47.91080800425787</v>
       </c>
     </row>
   </sheetData>
@@ -16450,31 +16450,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.96358849642836</v>
+        <v>33.27181920690408</v>
       </c>
       <c r="C2" t="n">
-        <v>38.72158833397709</v>
+        <v>53.41810202405977</v>
       </c>
       <c r="D2" t="n">
-        <v>34.61606348109999</v>
+        <v>40.35048508118303</v>
       </c>
       <c r="E2" t="n">
-        <v>43.89367399640931</v>
+        <v>36.25374369058716</v>
       </c>
       <c r="F2" t="n">
-        <v>52.03593018784481</v>
+        <v>39.2212115515273</v>
       </c>
       <c r="G2" t="n">
-        <v>42.18898628775379</v>
+        <v>51.13867447341192</v>
       </c>
       <c r="H2" t="n">
-        <v>39.48510198446264</v>
+        <v>40.22152899483955</v>
       </c>
       <c r="I2" t="n">
-        <v>45.41025939960223</v>
+        <v>35.47418676126721</v>
       </c>
       <c r="J2" t="n">
-        <v>32.31570949862581</v>
+        <v>39.76575470478552</v>
       </c>
     </row>
   </sheetData>
@@ -16548,31 +16548,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.35512033174817</v>
+        <v>37.76615064722245</v>
       </c>
       <c r="C2" t="n">
-        <v>39.03584924620684</v>
+        <v>40.28168896502684</v>
       </c>
       <c r="D2" t="n">
-        <v>37.073990687322</v>
+        <v>32.13280597401808</v>
       </c>
       <c r="E2" t="n">
-        <v>33.25981468929406</v>
+        <v>34.7378086399188</v>
       </c>
       <c r="F2" t="n">
-        <v>28.81809439960701</v>
+        <v>49.98174315641208</v>
       </c>
       <c r="G2" t="n">
-        <v>46.10972057549431</v>
+        <v>36.71833607621745</v>
       </c>
       <c r="H2" t="n">
-        <v>34.65003835175026</v>
+        <v>46.01013213657215</v>
       </c>
       <c r="I2" t="n">
-        <v>27.9769825933577</v>
+        <v>39.93037682036671</v>
       </c>
       <c r="J2" t="n">
-        <v>45.83620164963115</v>
+        <v>54.69933989723117</v>
       </c>
     </row>
   </sheetData>
@@ -16646,31 +16646,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.85390274128356</v>
+        <v>32.39427216745162</v>
       </c>
       <c r="C2" t="n">
-        <v>43.42570371615094</v>
+        <v>36.00419821328902</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53275477396551</v>
+        <v>42.99363659910733</v>
       </c>
       <c r="E2" t="n">
-        <v>34.49992978470306</v>
+        <v>45.17700430428655</v>
       </c>
       <c r="F2" t="n">
-        <v>33.57200764851851</v>
+        <v>36.73188222944448</v>
       </c>
       <c r="G2" t="n">
-        <v>37.78391653600087</v>
+        <v>45.52933795077109</v>
       </c>
       <c r="H2" t="n">
-        <v>26.83021787741737</v>
+        <v>51.63636441761092</v>
       </c>
       <c r="I2" t="n">
-        <v>36.2352445408922</v>
+        <v>40.47526022915621</v>
       </c>
       <c r="J2" t="n">
-        <v>58.40713282710582</v>
+        <v>35.63607263350027</v>
       </c>
     </row>
   </sheetData>
@@ -16744,31 +16744,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.86040696703485</v>
+        <v>42.10348763835523</v>
       </c>
       <c r="C2" t="n">
-        <v>35.56040327540968</v>
+        <v>60.42204608448409</v>
       </c>
       <c r="D2" t="n">
-        <v>37.93063962090567</v>
+        <v>30.94191615980661</v>
       </c>
       <c r="E2" t="n">
-        <v>36.38822601127267</v>
+        <v>39.58984708997377</v>
       </c>
       <c r="F2" t="n">
-        <v>42.90761716536242</v>
+        <v>38.13253286805252</v>
       </c>
       <c r="G2" t="n">
-        <v>23.70063525276077</v>
+        <v>45.85052085270554</v>
       </c>
       <c r="H2" t="n">
-        <v>48.69849048820279</v>
+        <v>27.49916302380628</v>
       </c>
       <c r="I2" t="n">
-        <v>37.59218864765795</v>
+        <v>41.60770355355735</v>
       </c>
       <c r="J2" t="n">
-        <v>36.21161024755483</v>
+        <v>40.65036452128241</v>
       </c>
     </row>
   </sheetData>
@@ -16842,31 +16842,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.33317931626567</v>
+        <v>29.95381914323065</v>
       </c>
       <c r="C2" t="n">
-        <v>41.6308906132164</v>
+        <v>32.95195889350581</v>
       </c>
       <c r="D2" t="n">
-        <v>36.52511581651476</v>
+        <v>30.38157713262926</v>
       </c>
       <c r="E2" t="n">
-        <v>37.7072366244221</v>
+        <v>44.0695104985378</v>
       </c>
       <c r="F2" t="n">
-        <v>40.65227246654241</v>
+        <v>32.36621105987221</v>
       </c>
       <c r="G2" t="n">
-        <v>28.85660492191604</v>
+        <v>31.10021117469375</v>
       </c>
       <c r="H2" t="n">
-        <v>28.81452462458814</v>
+        <v>28.2466472379758</v>
       </c>
       <c r="I2" t="n">
-        <v>27.3154619161492</v>
+        <v>49.57397139238705</v>
       </c>
       <c r="J2" t="n">
-        <v>32.93711706390667</v>
+        <v>40.5541469210009</v>
       </c>
     </row>
   </sheetData>
@@ -16940,31 +16940,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.34097910558381</v>
+        <v>50.22101836779273</v>
       </c>
       <c r="C2" t="n">
-        <v>47.8599794004049</v>
+        <v>39.99783431277967</v>
       </c>
       <c r="D2" t="n">
-        <v>35.25394987318218</v>
+        <v>45.01415542782202</v>
       </c>
       <c r="E2" t="n">
-        <v>200.6472824286174</v>
+        <v>39.117579646432</v>
       </c>
       <c r="F2" t="n">
-        <v>32.59277647422012</v>
+        <v>24.63606929205865</v>
       </c>
       <c r="G2" t="n">
-        <v>27.60732978089887</v>
+        <v>43.19015239883166</v>
       </c>
       <c r="H2" t="n">
-        <v>28.53788934505835</v>
+        <v>50.49961424004492</v>
       </c>
       <c r="I2" t="n">
-        <v>30.67241884954229</v>
+        <v>34.758967218929</v>
       </c>
       <c r="J2" t="n">
-        <v>35.37854562398322</v>
+        <v>42.8559323083746</v>
       </c>
     </row>
   </sheetData>
@@ -17038,31 +17038,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.30689292517089</v>
+        <v>30.00388866297027</v>
       </c>
       <c r="C2" t="n">
-        <v>40.71853343725636</v>
+        <v>54.94163516294259</v>
       </c>
       <c r="D2" t="n">
-        <v>29.70384896617308</v>
+        <v>41.3390722177339</v>
       </c>
       <c r="E2" t="n">
-        <v>35.61627468149412</v>
+        <v>23.65209137504724</v>
       </c>
       <c r="F2" t="n">
-        <v>35.0439274110399</v>
+        <v>37.08047222301085</v>
       </c>
       <c r="G2" t="n">
-        <v>28.5207523544325</v>
+        <v>32.17838162507119</v>
       </c>
       <c r="H2" t="n">
-        <v>29.83668554616255</v>
+        <v>36.7428771769826</v>
       </c>
       <c r="I2" t="n">
-        <v>39.37480447706509</v>
+        <v>21.81867563031703</v>
       </c>
       <c r="J2" t="n">
-        <v>36.44427254791518</v>
+        <v>50.43152176290972</v>
       </c>
     </row>
   </sheetData>
@@ -17136,31 +17136,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>55.6657951606249</v>
+        <v>41.01021892704391</v>
       </c>
       <c r="C2" t="n">
-        <v>38.42058611550652</v>
+        <v>52.02488261232609</v>
       </c>
       <c r="D2" t="n">
-        <v>18.94898551970428</v>
+        <v>31.7880098592979</v>
       </c>
       <c r="E2" t="n">
-        <v>43.11433703057941</v>
+        <v>36.67901842781567</v>
       </c>
       <c r="F2" t="n">
-        <v>35.80232984946041</v>
+        <v>33.4103527937311</v>
       </c>
       <c r="G2" t="n">
-        <v>44.16962431644205</v>
+        <v>32.49182061057745</v>
       </c>
       <c r="H2" t="n">
-        <v>34.97787123080006</v>
+        <v>49.78102981238948</v>
       </c>
       <c r="I2" t="n">
-        <v>49.15731569235764</v>
+        <v>47.67904389350451</v>
       </c>
       <c r="J2" t="n">
-        <v>41.16177621799332</v>
+        <v>46.77697015631954</v>
       </c>
     </row>
   </sheetData>
@@ -17234,31 +17234,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.24674659312049</v>
+        <v>33.18210017465557</v>
       </c>
       <c r="C2" t="n">
-        <v>39.81745361427872</v>
+        <v>55.17987963365979</v>
       </c>
       <c r="D2" t="n">
-        <v>32.43940719437754</v>
+        <v>48.89143401561772</v>
       </c>
       <c r="E2" t="n">
-        <v>40.56265005377067</v>
+        <v>32.6425448556022</v>
       </c>
       <c r="F2" t="n">
-        <v>37.47101934138877</v>
+        <v>41.2184049068274</v>
       </c>
       <c r="G2" t="n">
-        <v>44.41322089093693</v>
+        <v>41.55594327241243</v>
       </c>
       <c r="H2" t="n">
-        <v>35.33252766152207</v>
+        <v>35.97641922258599</v>
       </c>
       <c r="I2" t="n">
-        <v>34.25497770150928</v>
+        <v>60.91796391422091</v>
       </c>
       <c r="J2" t="n">
-        <v>44.13233160362898</v>
+        <v>46.06010694905982</v>
       </c>
     </row>
   </sheetData>
@@ -17332,31 +17332,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.87096831953377</v>
+        <v>27.68827603214214</v>
       </c>
       <c r="C2" t="n">
-        <v>29.20927913889346</v>
+        <v>42.65798923590913</v>
       </c>
       <c r="D2" t="n">
-        <v>37.59166327078646</v>
+        <v>55.3897792788999</v>
       </c>
       <c r="E2" t="n">
-        <v>45.44781543449768</v>
+        <v>33.77623709734583</v>
       </c>
       <c r="F2" t="n">
-        <v>43.2262376449491</v>
+        <v>64.56926601861871</v>
       </c>
       <c r="G2" t="n">
-        <v>30.73995802266921</v>
+        <v>47.41668704245101</v>
       </c>
       <c r="H2" t="n">
-        <v>35.60138066906612</v>
+        <v>28.85922086580734</v>
       </c>
       <c r="I2" t="n">
-        <v>24.97109684109095</v>
+        <v>35.03569249399313</v>
       </c>
       <c r="J2" t="n">
-        <v>42.70775652594845</v>
+        <v>31.11045464653299</v>
       </c>
     </row>
   </sheetData>
@@ -17430,31 +17430,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.32086033710762</v>
+        <v>30.78240587071594</v>
       </c>
       <c r="C2" t="n">
-        <v>50.89783642487609</v>
+        <v>41.58563769071878</v>
       </c>
       <c r="D2" t="n">
-        <v>13.56667651166553</v>
+        <v>42.2189660195952</v>
       </c>
       <c r="E2" t="n">
-        <v>42.82106486093517</v>
+        <v>30.47910520816109</v>
       </c>
       <c r="F2" t="n">
-        <v>52.22967888588427</v>
+        <v>55.05590019963081</v>
       </c>
       <c r="G2" t="n">
-        <v>44.1225938822765</v>
+        <v>38.80722360038503</v>
       </c>
       <c r="H2" t="n">
-        <v>30.32752612201026</v>
+        <v>35.78841192757048</v>
       </c>
       <c r="I2" t="n">
-        <v>28.92621962774865</v>
+        <v>66.40390292262057</v>
       </c>
       <c r="J2" t="n">
-        <v>36.59392513343022</v>
+        <v>51.30111872709173</v>
       </c>
     </row>
   </sheetData>
@@ -17528,31 +17528,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.21979583542616</v>
+        <v>34.80935726738667</v>
       </c>
       <c r="C2" t="n">
-        <v>46.38869032717103</v>
+        <v>45.33980457528291</v>
       </c>
       <c r="D2" t="n">
-        <v>37.39970252641484</v>
+        <v>54.20683055373667</v>
       </c>
       <c r="E2" t="n">
-        <v>44.71078652461741</v>
+        <v>35.73211948478784</v>
       </c>
       <c r="F2" t="n">
-        <v>45.69092578412201</v>
+        <v>32.63515894125891</v>
       </c>
       <c r="G2" t="n">
-        <v>38.5379606306148</v>
+        <v>36.19298742425925</v>
       </c>
       <c r="H2" t="n">
-        <v>35.1841746490737</v>
+        <v>55.14114807102496</v>
       </c>
       <c r="I2" t="n">
-        <v>26.8053181170298</v>
+        <v>43.82821927097839</v>
       </c>
       <c r="J2" t="n">
-        <v>32.60681230704262</v>
+        <v>45.75778939871232</v>
       </c>
     </row>
   </sheetData>
@@ -17626,31 +17626,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.17632775205912</v>
+        <v>35.90357900332453</v>
       </c>
       <c r="C2" t="n">
-        <v>33.90891466149888</v>
+        <v>54.53984213547609</v>
       </c>
       <c r="D2" t="n">
-        <v>23.83176992738596</v>
+        <v>51.73389216871408</v>
       </c>
       <c r="E2" t="n">
-        <v>42.4926642544233</v>
+        <v>39.43666153012668</v>
       </c>
       <c r="F2" t="n">
-        <v>36.9724800736479</v>
+        <v>48.07917632472507</v>
       </c>
       <c r="G2" t="n">
-        <v>51.45046834742558</v>
+        <v>40.97991861591773</v>
       </c>
       <c r="H2" t="n">
-        <v>32.89027591076722</v>
+        <v>52.76572244547724</v>
       </c>
       <c r="I2" t="n">
-        <v>39.83667521862229</v>
+        <v>38.84090056680666</v>
       </c>
       <c r="J2" t="n">
-        <v>55.55213156155604</v>
+        <v>43.26837582740055</v>
       </c>
     </row>
   </sheetData>
@@ -17724,31 +17724,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.60717579932812</v>
+        <v>28.06796002688398</v>
       </c>
       <c r="C2" t="n">
-        <v>35.75422814613394</v>
+        <v>51.68807542484186</v>
       </c>
       <c r="D2" t="n">
-        <v>38.55610436595286</v>
+        <v>34.73792049408568</v>
       </c>
       <c r="E2" t="n">
-        <v>32.10765650101797</v>
+        <v>35.29585785520825</v>
       </c>
       <c r="F2" t="n">
-        <v>28.60089131978167</v>
+        <v>37.35261603958124</v>
       </c>
       <c r="G2" t="n">
-        <v>31.43045806676836</v>
+        <v>30.97783144697967</v>
       </c>
       <c r="H2" t="n">
-        <v>36.89362564998214</v>
+        <v>36.12933572735412</v>
       </c>
       <c r="I2" t="n">
-        <v>35.47857320789875</v>
+        <v>33.11963779868262</v>
       </c>
       <c r="J2" t="n">
-        <v>37.47597504495204</v>
+        <v>34.58029554413309</v>
       </c>
     </row>
   </sheetData>
@@ -17822,31 +17822,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.37221890840963</v>
+        <v>32.07959381899208</v>
       </c>
       <c r="C2" t="n">
-        <v>38.03654346079085</v>
+        <v>43.5851658170934</v>
       </c>
       <c r="D2" t="n">
-        <v>38.52195457411026</v>
+        <v>36.73271015911169</v>
       </c>
       <c r="E2" t="n">
-        <v>34.24364850598979</v>
+        <v>26.37082033542575</v>
       </c>
       <c r="F2" t="n">
-        <v>57.38892876825232</v>
+        <v>46.23954397645982</v>
       </c>
       <c r="G2" t="n">
-        <v>38.35416924503114</v>
+        <v>29.1303642976455</v>
       </c>
       <c r="H2" t="n">
-        <v>17.52399814906673</v>
+        <v>50.06420873115688</v>
       </c>
       <c r="I2" t="n">
-        <v>27.49895731394245</v>
+        <v>31.50171642553045</v>
       </c>
       <c r="J2" t="n">
-        <v>32.97788953078054</v>
+        <v>36.73926337290575</v>
       </c>
     </row>
   </sheetData>
@@ -17920,31 +17920,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.793191584991</v>
+        <v>32.64557917854667</v>
       </c>
       <c r="C2" t="n">
-        <v>42.23924540849214</v>
+        <v>52.79535983052093</v>
       </c>
       <c r="D2" t="n">
-        <v>25.936150866666</v>
+        <v>43.08168448563917</v>
       </c>
       <c r="E2" t="n">
-        <v>54.96823064342274</v>
+        <v>44.94287768511288</v>
       </c>
       <c r="F2" t="n">
-        <v>35.75539856105311</v>
+        <v>33.44701978111944</v>
       </c>
       <c r="G2" t="n">
-        <v>47.93272397178372</v>
+        <v>36.74654916467194</v>
       </c>
       <c r="H2" t="n">
-        <v>28.64484139943886</v>
+        <v>43.79104676556146</v>
       </c>
       <c r="I2" t="n">
-        <v>28.45645422480604</v>
+        <v>34.73450963463016</v>
       </c>
       <c r="J2" t="n">
-        <v>39.88016064940497</v>
+        <v>44.82909123343011</v>
       </c>
     </row>
   </sheetData>
@@ -18018,31 +18018,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.34967988502729</v>
+        <v>40.96376206239983</v>
       </c>
       <c r="C2" t="n">
-        <v>33.40988050128473</v>
+        <v>41.30435558485154</v>
       </c>
       <c r="D2" t="n">
-        <v>50.63339827155753</v>
+        <v>23.92204173490612</v>
       </c>
       <c r="E2" t="n">
-        <v>29.54859297663558</v>
+        <v>36.20988878022398</v>
       </c>
       <c r="F2" t="n">
-        <v>36.45817369845386</v>
+        <v>27.50182451494792</v>
       </c>
       <c r="G2" t="n">
-        <v>48.06689306810055</v>
+        <v>39.45437742450078</v>
       </c>
       <c r="H2" t="n">
-        <v>41.08729831222961</v>
+        <v>44.76771167847027</v>
       </c>
       <c r="I2" t="n">
-        <v>29.44305754101535</v>
+        <v>45.1092357514806</v>
       </c>
       <c r="J2" t="n">
-        <v>23.6058540398116</v>
+        <v>33.44021188276987</v>
       </c>
     </row>
   </sheetData>
@@ -18116,31 +18116,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.08013678483367</v>
+        <v>43.62335698059099</v>
       </c>
       <c r="C2" t="n">
-        <v>43.7463457135829</v>
+        <v>41.35572421359129</v>
       </c>
       <c r="D2" t="n">
-        <v>46.78824011053799</v>
+        <v>47.98224120960816</v>
       </c>
       <c r="E2" t="n">
-        <v>34.77821058401182</v>
+        <v>35.43529956974584</v>
       </c>
       <c r="F2" t="n">
-        <v>44.6893608843893</v>
+        <v>36.71172690101233</v>
       </c>
       <c r="G2" t="n">
-        <v>34.38690367139552</v>
+        <v>38.44679583164853</v>
       </c>
       <c r="H2" t="n">
-        <v>60.0159906986973</v>
+        <v>53.69503370229364</v>
       </c>
       <c r="I2" t="n">
-        <v>33.75655633895398</v>
+        <v>40.97320218719373</v>
       </c>
       <c r="J2" t="n">
-        <v>42.41600493725962</v>
+        <v>42.36470825380742</v>
       </c>
     </row>
   </sheetData>
@@ -18214,31 +18214,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.1317287155082</v>
+        <v>35.63871305598763</v>
       </c>
       <c r="C2" t="n">
-        <v>46.50378001827863</v>
+        <v>47.04521987635943</v>
       </c>
       <c r="D2" t="n">
-        <v>44.65275171521311</v>
+        <v>43.61420601075396</v>
       </c>
       <c r="E2" t="n">
-        <v>37.47782382165185</v>
+        <v>37.24285806343745</v>
       </c>
       <c r="F2" t="n">
-        <v>37.3417130984495</v>
+        <v>41.38264501722431</v>
       </c>
       <c r="G2" t="n">
-        <v>41.18819939550031</v>
+        <v>41.54532590379063</v>
       </c>
       <c r="H2" t="n">
-        <v>21.75484482742597</v>
+        <v>32.79838170769828</v>
       </c>
       <c r="I2" t="n">
-        <v>32.26177852188911</v>
+        <v>41.06657022474525</v>
       </c>
       <c r="J2" t="n">
-        <v>48.14489458650331</v>
+        <v>55.65034306018288</v>
       </c>
     </row>
   </sheetData>
@@ -18312,31 +18312,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.83030550726662</v>
+        <v>31.51532884324046</v>
       </c>
       <c r="C2" t="n">
-        <v>31.31916608106744</v>
+        <v>35.88287701765589</v>
       </c>
       <c r="D2" t="n">
-        <v>38.11997808018324</v>
+        <v>47.7898779118234</v>
       </c>
       <c r="E2" t="n">
-        <v>34.9096986486984</v>
+        <v>25.26367129591984</v>
       </c>
       <c r="F2" t="n">
-        <v>44.07807875378264</v>
+        <v>41.55250744328867</v>
       </c>
       <c r="G2" t="n">
-        <v>28.73119820069676</v>
+        <v>41.11366564946215</v>
       </c>
       <c r="H2" t="n">
-        <v>38.63311314749038</v>
+        <v>47.02942536231267</v>
       </c>
       <c r="I2" t="n">
-        <v>35.15792795608937</v>
+        <v>39.98232496856214</v>
       </c>
       <c r="J2" t="n">
-        <v>39.4352440565653</v>
+        <v>24.01137706087258</v>
       </c>
     </row>
   </sheetData>
@@ -18410,31 +18410,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.19026591841388</v>
+        <v>25.74753667841571</v>
       </c>
       <c r="C2" t="n">
-        <v>34.91600579980822</v>
+        <v>29.1776620871608</v>
       </c>
       <c r="D2" t="n">
-        <v>40.42728525010339</v>
+        <v>50.7746780784603</v>
       </c>
       <c r="E2" t="n">
-        <v>49.18060322825249</v>
+        <v>31.93522899324089</v>
       </c>
       <c r="F2" t="n">
-        <v>43.14371668239549</v>
+        <v>40.67642151731997</v>
       </c>
       <c r="G2" t="n">
-        <v>45.69307311510275</v>
+        <v>34.56220331159557</v>
       </c>
       <c r="H2" t="n">
-        <v>32.58959551115257</v>
+        <v>31.96968732543535</v>
       </c>
       <c r="I2" t="n">
-        <v>24.43860696901535</v>
+        <v>44.6365740440401</v>
       </c>
       <c r="J2" t="n">
-        <v>23.47199365130995</v>
+        <v>38.50174107432957</v>
       </c>
     </row>
   </sheetData>
@@ -18508,31 +18508,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.41429233406807</v>
+        <v>35.11305744233974</v>
       </c>
       <c r="C2" t="n">
-        <v>39.95623145462177</v>
+        <v>36.4325857839947</v>
       </c>
       <c r="D2" t="n">
-        <v>25.46002900429589</v>
+        <v>45.47458298990649</v>
       </c>
       <c r="E2" t="n">
-        <v>31.03344621292534</v>
+        <v>31.74713444242166</v>
       </c>
       <c r="F2" t="n">
-        <v>36.69178551524646</v>
+        <v>35.43481646812431</v>
       </c>
       <c r="G2" t="n">
-        <v>43.81541106408622</v>
+        <v>32.94061056999787</v>
       </c>
       <c r="H2" t="n">
-        <v>35.38880613580042</v>
+        <v>37.49870602959881</v>
       </c>
       <c r="I2" t="n">
-        <v>35.00533852501336</v>
+        <v>48.22417643854237</v>
       </c>
       <c r="J2" t="n">
-        <v>24.92086235594194</v>
+        <v>47.37243600662708</v>
       </c>
     </row>
   </sheetData>
@@ -18606,31 +18606,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.59384540901888</v>
+        <v>27.47188717881112</v>
       </c>
       <c r="C2" t="n">
-        <v>37.75223212232636</v>
+        <v>46.78428580075001</v>
       </c>
       <c r="D2" t="n">
-        <v>39.51143189636722</v>
+        <v>65.01918884115648</v>
       </c>
       <c r="E2" t="n">
-        <v>38.7491207894275</v>
+        <v>44.20864386579453</v>
       </c>
       <c r="F2" t="n">
-        <v>35.19774551921414</v>
+        <v>31.92274680507654</v>
       </c>
       <c r="G2" t="n">
-        <v>36.38147919482132</v>
+        <v>34.5021666186233</v>
       </c>
       <c r="H2" t="n">
-        <v>52.40404658876355</v>
+        <v>35.28477908188891</v>
       </c>
       <c r="I2" t="n">
-        <v>23.83732374663985</v>
+        <v>38.71735155359821</v>
       </c>
       <c r="J2" t="n">
-        <v>39.41189633134656</v>
+        <v>44.66816843557823</v>
       </c>
     </row>
   </sheetData>
@@ -18704,31 +18704,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.32840679035408</v>
+        <v>33.8904756271515</v>
       </c>
       <c r="C2" t="n">
-        <v>31.1439951104258</v>
+        <v>36.78071379665249</v>
       </c>
       <c r="D2" t="n">
-        <v>31.75072892539879</v>
+        <v>24.80315912663258</v>
       </c>
       <c r="E2" t="n">
-        <v>34.18430960269706</v>
+        <v>28.87793004911451</v>
       </c>
       <c r="F2" t="n">
-        <v>57.02083496311805</v>
+        <v>35.75131929929319</v>
       </c>
       <c r="G2" t="n">
-        <v>37.95854146179388</v>
+        <v>51.59116892524449</v>
       </c>
       <c r="H2" t="n">
-        <v>37.39996659063128</v>
+        <v>29.86929722591045</v>
       </c>
       <c r="I2" t="n">
-        <v>29.24889724049673</v>
+        <v>48.77458226927895</v>
       </c>
       <c r="J2" t="n">
-        <v>43.32483253185271</v>
+        <v>57.74254958057938</v>
       </c>
     </row>
   </sheetData>
@@ -18802,31 +18802,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.68715439418113</v>
+        <v>37.0648335123449</v>
       </c>
       <c r="C2" t="n">
-        <v>48.80394683036452</v>
+        <v>38.48031615037979</v>
       </c>
       <c r="D2" t="n">
-        <v>43.24248104523025</v>
+        <v>42.32360312541466</v>
       </c>
       <c r="E2" t="n">
-        <v>35.27845400916728</v>
+        <v>44.64412540523097</v>
       </c>
       <c r="F2" t="n">
-        <v>38.05162955903062</v>
+        <v>37.09796904311075</v>
       </c>
       <c r="G2" t="n">
-        <v>21.50292561005059</v>
+        <v>36.77660561557634</v>
       </c>
       <c r="H2" t="n">
-        <v>33.92673070571996</v>
+        <v>49.54618378470361</v>
       </c>
       <c r="I2" t="n">
-        <v>42.87195062949373</v>
+        <v>27.3023363311768</v>
       </c>
       <c r="J2" t="n">
-        <v>38.44657977633171</v>
+        <v>60.7309002693973</v>
       </c>
     </row>
   </sheetData>
@@ -18900,31 +18900,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.05320005918379</v>
+        <v>24.99805471555504</v>
       </c>
       <c r="C2" t="n">
-        <v>45.07685512947718</v>
+        <v>33.64078213556085</v>
       </c>
       <c r="D2" t="n">
-        <v>24.37698205839924</v>
+        <v>46.9394744327583</v>
       </c>
       <c r="E2" t="n">
-        <v>28.66713318716668</v>
+        <v>38.08750754712739</v>
       </c>
       <c r="F2" t="n">
-        <v>43.73914660534115</v>
+        <v>32.51905473952898</v>
       </c>
       <c r="G2" t="n">
-        <v>27.68691622717072</v>
+        <v>39.82017348129609</v>
       </c>
       <c r="H2" t="n">
-        <v>34.3731682447039</v>
+        <v>44.46061721454399</v>
       </c>
       <c r="I2" t="n">
-        <v>47.46524210927047</v>
+        <v>49.39592609251421</v>
       </c>
       <c r="J2" t="n">
-        <v>43.80664004990903</v>
+        <v>39.56466572904429</v>
       </c>
     </row>
   </sheetData>
@@ -18998,31 +18998,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.6946084104972</v>
+        <v>32.67294028432151</v>
       </c>
       <c r="C2" t="n">
-        <v>35.75047454449643</v>
+        <v>36.70868640909769</v>
       </c>
       <c r="D2" t="n">
-        <v>33.35708987635326</v>
+        <v>40.53190010319025</v>
       </c>
       <c r="E2" t="n">
-        <v>29.3201067337456</v>
+        <v>28.48222765852147</v>
       </c>
       <c r="F2" t="n">
-        <v>36.82695527593376</v>
+        <v>44.33578246912824</v>
       </c>
       <c r="G2" t="n">
-        <v>65.27382136295446</v>
+        <v>49.42934079829266</v>
       </c>
       <c r="H2" t="n">
-        <v>29.59201701456776</v>
+        <v>59.74703512821277</v>
       </c>
       <c r="I2" t="n">
-        <v>49.01727541060787</v>
+        <v>42.56655843627355</v>
       </c>
       <c r="J2" t="n">
-        <v>40.79474527204274</v>
+        <v>34.27428696624344</v>
       </c>
     </row>
   </sheetData>
@@ -19096,31 +19096,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.87308697415262</v>
+        <v>45.36511575527986</v>
       </c>
       <c r="C2" t="n">
-        <v>32.79410220203656</v>
+        <v>52.97863277391285</v>
       </c>
       <c r="D2" t="n">
-        <v>37.93954191902631</v>
+        <v>34.17346664752257</v>
       </c>
       <c r="E2" t="n">
-        <v>37.94596783767332</v>
+        <v>36.26367528291618</v>
       </c>
       <c r="F2" t="n">
-        <v>34.29654907687881</v>
+        <v>46.68734746575895</v>
       </c>
       <c r="G2" t="n">
-        <v>34.50954909919916</v>
+        <v>30.09187543496311</v>
       </c>
       <c r="H2" t="n">
-        <v>29.08351791475328</v>
+        <v>42.27833617983637</v>
       </c>
       <c r="I2" t="n">
-        <v>41.73175320653485</v>
+        <v>45.44865845981867</v>
       </c>
       <c r="J2" t="n">
-        <v>29.79710771070628</v>
+        <v>41.13689880982395</v>
       </c>
     </row>
   </sheetData>
@@ -19194,31 +19194,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>19.28452754913693</v>
+        <v>30.14245597807811</v>
       </c>
       <c r="C2" t="n">
-        <v>46.65625578513497</v>
+        <v>34.19609389023198</v>
       </c>
       <c r="D2" t="n">
-        <v>23.73631909783453</v>
+        <v>46.97040572375074</v>
       </c>
       <c r="E2" t="n">
-        <v>33.92479844135692</v>
+        <v>41.4281427923183</v>
       </c>
       <c r="F2" t="n">
-        <v>43.04537712673775</v>
+        <v>39.78490633786926</v>
       </c>
       <c r="G2" t="n">
-        <v>57.74715986442884</v>
+        <v>34.69534835452774</v>
       </c>
       <c r="H2" t="n">
-        <v>40.08829781713288</v>
+        <v>40.41174867171957</v>
       </c>
       <c r="I2" t="n">
-        <v>33.61737961232929</v>
+        <v>46.36712508587729</v>
       </c>
       <c r="J2" t="n">
-        <v>32.1236528494823</v>
+        <v>45.01198706479607</v>
       </c>
     </row>
   </sheetData>
@@ -19292,31 +19292,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.59286366862744</v>
+        <v>38.18522628264267</v>
       </c>
       <c r="C2" t="n">
-        <v>82.80913132542995</v>
+        <v>37.2121713032919</v>
       </c>
       <c r="D2" t="n">
-        <v>33.65649261989314</v>
+        <v>38.94476262838484</v>
       </c>
       <c r="E2" t="n">
-        <v>45.76733383461317</v>
+        <v>32.97373437594345</v>
       </c>
       <c r="F2" t="n">
-        <v>23.30192068273305</v>
+        <v>43.84015958180407</v>
       </c>
       <c r="G2" t="n">
-        <v>35.27011664913488</v>
+        <v>45.31005966271477</v>
       </c>
       <c r="H2" t="n">
-        <v>35.3005091786783</v>
+        <v>31.08494348221395</v>
       </c>
       <c r="I2" t="n">
-        <v>24.53650514430938</v>
+        <v>52.89714072796799</v>
       </c>
       <c r="J2" t="n">
-        <v>21.30714543642696</v>
+        <v>58.05694166668732</v>
       </c>
     </row>
   </sheetData>
@@ -19390,31 +19390,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.71533301534644</v>
+        <v>44.29031544138937</v>
       </c>
       <c r="C2" t="n">
-        <v>48.42461872994073</v>
+        <v>53.67595546127923</v>
       </c>
       <c r="D2" t="n">
-        <v>35.30811560730265</v>
+        <v>39.17801664239248</v>
       </c>
       <c r="E2" t="n">
-        <v>36.09789123043177</v>
+        <v>35.38048066742862</v>
       </c>
       <c r="F2" t="n">
-        <v>30.98604594853872</v>
+        <v>43.54783675799536</v>
       </c>
       <c r="G2" t="n">
-        <v>41.94485500871361</v>
+        <v>34.83926294806532</v>
       </c>
       <c r="H2" t="n">
-        <v>40.20262253803602</v>
+        <v>36.58638223115205</v>
       </c>
       <c r="I2" t="n">
-        <v>27.99520981087139</v>
+        <v>29.6491105070741</v>
       </c>
       <c r="J2" t="n">
-        <v>35.6055395706811</v>
+        <v>33.36767508830417</v>
       </c>
     </row>
   </sheetData>
@@ -19488,31 +19488,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.84235838053294</v>
+        <v>25.90629228751579</v>
       </c>
       <c r="C2" t="n">
-        <v>53.61964414757798</v>
+        <v>53.96349168795282</v>
       </c>
       <c r="D2" t="n">
-        <v>39.24484093978628</v>
+        <v>48.13953016783547</v>
       </c>
       <c r="E2" t="n">
-        <v>43.96716901992779</v>
+        <v>37.98678737934531</v>
       </c>
       <c r="F2" t="n">
-        <v>32.89976583744296</v>
+        <v>36.73187778306215</v>
       </c>
       <c r="G2" t="n">
-        <v>40.02125726783074</v>
+        <v>39.13795927402126</v>
       </c>
       <c r="H2" t="n">
-        <v>35.88702907344351</v>
+        <v>36.73193545541644</v>
       </c>
       <c r="I2" t="n">
-        <v>39.49134084694597</v>
+        <v>39.47123988494486</v>
       </c>
       <c r="J2" t="n">
-        <v>27.69154251046767</v>
+        <v>58.64974888975854</v>
       </c>
     </row>
   </sheetData>
@@ -19586,31 +19586,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.50565942750748</v>
+        <v>33.7075126941997</v>
       </c>
       <c r="C2" t="n">
-        <v>36.49015748690579</v>
+        <v>49.27579863384979</v>
       </c>
       <c r="D2" t="n">
-        <v>46.95209044836754</v>
+        <v>49.2996444591469</v>
       </c>
       <c r="E2" t="n">
-        <v>33.47861593630852</v>
+        <v>26.5229543409163</v>
       </c>
       <c r="F2" t="n">
-        <v>55.79938961022275</v>
+        <v>44.12630469973219</v>
       </c>
       <c r="G2" t="n">
-        <v>26.11704824822669</v>
+        <v>37.15773500623426</v>
       </c>
       <c r="H2" t="n">
-        <v>25.88797547942163</v>
+        <v>40.14326011189902</v>
       </c>
       <c r="I2" t="n">
-        <v>38.50700650793457</v>
+        <v>48.18002698375906</v>
       </c>
       <c r="J2" t="n">
-        <v>22.98591058961249</v>
+        <v>35.92870078821552</v>
       </c>
     </row>
   </sheetData>
@@ -19684,31 +19684,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.66374780445305</v>
+        <v>33.61031821208294</v>
       </c>
       <c r="C2" t="n">
-        <v>33.95076581596514</v>
+        <v>33.81279436814992</v>
       </c>
       <c r="D2" t="n">
-        <v>26.54832235505304</v>
+        <v>50.59709216449473</v>
       </c>
       <c r="E2" t="n">
-        <v>47.49146833489332</v>
+        <v>33.22613131208878</v>
       </c>
       <c r="F2" t="n">
-        <v>55.83284170981976</v>
+        <v>44.64153409367033</v>
       </c>
       <c r="G2" t="n">
-        <v>35.47869685952538</v>
+        <v>31.42292620036391</v>
       </c>
       <c r="H2" t="n">
-        <v>29.54254452006072</v>
+        <v>41.87133890691444</v>
       </c>
       <c r="I2" t="n">
-        <v>34.82866847107902</v>
+        <v>44.44750240081876</v>
       </c>
       <c r="J2" t="n">
-        <v>29.89578063767309</v>
+        <v>37.78017845525903</v>
       </c>
     </row>
   </sheetData>
@@ -19782,31 +19782,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.92468376145692</v>
+        <v>26.21151140243977</v>
       </c>
       <c r="C2" t="n">
-        <v>40.6102421434146</v>
+        <v>30.29547297579052</v>
       </c>
       <c r="D2" t="n">
-        <v>46.38952836721121</v>
+        <v>37.88718292405875</v>
       </c>
       <c r="E2" t="n">
-        <v>32.71326868424059</v>
+        <v>34.21324981817822</v>
       </c>
       <c r="F2" t="n">
-        <v>36.89426994616257</v>
+        <v>34.69875578666876</v>
       </c>
       <c r="G2" t="n">
-        <v>30.65249078291799</v>
+        <v>32.1897067762531</v>
       </c>
       <c r="H2" t="n">
-        <v>36.09632352598876</v>
+        <v>38.7581948999607</v>
       </c>
       <c r="I2" t="n">
-        <v>41.61701381406442</v>
+        <v>36.81040928948204</v>
       </c>
       <c r="J2" t="n">
-        <v>24.81478223881939</v>
+        <v>57.43868188591547</v>
       </c>
     </row>
   </sheetData>
@@ -19880,31 +19880,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.14921045485179</v>
+        <v>34.19809047330111</v>
       </c>
       <c r="C2" t="n">
-        <v>45.35507614799225</v>
+        <v>47.59986948453645</v>
       </c>
       <c r="D2" t="n">
-        <v>27.39927941567651</v>
+        <v>43.49786567396309</v>
       </c>
       <c r="E2" t="n">
-        <v>47.34046606683754</v>
+        <v>37.79138945322824</v>
       </c>
       <c r="F2" t="n">
-        <v>33.16347976069062</v>
+        <v>33.99438594847332</v>
       </c>
       <c r="G2" t="n">
-        <v>34.82549908925002</v>
+        <v>35.12074559383224</v>
       </c>
       <c r="H2" t="n">
-        <v>30.93202086158628</v>
+        <v>35.01528387933192</v>
       </c>
       <c r="I2" t="n">
-        <v>35.40290403733443</v>
+        <v>39.36548848240278</v>
       </c>
       <c r="J2" t="n">
-        <v>23.33321468273839</v>
+        <v>47.79545732133307</v>
       </c>
     </row>
   </sheetData>
@@ -19978,31 +19978,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.07689343692514</v>
+        <v>28.92204091328061</v>
       </c>
       <c r="C2" t="n">
-        <v>54.02641944733023</v>
+        <v>37.60315550008447</v>
       </c>
       <c r="D2" t="n">
-        <v>41.47243505632671</v>
+        <v>34.15278457712056</v>
       </c>
       <c r="E2" t="n">
-        <v>37.67242053432978</v>
+        <v>33.47875081981989</v>
       </c>
       <c r="F2" t="n">
-        <v>34.08697450149584</v>
+        <v>43.50452245674105</v>
       </c>
       <c r="G2" t="n">
-        <v>29.4662230898749</v>
+        <v>38.0478255507736</v>
       </c>
       <c r="H2" t="n">
-        <v>31.2140040571384</v>
+        <v>36.42623640832333</v>
       </c>
       <c r="I2" t="n">
-        <v>23.77244395574985</v>
+        <v>45.31157372995483</v>
       </c>
       <c r="J2" t="n">
-        <v>53.47760102552164</v>
+        <v>45.85013917729479</v>
       </c>
     </row>
   </sheetData>
@@ -20076,31 +20076,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.18803092701329</v>
+        <v>37.20245733829628</v>
       </c>
       <c r="C2" t="n">
-        <v>45.27806375944433</v>
+        <v>47.23226654445961</v>
       </c>
       <c r="D2" t="n">
-        <v>27.61280732446609</v>
+        <v>55.11321597255743</v>
       </c>
       <c r="E2" t="n">
-        <v>49.03264781658633</v>
+        <v>27.57730817691092</v>
       </c>
       <c r="F2" t="n">
-        <v>43.15360603303686</v>
+        <v>33.25562634175053</v>
       </c>
       <c r="G2" t="n">
-        <v>36.44633415650246</v>
+        <v>49.98254519688508</v>
       </c>
       <c r="H2" t="n">
-        <v>50.28735349186856</v>
+        <v>43.60696647364723</v>
       </c>
       <c r="I2" t="n">
-        <v>39.36980534289118</v>
+        <v>39.86346228899683</v>
       </c>
       <c r="J2" t="n">
-        <v>36.89580057727926</v>
+        <v>59.65413094908577</v>
       </c>
     </row>
   </sheetData>
@@ -20174,31 +20174,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.62231621247762</v>
+        <v>40.71898025391983</v>
       </c>
       <c r="C2" t="n">
-        <v>34.09948334744492</v>
+        <v>48.01498839839373</v>
       </c>
       <c r="D2" t="n">
-        <v>30.74072102222173</v>
+        <v>37.52723534926417</v>
       </c>
       <c r="E2" t="n">
-        <v>34.70844665576629</v>
+        <v>44.30777864296009</v>
       </c>
       <c r="F2" t="n">
-        <v>36.10408852245851</v>
+        <v>41.97851341763848</v>
       </c>
       <c r="G2" t="n">
-        <v>34.69733044257235</v>
+        <v>34.44013307872686</v>
       </c>
       <c r="H2" t="n">
-        <v>39.62557323981351</v>
+        <v>50.84710432473318</v>
       </c>
       <c r="I2" t="n">
-        <v>40.11409334886709</v>
+        <v>38.05871415566288</v>
       </c>
       <c r="J2" t="n">
-        <v>40.28687925522023</v>
+        <v>30.92998073014765</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
+++ b/results/cluster_ga/UAVs9_GRID13/revenue/UAVs9_GRID13_Greedy.xlsx
@@ -672,31 +672,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.69129801235542</v>
+        <v>36.52521166489935</v>
       </c>
       <c r="C2" t="n">
-        <v>41.72556510633359</v>
+        <v>44.29201069283035</v>
       </c>
       <c r="D2" t="n">
-        <v>30.89476832700868</v>
+        <v>48.51398959690619</v>
       </c>
       <c r="E2" t="n">
-        <v>26.11306329430092</v>
+        <v>33.91637837885976</v>
       </c>
       <c r="F2" t="n">
-        <v>31.05914109135398</v>
+        <v>32.11081397054595</v>
       </c>
       <c r="G2" t="n">
-        <v>43.99024550258977</v>
+        <v>39.19773741147801</v>
       </c>
       <c r="H2" t="n">
-        <v>58.10445935612326</v>
+        <v>31.1789042269396</v>
       </c>
       <c r="I2" t="n">
-        <v>33.46674495411732</v>
+        <v>26.73702394485368</v>
       </c>
       <c r="J2" t="n">
-        <v>49.80966224685074</v>
+        <v>36.81394962314895</v>
       </c>
     </row>
   </sheetData>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.35319382345633</v>
+        <v>47.89275299812947</v>
       </c>
       <c r="C2" t="n">
-        <v>41.62324811871258</v>
+        <v>44.82490575254926</v>
       </c>
       <c r="D2" t="n">
-        <v>45.72411569920189</v>
+        <v>31.27317784101329</v>
       </c>
       <c r="E2" t="n">
-        <v>28.60179658692508</v>
+        <v>39.7276951448806</v>
       </c>
       <c r="F2" t="n">
-        <v>47.58226902434697</v>
+        <v>36.13961428130512</v>
       </c>
       <c r="G2" t="n">
-        <v>45.73172145751793</v>
+        <v>48.02655782527111</v>
       </c>
       <c r="H2" t="n">
-        <v>43.71857499395353</v>
+        <v>45.35110053825066</v>
       </c>
       <c r="I2" t="n">
-        <v>41.65382843780496</v>
+        <v>35.60523612436576</v>
       </c>
       <c r="J2" t="n">
-        <v>60.54739188628798</v>
+        <v>44.76622665257445</v>
       </c>
     </row>
   </sheetData>
@@ -868,31 +868,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.48050345642972</v>
+        <v>47.38510378848256</v>
       </c>
       <c r="C2" t="n">
-        <v>41.47990192373307</v>
+        <v>55.76451667104444</v>
       </c>
       <c r="D2" t="n">
-        <v>46.0635621214688</v>
+        <v>37.40122977760706</v>
       </c>
       <c r="E2" t="n">
-        <v>31.7468036390663</v>
+        <v>47.50238398913102</v>
       </c>
       <c r="F2" t="n">
-        <v>38.36751136909455</v>
+        <v>35.82749500452042</v>
       </c>
       <c r="G2" t="n">
-        <v>37.43876463179905</v>
+        <v>37.10385356645573</v>
       </c>
       <c r="H2" t="n">
-        <v>48.76167257886615</v>
+        <v>43.1189221662612</v>
       </c>
       <c r="I2" t="n">
-        <v>36.54156351307486</v>
+        <v>38.27798468807184</v>
       </c>
       <c r="J2" t="n">
-        <v>46.34764269789114</v>
+        <v>41.73964997391797</v>
       </c>
     </row>
   </sheetData>
@@ -966,31 +966,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.52881107506214</v>
+        <v>27.18439225377464</v>
       </c>
       <c r="C2" t="n">
-        <v>26.93408792543321</v>
+        <v>27.12712251333481</v>
       </c>
       <c r="D2" t="n">
-        <v>47.32381236780249</v>
+        <v>34.97697291899004</v>
       </c>
       <c r="E2" t="n">
-        <v>32.38823419172655</v>
+        <v>30.21145361030714</v>
       </c>
       <c r="F2" t="n">
-        <v>32.70473607303069</v>
+        <v>47.17102784049868</v>
       </c>
       <c r="G2" t="n">
-        <v>34.61454054347676</v>
+        <v>40.82849784292818</v>
       </c>
       <c r="H2" t="n">
-        <v>46.15947403785714</v>
+        <v>35.13061114772589</v>
       </c>
       <c r="I2" t="n">
-        <v>46.42411938610034</v>
+        <v>41.28198473565381</v>
       </c>
       <c r="J2" t="n">
-        <v>34.53498010129823</v>
+        <v>46.81362403794565</v>
       </c>
     </row>
   </sheetData>
@@ -1064,31 +1064,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.46100516995968</v>
+        <v>48.16935834343537</v>
       </c>
       <c r="C2" t="n">
-        <v>42.06537849224643</v>
+        <v>42.42611642523279</v>
       </c>
       <c r="D2" t="n">
-        <v>43.22468196584116</v>
+        <v>24.44881589118826</v>
       </c>
       <c r="E2" t="n">
-        <v>35.41268828680094</v>
+        <v>32.27712361445989</v>
       </c>
       <c r="F2" t="n">
-        <v>29.21757054321095</v>
+        <v>32.8801678544956</v>
       </c>
       <c r="G2" t="n">
-        <v>37.61743016924664</v>
+        <v>43.77946488486503</v>
       </c>
       <c r="H2" t="n">
-        <v>39.47662702629052</v>
+        <v>42.18070454354297</v>
       </c>
       <c r="I2" t="n">
-        <v>46.5688901665752</v>
+        <v>42.81269334276701</v>
       </c>
       <c r="J2" t="n">
-        <v>40.87212880245769</v>
+        <v>41.46844420540113</v>
       </c>
     </row>
   </sheetData>
@@ -1162,31 +1162,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.10076791220516</v>
+        <v>37.53585034970975</v>
       </c>
       <c r="C2" t="n">
-        <v>35.40868195306519</v>
+        <v>45.47149541276636</v>
       </c>
       <c r="D2" t="n">
-        <v>48.39259785541164</v>
+        <v>47.42116976770163</v>
       </c>
       <c r="E2" t="n">
-        <v>39.64407447899148</v>
+        <v>49.2813638363715</v>
       </c>
       <c r="F2" t="n">
-        <v>41.22692326139941</v>
+        <v>36.26586992830113</v>
       </c>
       <c r="G2" t="n">
-        <v>42.20625657602751</v>
+        <v>32.50021596996221</v>
       </c>
       <c r="H2" t="n">
-        <v>37.17746183381674</v>
+        <v>47.0597306789243</v>
       </c>
       <c r="I2" t="n">
-        <v>50.19794233334264</v>
+        <v>66.35111930094295</v>
       </c>
       <c r="J2" t="n">
-        <v>54.09001493132165</v>
+        <v>40.73830118157693</v>
       </c>
     </row>
   </sheetData>
@@ -1260,31 +1260,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.19995914765622</v>
+        <v>37.28309289091344</v>
       </c>
       <c r="C2" t="n">
-        <v>49.31411233857364</v>
+        <v>29.91855769198801</v>
       </c>
       <c r="D2" t="n">
-        <v>32.38021193273439</v>
+        <v>35.69366175356891</v>
       </c>
       <c r="E2" t="n">
-        <v>27.58619012779657</v>
+        <v>45.63270133640038</v>
       </c>
       <c r="F2" t="n">
-        <v>35.11034824874898</v>
+        <v>34.2833593024264</v>
       </c>
       <c r="G2" t="n">
-        <v>55.51152464792543</v>
+        <v>30.54821532243135</v>
       </c>
       <c r="H2" t="n">
-        <v>33.06055472507566</v>
+        <v>37.13145693495867</v>
       </c>
       <c r="I2" t="n">
-        <v>37.54658991751047</v>
+        <v>39.41452102748139</v>
       </c>
       <c r="J2" t="n">
-        <v>40.64884726222676</v>
+        <v>24.75182439656519</v>
       </c>
     </row>
   </sheetData>
@@ -1358,31 +1358,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.19923855882721</v>
+        <v>36.99725860801272</v>
       </c>
       <c r="C2" t="n">
-        <v>48.42339104085832</v>
+        <v>42.15272258836161</v>
       </c>
       <c r="D2" t="n">
-        <v>40.01793183492877</v>
+        <v>43.37281783625541</v>
       </c>
       <c r="E2" t="n">
-        <v>37.48677088044374</v>
+        <v>38.12946050672807</v>
       </c>
       <c r="F2" t="n">
-        <v>42.37709137076293</v>
+        <v>36.21678403448167</v>
       </c>
       <c r="G2" t="n">
-        <v>43.43188697159024</v>
+        <v>33.53849248103984</v>
       </c>
       <c r="H2" t="n">
-        <v>28.9791906253258</v>
+        <v>49.29942652661326</v>
       </c>
       <c r="I2" t="n">
-        <v>35.91241513787045</v>
+        <v>39.51271275349345</v>
       </c>
       <c r="J2" t="n">
-        <v>52.59779024731688</v>
+        <v>51.22595717127621</v>
       </c>
     </row>
   </sheetData>
@@ -1456,31 +1456,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.71516984137358</v>
+        <v>32.49604793055061</v>
       </c>
       <c r="C2" t="n">
-        <v>45.7260688948633</v>
+        <v>33.557233754614</v>
       </c>
       <c r="D2" t="n">
-        <v>45.0010238550098</v>
+        <v>49.96284976044117</v>
       </c>
       <c r="E2" t="n">
-        <v>28.63177175297437</v>
+        <v>40.05313224436389</v>
       </c>
       <c r="F2" t="n">
-        <v>40.15553856741342</v>
+        <v>31.74818549775707</v>
       </c>
       <c r="G2" t="n">
-        <v>49.4971391333893</v>
+        <v>37.3097934879866</v>
       </c>
       <c r="H2" t="n">
-        <v>35.27271873756037</v>
+        <v>40.08722158228596</v>
       </c>
       <c r="I2" t="n">
-        <v>43.78151380034631</v>
+        <v>35.19677699054563</v>
       </c>
       <c r="J2" t="n">
-        <v>38.6595292691327</v>
+        <v>46.89855293189972</v>
       </c>
     </row>
   </sheetData>
@@ -1554,31 +1554,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.03136883495579</v>
+        <v>29.58946312193718</v>
       </c>
       <c r="C2" t="n">
-        <v>42.19090883629073</v>
+        <v>44.26667005269555</v>
       </c>
       <c r="D2" t="n">
-        <v>37.40199857172991</v>
+        <v>36.54379428258619</v>
       </c>
       <c r="E2" t="n">
-        <v>27.5985491410315</v>
+        <v>26.19280507610913</v>
       </c>
       <c r="F2" t="n">
-        <v>36.21895376028461</v>
+        <v>25.10625279566293</v>
       </c>
       <c r="G2" t="n">
-        <v>28.40670828467011</v>
+        <v>43.77223712276074</v>
       </c>
       <c r="H2" t="n">
-        <v>37.20983367356916</v>
+        <v>46.30948059495691</v>
       </c>
       <c r="I2" t="n">
-        <v>59.15844491872449</v>
+        <v>28.78687607125627</v>
       </c>
       <c r="J2" t="n">
-        <v>37.68636012245775</v>
+        <v>41.67619533894562</v>
       </c>
     </row>
   </sheetData>
@@ -1652,31 +1652,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.41471829979307</v>
+        <v>33.17469895184376</v>
       </c>
       <c r="C2" t="n">
-        <v>43.92034106243117</v>
+        <v>43.37001038352215</v>
       </c>
       <c r="D2" t="n">
-        <v>59.68274878075805</v>
+        <v>38.88988269185287</v>
       </c>
       <c r="E2" t="n">
-        <v>35.45646632731006</v>
+        <v>36.03781821634313</v>
       </c>
       <c r="F2" t="n">
-        <v>51.11880086875968</v>
+        <v>53.59123049624387</v>
       </c>
       <c r="G2" t="n">
-        <v>26.36685417281074</v>
+        <v>42.48633545151083</v>
       </c>
       <c r="H2" t="n">
-        <v>43.01089255262244</v>
+        <v>34.65656955838688</v>
       </c>
       <c r="I2" t="n">
-        <v>43.61495330370686</v>
+        <v>47.60153437389215</v>
       </c>
       <c r="J2" t="n">
-        <v>41.75282033312715</v>
+        <v>57.34661503051519</v>
       </c>
     </row>
   </sheetData>
@@ -1750,31 +1750,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.8541413347068</v>
+        <v>37.34346120393371</v>
       </c>
       <c r="C2" t="n">
-        <v>42.43297368622365</v>
+        <v>43.5970903658147</v>
       </c>
       <c r="D2" t="n">
-        <v>38.5586388590326</v>
+        <v>27.57424638915954</v>
       </c>
       <c r="E2" t="n">
-        <v>38.49417147016621</v>
+        <v>36.78569110855181</v>
       </c>
       <c r="F2" t="n">
-        <v>50.28051213654314</v>
+        <v>45.54044016788706</v>
       </c>
       <c r="G2" t="n">
-        <v>43.11685309140387</v>
+        <v>41.2309211103217</v>
       </c>
       <c r="H2" t="n">
-        <v>41.35173293915548</v>
+        <v>38.99848848913575</v>
       </c>
       <c r="I2" t="n">
-        <v>44.34566150088659</v>
+        <v>42.75133239986086</v>
       </c>
       <c r="J2" t="n">
-        <v>39.58266069305766</v>
+        <v>28.70360742450761</v>
       </c>
     </row>
   </sheetData>
@@ -1848,31 +1848,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.4067367691213</v>
+        <v>36.81458160609905</v>
       </c>
       <c r="C2" t="n">
-        <v>30.92517187740832</v>
+        <v>55.78245715169634</v>
       </c>
       <c r="D2" t="n">
-        <v>35.98347426723101</v>
+        <v>32.9073041331429</v>
       </c>
       <c r="E2" t="n">
-        <v>45.941875635023</v>
+        <v>34.14529442404189</v>
       </c>
       <c r="F2" t="n">
-        <v>42.0968705691418</v>
+        <v>38.39770690448336</v>
       </c>
       <c r="G2" t="n">
-        <v>46.26393712262565</v>
+        <v>36.32941748850013</v>
       </c>
       <c r="H2" t="n">
-        <v>37.47651521260529</v>
+        <v>45.88309397873645</v>
       </c>
       <c r="I2" t="n">
-        <v>40.02580354490414</v>
+        <v>41.56426149116005</v>
       </c>
       <c r="J2" t="n">
-        <v>52.64349386148013</v>
+        <v>35.23705126928763</v>
       </c>
     </row>
   </sheetData>
@@ -1946,31 +1946,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.73691776008177</v>
+        <v>32.92585796033961</v>
       </c>
       <c r="C2" t="n">
-        <v>49.29613526005254</v>
+        <v>40.48422226215298</v>
       </c>
       <c r="D2" t="n">
-        <v>42.59737097341799</v>
+        <v>41.44463000187861</v>
       </c>
       <c r="E2" t="n">
-        <v>34.8477772560128</v>
+        <v>46.77109835110247</v>
       </c>
       <c r="F2" t="n">
-        <v>41.26999053707455</v>
+        <v>46.67526419982755</v>
       </c>
       <c r="G2" t="n">
-        <v>42.11679517522072</v>
+        <v>39.15231219214275</v>
       </c>
       <c r="H2" t="n">
-        <v>36.80758049276486</v>
+        <v>24.21280758861913</v>
       </c>
       <c r="I2" t="n">
-        <v>44.32743306478221</v>
+        <v>33.74084077918067</v>
       </c>
       <c r="J2" t="n">
-        <v>35.9504773978917</v>
+        <v>40.33473872727672</v>
       </c>
     </row>
   </sheetData>
@@ -2044,31 +2044,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.46484645393207</v>
+        <v>41.0141996808892</v>
       </c>
       <c r="C2" t="n">
-        <v>38.26929393815428</v>
+        <v>36.34601741356126</v>
       </c>
       <c r="D2" t="n">
-        <v>38.10145256656755</v>
+        <v>44.3004095072777</v>
       </c>
       <c r="E2" t="n">
-        <v>30.14462050272892</v>
+        <v>22.40131006899816</v>
       </c>
       <c r="F2" t="n">
-        <v>30.17079723184112</v>
+        <v>38.07672503057728</v>
       </c>
       <c r="G2" t="n">
-        <v>38.24952215710075</v>
+        <v>48.85297484804715</v>
       </c>
       <c r="H2" t="n">
-        <v>68.37134300852337</v>
+        <v>38.31056007588631</v>
       </c>
       <c r="I2" t="n">
-        <v>40.28851697475802</v>
+        <v>41.83944283220555</v>
       </c>
       <c r="J2" t="n">
-        <v>38.90299767779575</v>
+        <v>32.43459961616007</v>
       </c>
     </row>
   </sheetData>
@@ -2142,31 +2142,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.22677645875252</v>
+        <v>45.1808306099642</v>
       </c>
       <c r="C2" t="n">
-        <v>30.71131169621209</v>
+        <v>31.7778129286711</v>
       </c>
       <c r="D2" t="n">
-        <v>36.03560483248351</v>
+        <v>35.05122252461349</v>
       </c>
       <c r="E2" t="n">
-        <v>35.13412891289613</v>
+        <v>42.9557572343397</v>
       </c>
       <c r="F2" t="n">
-        <v>34.06307768495812</v>
+        <v>35.38296201637734</v>
       </c>
       <c r="G2" t="n">
-        <v>34.59243038399026</v>
+        <v>44.40194621944337</v>
       </c>
       <c r="H2" t="n">
-        <v>55.38063714228797</v>
+        <v>36.59869405015463</v>
       </c>
       <c r="I2" t="n">
-        <v>27.60549091882253</v>
+        <v>30.17657560715459</v>
       </c>
       <c r="J2" t="n">
-        <v>32.09477682831024</v>
+        <v>27.17149589716499</v>
       </c>
     </row>
   </sheetData>
@@ -2240,31 +2240,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.95234954461181</v>
+        <v>39.77940413036482</v>
       </c>
       <c r="C2" t="n">
-        <v>38.30724370695803</v>
+        <v>57.43425083695004</v>
       </c>
       <c r="D2" t="n">
-        <v>63.89941210882294</v>
+        <v>38.02028696198705</v>
       </c>
       <c r="E2" t="n">
-        <v>34.43181157939578</v>
+        <v>34.31675543255081</v>
       </c>
       <c r="F2" t="n">
-        <v>44.48629775112433</v>
+        <v>26.08910892333834</v>
       </c>
       <c r="G2" t="n">
-        <v>37.30763788326239</v>
+        <v>35.30416375831643</v>
       </c>
       <c r="H2" t="n">
-        <v>44.46999864898968</v>
+        <v>39.2707962596074</v>
       </c>
       <c r="I2" t="n">
-        <v>35.58648931836431</v>
+        <v>42.32596295029187</v>
       </c>
       <c r="J2" t="n">
-        <v>53.07494211616775</v>
+        <v>44.8305756154441</v>
       </c>
     </row>
   </sheetData>
@@ -2338,31 +2338,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.84378518211428</v>
+        <v>47.91990330798485</v>
       </c>
       <c r="C2" t="n">
-        <v>38.95426649803407</v>
+        <v>44.94477142388631</v>
       </c>
       <c r="D2" t="n">
-        <v>40.47361221905489</v>
+        <v>51.79086462743717</v>
       </c>
       <c r="E2" t="n">
-        <v>44.69976220306939</v>
+        <v>32.91431393791138</v>
       </c>
       <c r="F2" t="n">
-        <v>32.09118079217689</v>
+        <v>56.45043534585022</v>
       </c>
       <c r="G2" t="n">
-        <v>38.736822813354</v>
+        <v>35.86396823732704</v>
       </c>
       <c r="H2" t="n">
-        <v>39.28075812016605</v>
+        <v>57.86772548069381</v>
       </c>
       <c r="I2" t="n">
-        <v>57.40570982825643</v>
+        <v>40.40258401282314</v>
       </c>
       <c r="J2" t="n">
-        <v>40.82023351035281</v>
+        <v>42.16660046540119</v>
       </c>
     </row>
   </sheetData>
@@ -2436,31 +2436,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.8028157779817</v>
+        <v>49.36810967718113</v>
       </c>
       <c r="C2" t="n">
-        <v>26.57434195519482</v>
+        <v>32.71330925941317</v>
       </c>
       <c r="D2" t="n">
-        <v>48.74349414478029</v>
+        <v>58.1489961300346</v>
       </c>
       <c r="E2" t="n">
-        <v>34.75348486771652</v>
+        <v>32.38091081454164</v>
       </c>
       <c r="F2" t="n">
-        <v>46.12404252517982</v>
+        <v>44.14949344079674</v>
       </c>
       <c r="G2" t="n">
-        <v>44.0321085974536</v>
+        <v>33.24039297845109</v>
       </c>
       <c r="H2" t="n">
-        <v>45.54933356171681</v>
+        <v>46.92012002645332</v>
       </c>
       <c r="I2" t="n">
-        <v>45.48686913758396</v>
+        <v>54.7899527666271</v>
       </c>
       <c r="J2" t="n">
-        <v>37.00002014188239</v>
+        <v>49.8038966288629</v>
       </c>
     </row>
   </sheetData>
@@ -2534,31 +2534,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.05823662253427</v>
+        <v>39.73121106104269</v>
       </c>
       <c r="C2" t="n">
-        <v>37.22557522123852</v>
+        <v>33.10827930409502</v>
       </c>
       <c r="D2" t="n">
-        <v>33.18615523986774</v>
+        <v>45.35670248959987</v>
       </c>
       <c r="E2" t="n">
-        <v>28.6505113760099</v>
+        <v>38.25152472549465</v>
       </c>
       <c r="F2" t="n">
-        <v>39.75577412996692</v>
+        <v>34.63814069648896</v>
       </c>
       <c r="G2" t="n">
-        <v>32.59211202888294</v>
+        <v>42.38979444355562</v>
       </c>
       <c r="H2" t="n">
-        <v>38.34713419500879</v>
+        <v>39.73866701338505</v>
       </c>
       <c r="I2" t="n">
-        <v>42.8958487072687</v>
+        <v>30.20218100217585</v>
       </c>
       <c r="J2" t="n">
-        <v>47.54572146463155</v>
+        <v>42.76240143548145</v>
       </c>
     </row>
   </sheetData>
@@ -2632,31 +2632,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.54942244784043</v>
+        <v>34.22650706346279</v>
       </c>
       <c r="C2" t="n">
-        <v>51.71121630962773</v>
+        <v>32.92731557060882</v>
       </c>
       <c r="D2" t="n">
-        <v>37.6430351653844</v>
+        <v>31.04433224174639</v>
       </c>
       <c r="E2" t="n">
-        <v>32.98367987132269</v>
+        <v>39.39451857888227</v>
       </c>
       <c r="F2" t="n">
-        <v>29.07935940337013</v>
+        <v>20.75439997527323</v>
       </c>
       <c r="G2" t="n">
-        <v>31.70907810887898</v>
+        <v>38.86896073276052</v>
       </c>
       <c r="H2" t="n">
-        <v>29.2093091742228</v>
+        <v>42.24725850027743</v>
       </c>
       <c r="I2" t="n">
-        <v>35.07948680272801</v>
+        <v>40.40113298781851</v>
       </c>
       <c r="J2" t="n">
-        <v>35.62315044837526</v>
+        <v>36.24443120389561</v>
       </c>
     </row>
   </sheetData>
@@ -2730,31 +2730,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.14837380880321</v>
+        <v>32.8873888373662</v>
       </c>
       <c r="C2" t="n">
-        <v>43.2237961641931</v>
+        <v>53.03966281636698</v>
       </c>
       <c r="D2" t="n">
-        <v>46.8137995560487</v>
+        <v>47.85530351549459</v>
       </c>
       <c r="E2" t="n">
-        <v>38.35980880555366</v>
+        <v>54.62140627577962</v>
       </c>
       <c r="F2" t="n">
-        <v>43.76341552338776</v>
+        <v>37.60391563125557</v>
       </c>
       <c r="G2" t="n">
-        <v>36.501723116839</v>
+        <v>38.65142313224823</v>
       </c>
       <c r="H2" t="n">
-        <v>45.05325681768022</v>
+        <v>47.58602348560701</v>
       </c>
       <c r="I2" t="n">
-        <v>51.29600082278006</v>
+        <v>39.9580229882154</v>
       </c>
       <c r="J2" t="n">
-        <v>30.99327800601064</v>
+        <v>44.93605313199865</v>
       </c>
     </row>
   </sheetData>
@@ -2828,31 +2828,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.667240777441</v>
+        <v>34.65486640612781</v>
       </c>
       <c r="C2" t="n">
-        <v>45.18626880185687</v>
+        <v>45.3570266566629</v>
       </c>
       <c r="D2" t="n">
-        <v>55.27072677603702</v>
+        <v>43.45481598020383</v>
       </c>
       <c r="E2" t="n">
-        <v>27.38351146077256</v>
+        <v>47.50703708033195</v>
       </c>
       <c r="F2" t="n">
-        <v>32.62594596760746</v>
+        <v>32.82584139054673</v>
       </c>
       <c r="G2" t="n">
-        <v>31.37583138420469</v>
+        <v>30.54248637601245</v>
       </c>
       <c r="H2" t="n">
-        <v>27.25189012413374</v>
+        <v>29.85125457787876</v>
       </c>
       <c r="I2" t="n">
-        <v>40.46631679953585</v>
+        <v>34.68039732126646</v>
       </c>
       <c r="J2" t="n">
-        <v>42.10428683288404</v>
+        <v>40.78099810161033</v>
       </c>
     </row>
   </sheetData>
@@ -2926,31 +2926,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.62171837771139</v>
+        <v>36.06112570151595</v>
       </c>
       <c r="C2" t="n">
-        <v>33.97094305301903</v>
+        <v>43.19172108799256</v>
       </c>
       <c r="D2" t="n">
-        <v>40.38671373885034</v>
+        <v>33.34767222102259</v>
       </c>
       <c r="E2" t="n">
-        <v>27.84934758105544</v>
+        <v>40.13946615040361</v>
       </c>
       <c r="F2" t="n">
-        <v>43.23608517267669</v>
+        <v>28.04110039490461</v>
       </c>
       <c r="G2" t="n">
-        <v>34.80533447000408</v>
+        <v>29.59692575156569</v>
       </c>
       <c r="H2" t="n">
-        <v>31.88254856759419</v>
+        <v>41.82667448453682</v>
       </c>
       <c r="I2" t="n">
-        <v>64.79315566998817</v>
+        <v>39.71738740701465</v>
       </c>
       <c r="J2" t="n">
-        <v>39.57220775745108</v>
+        <v>34.76404431408994</v>
       </c>
     </row>
   </sheetData>
@@ -3024,31 +3024,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.43161501288023</v>
+        <v>29.58624361625877</v>
       </c>
       <c r="C2" t="n">
-        <v>33.8496498820063</v>
+        <v>37.82853468802035</v>
       </c>
       <c r="D2" t="n">
-        <v>53.43263946539157</v>
+        <v>52.38291642917022</v>
       </c>
       <c r="E2" t="n">
-        <v>41.54787503178428</v>
+        <v>44.19848934987697</v>
       </c>
       <c r="F2" t="n">
-        <v>43.1321253449903</v>
+        <v>34.7322941374561</v>
       </c>
       <c r="G2" t="n">
-        <v>45.60647049246208</v>
+        <v>37.64447552844464</v>
       </c>
       <c r="H2" t="n">
-        <v>36.3356455245756</v>
+        <v>35.83357106131299</v>
       </c>
       <c r="I2" t="n">
-        <v>46.65252606220243</v>
+        <v>40.25399217635849</v>
       </c>
       <c r="J2" t="n">
-        <v>46.74381902619493</v>
+        <v>33.29933079453213</v>
       </c>
     </row>
   </sheetData>
@@ -3122,31 +3122,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.93607999386793</v>
+        <v>30.77316894519041</v>
       </c>
       <c r="C2" t="n">
-        <v>24.84862113253838</v>
+        <v>39.76748059088169</v>
       </c>
       <c r="D2" t="n">
-        <v>40.66686708302818</v>
+        <v>59.54087727938318</v>
       </c>
       <c r="E2" t="n">
-        <v>28.78772650029489</v>
+        <v>35.70779628284133</v>
       </c>
       <c r="F2" t="n">
-        <v>40.96483871819225</v>
+        <v>27.84598049322405</v>
       </c>
       <c r="G2" t="n">
-        <v>49.3013071043428</v>
+        <v>51.70127355684999</v>
       </c>
       <c r="H2" t="n">
-        <v>50.07641400805874</v>
+        <v>26.80791684811247</v>
       </c>
       <c r="I2" t="n">
-        <v>39.45008044009375</v>
+        <v>30.21692229521463</v>
       </c>
       <c r="J2" t="n">
-        <v>34.75285777405747</v>
+        <v>32.64035811701739</v>
       </c>
     </row>
   </sheetData>
@@ -3220,31 +3220,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.33719210032627</v>
+        <v>37.67990124005943</v>
       </c>
       <c r="C2" t="n">
-        <v>41.69100373562902</v>
+        <v>45.0461375809858</v>
       </c>
       <c r="D2" t="n">
-        <v>36.71764533626795</v>
+        <v>39.2064766758563</v>
       </c>
       <c r="E2" t="n">
-        <v>38.79473085599896</v>
+        <v>38.23470126415409</v>
       </c>
       <c r="F2" t="n">
-        <v>42.77259704644244</v>
+        <v>39.27359034174625</v>
       </c>
       <c r="G2" t="n">
-        <v>40.48479396895411</v>
+        <v>56.23104380543061</v>
       </c>
       <c r="H2" t="n">
-        <v>46.52982807494229</v>
+        <v>32.75333318567377</v>
       </c>
       <c r="I2" t="n">
-        <v>28.60273238234328</v>
+        <v>43.04014590728123</v>
       </c>
       <c r="J2" t="n">
-        <v>59.44419421797414</v>
+        <v>32.53809918864792</v>
       </c>
     </row>
   </sheetData>
@@ -3318,31 +3318,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.78717858523296</v>
+        <v>37.61056369613514</v>
       </c>
       <c r="C2" t="n">
-        <v>43.9153657715057</v>
+        <v>42.09974299052405</v>
       </c>
       <c r="D2" t="n">
-        <v>37.3989184228806</v>
+        <v>47.99382407906715</v>
       </c>
       <c r="E2" t="n">
-        <v>35.45767391189519</v>
+        <v>47.4830243141306</v>
       </c>
       <c r="F2" t="n">
-        <v>35.63806568599209</v>
+        <v>46.94376559501155</v>
       </c>
       <c r="G2" t="n">
-        <v>34.91469437858259</v>
+        <v>36.63619552595504</v>
       </c>
       <c r="H2" t="n">
-        <v>49.91908312852672</v>
+        <v>52.86441051269594</v>
       </c>
       <c r="I2" t="n">
-        <v>48.58690251400408</v>
+        <v>34.49592491556551</v>
       </c>
       <c r="J2" t="n">
-        <v>35.95107480511042</v>
+        <v>45.29095647291958</v>
       </c>
     </row>
   </sheetData>
@@ -3416,31 +3416,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.80811018620588</v>
+        <v>49.54027179155803</v>
       </c>
       <c r="C2" t="n">
-        <v>55.70421933438183</v>
+        <v>38.57608639503631</v>
       </c>
       <c r="D2" t="n">
-        <v>48.67602762117096</v>
+        <v>29.28228286422408</v>
       </c>
       <c r="E2" t="n">
-        <v>36.79338797612766</v>
+        <v>36.67925537382829</v>
       </c>
       <c r="F2" t="n">
-        <v>42.8128720114946</v>
+        <v>31.57028556413417</v>
       </c>
       <c r="G2" t="n">
-        <v>31.26385866099676</v>
+        <v>42.99032802889607</v>
       </c>
       <c r="H2" t="n">
-        <v>45.24950605569077</v>
+        <v>36.03323194432977</v>
       </c>
       <c r="I2" t="n">
-        <v>31.54183145189589</v>
+        <v>28.50486904399126</v>
       </c>
       <c r="J2" t="n">
-        <v>37.19493196788586</v>
+        <v>48.19814846268329</v>
       </c>
     </row>
   </sheetData>
@@ -3514,31 +3514,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.49437681695932</v>
+        <v>40.85899045884698</v>
       </c>
       <c r="C2" t="n">
-        <v>41.41180861969016</v>
+        <v>49.3377267985347</v>
       </c>
       <c r="D2" t="n">
-        <v>37.54804444960037</v>
+        <v>37.77506461387399</v>
       </c>
       <c r="E2" t="n">
-        <v>28.8662096919513</v>
+        <v>40.88032380955873</v>
       </c>
       <c r="F2" t="n">
-        <v>30.20869844255792</v>
+        <v>38.12700676561972</v>
       </c>
       <c r="G2" t="n">
-        <v>43.09849267834051</v>
+        <v>44.66197869848173</v>
       </c>
       <c r="H2" t="n">
-        <v>41.78990505862818</v>
+        <v>35.67384103310928</v>
       </c>
       <c r="I2" t="n">
-        <v>37.95278024635412</v>
+        <v>38.00579365588482</v>
       </c>
       <c r="J2" t="n">
-        <v>40.47638939510023</v>
+        <v>33.19595649536525</v>
       </c>
     </row>
   </sheetData>
@@ -3612,31 +3612,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.7753772722445</v>
+        <v>49.0584601725875</v>
       </c>
       <c r="C2" t="n">
-        <v>25.56140653589319</v>
+        <v>28.90244680146024</v>
       </c>
       <c r="D2" t="n">
-        <v>36.40763771550455</v>
+        <v>38.83972556619317</v>
       </c>
       <c r="E2" t="n">
-        <v>45.8459631111736</v>
+        <v>52.71292655583019</v>
       </c>
       <c r="F2" t="n">
-        <v>36.60908414269655</v>
+        <v>60.80729116081995</v>
       </c>
       <c r="G2" t="n">
-        <v>44.59894201372272</v>
+        <v>45.47504646697902</v>
       </c>
       <c r="H2" t="n">
-        <v>53.52380688209839</v>
+        <v>37.37410751904209</v>
       </c>
       <c r="I2" t="n">
-        <v>43.59339420969123</v>
+        <v>35.39977970991644</v>
       </c>
       <c r="J2" t="n">
-        <v>33.2575504722754</v>
+        <v>32.55532512525517</v>
       </c>
     </row>
   </sheetData>
@@ -3710,31 +3710,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.04097975460691</v>
+        <v>48.81467366996101</v>
       </c>
       <c r="C2" t="n">
-        <v>45.45619873840622</v>
+        <v>41.67254294251637</v>
       </c>
       <c r="D2" t="n">
-        <v>33.0771139281985</v>
+        <v>55.21035659322128</v>
       </c>
       <c r="E2" t="n">
-        <v>38.32224106479834</v>
+        <v>31.26160287539283</v>
       </c>
       <c r="F2" t="n">
-        <v>37.9260036258578</v>
+        <v>42.36625427824666</v>
       </c>
       <c r="G2" t="n">
-        <v>44.54147443296369</v>
+        <v>34.77979553914762</v>
       </c>
       <c r="H2" t="n">
-        <v>42.54061361128965</v>
+        <v>35.25284467349755</v>
       </c>
       <c r="I2" t="n">
-        <v>41.25918402593918</v>
+        <v>30.64360554595052</v>
       </c>
       <c r="J2" t="n">
-        <v>29.50612899588394</v>
+        <v>41.35304586277254</v>
       </c>
     </row>
   </sheetData>
@@ -3808,31 +3808,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.21484541022535</v>
+        <v>40.04276935464662</v>
       </c>
       <c r="C2" t="n">
-        <v>46.19778125534253</v>
+        <v>28.66012507341495</v>
       </c>
       <c r="D2" t="n">
-        <v>61.05766351996888</v>
+        <v>38.06907135940087</v>
       </c>
       <c r="E2" t="n">
-        <v>38.65450238348752</v>
+        <v>33.75220902843026</v>
       </c>
       <c r="F2" t="n">
-        <v>35.25357096036107</v>
+        <v>32.74284733300524</v>
       </c>
       <c r="G2" t="n">
-        <v>36.61796019145353</v>
+        <v>49.25879603169069</v>
       </c>
       <c r="H2" t="n">
-        <v>39.86987885030459</v>
+        <v>49.38562108922168</v>
       </c>
       <c r="I2" t="n">
-        <v>35.41671342257799</v>
+        <v>42.35287845185336</v>
       </c>
       <c r="J2" t="n">
-        <v>37.36119314341906</v>
+        <v>33.46181702383826</v>
       </c>
     </row>
   </sheetData>
@@ -3906,31 +3906,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.80123613610603</v>
+        <v>45.15337237399221</v>
       </c>
       <c r="C2" t="n">
-        <v>38.7257142373747</v>
+        <v>35.91397065100726</v>
       </c>
       <c r="D2" t="n">
-        <v>41.02124861266001</v>
+        <v>36.79917194343741</v>
       </c>
       <c r="E2" t="n">
-        <v>27.21464353820082</v>
+        <v>47.58257229531765</v>
       </c>
       <c r="F2" t="n">
-        <v>37.42208472299806</v>
+        <v>42.64302502977323</v>
       </c>
       <c r="G2" t="n">
-        <v>36.40848817490798</v>
+        <v>43.02107445580373</v>
       </c>
       <c r="H2" t="n">
-        <v>44.76688883025918</v>
+        <v>39.44496277100652</v>
       </c>
       <c r="I2" t="n">
-        <v>51.43818253125096</v>
+        <v>32.90041941943344</v>
       </c>
       <c r="J2" t="n">
-        <v>44.11097889775676</v>
+        <v>35.09255095723466</v>
       </c>
     </row>
   </sheetData>
@@ -4004,31 +4004,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.91136937672216</v>
+        <v>52.19567122176137</v>
       </c>
       <c r="C2" t="n">
-        <v>43.11238464702846</v>
+        <v>30.3953189276787</v>
       </c>
       <c r="D2" t="n">
-        <v>34.27383716494216</v>
+        <v>38.18915286885204</v>
       </c>
       <c r="E2" t="n">
-        <v>30.20971110468276</v>
+        <v>33.28097953162693</v>
       </c>
       <c r="F2" t="n">
-        <v>53.00266546514386</v>
+        <v>37.2631366869273</v>
       </c>
       <c r="G2" t="n">
-        <v>41.40253041100949</v>
+        <v>32.6069336016377</v>
       </c>
       <c r="H2" t="n">
-        <v>36.53481392324134</v>
+        <v>42.44713597907991</v>
       </c>
       <c r="I2" t="n">
-        <v>38.45494106466679</v>
+        <v>33.35210907528635</v>
       </c>
       <c r="J2" t="n">
-        <v>52.14771570811113</v>
+        <v>43.40020758792673</v>
       </c>
     </row>
   </sheetData>
@@ -4102,31 +4102,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.50836390779991</v>
+        <v>38.24351954251371</v>
       </c>
       <c r="C2" t="n">
-        <v>43.19947175454884</v>
+        <v>42.06598736575615</v>
       </c>
       <c r="D2" t="n">
-        <v>32.02069455274974</v>
+        <v>38.37231852027821</v>
       </c>
       <c r="E2" t="n">
-        <v>41.84262922598575</v>
+        <v>42.77832752706248</v>
       </c>
       <c r="F2" t="n">
-        <v>28.71995108931697</v>
+        <v>31.24584691521707</v>
       </c>
       <c r="G2" t="n">
-        <v>36.83839640960487</v>
+        <v>40.05935763647885</v>
       </c>
       <c r="H2" t="n">
-        <v>39.93895893311682</v>
+        <v>42.07389481098151</v>
       </c>
       <c r="I2" t="n">
-        <v>54.44619695157956</v>
+        <v>39.54089750502823</v>
       </c>
       <c r="J2" t="n">
-        <v>42.10995138115279</v>
+        <v>39.46562960880118</v>
       </c>
     </row>
   </sheetData>
@@ -4200,31 +4200,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.48295746928797</v>
+        <v>38.38660287500253</v>
       </c>
       <c r="C2" t="n">
-        <v>42.99985672208966</v>
+        <v>40.24281592196308</v>
       </c>
       <c r="D2" t="n">
-        <v>49.05732625898384</v>
+        <v>59.30577604101163</v>
       </c>
       <c r="E2" t="n">
-        <v>32.60340019627131</v>
+        <v>34.86043691752766</v>
       </c>
       <c r="F2" t="n">
-        <v>40.63477329916049</v>
+        <v>42.33347974246912</v>
       </c>
       <c r="G2" t="n">
-        <v>39.12860925406809</v>
+        <v>28.00020915156998</v>
       </c>
       <c r="H2" t="n">
-        <v>48.33821266692475</v>
+        <v>36.51415754893987</v>
       </c>
       <c r="I2" t="n">
-        <v>51.65659136669579</v>
+        <v>44.05439004587931</v>
       </c>
       <c r="J2" t="n">
-        <v>39.10728388166558</v>
+        <v>55.54781544648042</v>
       </c>
     </row>
   </sheetData>
@@ -4298,31 +4298,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.85939292049749</v>
+        <v>34.60690305307732</v>
       </c>
       <c r="C2" t="n">
-        <v>38.59507819654371</v>
+        <v>40.91895749715314</v>
       </c>
       <c r="D2" t="n">
-        <v>43.37677978855267</v>
+        <v>47.08034811599209</v>
       </c>
       <c r="E2" t="n">
-        <v>31.52266648798739</v>
+        <v>41.70237109813016</v>
       </c>
       <c r="F2" t="n">
-        <v>46.51151799880513</v>
+        <v>28.69919437957464</v>
       </c>
       <c r="G2" t="n">
-        <v>37.99732752047375</v>
+        <v>56.58655243071732</v>
       </c>
       <c r="H2" t="n">
-        <v>44.59213900390329</v>
+        <v>34.50321848851173</v>
       </c>
       <c r="I2" t="n">
-        <v>50.70962536598678</v>
+        <v>37.96980457141955</v>
       </c>
       <c r="J2" t="n">
-        <v>50.63623679550923</v>
+        <v>38.49348522369628</v>
       </c>
     </row>
   </sheetData>
@@ -4396,31 +4396,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.04448666042192</v>
+        <v>37.91018244607998</v>
       </c>
       <c r="C2" t="n">
-        <v>40.08139894521247</v>
+        <v>40.82307123914055</v>
       </c>
       <c r="D2" t="n">
-        <v>32.51787872765044</v>
+        <v>31.05728864578252</v>
       </c>
       <c r="E2" t="n">
-        <v>28.79451797664942</v>
+        <v>47.40713247627497</v>
       </c>
       <c r="F2" t="n">
-        <v>49.07008897521567</v>
+        <v>36.32653469448682</v>
       </c>
       <c r="G2" t="n">
-        <v>35.17809550082776</v>
+        <v>37.17620505288879</v>
       </c>
       <c r="H2" t="n">
-        <v>41.35613383469461</v>
+        <v>29.93171884780524</v>
       </c>
       <c r="I2" t="n">
-        <v>52.96234159603147</v>
+        <v>33.02595588798684</v>
       </c>
       <c r="J2" t="n">
-        <v>35.82510586689799</v>
+        <v>46.10934256010464</v>
       </c>
     </row>
   </sheetData>
@@ -4494,31 +4494,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.85830698855668</v>
+        <v>43.36784179893902</v>
       </c>
       <c r="C2" t="n">
-        <v>23.47071460950983</v>
+        <v>34.9700699263288</v>
       </c>
       <c r="D2" t="n">
-        <v>40.91521346575011</v>
+        <v>31.36814881475146</v>
       </c>
       <c r="E2" t="n">
-        <v>32.78415072287432</v>
+        <v>38.87522681944862</v>
       </c>
       <c r="F2" t="n">
-        <v>34.35775525898011</v>
+        <v>44.52165592000309</v>
       </c>
       <c r="G2" t="n">
-        <v>29.17409765115641</v>
+        <v>46.34117507098016</v>
       </c>
       <c r="H2" t="n">
-        <v>46.28427023902551</v>
+        <v>38.55189104043752</v>
       </c>
       <c r="I2" t="n">
-        <v>44.05618099279799</v>
+        <v>43.32046042009242</v>
       </c>
       <c r="J2" t="n">
-        <v>51.44281261872213</v>
+        <v>31.34839414110012</v>
       </c>
     </row>
   </sheetData>
@@ -4592,31 +4592,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.49535479874496</v>
+        <v>28.57223367316249</v>
       </c>
       <c r="C2" t="n">
-        <v>45.76481823228914</v>
+        <v>48.55641068768205</v>
       </c>
       <c r="D2" t="n">
-        <v>30.87334387776957</v>
+        <v>38.61791133083405</v>
       </c>
       <c r="E2" t="n">
-        <v>29.30561805378533</v>
+        <v>34.29166547076932</v>
       </c>
       <c r="F2" t="n">
-        <v>46.5274963112311</v>
+        <v>28.24030499131683</v>
       </c>
       <c r="G2" t="n">
-        <v>49.38928693088891</v>
+        <v>37.21874769062776</v>
       </c>
       <c r="H2" t="n">
-        <v>30.58235220051913</v>
+        <v>42.39609520071221</v>
       </c>
       <c r="I2" t="n">
-        <v>45.64062525828559</v>
+        <v>58.70740476155937</v>
       </c>
       <c r="J2" t="n">
-        <v>32.97018352898615</v>
+        <v>33.3728215431132</v>
       </c>
     </row>
   </sheetData>
@@ -4690,31 +4690,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.83721981887997</v>
+        <v>32.96241815177006</v>
       </c>
       <c r="C2" t="n">
-        <v>33.96316731210241</v>
+        <v>41.89441354386257</v>
       </c>
       <c r="D2" t="n">
-        <v>40.2076901553263</v>
+        <v>39.72345604243056</v>
       </c>
       <c r="E2" t="n">
-        <v>31.33718866340778</v>
+        <v>48.2004293661176</v>
       </c>
       <c r="F2" t="n">
-        <v>38.12045766484317</v>
+        <v>49.27607475124383</v>
       </c>
       <c r="G2" t="n">
-        <v>43.96662998855363</v>
+        <v>29.70415877646393</v>
       </c>
       <c r="H2" t="n">
-        <v>43.80097724170994</v>
+        <v>42.91085518378381</v>
       </c>
       <c r="I2" t="n">
-        <v>43.58170959799962</v>
+        <v>41.60317673119399</v>
       </c>
       <c r="J2" t="n">
-        <v>49.73566276878405</v>
+        <v>38.79687338179126</v>
       </c>
     </row>
   </sheetData>
@@ -4788,31 +4788,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.878731409487</v>
+        <v>36.40987077903897</v>
       </c>
       <c r="C2" t="n">
-        <v>56.05926992893282</v>
+        <v>48.66914918956061</v>
       </c>
       <c r="D2" t="n">
-        <v>54.19852557319138</v>
+        <v>53.12695771964761</v>
       </c>
       <c r="E2" t="n">
-        <v>29.84814784016237</v>
+        <v>30.80568255251285</v>
       </c>
       <c r="F2" t="n">
-        <v>54.27458766931039</v>
+        <v>55.74337400147623</v>
       </c>
       <c r="G2" t="n">
-        <v>52.11805675214714</v>
+        <v>48.97601766901552</v>
       </c>
       <c r="H2" t="n">
-        <v>41.26804319843006</v>
+        <v>43.42243577745651</v>
       </c>
       <c r="I2" t="n">
-        <v>53.74844419970165</v>
+        <v>29.66823669019922</v>
       </c>
       <c r="J2" t="n">
-        <v>27.05899841620186</v>
+        <v>32.7465617789108</v>
       </c>
     </row>
   </sheetData>
@@ -4886,31 +4886,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.92485187653438</v>
+        <v>33.85292367727689</v>
       </c>
       <c r="C2" t="n">
-        <v>43.79412827692465</v>
+        <v>31.46229469467519</v>
       </c>
       <c r="D2" t="n">
-        <v>34.22460138804702</v>
+        <v>36.53082592333439</v>
       </c>
       <c r="E2" t="n">
-        <v>31.86612592823591</v>
+        <v>45.10296096718966</v>
       </c>
       <c r="F2" t="n">
-        <v>50.90553691700425</v>
+        <v>33.04362057437336</v>
       </c>
       <c r="G2" t="n">
-        <v>39.55683899821663</v>
+        <v>32.90813183367997</v>
       </c>
       <c r="H2" t="n">
-        <v>36.4449306716967</v>
+        <v>46.08342142096341</v>
       </c>
       <c r="I2" t="n">
-        <v>46.41693178499447</v>
+        <v>43.57161458339632</v>
       </c>
       <c r="J2" t="n">
-        <v>47.04410591210485</v>
+        <v>28.1485760089179</v>
       </c>
     </row>
   </sheetData>
@@ -4984,31 +4984,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.01134980558857</v>
+        <v>39.08624863054679</v>
       </c>
       <c r="C2" t="n">
-        <v>41.84309188103682</v>
+        <v>48.74950185199378</v>
       </c>
       <c r="D2" t="n">
-        <v>48.43151990194294</v>
+        <v>35.75788734574965</v>
       </c>
       <c r="E2" t="n">
-        <v>35.64693291853079</v>
+        <v>42.59863740286277</v>
       </c>
       <c r="F2" t="n">
-        <v>31.30831562638745</v>
+        <v>34.36014978443909</v>
       </c>
       <c r="G2" t="n">
-        <v>38.56257352331381</v>
+        <v>47.0185543525545</v>
       </c>
       <c r="H2" t="n">
-        <v>37.78791270017622</v>
+        <v>41.48365016978529</v>
       </c>
       <c r="I2" t="n">
-        <v>45.44171351538792</v>
+        <v>39.45706964717122</v>
       </c>
       <c r="J2" t="n">
-        <v>32.14198073773235</v>
+        <v>50.5316422908078</v>
       </c>
     </row>
   </sheetData>
@@ -5082,31 +5082,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.1491949519713</v>
+        <v>52.67073997653606</v>
       </c>
       <c r="C2" t="n">
-        <v>39.03286042842225</v>
+        <v>37.0190411655624</v>
       </c>
       <c r="D2" t="n">
-        <v>38.36851776648138</v>
+        <v>34.0203977060658</v>
       </c>
       <c r="E2" t="n">
-        <v>31.86474591222676</v>
+        <v>30.85883000659729</v>
       </c>
       <c r="F2" t="n">
-        <v>30.24936415219033</v>
+        <v>41.91945268794569</v>
       </c>
       <c r="G2" t="n">
-        <v>46.65546783549189</v>
+        <v>34.21954278140596</v>
       </c>
       <c r="H2" t="n">
-        <v>47.5252105359639</v>
+        <v>34.71384668634809</v>
       </c>
       <c r="I2" t="n">
-        <v>35.50190751414411</v>
+        <v>55.21334217043446</v>
       </c>
       <c r="J2" t="n">
-        <v>42.8375191676022</v>
+        <v>34.56206232670716</v>
       </c>
     </row>
   </sheetData>
@@ -5180,31 +5180,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.73001131593698</v>
+        <v>29.96044314697076</v>
       </c>
       <c r="C2" t="n">
-        <v>39.12507387664088</v>
+        <v>35.19250099702408</v>
       </c>
       <c r="D2" t="n">
-        <v>38.45304297280331</v>
+        <v>31.51376007916538</v>
       </c>
       <c r="E2" t="n">
-        <v>35.56346992709531</v>
+        <v>39.3549996720421</v>
       </c>
       <c r="F2" t="n">
-        <v>36.31413225822384</v>
+        <v>39.17254544516066</v>
       </c>
       <c r="G2" t="n">
-        <v>29.91530048444214</v>
+        <v>44.54934027156988</v>
       </c>
       <c r="H2" t="n">
-        <v>42.18333123127182</v>
+        <v>42.30975492973165</v>
       </c>
       <c r="I2" t="n">
-        <v>41.46616170354575</v>
+        <v>39.49158837325091</v>
       </c>
       <c r="J2" t="n">
-        <v>36.72598148754447</v>
+        <v>30.14217562989617</v>
       </c>
     </row>
   </sheetData>
@@ -5278,31 +5278,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.27350538805951</v>
+        <v>27.04050550338095</v>
       </c>
       <c r="C2" t="n">
-        <v>27.1393984705589</v>
+        <v>32.6787023246665</v>
       </c>
       <c r="D2" t="n">
-        <v>41.99827096035759</v>
+        <v>40.38755782884523</v>
       </c>
       <c r="E2" t="n">
-        <v>27.77281056353472</v>
+        <v>32.27413804394202</v>
       </c>
       <c r="F2" t="n">
-        <v>37.35644115231381</v>
+        <v>33.65082765093906</v>
       </c>
       <c r="G2" t="n">
-        <v>40.1935412240972</v>
+        <v>44.54382770299846</v>
       </c>
       <c r="H2" t="n">
-        <v>42.05722380236808</v>
+        <v>31.57047283821555</v>
       </c>
       <c r="I2" t="n">
-        <v>37.00937422358763</v>
+        <v>32.22657258876491</v>
       </c>
       <c r="J2" t="n">
-        <v>37.26126504974896</v>
+        <v>41.58329941452806</v>
       </c>
     </row>
   </sheetData>
@@ -5376,31 +5376,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.0795094727487</v>
+        <v>52.084057492208</v>
       </c>
       <c r="C2" t="n">
-        <v>53.42256238779951</v>
+        <v>37.79477730912675</v>
       </c>
       <c r="D2" t="n">
-        <v>46.67037844126257</v>
+        <v>32.17411650680243</v>
       </c>
       <c r="E2" t="n">
-        <v>32.62418817071929</v>
+        <v>33.87824434791165</v>
       </c>
       <c r="F2" t="n">
-        <v>39.42939989989358</v>
+        <v>39.06012481858855</v>
       </c>
       <c r="G2" t="n">
-        <v>35.84859686532749</v>
+        <v>44.87925068629672</v>
       </c>
       <c r="H2" t="n">
-        <v>42.58962388546112</v>
+        <v>64.84430536743443</v>
       </c>
       <c r="I2" t="n">
-        <v>43.09909886509781</v>
+        <v>38.23987895892057</v>
       </c>
       <c r="J2" t="n">
-        <v>46.2384924593809</v>
+        <v>36.01234552696493</v>
       </c>
     </row>
   </sheetData>
@@ -5474,31 +5474,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.67210076449411</v>
+        <v>31.78128994805867</v>
       </c>
       <c r="C2" t="n">
-        <v>25.04799592837143</v>
+        <v>38.10045686798313</v>
       </c>
       <c r="D2" t="n">
-        <v>53.1190465905711</v>
+        <v>45.35331655211602</v>
       </c>
       <c r="E2" t="n">
-        <v>30.20282903891719</v>
+        <v>49.00043135768285</v>
       </c>
       <c r="F2" t="n">
-        <v>40.41850516164353</v>
+        <v>29.69848910116918</v>
       </c>
       <c r="G2" t="n">
-        <v>37.56340831148523</v>
+        <v>38.88703797228444</v>
       </c>
       <c r="H2" t="n">
-        <v>41.37549298757249</v>
+        <v>38.298804599169</v>
       </c>
       <c r="I2" t="n">
-        <v>33.08911434019052</v>
+        <v>36.30111876769793</v>
       </c>
       <c r="J2" t="n">
-        <v>45.54541856499309</v>
+        <v>30.01168396904666</v>
       </c>
     </row>
   </sheetData>
@@ -5572,31 +5572,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.38911128796357</v>
+        <v>35.97622145189838</v>
       </c>
       <c r="C2" t="n">
-        <v>35.13618866808125</v>
+        <v>39.25802283211391</v>
       </c>
       <c r="D2" t="n">
-        <v>48.64489970090057</v>
+        <v>48.18196908389754</v>
       </c>
       <c r="E2" t="n">
-        <v>37.36557465248157</v>
+        <v>49.96561674984813</v>
       </c>
       <c r="F2" t="n">
-        <v>37.07925088038933</v>
+        <v>36.51230204945927</v>
       </c>
       <c r="G2" t="n">
-        <v>45.83806767215177</v>
+        <v>36.5809804214021</v>
       </c>
       <c r="H2" t="n">
-        <v>52.59652676038849</v>
+        <v>41.54825281965992</v>
       </c>
       <c r="I2" t="n">
-        <v>61.65678431317322</v>
+        <v>43.29860213279225</v>
       </c>
       <c r="J2" t="n">
-        <v>46.0940843322322</v>
+        <v>51.64152430462016</v>
       </c>
     </row>
   </sheetData>
@@ -5670,31 +5670,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.48746464167787</v>
+        <v>38.5021612749605</v>
       </c>
       <c r="C2" t="n">
-        <v>41.40925371848645</v>
+        <v>41.94440817963375</v>
       </c>
       <c r="D2" t="n">
-        <v>38.40148665710482</v>
+        <v>40.87032761862683</v>
       </c>
       <c r="E2" t="n">
-        <v>36.26730155227834</v>
+        <v>38.48362364315205</v>
       </c>
       <c r="F2" t="n">
-        <v>43.36345037890836</v>
+        <v>37.01249757347393</v>
       </c>
       <c r="G2" t="n">
-        <v>42.45808098503245</v>
+        <v>42.52209080074494</v>
       </c>
       <c r="H2" t="n">
-        <v>33.57927507920353</v>
+        <v>48.15135993867132</v>
       </c>
       <c r="I2" t="n">
-        <v>53.51102056372133</v>
+        <v>34.11699904593345</v>
       </c>
       <c r="J2" t="n">
-        <v>55.27520941862584</v>
+        <v>29.65059940906911</v>
       </c>
     </row>
   </sheetData>
@@ -5768,31 +5768,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.7032211366889</v>
+        <v>41.26115008943943</v>
       </c>
       <c r="C2" t="n">
-        <v>56.01128331415059</v>
+        <v>35.78715014943503</v>
       </c>
       <c r="D2" t="n">
-        <v>31.21602035296804</v>
+        <v>34.85223516309205</v>
       </c>
       <c r="E2" t="n">
-        <v>37.01747809404844</v>
+        <v>35.94522532669782</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25273271204517</v>
+        <v>37.02398206853163</v>
       </c>
       <c r="G2" t="n">
-        <v>41.71162766519811</v>
+        <v>52.13504615543447</v>
       </c>
       <c r="H2" t="n">
-        <v>33.55736101232346</v>
+        <v>43.07154532763485</v>
       </c>
       <c r="I2" t="n">
-        <v>48.77650165594473</v>
+        <v>41.64556903672359</v>
       </c>
       <c r="J2" t="n">
-        <v>47.3343790072167</v>
+        <v>33.75402214770998</v>
       </c>
     </row>
   </sheetData>
@@ -5866,31 +5866,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.6187952150399</v>
+        <v>39.49391988221472</v>
       </c>
       <c r="C2" t="n">
-        <v>46.00168173062237</v>
+        <v>37.18492130227676</v>
       </c>
       <c r="D2" t="n">
-        <v>38.53340939323173</v>
+        <v>24.09486164840079</v>
       </c>
       <c r="E2" t="n">
-        <v>24.26659983395137</v>
+        <v>41.77326207332896</v>
       </c>
       <c r="F2" t="n">
-        <v>41.85458887240108</v>
+        <v>44.6975941218691</v>
       </c>
       <c r="G2" t="n">
-        <v>34.03063455060407</v>
+        <v>35.48950985357092</v>
       </c>
       <c r="H2" t="n">
-        <v>35.51882491203666</v>
+        <v>45.44971585675214</v>
       </c>
       <c r="I2" t="n">
-        <v>46.76449011670181</v>
+        <v>33.43752405291347</v>
       </c>
       <c r="J2" t="n">
-        <v>25.46415049541892</v>
+        <v>35.65961935115387</v>
       </c>
     </row>
   </sheetData>
@@ -5964,31 +5964,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.60993627711669</v>
+        <v>33.26775322749695</v>
       </c>
       <c r="C2" t="n">
-        <v>41.75256288247564</v>
+        <v>28.50774264930209</v>
       </c>
       <c r="D2" t="n">
-        <v>47.69861840111147</v>
+        <v>36.72459476129068</v>
       </c>
       <c r="E2" t="n">
-        <v>32.34211694077875</v>
+        <v>37.72722440139304</v>
       </c>
       <c r="F2" t="n">
-        <v>33.42990224316042</v>
+        <v>35.97732132726313</v>
       </c>
       <c r="G2" t="n">
-        <v>20.51767894607903</v>
+        <v>40.62316971870304</v>
       </c>
       <c r="H2" t="n">
-        <v>44.3145764273787</v>
+        <v>50.66431168657405</v>
       </c>
       <c r="I2" t="n">
-        <v>56.44613826294831</v>
+        <v>35.00564815378335</v>
       </c>
       <c r="J2" t="n">
-        <v>20.78368738834571</v>
+        <v>37.4765939564435</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.05216881725627</v>
+        <v>53.79599826693502</v>
       </c>
       <c r="C2" t="n">
-        <v>30.04926667292741</v>
+        <v>35.05360793112846</v>
       </c>
       <c r="D2" t="n">
-        <v>37.72893817275848</v>
+        <v>25.01811960759657</v>
       </c>
       <c r="E2" t="n">
-        <v>35.91231214789197</v>
+        <v>48.59734688231526</v>
       </c>
       <c r="F2" t="n">
-        <v>28.01614124919016</v>
+        <v>23.73371436098344</v>
       </c>
       <c r="G2" t="n">
-        <v>28.22819744884106</v>
+        <v>43.0755881131251</v>
       </c>
       <c r="H2" t="n">
-        <v>42.9401888142816</v>
+        <v>32.44546386415085</v>
       </c>
       <c r="I2" t="n">
-        <v>34.29227923943357</v>
+        <v>43.62101275730674</v>
       </c>
       <c r="J2" t="n">
-        <v>33.48824679361343</v>
+        <v>40.51533865229033</v>
       </c>
     </row>
   </sheetData>
@@ -6160,31 +6160,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.59569602668072</v>
+        <v>33.44883154871168</v>
       </c>
       <c r="C2" t="n">
-        <v>44.85962954409549</v>
+        <v>32.55776428565654</v>
       </c>
       <c r="D2" t="n">
-        <v>23.83230780520802</v>
+        <v>30.04115309492187</v>
       </c>
       <c r="E2" t="n">
-        <v>26.13665432335064</v>
+        <v>43.22381869149422</v>
       </c>
       <c r="F2" t="n">
-        <v>34.51831419218973</v>
+        <v>43.37886095698981</v>
       </c>
       <c r="G2" t="n">
-        <v>38.909943081069</v>
+        <v>39.00145805836138</v>
       </c>
       <c r="H2" t="n">
-        <v>40.11143013186368</v>
+        <v>27.68618482968332</v>
       </c>
       <c r="I2" t="n">
-        <v>52.1522983975097</v>
+        <v>31.99693343459228</v>
       </c>
       <c r="J2" t="n">
-        <v>51.24269591869628</v>
+        <v>50.38147119988057</v>
       </c>
     </row>
   </sheetData>
@@ -6258,31 +6258,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.74496121575465</v>
+        <v>35.19495845983408</v>
       </c>
       <c r="C2" t="n">
-        <v>38.92559590569908</v>
+        <v>37.36593148642514</v>
       </c>
       <c r="D2" t="n">
-        <v>52.2196826281374</v>
+        <v>48.31742016250914</v>
       </c>
       <c r="E2" t="n">
-        <v>30.12769312774783</v>
+        <v>43.9575441198902</v>
       </c>
       <c r="F2" t="n">
-        <v>42.58339527543784</v>
+        <v>37.27821247040163</v>
       </c>
       <c r="G2" t="n">
-        <v>42.47714289356094</v>
+        <v>39.4341915970104</v>
       </c>
       <c r="H2" t="n">
-        <v>37.48720840055997</v>
+        <v>47.29226926614527</v>
       </c>
       <c r="I2" t="n">
-        <v>42.71526232337662</v>
+        <v>40.23629818915787</v>
       </c>
       <c r="J2" t="n">
-        <v>40.04039459951469</v>
+        <v>29.75147387694005</v>
       </c>
     </row>
   </sheetData>
@@ -6356,31 +6356,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.93317683345457</v>
+        <v>33.63744178966074</v>
       </c>
       <c r="C2" t="n">
-        <v>31.48072587660169</v>
+        <v>34.61637613504815</v>
       </c>
       <c r="D2" t="n">
-        <v>47.65006125263304</v>
+        <v>41.53443186999272</v>
       </c>
       <c r="E2" t="n">
-        <v>39.91007921226749</v>
+        <v>31.84878038558535</v>
       </c>
       <c r="F2" t="n">
-        <v>42.17268615824759</v>
+        <v>36.21541041496733</v>
       </c>
       <c r="G2" t="n">
-        <v>32.22563074510575</v>
+        <v>43.08938450601495</v>
       </c>
       <c r="H2" t="n">
-        <v>41.25887334332889</v>
+        <v>27.60218298600461</v>
       </c>
       <c r="I2" t="n">
-        <v>45.35064144010723</v>
+        <v>49.48909743051323</v>
       </c>
       <c r="J2" t="n">
-        <v>37.8710556810484</v>
+        <v>33.34892892387095</v>
       </c>
     </row>
   </sheetData>
@@ -6454,31 +6454,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.54174352785417</v>
+        <v>35.60621145466354</v>
       </c>
       <c r="C2" t="n">
-        <v>58.28438434475243</v>
+        <v>40.6003116941618</v>
       </c>
       <c r="D2" t="n">
-        <v>41.1322671910449</v>
+        <v>32.49087652719986</v>
       </c>
       <c r="E2" t="n">
-        <v>33.91389638427361</v>
+        <v>46.51665874623018</v>
       </c>
       <c r="F2" t="n">
-        <v>35.61189300215473</v>
+        <v>27.02678719565024</v>
       </c>
       <c r="G2" t="n">
-        <v>47.32773759280258</v>
+        <v>37.29634435999746</v>
       </c>
       <c r="H2" t="n">
-        <v>37.54744802301435</v>
+        <v>40.50343980895511</v>
       </c>
       <c r="I2" t="n">
-        <v>30.93750548452154</v>
+        <v>35.62154517966692</v>
       </c>
       <c r="J2" t="n">
-        <v>31.24708610819341</v>
+        <v>44.62160021057545</v>
       </c>
     </row>
   </sheetData>
@@ -6552,31 +6552,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.89778036776197</v>
+        <v>29.65053148991316</v>
       </c>
       <c r="C2" t="n">
-        <v>46.64381185632803</v>
+        <v>46.36926773443343</v>
       </c>
       <c r="D2" t="n">
-        <v>33.08200734909907</v>
+        <v>38.53658828318962</v>
       </c>
       <c r="E2" t="n">
-        <v>31.54149279453784</v>
+        <v>29.16753940670385</v>
       </c>
       <c r="F2" t="n">
-        <v>42.96880055390665</v>
+        <v>49.0449816025621</v>
       </c>
       <c r="G2" t="n">
-        <v>38.75068076370842</v>
+        <v>29.12229298849997</v>
       </c>
       <c r="H2" t="n">
-        <v>51.20451425989114</v>
+        <v>42.10988388721929</v>
       </c>
       <c r="I2" t="n">
-        <v>44.24319287515893</v>
+        <v>48.807961091275</v>
       </c>
       <c r="J2" t="n">
-        <v>39.47183695263826</v>
+        <v>44.63715481357192</v>
       </c>
     </row>
   </sheetData>
@@ -6650,31 +6650,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.45295021123692</v>
+        <v>36.60812528092669</v>
       </c>
       <c r="C2" t="n">
-        <v>49.23738928420465</v>
+        <v>33.80059939913095</v>
       </c>
       <c r="D2" t="n">
-        <v>49.08380209885699</v>
+        <v>38.47420999230062</v>
       </c>
       <c r="E2" t="n">
-        <v>31.42790368129342</v>
+        <v>43.67630900663915</v>
       </c>
       <c r="F2" t="n">
-        <v>30.56518736828512</v>
+        <v>29.96024872319397</v>
       </c>
       <c r="G2" t="n">
-        <v>26.77642924295497</v>
+        <v>36.31299032666193</v>
       </c>
       <c r="H2" t="n">
-        <v>48.40494057407253</v>
+        <v>32.23521926529226</v>
       </c>
       <c r="I2" t="n">
-        <v>42.33647814653461</v>
+        <v>46.14351781760165</v>
       </c>
       <c r="J2" t="n">
-        <v>50.57148461529727</v>
+        <v>41.22805366530019</v>
       </c>
     </row>
   </sheetData>
@@ -6748,31 +6748,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.15432137208386</v>
+        <v>33.52513190801446</v>
       </c>
       <c r="C2" t="n">
-        <v>37.8280999042723</v>
+        <v>37.47143110959567</v>
       </c>
       <c r="D2" t="n">
-        <v>37.40455555285877</v>
+        <v>36.09727629399636</v>
       </c>
       <c r="E2" t="n">
-        <v>34.34880045479926</v>
+        <v>47.15881373713996</v>
       </c>
       <c r="F2" t="n">
-        <v>37.88586795152371</v>
+        <v>45.01307154443534</v>
       </c>
       <c r="G2" t="n">
-        <v>35.70469025731659</v>
+        <v>50.88372388236073</v>
       </c>
       <c r="H2" t="n">
-        <v>42.37060259071025</v>
+        <v>37.0124690319302</v>
       </c>
       <c r="I2" t="n">
-        <v>35.77434268456354</v>
+        <v>36.16017534918779</v>
       </c>
       <c r="J2" t="n">
-        <v>51.37231723456615</v>
+        <v>50.79246116425981</v>
       </c>
     </row>
   </sheetData>
@@ -6846,31 +6846,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.62266975655254</v>
+        <v>41.87151599650774</v>
       </c>
       <c r="C2" t="n">
-        <v>42.89397766902082</v>
+        <v>32.54384325054366</v>
       </c>
       <c r="D2" t="n">
-        <v>35.6594700762341</v>
+        <v>32.19581199666506</v>
       </c>
       <c r="E2" t="n">
-        <v>34.11436503649102</v>
+        <v>50.81054089986038</v>
       </c>
       <c r="F2" t="n">
-        <v>38.85274646779835</v>
+        <v>31.92167724438857</v>
       </c>
       <c r="G2" t="n">
-        <v>33.15272284898351</v>
+        <v>51.1195180855425</v>
       </c>
       <c r="H2" t="n">
-        <v>38.70388910835693</v>
+        <v>32.84078790750065</v>
       </c>
       <c r="I2" t="n">
-        <v>37.59991542516732</v>
+        <v>41.33996819471668</v>
       </c>
       <c r="J2" t="n">
-        <v>56.00929083262253</v>
+        <v>32.21772260053302</v>
       </c>
     </row>
   </sheetData>
@@ -6944,31 +6944,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.4036010699164</v>
+        <v>41.81508656735561</v>
       </c>
       <c r="C2" t="n">
-        <v>61.174117074687</v>
+        <v>47.55605665045945</v>
       </c>
       <c r="D2" t="n">
-        <v>56.30448138091793</v>
+        <v>33.50637006067345</v>
       </c>
       <c r="E2" t="n">
-        <v>29.62204385521795</v>
+        <v>31.32416938105232</v>
       </c>
       <c r="F2" t="n">
-        <v>40.74159328210646</v>
+        <v>49.12758098464851</v>
       </c>
       <c r="G2" t="n">
-        <v>37.67940543779872</v>
+        <v>46.67770168968539</v>
       </c>
       <c r="H2" t="n">
-        <v>38.26610657904303</v>
+        <v>37.7938781109267</v>
       </c>
       <c r="I2" t="n">
-        <v>39.58643824979596</v>
+        <v>34.77503724404324</v>
       </c>
       <c r="J2" t="n">
-        <v>46.01984490536503</v>
+        <v>47.3766722389546</v>
       </c>
     </row>
   </sheetData>
@@ -7042,31 +7042,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.85406619470765</v>
+        <v>33.72308448460492</v>
       </c>
       <c r="C2" t="n">
-        <v>41.81137748667754</v>
+        <v>38.37608356254933</v>
       </c>
       <c r="D2" t="n">
-        <v>43.06484074640486</v>
+        <v>45.53755197649571</v>
       </c>
       <c r="E2" t="n">
-        <v>32.44774285737381</v>
+        <v>38.09070305950448</v>
       </c>
       <c r="F2" t="n">
-        <v>40.87812798443665</v>
+        <v>35.62566558155175</v>
       </c>
       <c r="G2" t="n">
-        <v>36.91485329148549</v>
+        <v>42.72237922873227</v>
       </c>
       <c r="H2" t="n">
-        <v>44.39920767852214</v>
+        <v>33.87939079969659</v>
       </c>
       <c r="I2" t="n">
-        <v>33.15052984691904</v>
+        <v>17.40890053888787</v>
       </c>
       <c r="J2" t="n">
-        <v>40.84463557012261</v>
+        <v>41.26487955653829</v>
       </c>
     </row>
   </sheetData>
@@ -7140,31 +7140,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.31138519898142</v>
+        <v>37.63041755703387</v>
       </c>
       <c r="C2" t="n">
-        <v>41.77975544337978</v>
+        <v>36.77189659686098</v>
       </c>
       <c r="D2" t="n">
-        <v>45.53582326534423</v>
+        <v>47.22805042002435</v>
       </c>
       <c r="E2" t="n">
-        <v>35.63676182524042</v>
+        <v>44.68075562726906</v>
       </c>
       <c r="F2" t="n">
-        <v>41.44514321463383</v>
+        <v>48.66091994904803</v>
       </c>
       <c r="G2" t="n">
-        <v>46.89945906036674</v>
+        <v>43.84957523368834</v>
       </c>
       <c r="H2" t="n">
-        <v>42.78304136527355</v>
+        <v>34.20607573614318</v>
       </c>
       <c r="I2" t="n">
-        <v>45.60630890792556</v>
+        <v>32.64302622025667</v>
       </c>
       <c r="J2" t="n">
-        <v>28.79851332880295</v>
+        <v>40.75398724608965</v>
       </c>
     </row>
   </sheetData>
@@ -7238,31 +7238,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.73560554311052</v>
+        <v>40.61848362211014</v>
       </c>
       <c r="C2" t="n">
-        <v>43.2618563802142</v>
+        <v>30.83396909561984</v>
       </c>
       <c r="D2" t="n">
-        <v>32.44129984503563</v>
+        <v>65.78112152183787</v>
       </c>
       <c r="E2" t="n">
-        <v>37.22312540854823</v>
+        <v>49.18327206561334</v>
       </c>
       <c r="F2" t="n">
-        <v>36.87911656066144</v>
+        <v>33.3460145730683</v>
       </c>
       <c r="G2" t="n">
-        <v>41.00096568328712</v>
+        <v>33.16130449783967</v>
       </c>
       <c r="H2" t="n">
-        <v>45.77385342056947</v>
+        <v>53.2584255683952</v>
       </c>
       <c r="I2" t="n">
-        <v>60.95914448471792</v>
+        <v>35.92800081111682</v>
       </c>
       <c r="J2" t="n">
-        <v>48.81374778599088</v>
+        <v>44.2020782077968</v>
       </c>
     </row>
   </sheetData>
@@ -7336,31 +7336,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.22260972592706</v>
+        <v>41.995137391908</v>
       </c>
       <c r="C2" t="n">
-        <v>44.48564115288806</v>
+        <v>41.39837005449763</v>
       </c>
       <c r="D2" t="n">
-        <v>42.43597888313234</v>
+        <v>35.06448551695953</v>
       </c>
       <c r="E2" t="n">
-        <v>34.29505227532075</v>
+        <v>44.69183818057253</v>
       </c>
       <c r="F2" t="n">
-        <v>42.47168675261062</v>
+        <v>36.92880163485741</v>
       </c>
       <c r="G2" t="n">
-        <v>28.25462843660228</v>
+        <v>40.61249987539933</v>
       </c>
       <c r="H2" t="n">
-        <v>39.27518201811337</v>
+        <v>33.66367973878409</v>
       </c>
       <c r="I2" t="n">
-        <v>47.61575929409493</v>
+        <v>37.13612835466352</v>
       </c>
       <c r="J2" t="n">
-        <v>61.68234613312993</v>
+        <v>60.96486123631398</v>
       </c>
     </row>
   </sheetData>
@@ -7434,31 +7434,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.7484883207772</v>
+        <v>61.89323136157762</v>
       </c>
       <c r="C2" t="n">
-        <v>41.57195911621769</v>
+        <v>34.40941905198778</v>
       </c>
       <c r="D2" t="n">
-        <v>47.65316695486101</v>
+        <v>36.32481224802321</v>
       </c>
       <c r="E2" t="n">
-        <v>44.49605907591378</v>
+        <v>41.41349061645546</v>
       </c>
       <c r="F2" t="n">
-        <v>33.30607226129098</v>
+        <v>49.16534583852624</v>
       </c>
       <c r="G2" t="n">
-        <v>45.50907302550596</v>
+        <v>37.54201618751929</v>
       </c>
       <c r="H2" t="n">
-        <v>28.74002308155081</v>
+        <v>34.96522338317166</v>
       </c>
       <c r="I2" t="n">
-        <v>61.89323136157762</v>
+        <v>42.48382832283767</v>
       </c>
       <c r="J2" t="n">
-        <v>38.16900935376687</v>
+        <v>28.31437017387575</v>
       </c>
     </row>
   </sheetData>
@@ -7532,31 +7532,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.41894767128341</v>
+        <v>43.00677480489664</v>
       </c>
       <c r="C2" t="n">
-        <v>36.60027657236033</v>
+        <v>31.87928810667843</v>
       </c>
       <c r="D2" t="n">
-        <v>35.61870072797061</v>
+        <v>24.33442200154023</v>
       </c>
       <c r="E2" t="n">
-        <v>32.76019032935437</v>
+        <v>36.42810580181817</v>
       </c>
       <c r="F2" t="n">
-        <v>36.18874503304168</v>
+        <v>31.60487383094761</v>
       </c>
       <c r="G2" t="n">
-        <v>34.46665946726061</v>
+        <v>33.27193793641139</v>
       </c>
       <c r="H2" t="n">
-        <v>38.17794209082246</v>
+        <v>45.6508035776636</v>
       </c>
       <c r="I2" t="n">
-        <v>43.97050203966985</v>
+        <v>40.61509225260119</v>
       </c>
       <c r="J2" t="n">
-        <v>32.33724718114509</v>
+        <v>53.77749427860859</v>
       </c>
     </row>
   </sheetData>
@@ -7630,31 +7630,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.83772402774586</v>
+        <v>36.12824248228113</v>
       </c>
       <c r="C2" t="n">
-        <v>30.73799947359387</v>
+        <v>44.54306071045217</v>
       </c>
       <c r="D2" t="n">
-        <v>46.164045641858</v>
+        <v>47.39311063341718</v>
       </c>
       <c r="E2" t="n">
-        <v>33.10006852132931</v>
+        <v>41.40273257935588</v>
       </c>
       <c r="F2" t="n">
-        <v>35.11508516597205</v>
+        <v>32.50507749016394</v>
       </c>
       <c r="G2" t="n">
-        <v>40.60526866537604</v>
+        <v>39.09730408027422</v>
       </c>
       <c r="H2" t="n">
-        <v>44.75390369903536</v>
+        <v>38.97966698905399</v>
       </c>
       <c r="I2" t="n">
-        <v>48.61504959145336</v>
+        <v>36.94910100206212</v>
       </c>
       <c r="J2" t="n">
-        <v>45.00815080808893</v>
+        <v>34.29889809510081</v>
       </c>
     </row>
   </sheetData>
@@ -7728,31 +7728,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.58441280909216</v>
+        <v>44.33386843129467</v>
       </c>
       <c r="C2" t="n">
-        <v>38.47438735956195</v>
+        <v>43.99713096535247</v>
       </c>
       <c r="D2" t="n">
-        <v>38.39706449439273</v>
+        <v>31.13248190100147</v>
       </c>
       <c r="E2" t="n">
-        <v>31.74537746752971</v>
+        <v>23.85195718291953</v>
       </c>
       <c r="F2" t="n">
-        <v>41.20419066874022</v>
+        <v>36.75440568289449</v>
       </c>
       <c r="G2" t="n">
-        <v>37.70177623311709</v>
+        <v>43.19381626996785</v>
       </c>
       <c r="H2" t="n">
-        <v>53.2866511732224</v>
+        <v>52.70772142365005</v>
       </c>
       <c r="I2" t="n">
-        <v>44.86150398983548</v>
+        <v>42.82985857780309</v>
       </c>
       <c r="J2" t="n">
-        <v>58.1972981529897</v>
+        <v>41.70881258851761</v>
       </c>
     </row>
   </sheetData>
@@ -7826,31 +7826,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.49535083595393</v>
+        <v>36.0149513129531</v>
       </c>
       <c r="C2" t="n">
-        <v>52.8631138037162</v>
+        <v>32.9809102210713</v>
       </c>
       <c r="D2" t="n">
-        <v>46.46578642967751</v>
+        <v>44.34890034627639</v>
       </c>
       <c r="E2" t="n">
-        <v>31.48086368717747</v>
+        <v>39.07870485904417</v>
       </c>
       <c r="F2" t="n">
-        <v>33.03775363277319</v>
+        <v>45.33558499434904</v>
       </c>
       <c r="G2" t="n">
-        <v>36.53971794938013</v>
+        <v>33.87398421184539</v>
       </c>
       <c r="H2" t="n">
-        <v>34.95182533942322</v>
+        <v>35.78079304229783</v>
       </c>
       <c r="I2" t="n">
-        <v>34.63697129574491</v>
+        <v>37.08962801981203</v>
       </c>
       <c r="J2" t="n">
-        <v>42.03770719624125</v>
+        <v>48.75349617409169</v>
       </c>
     </row>
   </sheetData>
@@ -7924,31 +7924,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.34347354377102</v>
+        <v>42.57424972084212</v>
       </c>
       <c r="C2" t="n">
-        <v>47.65028801604439</v>
+        <v>37.08409026654583</v>
       </c>
       <c r="D2" t="n">
-        <v>49.05422436890254</v>
+        <v>40.76409769024829</v>
       </c>
       <c r="E2" t="n">
-        <v>39.21818115671925</v>
+        <v>39.29261412940284</v>
       </c>
       <c r="F2" t="n">
-        <v>30.75783320133931</v>
+        <v>44.16092052328145</v>
       </c>
       <c r="G2" t="n">
-        <v>30.38181465318678</v>
+        <v>42.11349121529846</v>
       </c>
       <c r="H2" t="n">
-        <v>43.31363612758464</v>
+        <v>43.84010075070149</v>
       </c>
       <c r="I2" t="n">
-        <v>36.8281361423053</v>
+        <v>39.27592909213201</v>
       </c>
       <c r="J2" t="n">
-        <v>40.48777151167292</v>
+        <v>37.27778045546048</v>
       </c>
     </row>
   </sheetData>
@@ -8022,31 +8022,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.3407640480975</v>
+        <v>35.08923696281782</v>
       </c>
       <c r="C2" t="n">
-        <v>51.07010221896373</v>
+        <v>39.4868503338161</v>
       </c>
       <c r="D2" t="n">
-        <v>50.96993433852938</v>
+        <v>39.40697142507859</v>
       </c>
       <c r="E2" t="n">
-        <v>36.12031981925319</v>
+        <v>51.06382210189416</v>
       </c>
       <c r="F2" t="n">
-        <v>29.98837761134963</v>
+        <v>43.23715067621939</v>
       </c>
       <c r="G2" t="n">
-        <v>56.11034298020468</v>
+        <v>36.84780498010261</v>
       </c>
       <c r="H2" t="n">
-        <v>44.64544966544253</v>
+        <v>31.32632690731356</v>
       </c>
       <c r="I2" t="n">
-        <v>26.45936667602497</v>
+        <v>32.37414250191659</v>
       </c>
       <c r="J2" t="n">
-        <v>33.95637680819508</v>
+        <v>35.93462077395218</v>
       </c>
     </row>
   </sheetData>
@@ -8120,31 +8120,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.02488124423183</v>
+        <v>57.52605341650661</v>
       </c>
       <c r="C2" t="n">
-        <v>48.16365766122921</v>
+        <v>44.8489638678111</v>
       </c>
       <c r="D2" t="n">
-        <v>32.99808289869161</v>
+        <v>45.91251335306302</v>
       </c>
       <c r="E2" t="n">
-        <v>28.94206465777996</v>
+        <v>35.56492391644284</v>
       </c>
       <c r="F2" t="n">
-        <v>29.54856946700651</v>
+        <v>29.34975354111701</v>
       </c>
       <c r="G2" t="n">
-        <v>53.47974835071876</v>
+        <v>34.8639653008089</v>
       </c>
       <c r="H2" t="n">
-        <v>35.70716101813636</v>
+        <v>39.84139071935345</v>
       </c>
       <c r="I2" t="n">
-        <v>44.48930164974913</v>
+        <v>32.17104244850669</v>
       </c>
       <c r="J2" t="n">
-        <v>40.44776105224816</v>
+        <v>30.84954607864124</v>
       </c>
     </row>
   </sheetData>
@@ -8218,31 +8218,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.53519912501255</v>
+        <v>43.00882858293863</v>
       </c>
       <c r="C2" t="n">
-        <v>48.33611488146229</v>
+        <v>41.10001290254304</v>
       </c>
       <c r="D2" t="n">
-        <v>38.89674664250671</v>
+        <v>36.618531367345</v>
       </c>
       <c r="E2" t="n">
-        <v>31.77389363236348</v>
+        <v>39.17601214520384</v>
       </c>
       <c r="F2" t="n">
-        <v>44.461968780314</v>
+        <v>47.46440211243912</v>
       </c>
       <c r="G2" t="n">
-        <v>26.15080675306413</v>
+        <v>44.60110229093664</v>
       </c>
       <c r="H2" t="n">
-        <v>36.30064314680875</v>
+        <v>47.77006668187599</v>
       </c>
       <c r="I2" t="n">
-        <v>65.35067653167884</v>
+        <v>50.94178699800255</v>
       </c>
       <c r="J2" t="n">
-        <v>46.43911581660265</v>
+        <v>31.34352871520252</v>
       </c>
     </row>
   </sheetData>
@@ -8316,31 +8316,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.51612086990797</v>
+        <v>41.80374265629152</v>
       </c>
       <c r="C2" t="n">
-        <v>49.99603619524415</v>
+        <v>24.28782556426923</v>
       </c>
       <c r="D2" t="n">
-        <v>22.99221912438695</v>
+        <v>31.65244349436998</v>
       </c>
       <c r="E2" t="n">
-        <v>42.49743686320823</v>
+        <v>39.0071831084953</v>
       </c>
       <c r="F2" t="n">
-        <v>32.98460608421814</v>
+        <v>40.91340487812446</v>
       </c>
       <c r="G2" t="n">
-        <v>37.67917408780153</v>
+        <v>40.15634852512697</v>
       </c>
       <c r="H2" t="n">
-        <v>36.99027219077468</v>
+        <v>49.55751858735617</v>
       </c>
       <c r="I2" t="n">
-        <v>39.73079305378414</v>
+        <v>54.58485431300404</v>
       </c>
       <c r="J2" t="n">
-        <v>56.740532036378</v>
+        <v>37.07106146079012</v>
       </c>
     </row>
   </sheetData>
@@ -8414,31 +8414,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.92794537038954</v>
+        <v>47.44869858682088</v>
       </c>
       <c r="C2" t="n">
-        <v>38.67338555249943</v>
+        <v>27.76409150402159</v>
       </c>
       <c r="D2" t="n">
-        <v>34.69502736827733</v>
+        <v>30.16353556488102</v>
       </c>
       <c r="E2" t="n">
-        <v>39.38626157813499</v>
+        <v>39.04588537079415</v>
       </c>
       <c r="F2" t="n">
-        <v>35.0080884429814</v>
+        <v>44.04172982107529</v>
       </c>
       <c r="G2" t="n">
-        <v>35.83479542760721</v>
+        <v>40.06054449394313</v>
       </c>
       <c r="H2" t="n">
-        <v>39.49442234019099</v>
+        <v>32.7558879571435</v>
       </c>
       <c r="I2" t="n">
-        <v>38.37427496262826</v>
+        <v>38.8194955202117</v>
       </c>
       <c r="J2" t="n">
-        <v>36.11057491762245</v>
+        <v>41.91415085642628</v>
       </c>
     </row>
   </sheetData>
@@ -8512,31 +8512,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.81455877116376</v>
+        <v>41.67516934118701</v>
       </c>
       <c r="C2" t="n">
-        <v>22.92451538033249</v>
+        <v>30.86084312088987</v>
       </c>
       <c r="D2" t="n">
-        <v>35.79670130890917</v>
+        <v>40.4713483703991</v>
       </c>
       <c r="E2" t="n">
-        <v>37.42870295981471</v>
+        <v>35.69232501448839</v>
       </c>
       <c r="F2" t="n">
-        <v>31.38595013045222</v>
+        <v>22.78969032952144</v>
       </c>
       <c r="G2" t="n">
-        <v>40.30720776658394</v>
+        <v>48.71679938590636</v>
       </c>
       <c r="H2" t="n">
-        <v>37.36038953319719</v>
+        <v>50.10262987186868</v>
       </c>
       <c r="I2" t="n">
-        <v>38.87565665477977</v>
+        <v>35.82853860855451</v>
       </c>
       <c r="J2" t="n">
-        <v>40.29022108746623</v>
+        <v>29.32117103045328</v>
       </c>
     </row>
   </sheetData>
@@ -8610,31 +8610,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.13343099759375</v>
+        <v>54.65110988819421</v>
       </c>
       <c r="C2" t="n">
-        <v>42.98833924545806</v>
+        <v>27.96178955945396</v>
       </c>
       <c r="D2" t="n">
-        <v>33.33264313344097</v>
+        <v>29.69040922632443</v>
       </c>
       <c r="E2" t="n">
-        <v>19.190440464479</v>
+        <v>33.40137424376707</v>
       </c>
       <c r="F2" t="n">
-        <v>37.12311142397331</v>
+        <v>31.58891996581778</v>
       </c>
       <c r="G2" t="n">
-        <v>42.44687797056082</v>
+        <v>43.79314149541882</v>
       </c>
       <c r="H2" t="n">
-        <v>36.48588301104306</v>
+        <v>23.42050018518982</v>
       </c>
       <c r="I2" t="n">
-        <v>37.77567638837535</v>
+        <v>27.45808777526241</v>
       </c>
       <c r="J2" t="n">
-        <v>36.96454154766724</v>
+        <v>40.69353789426287</v>
       </c>
     </row>
   </sheetData>
@@ -8708,31 +8708,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.0952455715126</v>
+        <v>37.4916034352118</v>
       </c>
       <c r="C2" t="n">
-        <v>41.65244761661972</v>
+        <v>34.21229541051093</v>
       </c>
       <c r="D2" t="n">
-        <v>48.69546448912782</v>
+        <v>45.07528243225035</v>
       </c>
       <c r="E2" t="n">
-        <v>35.63116408557293</v>
+        <v>56.69883840304259</v>
       </c>
       <c r="F2" t="n">
-        <v>29.46724982464909</v>
+        <v>30.29234046302488</v>
       </c>
       <c r="G2" t="n">
-        <v>26.15350771193466</v>
+        <v>43.47133327935528</v>
       </c>
       <c r="H2" t="n">
-        <v>48.35845816397156</v>
+        <v>41.55155817941036</v>
       </c>
       <c r="I2" t="n">
-        <v>35.02939183421395</v>
+        <v>29.17274202003404</v>
       </c>
       <c r="J2" t="n">
-        <v>46.23209430308491</v>
+        <v>35.51881121045857</v>
       </c>
     </row>
   </sheetData>
@@ -8806,31 +8806,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.08650110790089</v>
+        <v>38.28154566228886</v>
       </c>
       <c r="C2" t="n">
-        <v>54.77146202055039</v>
+        <v>58.13847768047802</v>
       </c>
       <c r="D2" t="n">
-        <v>38.25718192916144</v>
+        <v>47.3473108783005</v>
       </c>
       <c r="E2" t="n">
-        <v>47.3719313252032</v>
+        <v>42.85227023488563</v>
       </c>
       <c r="F2" t="n">
-        <v>41.59799650304888</v>
+        <v>27.25895603543245</v>
       </c>
       <c r="G2" t="n">
-        <v>39.15282499866093</v>
+        <v>45.25396031528616</v>
       </c>
       <c r="H2" t="n">
-        <v>43.39736250725615</v>
+        <v>50.21156586127227</v>
       </c>
       <c r="I2" t="n">
-        <v>50.70539582585416</v>
+        <v>55.07368078181592</v>
       </c>
       <c r="J2" t="n">
-        <v>43.15103372139293</v>
+        <v>37.2384366006305</v>
       </c>
     </row>
   </sheetData>
@@ -8904,31 +8904,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.66658710780847</v>
+        <v>36.57816217010694</v>
       </c>
       <c r="C2" t="n">
-        <v>36.44603520020548</v>
+        <v>25.82679626127885</v>
       </c>
       <c r="D2" t="n">
-        <v>31.22626132077709</v>
+        <v>36.580449949084</v>
       </c>
       <c r="E2" t="n">
-        <v>64.93914559784375</v>
+        <v>53.18718573416071</v>
       </c>
       <c r="F2" t="n">
-        <v>47.8890171930046</v>
+        <v>36.52206946186672</v>
       </c>
       <c r="G2" t="n">
-        <v>36.80245593151528</v>
+        <v>40.86964451951201</v>
       </c>
       <c r="H2" t="n">
-        <v>25.82679626127884</v>
+        <v>44.19323859420904</v>
       </c>
       <c r="I2" t="n">
-        <v>35.3083571597705</v>
+        <v>35.26170428917253</v>
       </c>
       <c r="J2" t="n">
-        <v>40.69641018960023</v>
+        <v>40.49739200017478</v>
       </c>
     </row>
   </sheetData>
@@ -9002,31 +9002,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.75126010562716</v>
+        <v>39.63233863120411</v>
       </c>
       <c r="C2" t="n">
-        <v>38.30163025086148</v>
+        <v>35.78343364109734</v>
       </c>
       <c r="D2" t="n">
-        <v>51.99834494531</v>
+        <v>39.89382126301911</v>
       </c>
       <c r="E2" t="n">
-        <v>24.51924912685853</v>
+        <v>27.40703485059523</v>
       </c>
       <c r="F2" t="n">
-        <v>37.02814173673011</v>
+        <v>33.01367315105087</v>
       </c>
       <c r="G2" t="n">
-        <v>45.84986597722957</v>
+        <v>38.35664791685132</v>
       </c>
       <c r="H2" t="n">
-        <v>40.96697132066213</v>
+        <v>45.61380647965201</v>
       </c>
       <c r="I2" t="n">
-        <v>49.47952952269954</v>
+        <v>46.21124101997445</v>
       </c>
       <c r="J2" t="n">
-        <v>43.11388478270717</v>
+        <v>46.85740009437617</v>
       </c>
     </row>
   </sheetData>
@@ -9100,31 +9100,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.25885264215</v>
+        <v>40.7002603559875</v>
       </c>
       <c r="C2" t="n">
-        <v>44.31688101529563</v>
+        <v>50.98800085263638</v>
       </c>
       <c r="D2" t="n">
-        <v>47.47218429448117</v>
+        <v>30.17616146736847</v>
       </c>
       <c r="E2" t="n">
-        <v>30.90768224651791</v>
+        <v>46.66758689963434</v>
       </c>
       <c r="F2" t="n">
-        <v>38.38958432631708</v>
+        <v>30.67887874846573</v>
       </c>
       <c r="G2" t="n">
-        <v>27.36843012509327</v>
+        <v>37.08826516064445</v>
       </c>
       <c r="H2" t="n">
-        <v>31.53501415218712</v>
+        <v>33.73106500514933</v>
       </c>
       <c r="I2" t="n">
-        <v>37.88016337089846</v>
+        <v>34.80563921596348</v>
       </c>
       <c r="J2" t="n">
-        <v>44.9917808938869</v>
+        <v>43.03834975618384</v>
       </c>
     </row>
   </sheetData>
@@ -9198,31 +9198,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.35041697006638</v>
+        <v>42.3084328144536</v>
       </c>
       <c r="C2" t="n">
-        <v>45.10353201291951</v>
+        <v>32.38456957450493</v>
       </c>
       <c r="D2" t="n">
-        <v>44.39896464399638</v>
+        <v>37.67771687508497</v>
       </c>
       <c r="E2" t="n">
-        <v>28.06171146450519</v>
+        <v>35.52656184626599</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25686267624836</v>
+        <v>40.4761054018845</v>
       </c>
       <c r="G2" t="n">
-        <v>46.75483341690743</v>
+        <v>53.91460867213576</v>
       </c>
       <c r="H2" t="n">
-        <v>41.59427419335068</v>
+        <v>41.56278357451254</v>
       </c>
       <c r="I2" t="n">
-        <v>46.51707038396744</v>
+        <v>38.74282255108414</v>
       </c>
       <c r="J2" t="n">
-        <v>43.78495495760458</v>
+        <v>51.24277278415747</v>
       </c>
     </row>
   </sheetData>
@@ -9296,31 +9296,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>22.08572474366878</v>
+        <v>37.83094884275737</v>
       </c>
       <c r="C2" t="n">
-        <v>41.64576705345534</v>
+        <v>34.35726177688012</v>
       </c>
       <c r="D2" t="n">
-        <v>38.07586636773674</v>
+        <v>37.53937060463347</v>
       </c>
       <c r="E2" t="n">
-        <v>34.911706458556</v>
+        <v>38.79841543845679</v>
       </c>
       <c r="F2" t="n">
-        <v>32.71728810538725</v>
+        <v>30.60287718212586</v>
       </c>
       <c r="G2" t="n">
-        <v>34.97169220040217</v>
+        <v>35.53021649731424</v>
       </c>
       <c r="H2" t="n">
-        <v>34.90775243158386</v>
+        <v>36.28975047500138</v>
       </c>
       <c r="I2" t="n">
-        <v>43.67566414629911</v>
+        <v>23.59188635706183</v>
       </c>
       <c r="J2" t="n">
-        <v>38.38408120387702</v>
+        <v>46.10837018612458</v>
       </c>
     </row>
   </sheetData>
@@ -9394,31 +9394,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.54123085478627</v>
+        <v>44.97855819883259</v>
       </c>
       <c r="C2" t="n">
-        <v>39.91172614031008</v>
+        <v>43.12395312764275</v>
       </c>
       <c r="D2" t="n">
-        <v>25.56663373565013</v>
+        <v>29.32091717084971</v>
       </c>
       <c r="E2" t="n">
-        <v>29.15635642924451</v>
+        <v>45.5374731649258</v>
       </c>
       <c r="F2" t="n">
-        <v>42.17991042914127</v>
+        <v>28.17428686423893</v>
       </c>
       <c r="G2" t="n">
-        <v>37.24405122468724</v>
+        <v>35.57242446798002</v>
       </c>
       <c r="H2" t="n">
-        <v>45.92587548281202</v>
+        <v>41.71626364270808</v>
       </c>
       <c r="I2" t="n">
-        <v>45.99372957654304</v>
+        <v>28.22268350268859</v>
       </c>
       <c r="J2" t="n">
-        <v>39.52029844927709</v>
+        <v>39.98904668309388</v>
       </c>
     </row>
   </sheetData>
@@ -9492,31 +9492,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.4373867666866</v>
+        <v>33.3464003622932</v>
       </c>
       <c r="C2" t="n">
-        <v>54.92463586339689</v>
+        <v>46.17585642607895</v>
       </c>
       <c r="D2" t="n">
-        <v>64.32515189209423</v>
+        <v>54.82288292106077</v>
       </c>
       <c r="E2" t="n">
-        <v>40.96209680041591</v>
+        <v>47.82078332102965</v>
       </c>
       <c r="F2" t="n">
-        <v>38.38411841553605</v>
+        <v>35.50696928928535</v>
       </c>
       <c r="G2" t="n">
-        <v>31.92130172417154</v>
+        <v>33.58302565916026</v>
       </c>
       <c r="H2" t="n">
-        <v>35.99448762051751</v>
+        <v>44.78976309770527</v>
       </c>
       <c r="I2" t="n">
-        <v>46.01468277847735</v>
+        <v>42.22514441849376</v>
       </c>
       <c r="J2" t="n">
-        <v>31.48998768956766</v>
+        <v>38.21358190586759</v>
       </c>
     </row>
   </sheetData>
@@ -9590,31 +9590,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.72482875975701</v>
+        <v>25.01562100791996</v>
       </c>
       <c r="C2" t="n">
-        <v>28.98671270441668</v>
+        <v>37.67651462870096</v>
       </c>
       <c r="D2" t="n">
-        <v>30.59006040445936</v>
+        <v>31.99508622651031</v>
       </c>
       <c r="E2" t="n">
-        <v>45.83148262704837</v>
+        <v>37.297765103015</v>
       </c>
       <c r="F2" t="n">
-        <v>32.06683307365419</v>
+        <v>37.61160657692486</v>
       </c>
       <c r="G2" t="n">
-        <v>25.99398230166549</v>
+        <v>47.00787081930871</v>
       </c>
       <c r="H2" t="n">
-        <v>40.55810203296313</v>
+        <v>40.02676648246612</v>
       </c>
       <c r="I2" t="n">
-        <v>37.84994311320799</v>
+        <v>38.00977125554838</v>
       </c>
       <c r="J2" t="n">
-        <v>37.25267798821143</v>
+        <v>34.56251195481092</v>
       </c>
     </row>
   </sheetData>
@@ -9688,31 +9688,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.63331246042956</v>
+        <v>33.51338009877008</v>
       </c>
       <c r="C2" t="n">
-        <v>49.79475487327638</v>
+        <v>35.64025747457254</v>
       </c>
       <c r="D2" t="n">
-        <v>40.99479608694661</v>
+        <v>46.44413764607098</v>
       </c>
       <c r="E2" t="n">
-        <v>45.23546204809858</v>
+        <v>30.45715175431413</v>
       </c>
       <c r="F2" t="n">
-        <v>48.91168124592528</v>
+        <v>45.47537386455401</v>
       </c>
       <c r="G2" t="n">
-        <v>32.58022466274244</v>
+        <v>43.71794678694642</v>
       </c>
       <c r="H2" t="n">
-        <v>29.8945144078654</v>
+        <v>36.81514251870886</v>
       </c>
       <c r="I2" t="n">
-        <v>33.42035517561729</v>
+        <v>29.02455171662589</v>
       </c>
       <c r="J2" t="n">
-        <v>28.61614148376232</v>
+        <v>43.27824998600693</v>
       </c>
     </row>
   </sheetData>
@@ -9786,31 +9786,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.88826988584783</v>
+        <v>40.34377626818537</v>
       </c>
       <c r="C2" t="n">
-        <v>34.35505780899832</v>
+        <v>46.98206998785693</v>
       </c>
       <c r="D2" t="n">
-        <v>31.6060259541558</v>
+        <v>25.93954838728524</v>
       </c>
       <c r="E2" t="n">
-        <v>33.25431443789868</v>
+        <v>42.4577340321155</v>
       </c>
       <c r="F2" t="n">
-        <v>36.7801756053632</v>
+        <v>35.31933826361577</v>
       </c>
       <c r="G2" t="n">
-        <v>38.14615078237259</v>
+        <v>40.47448711801397</v>
       </c>
       <c r="H2" t="n">
-        <v>54.0162004094977</v>
+        <v>43.68104142979795</v>
       </c>
       <c r="I2" t="n">
-        <v>35.88254830574998</v>
+        <v>34.13881333089289</v>
       </c>
       <c r="J2" t="n">
-        <v>37.53933802084379</v>
+        <v>35.78460857292794</v>
       </c>
     </row>
   </sheetData>
@@ -9884,31 +9884,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>47.5419474820787</v>
+        <v>32.05582868319853</v>
       </c>
       <c r="C2" t="n">
-        <v>31.44848308415364</v>
+        <v>41.60667511535291</v>
       </c>
       <c r="D2" t="n">
-        <v>41.46713990203323</v>
+        <v>48.54385723327637</v>
       </c>
       <c r="E2" t="n">
-        <v>35.92099422474178</v>
+        <v>42.13645721037197</v>
       </c>
       <c r="F2" t="n">
-        <v>29.63977438911681</v>
+        <v>46.86667335257143</v>
       </c>
       <c r="G2" t="n">
-        <v>40.72287721281418</v>
+        <v>33.30639202322062</v>
       </c>
       <c r="H2" t="n">
-        <v>26.33238096394221</v>
+        <v>37.10214647563888</v>
       </c>
       <c r="I2" t="n">
-        <v>46.23323016544079</v>
+        <v>37.74742453902459</v>
       </c>
       <c r="J2" t="n">
-        <v>45.41141141083523</v>
+        <v>29.2612374219729</v>
       </c>
     </row>
   </sheetData>
@@ -9982,31 +9982,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.12456182833483</v>
+        <v>40.65723617200121</v>
       </c>
       <c r="C2" t="n">
-        <v>36.85285755148495</v>
+        <v>38.53465964102694</v>
       </c>
       <c r="D2" t="n">
-        <v>37.93725200964871</v>
+        <v>32.43696324318712</v>
       </c>
       <c r="E2" t="n">
-        <v>29.66612784925144</v>
+        <v>47.41991252912437</v>
       </c>
       <c r="F2" t="n">
-        <v>35.67078498585364</v>
+        <v>35.10081828931484</v>
       </c>
       <c r="G2" t="n">
-        <v>33.58058670313217</v>
+        <v>32.30040655807805</v>
       </c>
       <c r="H2" t="n">
-        <v>34.03438850136492</v>
+        <v>34.29668776909725</v>
       </c>
       <c r="I2" t="n">
-        <v>38.67820522418337</v>
+        <v>37.12880755682989</v>
       </c>
       <c r="J2" t="n">
-        <v>40.63416606345331</v>
+        <v>49.77888804345385</v>
       </c>
     </row>
   </sheetData>
@@ -10080,31 +10080,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.74077700487566</v>
+        <v>29.98065496329334</v>
       </c>
       <c r="C2" t="n">
-        <v>50.05589098951727</v>
+        <v>29.47957487103275</v>
       </c>
       <c r="D2" t="n">
-        <v>46.01614779105635</v>
+        <v>40.08786596287825</v>
       </c>
       <c r="E2" t="n">
-        <v>33.98531710914836</v>
+        <v>34.67537684403851</v>
       </c>
       <c r="F2" t="n">
-        <v>42.70369611319779</v>
+        <v>42.80217846184662</v>
       </c>
       <c r="G2" t="n">
-        <v>52.55131876147743</v>
+        <v>40.75923342751411</v>
       </c>
       <c r="H2" t="n">
-        <v>33.44847339649719</v>
+        <v>54.22919165240058</v>
       </c>
       <c r="I2" t="n">
-        <v>38.07189763978016</v>
+        <v>35.31299929978861</v>
       </c>
       <c r="J2" t="n">
-        <v>43.49603211550068</v>
+        <v>57.85171862081759</v>
       </c>
     </row>
   </sheetData>
@@ -10178,31 +10178,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.47123770408634</v>
+        <v>44.10222961037762</v>
       </c>
       <c r="C2" t="n">
-        <v>35.84905801044288</v>
+        <v>29.4988726112582</v>
       </c>
       <c r="D2" t="n">
-        <v>42.939018210725</v>
+        <v>37.21288919207529</v>
       </c>
       <c r="E2" t="n">
-        <v>30.14303461531438</v>
+        <v>41.76179079814078</v>
       </c>
       <c r="F2" t="n">
-        <v>35.81917826445756</v>
+        <v>38.84902664498566</v>
       </c>
       <c r="G2" t="n">
-        <v>46.68088738711363</v>
+        <v>37.72770973554782</v>
       </c>
       <c r="H2" t="n">
-        <v>37.71354631694783</v>
+        <v>41.01471303707437</v>
       </c>
       <c r="I2" t="n">
-        <v>37.24433761270111</v>
+        <v>30.69862313346951</v>
       </c>
       <c r="J2" t="n">
-        <v>56.59918596930849</v>
+        <v>40.56402030189068</v>
       </c>
     </row>
   </sheetData>
@@ -10276,31 +10276,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.56610572054766</v>
+        <v>34.45191460736952</v>
       </c>
       <c r="C2" t="n">
-        <v>32.48883894912959</v>
+        <v>42.2937062145153</v>
       </c>
       <c r="D2" t="n">
-        <v>38.30020868031664</v>
+        <v>43.49932706454132</v>
       </c>
       <c r="E2" t="n">
-        <v>29.37974863020761</v>
+        <v>49.10902888540397</v>
       </c>
       <c r="F2" t="n">
-        <v>36.16052540679778</v>
+        <v>30.10125762562824</v>
       </c>
       <c r="G2" t="n">
-        <v>35.52036047342052</v>
+        <v>39.63524749355196</v>
       </c>
       <c r="H2" t="n">
-        <v>50.57224685347197</v>
+        <v>35.06380942905427</v>
       </c>
       <c r="I2" t="n">
-        <v>37.51737829967092</v>
+        <v>31.68496907097056</v>
       </c>
       <c r="J2" t="n">
-        <v>49.45487164799093</v>
+        <v>43.71528884613718</v>
       </c>
     </row>
   </sheetData>
@@ -10374,31 +10374,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.11709026800217</v>
+        <v>41.65173909076881</v>
       </c>
       <c r="C2" t="n">
-        <v>43.69531684361355</v>
+        <v>26.55125257344698</v>
       </c>
       <c r="D2" t="n">
-        <v>36.72029701656959</v>
+        <v>34.35165042501939</v>
       </c>
       <c r="E2" t="n">
-        <v>28.76538076085821</v>
+        <v>43.41493900882654</v>
       </c>
       <c r="F2" t="n">
-        <v>34.98178731073273</v>
+        <v>55.46592407584106</v>
       </c>
       <c r="G2" t="n">
-        <v>37.01972346562368</v>
+        <v>46.69569913837075</v>
       </c>
       <c r="H2" t="n">
-        <v>41.55763367426365</v>
+        <v>53.83628895514443</v>
       </c>
       <c r="I2" t="n">
-        <v>29.29869321136971</v>
+        <v>35.26062040025452</v>
       </c>
       <c r="J2" t="n">
-        <v>40.19558555746423</v>
+        <v>28.09111018038872</v>
       </c>
     </row>
   </sheetData>
@@ -10472,31 +10472,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.54355732875267</v>
+        <v>42.84376823611084</v>
       </c>
       <c r="C2" t="n">
-        <v>48.7562946987666</v>
+        <v>31.32210291438665</v>
       </c>
       <c r="D2" t="n">
-        <v>35.90685841207765</v>
+        <v>35.8441146016688</v>
       </c>
       <c r="E2" t="n">
-        <v>27.63942001084954</v>
+        <v>27.35145602993793</v>
       </c>
       <c r="F2" t="n">
-        <v>35.93728042442933</v>
+        <v>36.5978966862539</v>
       </c>
       <c r="G2" t="n">
-        <v>37.54109667493673</v>
+        <v>39.20272053450456</v>
       </c>
       <c r="H2" t="n">
-        <v>33.9254192369546</v>
+        <v>40.40388640923239</v>
       </c>
       <c r="I2" t="n">
-        <v>43.7384390823283</v>
+        <v>29.54744253480021</v>
       </c>
       <c r="J2" t="n">
-        <v>54.78262327323097</v>
+        <v>30.42638829015578</v>
       </c>
     </row>
   </sheetData>
@@ -10570,31 +10570,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.33738125721516</v>
+        <v>48.46006287034399</v>
       </c>
       <c r="C2" t="n">
-        <v>27.66141611843057</v>
+        <v>49.56140966531857</v>
       </c>
       <c r="D2" t="n">
-        <v>48.18799305734927</v>
+        <v>31.83630517209162</v>
       </c>
       <c r="E2" t="n">
-        <v>46.36581538488582</v>
+        <v>44.68997949836759</v>
       </c>
       <c r="F2" t="n">
-        <v>40.82449333090664</v>
+        <v>27.82980259855044</v>
       </c>
       <c r="G2" t="n">
-        <v>37.49840784024178</v>
+        <v>31.91774065065404</v>
       </c>
       <c r="H2" t="n">
-        <v>40.80919819431578</v>
+        <v>39.28671367689569</v>
       </c>
       <c r="I2" t="n">
-        <v>35.56268938671899</v>
+        <v>55.41297564448912</v>
       </c>
       <c r="J2" t="n">
-        <v>51.94935250389901</v>
+        <v>37.24262796508031</v>
       </c>
     </row>
   </sheetData>
@@ -10668,31 +10668,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.73654867761504</v>
+        <v>48.48972035258528</v>
       </c>
       <c r="C2" t="n">
-        <v>49.81750198854631</v>
+        <v>44.84675242301416</v>
       </c>
       <c r="D2" t="n">
-        <v>47.04146047493789</v>
+        <v>44.74678061341593</v>
       </c>
       <c r="E2" t="n">
-        <v>35.19990246745022</v>
+        <v>39.95348546953642</v>
       </c>
       <c r="F2" t="n">
-        <v>40.47985366555904</v>
+        <v>37.25004197577553</v>
       </c>
       <c r="G2" t="n">
-        <v>40.98141457074963</v>
+        <v>36.16970623928565</v>
       </c>
       <c r="H2" t="n">
-        <v>35.70249352158983</v>
+        <v>59.85130894696212</v>
       </c>
       <c r="I2" t="n">
-        <v>50.7811763060439</v>
+        <v>40.7729822710974</v>
       </c>
       <c r="J2" t="n">
-        <v>42.48307223489603</v>
+        <v>43.95269544079307</v>
       </c>
     </row>
   </sheetData>
@@ -10766,31 +10766,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.92351354876077</v>
+        <v>35.38777889672282</v>
       </c>
       <c r="C2" t="n">
-        <v>35.52883207749991</v>
+        <v>34.52012996044073</v>
       </c>
       <c r="D2" t="n">
-        <v>46.88362050355783</v>
+        <v>37.34756722969621</v>
       </c>
       <c r="E2" t="n">
-        <v>27.13251123064445</v>
+        <v>26.29029879319236</v>
       </c>
       <c r="F2" t="n">
-        <v>28.0682382292948</v>
+        <v>25.69242575562241</v>
       </c>
       <c r="G2" t="n">
-        <v>39.5144877380895</v>
+        <v>33.59811179262928</v>
       </c>
       <c r="H2" t="n">
-        <v>36.82128984680624</v>
+        <v>33.98172756051028</v>
       </c>
       <c r="I2" t="n">
-        <v>33.85544486367287</v>
+        <v>48.31831606227959</v>
       </c>
       <c r="J2" t="n">
-        <v>33.96884961142644</v>
+        <v>24.21553389237361</v>
       </c>
     </row>
   </sheetData>
@@ -10864,31 +10864,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.94995683447998</v>
+        <v>23.29845364508206</v>
       </c>
       <c r="C2" t="n">
-        <v>43.57832377171413</v>
+        <v>57.27952069450661</v>
       </c>
       <c r="D2" t="n">
-        <v>40.02965866699503</v>
+        <v>38.72089633709845</v>
       </c>
       <c r="E2" t="n">
-        <v>32.62931096912003</v>
+        <v>29.50472371212513</v>
       </c>
       <c r="F2" t="n">
-        <v>35.89313628601901</v>
+        <v>51.20117787862846</v>
       </c>
       <c r="G2" t="n">
-        <v>30.55018145169432</v>
+        <v>46.72025378304969</v>
       </c>
       <c r="H2" t="n">
-        <v>22.56033288723687</v>
+        <v>42.71134674415136</v>
       </c>
       <c r="I2" t="n">
-        <v>32.80184353779788</v>
+        <v>34.92076639096255</v>
       </c>
       <c r="J2" t="n">
-        <v>39.44426429684906</v>
+        <v>42.08554774807774</v>
       </c>
     </row>
   </sheetData>
@@ -10962,31 +10962,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.18421077312617</v>
+        <v>52.35609725575962</v>
       </c>
       <c r="C2" t="n">
-        <v>53.08958353945789</v>
+        <v>28.11206124528122</v>
       </c>
       <c r="D2" t="n">
-        <v>42.53465403890101</v>
+        <v>41.80307868242242</v>
       </c>
       <c r="E2" t="n">
-        <v>21.97403482565366</v>
+        <v>24.46236416063958</v>
       </c>
       <c r="F2" t="n">
-        <v>51.56767598923325</v>
+        <v>40.47647081947846</v>
       </c>
       <c r="G2" t="n">
-        <v>33.4814462076617</v>
+        <v>46.01960460063828</v>
       </c>
       <c r="H2" t="n">
-        <v>53.51197335392486</v>
+        <v>39.92110731198439</v>
       </c>
       <c r="I2" t="n">
-        <v>37.92014668426754</v>
+        <v>40.61719330376702</v>
       </c>
       <c r="J2" t="n">
-        <v>55.94668004794175</v>
+        <v>43.63267063142405</v>
       </c>
     </row>
   </sheetData>
@@ -11060,31 +11060,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.87297746786067</v>
+        <v>34.29985917363665</v>
       </c>
       <c r="C2" t="n">
-        <v>44.78168426004299</v>
+        <v>58.08540419427045</v>
       </c>
       <c r="D2" t="n">
-        <v>44.74023062258476</v>
+        <v>26.55808394574292</v>
       </c>
       <c r="E2" t="n">
-        <v>30.33648666488289</v>
+        <v>62.14603754024636</v>
       </c>
       <c r="F2" t="n">
-        <v>45.4530960516061</v>
+        <v>47.20719366722696</v>
       </c>
       <c r="G2" t="n">
-        <v>41.88548351579973</v>
+        <v>34.0990906122785</v>
       </c>
       <c r="H2" t="n">
-        <v>27.60504664245588</v>
+        <v>36.67829354846082</v>
       </c>
       <c r="I2" t="n">
-        <v>24.38375175472018</v>
+        <v>33.56619933705622</v>
       </c>
       <c r="J2" t="n">
-        <v>45.04708580744758</v>
+        <v>19.93914035117591</v>
       </c>
     </row>
   </sheetData>
@@ -11158,31 +11158,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.83810349947691</v>
+        <v>39.76924188028502</v>
       </c>
       <c r="C2" t="n">
-        <v>40.54741478018603</v>
+        <v>46.75276819646815</v>
       </c>
       <c r="D2" t="n">
-        <v>30.80597212645095</v>
+        <v>35.87948185250389</v>
       </c>
       <c r="E2" t="n">
-        <v>26.83729375231882</v>
+        <v>48.13265381695668</v>
       </c>
       <c r="F2" t="n">
-        <v>44.91112773617568</v>
+        <v>32.51384673254864</v>
       </c>
       <c r="G2" t="n">
-        <v>33.47685590099892</v>
+        <v>38.16650554138585</v>
       </c>
       <c r="H2" t="n">
-        <v>38.11248666169506</v>
+        <v>35.1040150975989</v>
       </c>
       <c r="I2" t="n">
-        <v>29.67162484947596</v>
+        <v>37.19106495526071</v>
       </c>
       <c r="J2" t="n">
-        <v>49.04472435407121</v>
+        <v>39.02309179720476</v>
       </c>
     </row>
   </sheetData>
@@ -11256,31 +11256,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.58114578406385</v>
+        <v>40.34399168092145</v>
       </c>
       <c r="C2" t="n">
-        <v>33.23292967176981</v>
+        <v>28.45604872123404</v>
       </c>
       <c r="D2" t="n">
-        <v>30.35818348099832</v>
+        <v>52.03889921496659</v>
       </c>
       <c r="E2" t="n">
-        <v>28.98392435847344</v>
+        <v>44.81092040191235</v>
       </c>
       <c r="F2" t="n">
-        <v>49.62061498502309</v>
+        <v>39.83108129359849</v>
       </c>
       <c r="G2" t="n">
-        <v>30.26820642323704</v>
+        <v>50.6734399649269</v>
       </c>
       <c r="H2" t="n">
-        <v>41.62254244451323</v>
+        <v>40.27389560090393</v>
       </c>
       <c r="I2" t="n">
-        <v>50.08726184519146</v>
+        <v>31.59517191431312</v>
       </c>
       <c r="J2" t="n">
-        <v>45.85381944613433</v>
+        <v>39.57887241021741</v>
       </c>
     </row>
   </sheetData>
@@ -11354,31 +11354,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.39295553354921</v>
+        <v>40.5798537304776</v>
       </c>
       <c r="C2" t="n">
-        <v>44.26911894401515</v>
+        <v>34.30848207000054</v>
       </c>
       <c r="D2" t="n">
-        <v>46.39589818177483</v>
+        <v>36.87404497717567</v>
       </c>
       <c r="E2" t="n">
-        <v>41.50303441459395</v>
+        <v>42.63732790003476</v>
       </c>
       <c r="F2" t="n">
-        <v>30.22275774245649</v>
+        <v>26.05578576664864</v>
       </c>
       <c r="G2" t="n">
-        <v>34.70008810143054</v>
+        <v>38.26622820599889</v>
       </c>
       <c r="H2" t="n">
-        <v>39.71290120076704</v>
+        <v>43.16261291585636</v>
       </c>
       <c r="I2" t="n">
-        <v>42.03850716546322</v>
+        <v>33.25160935168292</v>
       </c>
       <c r="J2" t="n">
-        <v>27.02905907333097</v>
+        <v>36.51610439387921</v>
       </c>
     </row>
   </sheetData>
@@ -11452,31 +11452,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.22531253410007</v>
+        <v>32.93214752479629</v>
       </c>
       <c r="C2" t="n">
-        <v>44.09001241342775</v>
+        <v>49.05010506249059</v>
       </c>
       <c r="D2" t="n">
-        <v>45.87687022785766</v>
+        <v>43.06843367022282</v>
       </c>
       <c r="E2" t="n">
-        <v>23.4109444465673</v>
+        <v>38.47473507628808</v>
       </c>
       <c r="F2" t="n">
-        <v>45.79238348362828</v>
+        <v>41.55040233919415</v>
       </c>
       <c r="G2" t="n">
-        <v>40.63313867266073</v>
+        <v>40.17149444294368</v>
       </c>
       <c r="H2" t="n">
-        <v>47.06081708576981</v>
+        <v>42.4917343287032</v>
       </c>
       <c r="I2" t="n">
-        <v>42.73502200434883</v>
+        <v>34.62130094850009</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4644615146906</v>
+        <v>39.53044509933062</v>
       </c>
     </row>
   </sheetData>
@@ -11550,31 +11550,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>36.82840720947992</v>
+        <v>35.98301264326219</v>
       </c>
       <c r="C2" t="n">
-        <v>56.33024231069633</v>
+        <v>33.07171021993998</v>
       </c>
       <c r="D2" t="n">
-        <v>52.04757500630598</v>
+        <v>36.5616017860012</v>
       </c>
       <c r="E2" t="n">
-        <v>42.09198350918652</v>
+        <v>35.9039075722188</v>
       </c>
       <c r="F2" t="n">
-        <v>29.69284137034828</v>
+        <v>36.20779705817871</v>
       </c>
       <c r="G2" t="n">
-        <v>44.9963155549942</v>
+        <v>45.41342694793229</v>
       </c>
       <c r="H2" t="n">
-        <v>31.16099331238422</v>
+        <v>43.50024826478416</v>
       </c>
       <c r="I2" t="n">
-        <v>41.05592410840912</v>
+        <v>54.03444709099022</v>
       </c>
       <c r="J2" t="n">
-        <v>33.00932271419988</v>
+        <v>51.80268600178807</v>
       </c>
     </row>
   </sheetData>
@@ -11648,31 +11648,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.90127997134904</v>
+        <v>37.471585274215</v>
       </c>
       <c r="C2" t="n">
-        <v>29.52994964952233</v>
+        <v>27.620323790047</v>
       </c>
       <c r="D2" t="n">
-        <v>56.07167797014998</v>
+        <v>25.46369495274432</v>
       </c>
       <c r="E2" t="n">
-        <v>32.995510935651</v>
+        <v>40.69317888366893</v>
       </c>
       <c r="F2" t="n">
-        <v>37.37212894528111</v>
+        <v>49.91813497122107</v>
       </c>
       <c r="G2" t="n">
-        <v>27.38438704571094</v>
+        <v>29.58267699492175</v>
       </c>
       <c r="H2" t="n">
-        <v>40.80302868556712</v>
+        <v>37.3882136786741</v>
       </c>
       <c r="I2" t="n">
-        <v>28.5214735195307</v>
+        <v>31.4367177276109</v>
       </c>
       <c r="J2" t="n">
-        <v>40.47620552327125</v>
+        <v>47.38869565225578</v>
       </c>
     </row>
   </sheetData>
@@ -11746,31 +11746,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.5726549916867</v>
+        <v>30.17712861813336</v>
       </c>
       <c r="C2" t="n">
-        <v>35.13310561227703</v>
+        <v>35.54862634564785</v>
       </c>
       <c r="D2" t="n">
-        <v>43.16593879076268</v>
+        <v>47.28337755347572</v>
       </c>
       <c r="E2" t="n">
-        <v>38.22154029894973</v>
+        <v>30.3278423421698</v>
       </c>
       <c r="F2" t="n">
-        <v>37.72981735154914</v>
+        <v>48.13289382914078</v>
       </c>
       <c r="G2" t="n">
-        <v>36.31992763570613</v>
+        <v>26.29751758964288</v>
       </c>
       <c r="H2" t="n">
-        <v>32.95108285384012</v>
+        <v>42.22507038683668</v>
       </c>
       <c r="I2" t="n">
-        <v>22.68546855056244</v>
+        <v>54.04640695246922</v>
       </c>
       <c r="J2" t="n">
-        <v>35.58159308262943</v>
+        <v>31.43580385553383</v>
       </c>
     </row>
   </sheetData>
@@ -11844,31 +11844,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.71905386416669</v>
+        <v>41.18188550630582</v>
       </c>
       <c r="C2" t="n">
-        <v>45.94384560353404</v>
+        <v>49.21656958723721</v>
       </c>
       <c r="D2" t="n">
-        <v>41.90172018340812</v>
+        <v>40.05785620723292</v>
       </c>
       <c r="E2" t="n">
-        <v>37.05227716136557</v>
+        <v>40.97709390106483</v>
       </c>
       <c r="F2" t="n">
-        <v>27.74243714254043</v>
+        <v>36.13578510453932</v>
       </c>
       <c r="G2" t="n">
-        <v>32.19680514956635</v>
+        <v>30.45195532998157</v>
       </c>
       <c r="H2" t="n">
-        <v>37.41281431284645</v>
+        <v>40.17623127102706</v>
       </c>
       <c r="I2" t="n">
-        <v>46.53149135790883</v>
+        <v>40.93871502097633</v>
       </c>
       <c r="J2" t="n">
-        <v>36.26446747082349</v>
+        <v>40.14575615801447</v>
       </c>
     </row>
   </sheetData>
@@ -11942,31 +11942,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.89060171371737</v>
+        <v>49.54255831808186</v>
       </c>
       <c r="C2" t="n">
-        <v>47.11228937723568</v>
+        <v>30.15881417363329</v>
       </c>
       <c r="D2" t="n">
-        <v>27.65038074685243</v>
+        <v>36.62379706019694</v>
       </c>
       <c r="E2" t="n">
-        <v>40.77449509176844</v>
+        <v>31.40055027997258</v>
       </c>
       <c r="F2" t="n">
-        <v>38.60088181419534</v>
+        <v>47.41006208560246</v>
       </c>
       <c r="G2" t="n">
-        <v>34.32058790562527</v>
+        <v>38.62673118720841</v>
       </c>
       <c r="H2" t="n">
-        <v>42.46608749351973</v>
+        <v>39.78694949812536</v>
       </c>
       <c r="I2" t="n">
-        <v>51.28238787819934</v>
+        <v>31.76608164919628</v>
       </c>
       <c r="J2" t="n">
-        <v>39.48749679191989</v>
+        <v>44.8781901101969</v>
       </c>
     </row>
   </sheetData>
@@ -12040,31 +12040,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.10090010186455</v>
+        <v>48.1076056379357</v>
       </c>
       <c r="C2" t="n">
-        <v>47.20571203088418</v>
+        <v>37.88181555168404</v>
       </c>
       <c r="D2" t="n">
-        <v>35.19183763568588</v>
+        <v>38.72695347364333</v>
       </c>
       <c r="E2" t="n">
-        <v>32.79408157980053</v>
+        <v>54.52698851217765</v>
       </c>
       <c r="F2" t="n">
-        <v>33.96801129807777</v>
+        <v>33.44055260559169</v>
       </c>
       <c r="G2" t="n">
-        <v>38.60815681186187</v>
+        <v>34.12590418124994</v>
       </c>
       <c r="H2" t="n">
-        <v>45.30490265809164</v>
+        <v>38.33803254956766</v>
       </c>
       <c r="I2" t="n">
-        <v>47.62851914905819</v>
+        <v>41.36157643852621</v>
       </c>
       <c r="J2" t="n">
-        <v>32.17804960099684</v>
+        <v>51.26962693069363</v>
       </c>
     </row>
   </sheetData>
@@ -12138,31 +12138,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.72957257117906</v>
+        <v>38.04157007727635</v>
       </c>
       <c r="C2" t="n">
-        <v>39.74201280121883</v>
+        <v>51.58241682103025</v>
       </c>
       <c r="D2" t="n">
-        <v>37.92732229183811</v>
+        <v>41.00453018630547</v>
       </c>
       <c r="E2" t="n">
-        <v>27.56138304968006</v>
+        <v>43.15759330990451</v>
       </c>
       <c r="F2" t="n">
-        <v>30.45006564114752</v>
+        <v>30.43693217265641</v>
       </c>
       <c r="G2" t="n">
-        <v>41.46857296269953</v>
+        <v>40.04985505063613</v>
       </c>
       <c r="H2" t="n">
-        <v>39.00743433520599</v>
+        <v>33.85983623104325</v>
       </c>
       <c r="I2" t="n">
-        <v>43.58526168846818</v>
+        <v>45.94377097820245</v>
       </c>
       <c r="J2" t="n">
-        <v>37.41233403839784</v>
+        <v>46.98381861431722</v>
       </c>
     </row>
   </sheetData>
@@ -12236,31 +12236,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>39.76063541752219</v>
+        <v>34.72542146033214</v>
       </c>
       <c r="C2" t="n">
-        <v>48.54660113103795</v>
+        <v>41.31638583414158</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9319650011232</v>
+        <v>32.65094909358309</v>
       </c>
       <c r="E2" t="n">
-        <v>39.96710571808319</v>
+        <v>48.47928768714004</v>
       </c>
       <c r="F2" t="n">
-        <v>44.92625348168536</v>
+        <v>46.55461782717969</v>
       </c>
       <c r="G2" t="n">
-        <v>45.88146627860492</v>
+        <v>50.32319122246248</v>
       </c>
       <c r="H2" t="n">
-        <v>46.24159979953161</v>
+        <v>37.51727575351214</v>
       </c>
       <c r="I2" t="n">
-        <v>40.98362454620361</v>
+        <v>38.61827562083948</v>
       </c>
       <c r="J2" t="n">
-        <v>39.40023571885678</v>
+        <v>41.87733895623406</v>
       </c>
     </row>
   </sheetData>
@@ -12334,31 +12334,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.56334131265682</v>
+        <v>32.36656882236493</v>
       </c>
       <c r="C2" t="n">
-        <v>53.07033334251197</v>
+        <v>45.93970102722803</v>
       </c>
       <c r="D2" t="n">
-        <v>36.09482919779981</v>
+        <v>31.62870918868292</v>
       </c>
       <c r="E2" t="n">
-        <v>40.44592552524038</v>
+        <v>48.29073471410109</v>
       </c>
       <c r="F2" t="n">
-        <v>54.83571820606598</v>
+        <v>37.90382033371981</v>
       </c>
       <c r="G2" t="n">
-        <v>42.40227579140084</v>
+        <v>51.1809539054966</v>
       </c>
       <c r="H2" t="n">
-        <v>35.16380595681611</v>
+        <v>36.15151625180961</v>
       </c>
       <c r="I2" t="n">
-        <v>44.60828471857125</v>
+        <v>32.5963669980343</v>
       </c>
       <c r="J2" t="n">
-        <v>34.04601269872518</v>
+        <v>38.69285097221193</v>
       </c>
     </row>
   </sheetData>
@@ -12432,31 +12432,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.13043340487193</v>
+        <v>40.11611458746764</v>
       </c>
       <c r="C2" t="n">
-        <v>55.46477462859256</v>
+        <v>61.63031107265754</v>
       </c>
       <c r="D2" t="n">
-        <v>54.44088410487981</v>
+        <v>35.15403800262105</v>
       </c>
       <c r="E2" t="n">
-        <v>23.39869204710016</v>
+        <v>31.10801846119227</v>
       </c>
       <c r="F2" t="n">
-        <v>37.70272105575276</v>
+        <v>48.00900860045475</v>
       </c>
       <c r="G2" t="n">
-        <v>30.44372612490623</v>
+        <v>43.69279431821261</v>
       </c>
       <c r="H2" t="n">
-        <v>44.57507026836404</v>
+        <v>39.96790462596442</v>
       </c>
       <c r="I2" t="n">
-        <v>43.42950875284534</v>
+        <v>40.33593063304588</v>
       </c>
       <c r="J2" t="n">
-        <v>44.92366999300583</v>
+        <v>33.40919573432208</v>
       </c>
     </row>
   </sheetData>
@@ -12530,31 +12530,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.71283512850223</v>
+        <v>48.03707291752303</v>
       </c>
       <c r="C2" t="n">
-        <v>40.96532440399498</v>
+        <v>32.09830292381027</v>
       </c>
       <c r="D2" t="n">
-        <v>48.26626457740466</v>
+        <v>47.55327300264481</v>
       </c>
       <c r="E2" t="n">
-        <v>37.76790763992302</v>
+        <v>41.39950014526719</v>
       </c>
       <c r="F2" t="n">
-        <v>45.13639771626802</v>
+        <v>40.7178887616469</v>
       </c>
       <c r="G2" t="n">
-        <v>33.23415811625073</v>
+        <v>29.32295461070126</v>
       </c>
       <c r="H2" t="n">
-        <v>37.1535285327497</v>
+        <v>39.0852583352012</v>
       </c>
       <c r="I2" t="n">
-        <v>39.42316210941656</v>
+        <v>43.47720259038714</v>
       </c>
       <c r="J2" t="n">
-        <v>37.91383656151285</v>
+        <v>49.24673861371028</v>
       </c>
     </row>
   </sheetData>
@@ -12628,31 +12628,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.59405600370111</v>
+        <v>44.6223303093383</v>
       </c>
       <c r="C2" t="n">
-        <v>42.58347727248456</v>
+        <v>44.19355438775867</v>
       </c>
       <c r="D2" t="n">
-        <v>52.83252283948703</v>
+        <v>29.76948196588098</v>
       </c>
       <c r="E2" t="n">
-        <v>28.42099728813059</v>
+        <v>33.09714122533775</v>
       </c>
       <c r="F2" t="n">
-        <v>30.29443872994508</v>
+        <v>44.32306229223988</v>
       </c>
       <c r="G2" t="n">
-        <v>60.61797067049148</v>
+        <v>27.98067991909346</v>
       </c>
       <c r="H2" t="n">
-        <v>35.09358754438568</v>
+        <v>33.55910300090461</v>
       </c>
       <c r="I2" t="n">
-        <v>35.14453129535773</v>
+        <v>38.71425110336783</v>
       </c>
       <c r="J2" t="n">
-        <v>46.83430132449742</v>
+        <v>35.47550166615792</v>
       </c>
     </row>
   </sheetData>
@@ -12726,31 +12726,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.15847531222924</v>
+        <v>42.46306157856563</v>
       </c>
       <c r="C2" t="n">
-        <v>49.75515744499121</v>
+        <v>33.85849033831261</v>
       </c>
       <c r="D2" t="n">
-        <v>33.73336591650334</v>
+        <v>31.0851788853542</v>
       </c>
       <c r="E2" t="n">
-        <v>39.18588067203475</v>
+        <v>44.55576464668356</v>
       </c>
       <c r="F2" t="n">
-        <v>39.08948470722528</v>
+        <v>24.94345798293926</v>
       </c>
       <c r="G2" t="n">
-        <v>34.37942508279712</v>
+        <v>31.03021281337188</v>
       </c>
       <c r="H2" t="n">
-        <v>35.8470892615716</v>
+        <v>40.72826855839319</v>
       </c>
       <c r="I2" t="n">
-        <v>44.68287547249659</v>
+        <v>38.70713694911938</v>
       </c>
       <c r="J2" t="n">
-        <v>25.75418027335452</v>
+        <v>71.89802788751588</v>
       </c>
     </row>
   </sheetData>
@@ -12824,31 +12824,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.69561036825863</v>
+        <v>40.17580453802628</v>
       </c>
       <c r="C2" t="n">
-        <v>31.40718778265666</v>
+        <v>42.83405507052607</v>
       </c>
       <c r="D2" t="n">
-        <v>43.74859926132564</v>
+        <v>37.70622094457839</v>
       </c>
       <c r="E2" t="n">
-        <v>44.06586387524026</v>
+        <v>38.69386880426511</v>
       </c>
       <c r="F2" t="n">
-        <v>38.99808854855888</v>
+        <v>28.16473201384224</v>
       </c>
       <c r="G2" t="n">
-        <v>29.89197348605143</v>
+        <v>44.96735869483069</v>
       </c>
       <c r="H2" t="n">
-        <v>51.93672750886437</v>
+        <v>48.67774555750106</v>
       </c>
       <c r="I2" t="n">
-        <v>40.11260780024229</v>
+        <v>65.31834447631053</v>
       </c>
       <c r="J2" t="n">
-        <v>39.4060867692145</v>
+        <v>36.82731902583588</v>
       </c>
     </row>
   </sheetData>
@@ -12922,31 +12922,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.07848688173906</v>
+        <v>33.34052133509027</v>
       </c>
       <c r="C2" t="n">
-        <v>37.84443455468656</v>
+        <v>43.49076801439983</v>
       </c>
       <c r="D2" t="n">
-        <v>36.21529796137833</v>
+        <v>43.6085951936378</v>
       </c>
       <c r="E2" t="n">
-        <v>31.41664650784049</v>
+        <v>45.36908369097943</v>
       </c>
       <c r="F2" t="n">
-        <v>31.25070245637761</v>
+        <v>31.80976392151014</v>
       </c>
       <c r="G2" t="n">
-        <v>31.67526779078166</v>
+        <v>29.7867161984497</v>
       </c>
       <c r="H2" t="n">
-        <v>39.58482592291774</v>
+        <v>43.05197176436494</v>
       </c>
       <c r="I2" t="n">
-        <v>63.2929546351555</v>
+        <v>34.8517628948652</v>
       </c>
       <c r="J2" t="n">
-        <v>55.0839093312557</v>
+        <v>30.21255009951234</v>
       </c>
     </row>
   </sheetData>
@@ -13020,31 +13020,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.15737265998499</v>
+        <v>27.6197615909281</v>
       </c>
       <c r="C2" t="n">
-        <v>48.11579496771089</v>
+        <v>29.691813924932</v>
       </c>
       <c r="D2" t="n">
-        <v>44.18873887960909</v>
+        <v>52.46811102083158</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08422832858863</v>
+        <v>38.39464268187031</v>
       </c>
       <c r="F2" t="n">
-        <v>29.16149749932534</v>
+        <v>52.28070148978591</v>
       </c>
       <c r="G2" t="n">
-        <v>44.05452181262508</v>
+        <v>50.29187631185026</v>
       </c>
       <c r="H2" t="n">
-        <v>42.24171023895497</v>
+        <v>51.60597925673753</v>
       </c>
       <c r="I2" t="n">
-        <v>52.28070148978591</v>
+        <v>39.92274394843395</v>
       </c>
       <c r="J2" t="n">
-        <v>33.453336612588</v>
+        <v>48.41610134988901</v>
       </c>
     </row>
   </sheetData>
@@ -13118,31 +13118,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.48890346322728</v>
+        <v>46.70778670706889</v>
       </c>
       <c r="C2" t="n">
-        <v>46.8810023516481</v>
+        <v>31.65723309661302</v>
       </c>
       <c r="D2" t="n">
-        <v>45.82731365099036</v>
+        <v>43.59254583176276</v>
       </c>
       <c r="E2" t="n">
-        <v>30.60543363688579</v>
+        <v>38.89714581090534</v>
       </c>
       <c r="F2" t="n">
-        <v>45.32194511122425</v>
+        <v>38.61248134994284</v>
       </c>
       <c r="G2" t="n">
-        <v>43.16475620448432</v>
+        <v>43.69618729880538</v>
       </c>
       <c r="H2" t="n">
-        <v>36.26841482290244</v>
+        <v>42.3490373232916</v>
       </c>
       <c r="I2" t="n">
-        <v>45.80709770710459</v>
+        <v>31.66743263215411</v>
       </c>
       <c r="J2" t="n">
-        <v>39.31585428187338</v>
+        <v>37.5436974509999</v>
       </c>
     </row>
   </sheetData>
@@ -13216,31 +13216,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.64701427639131</v>
+        <v>50.47284076710374</v>
       </c>
       <c r="C2" t="n">
-        <v>55.5963276730935</v>
+        <v>41.07789946280729</v>
       </c>
       <c r="D2" t="n">
-        <v>34.33374388528846</v>
+        <v>65.06094928227208</v>
       </c>
       <c r="E2" t="n">
-        <v>33.65194056599105</v>
+        <v>38.13077668297961</v>
       </c>
       <c r="F2" t="n">
-        <v>42.25269130521183</v>
+        <v>31.42104281366519</v>
       </c>
       <c r="G2" t="n">
-        <v>56.21940791346515</v>
+        <v>42.67304947553514</v>
       </c>
       <c r="H2" t="n">
-        <v>47.57550790796358</v>
+        <v>27.83288701231193</v>
       </c>
       <c r="I2" t="n">
-        <v>37.19796028693453</v>
+        <v>31.72525494006651</v>
       </c>
       <c r="J2" t="n">
-        <v>34.44884809381626</v>
+        <v>37.88577038726399</v>
       </c>
     </row>
   </sheetData>
@@ -13314,31 +13314,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.29629601222289</v>
+        <v>30.11932564366663</v>
       </c>
       <c r="C2" t="n">
-        <v>43.59910790738163</v>
+        <v>42.69850454786812</v>
       </c>
       <c r="D2" t="n">
-        <v>42.64175134832512</v>
+        <v>32.1202197422615</v>
       </c>
       <c r="E2" t="n">
-        <v>28.39746800252593</v>
+        <v>39.94168020360417</v>
       </c>
       <c r="F2" t="n">
-        <v>40.12454295604651</v>
+        <v>40.33996003489085</v>
       </c>
       <c r="G2" t="n">
-        <v>31.15950519019272</v>
+        <v>53.10696401107231</v>
       </c>
       <c r="H2" t="n">
-        <v>50.2808610790356</v>
+        <v>43.17898609711544</v>
       </c>
       <c r="I2" t="n">
-        <v>61.56360847617074</v>
+        <v>34.66587540313363</v>
       </c>
       <c r="J2" t="n">
-        <v>39.35039761767561</v>
+        <v>31.73332109190588</v>
       </c>
     </row>
   </sheetData>
@@ -13412,31 +13412,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.50835349841697</v>
+        <v>40.05550086813695</v>
       </c>
       <c r="C2" t="n">
-        <v>40.81766755690691</v>
+        <v>32.52280472060676</v>
       </c>
       <c r="D2" t="n">
-        <v>40.03082054157797</v>
+        <v>40.03326209770956</v>
       </c>
       <c r="E2" t="n">
-        <v>39.99033585690373</v>
+        <v>54.25716360930314</v>
       </c>
       <c r="F2" t="n">
-        <v>46.09500283300553</v>
+        <v>27.93170536696899</v>
       </c>
       <c r="G2" t="n">
-        <v>34.61995651006524</v>
+        <v>52.68915933676708</v>
       </c>
       <c r="H2" t="n">
-        <v>29.61457456752644</v>
+        <v>39.5425401374548</v>
       </c>
       <c r="I2" t="n">
-        <v>35.56891006285166</v>
+        <v>35.31788996936128</v>
       </c>
       <c r="J2" t="n">
-        <v>41.73693300965699</v>
+        <v>33.82656753839581</v>
       </c>
     </row>
   </sheetData>
@@ -13510,31 +13510,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.78211705653271</v>
+        <v>33.46571131533369</v>
       </c>
       <c r="C2" t="n">
-        <v>34.95263292929236</v>
+        <v>36.12052227932897</v>
       </c>
       <c r="D2" t="n">
-        <v>51.47670711338414</v>
+        <v>37.65802172884911</v>
       </c>
       <c r="E2" t="n">
-        <v>32.74955740335786</v>
+        <v>29.29834243292982</v>
       </c>
       <c r="F2" t="n">
-        <v>36.52506241980483</v>
+        <v>49.06930645226262</v>
       </c>
       <c r="G2" t="n">
-        <v>37.91268392695289</v>
+        <v>39.61480454405696</v>
       </c>
       <c r="H2" t="n">
-        <v>45.05306502844978</v>
+        <v>45.21523861264433</v>
       </c>
       <c r="I2" t="n">
-        <v>41.43330088799004</v>
+        <v>43.33790677487605</v>
       </c>
       <c r="J2" t="n">
-        <v>59.97248789418503</v>
+        <v>36.05791153573448</v>
       </c>
     </row>
   </sheetData>
@@ -13608,31 +13608,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.28965803407371</v>
+        <v>26.27898252708849</v>
       </c>
       <c r="C2" t="n">
-        <v>36.40283220676886</v>
+        <v>42.15893758699794</v>
       </c>
       <c r="D2" t="n">
-        <v>38.76020600960967</v>
+        <v>45.5154474532057</v>
       </c>
       <c r="E2" t="n">
-        <v>35.51291921919398</v>
+        <v>36.53035944271562</v>
       </c>
       <c r="F2" t="n">
-        <v>32.69621682061677</v>
+        <v>31.71555301028779</v>
       </c>
       <c r="G2" t="n">
-        <v>31.95075531118119</v>
+        <v>44.24578939365007</v>
       </c>
       <c r="H2" t="n">
-        <v>36.52582862883867</v>
+        <v>44.33785416474691</v>
       </c>
       <c r="I2" t="n">
-        <v>47.11506797408585</v>
+        <v>44.35369168704327</v>
       </c>
       <c r="J2" t="n">
-        <v>52.59665925921327</v>
+        <v>40.98775503987601</v>
       </c>
     </row>
   </sheetData>
@@ -13706,31 +13706,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.82310109936016</v>
+        <v>33.68674513111791</v>
       </c>
       <c r="C2" t="n">
-        <v>31.13664547621954</v>
+        <v>36.47237851376567</v>
       </c>
       <c r="D2" t="n">
-        <v>40.35679294527691</v>
+        <v>48.39492398160662</v>
       </c>
       <c r="E2" t="n">
-        <v>28.48017972632914</v>
+        <v>37.97157561388924</v>
       </c>
       <c r="F2" t="n">
-        <v>41.19188398613464</v>
+        <v>46.67681892176629</v>
       </c>
       <c r="G2" t="n">
-        <v>37.12899420925197</v>
+        <v>33.120871700961</v>
       </c>
       <c r="H2" t="n">
-        <v>46.85705888385455</v>
+        <v>28.11134325926527</v>
       </c>
       <c r="I2" t="n">
-        <v>58.8272685233741</v>
+        <v>38.44999428511015</v>
       </c>
       <c r="J2" t="n">
-        <v>31.48642832132083</v>
+        <v>27.18842868300435</v>
       </c>
     </row>
   </sheetData>
@@ -13804,31 +13804,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.9114616724227</v>
+        <v>43.02264403361686</v>
       </c>
       <c r="C2" t="n">
-        <v>48.04609195229148</v>
+        <v>31.53782917637739</v>
       </c>
       <c r="D2" t="n">
-        <v>37.36242502948266</v>
+        <v>37.57710383058637</v>
       </c>
       <c r="E2" t="n">
-        <v>31.21506249004051</v>
+        <v>51.2504838879337</v>
       </c>
       <c r="F2" t="n">
-        <v>49.49612287856652</v>
+        <v>39.4209487446434</v>
       </c>
       <c r="G2" t="n">
-        <v>38.91493190980846</v>
+        <v>45.33851130137973</v>
       </c>
       <c r="H2" t="n">
-        <v>45.79008661684759</v>
+        <v>46.07822418410401</v>
       </c>
       <c r="I2" t="n">
-        <v>48.62471458849416</v>
+        <v>43.00993359204896</v>
       </c>
       <c r="J2" t="n">
-        <v>45.46835403178432</v>
+        <v>49.42913813909353</v>
       </c>
     </row>
   </sheetData>
@@ -13902,31 +13902,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>51.01262710804344</v>
+        <v>54.1039630931264</v>
       </c>
       <c r="C2" t="n">
-        <v>40.72700039874542</v>
+        <v>31.05460101849877</v>
       </c>
       <c r="D2" t="n">
-        <v>47.34303740621963</v>
+        <v>38.45990675240307</v>
       </c>
       <c r="E2" t="n">
-        <v>43.19917674633928</v>
+        <v>34.59389841931361</v>
       </c>
       <c r="F2" t="n">
-        <v>38.14974200534588</v>
+        <v>32.07762899629159</v>
       </c>
       <c r="G2" t="n">
-        <v>30.52416095016967</v>
+        <v>36.32043044256737</v>
       </c>
       <c r="H2" t="n">
-        <v>52.29243437299948</v>
+        <v>39.23500395311627</v>
       </c>
       <c r="I2" t="n">
-        <v>32.94757802509053</v>
+        <v>44.26746380244592</v>
       </c>
       <c r="J2" t="n">
-        <v>43.35703599135397</v>
+        <v>26.56676332403993</v>
       </c>
     </row>
   </sheetData>
@@ -14000,31 +14000,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.47457651896413</v>
+        <v>42.23578633059733</v>
       </c>
       <c r="C2" t="n">
-        <v>42.7563635220091</v>
+        <v>48.3182916410027</v>
       </c>
       <c r="D2" t="n">
-        <v>57.03709409794535</v>
+        <v>50.38428733316339</v>
       </c>
       <c r="E2" t="n">
-        <v>34.42192604513549</v>
+        <v>39.07495523033635</v>
       </c>
       <c r="F2" t="n">
-        <v>46.59109097055699</v>
+        <v>44.1921164313006</v>
       </c>
       <c r="G2" t="n">
-        <v>45.15971769154141</v>
+        <v>35.86714813399911</v>
       </c>
       <c r="H2" t="n">
-        <v>40.57421961483621</v>
+        <v>40.92157540200017</v>
       </c>
       <c r="I2" t="n">
-        <v>28.89417118826998</v>
+        <v>32.11538205232339</v>
       </c>
       <c r="J2" t="n">
-        <v>52.17925290920123</v>
+        <v>42.9966314599658</v>
       </c>
     </row>
   </sheetData>
@@ -14098,31 +14098,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.23713159368589</v>
+        <v>34.00847022164053</v>
       </c>
       <c r="C2" t="n">
-        <v>37.47581667289957</v>
+        <v>55.76083254429289</v>
       </c>
       <c r="D2" t="n">
-        <v>47.45869759155231</v>
+        <v>34.18551074111329</v>
       </c>
       <c r="E2" t="n">
-        <v>29.25582972778069</v>
+        <v>36.20809369045633</v>
       </c>
       <c r="F2" t="n">
-        <v>43.93195219694224</v>
+        <v>44.76600695933022</v>
       </c>
       <c r="G2" t="n">
-        <v>39.14218318946426</v>
+        <v>63.21853942267515</v>
       </c>
       <c r="H2" t="n">
-        <v>39.13797791716838</v>
+        <v>52.82047208286274</v>
       </c>
       <c r="I2" t="n">
-        <v>58.1472265518813</v>
+        <v>41.20759372500071</v>
       </c>
       <c r="J2" t="n">
-        <v>39.41846044071964</v>
+        <v>35.46565723710431</v>
       </c>
     </row>
   </sheetData>
@@ -14196,31 +14196,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.04786427978851</v>
+        <v>35.07519346358981</v>
       </c>
       <c r="C2" t="n">
-        <v>43.94615687841726</v>
+        <v>36.11464215601472</v>
       </c>
       <c r="D2" t="n">
-        <v>42.56518778970728</v>
+        <v>35.82967935891423</v>
       </c>
       <c r="E2" t="n">
-        <v>25.96669986256119</v>
+        <v>31.2139085528425</v>
       </c>
       <c r="F2" t="n">
-        <v>44.20300587337483</v>
+        <v>51.68037758600397</v>
       </c>
       <c r="G2" t="n">
-        <v>42.59461910455515</v>
+        <v>34.78443373611835</v>
       </c>
       <c r="H2" t="n">
-        <v>29.94371955514769</v>
+        <v>39.73382742114237</v>
       </c>
       <c r="I2" t="n">
-        <v>31.65802772954805</v>
+        <v>34.72400431257789</v>
       </c>
       <c r="J2" t="n">
-        <v>43.45410247497241</v>
+        <v>30.87284663345445</v>
       </c>
     </row>
   </sheetData>
@@ -14294,31 +14294,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.2493378696533</v>
+        <v>36.27780062839452</v>
       </c>
       <c r="C2" t="n">
-        <v>62.05653733091682</v>
+        <v>44.43758448135726</v>
       </c>
       <c r="D2" t="n">
-        <v>37.35011965501319</v>
+        <v>45.73193832659833</v>
       </c>
       <c r="E2" t="n">
-        <v>26.4838446170847</v>
+        <v>31.32882744833206</v>
       </c>
       <c r="F2" t="n">
-        <v>31.69222589031865</v>
+        <v>43.78184968390665</v>
       </c>
       <c r="G2" t="n">
-        <v>40.93109353253086</v>
+        <v>33.33049786993939</v>
       </c>
       <c r="H2" t="n">
-        <v>52.01375412533192</v>
+        <v>55.65687929241753</v>
       </c>
       <c r="I2" t="n">
-        <v>44.58388306004062</v>
+        <v>41.64891140073667</v>
       </c>
       <c r="J2" t="n">
-        <v>47.14201072359398</v>
+        <v>50.55461848740328</v>
       </c>
     </row>
   </sheetData>
@@ -14392,31 +14392,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.83279170282424</v>
+        <v>44.09937062327162</v>
       </c>
       <c r="C2" t="n">
-        <v>43.88415680412544</v>
+        <v>46.11649244109395</v>
       </c>
       <c r="D2" t="n">
-        <v>54.57532526803944</v>
+        <v>39.07090679053692</v>
       </c>
       <c r="E2" t="n">
-        <v>34.4303591967447</v>
+        <v>37.4721355089273</v>
       </c>
       <c r="F2" t="n">
-        <v>52.0344656979312</v>
+        <v>34.01858750462051</v>
       </c>
       <c r="G2" t="n">
-        <v>23.3582550055195</v>
+        <v>53.76229595772214</v>
       </c>
       <c r="H2" t="n">
-        <v>43.07625067027902</v>
+        <v>42.41954976786168</v>
       </c>
       <c r="I2" t="n">
-        <v>53.48736564516992</v>
+        <v>40.28705681822075</v>
       </c>
       <c r="J2" t="n">
-        <v>52.71973167830293</v>
+        <v>30.87208408100003</v>
       </c>
     </row>
   </sheetData>
@@ -14490,31 +14490,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.38044779960575</v>
+        <v>34.41683779334446</v>
       </c>
       <c r="C2" t="n">
-        <v>32.3106621648838</v>
+        <v>37.7242754701186</v>
       </c>
       <c r="D2" t="n">
-        <v>40.51969820341996</v>
+        <v>43.50099452648609</v>
       </c>
       <c r="E2" t="n">
-        <v>37.13385806608039</v>
+        <v>27.3563816889192</v>
       </c>
       <c r="F2" t="n">
-        <v>35.79562355481367</v>
+        <v>50.95204253211214</v>
       </c>
       <c r="G2" t="n">
-        <v>28.00282727843424</v>
+        <v>39.69925461189469</v>
       </c>
       <c r="H2" t="n">
-        <v>53.03847353139626</v>
+        <v>37.63630615815997</v>
       </c>
       <c r="I2" t="n">
-        <v>52.2072162029388</v>
+        <v>53.86797698859669</v>
       </c>
       <c r="J2" t="n">
-        <v>41.32408888765523</v>
+        <v>37.24856326465528</v>
       </c>
     </row>
   </sheetData>
@@ -14588,31 +14588,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.47384169922073</v>
+        <v>31.42702329932063</v>
       </c>
       <c r="C2" t="n">
-        <v>40.8001802504058</v>
+        <v>38.02199674029298</v>
       </c>
       <c r="D2" t="n">
-        <v>35.83970737450797</v>
+        <v>34.69065949366389</v>
       </c>
       <c r="E2" t="n">
-        <v>32.27598947444564</v>
+        <v>34.80106937000222</v>
       </c>
       <c r="F2" t="n">
-        <v>42.47921348792428</v>
+        <v>56.91775902020471</v>
       </c>
       <c r="G2" t="n">
-        <v>47.31392034788489</v>
+        <v>50.93199620231015</v>
       </c>
       <c r="H2" t="n">
-        <v>64.59833005171576</v>
+        <v>37.75091911875333</v>
       </c>
       <c r="I2" t="n">
-        <v>43.70379858468031</v>
+        <v>46.74877357280636</v>
       </c>
       <c r="J2" t="n">
-        <v>50.30991220018599</v>
+        <v>45.77844599745114</v>
       </c>
     </row>
   </sheetData>
@@ -14686,31 +14686,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.18739575489785</v>
+        <v>48.23702846316528</v>
       </c>
       <c r="C2" t="n">
-        <v>31.23608929852049</v>
+        <v>36.4824202318943</v>
       </c>
       <c r="D2" t="n">
-        <v>40.46597865672474</v>
+        <v>44.57646361424764</v>
       </c>
       <c r="E2" t="n">
-        <v>29.29406978614281</v>
+        <v>42.18569259586243</v>
       </c>
       <c r="F2" t="n">
-        <v>42.89719354675477</v>
+        <v>40.31648615798743</v>
       </c>
       <c r="G2" t="n">
-        <v>42.021799810894</v>
+        <v>48.04745426867723</v>
       </c>
       <c r="H2" t="n">
-        <v>31.73335942305809</v>
+        <v>44.70397164045475</v>
       </c>
       <c r="I2" t="n">
-        <v>49.06028521371098</v>
+        <v>38.63944866233786</v>
       </c>
       <c r="J2" t="n">
-        <v>56.53802883123848</v>
+        <v>36.60809791997167</v>
       </c>
     </row>
   </sheetData>
@@ -14784,31 +14784,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.99501954243282</v>
+        <v>44.38834541345359</v>
       </c>
       <c r="C2" t="n">
-        <v>50.35324355427786</v>
+        <v>28.33608609195851</v>
       </c>
       <c r="D2" t="n">
-        <v>31.34637944343174</v>
+        <v>34.6647166115489</v>
       </c>
       <c r="E2" t="n">
-        <v>34.98903036853771</v>
+        <v>38.47659589565308</v>
       </c>
       <c r="F2" t="n">
-        <v>31.93494487151616</v>
+        <v>43.46756685563496</v>
       </c>
       <c r="G2" t="n">
-        <v>33.97221480580994</v>
+        <v>31.08529023007036</v>
       </c>
       <c r="H2" t="n">
-        <v>35.50374449673586</v>
+        <v>44.01327328053981</v>
       </c>
       <c r="I2" t="n">
-        <v>49.01277932336271</v>
+        <v>37.59218076213814</v>
       </c>
       <c r="J2" t="n">
-        <v>47.89589577919704</v>
+        <v>38.96622639002813</v>
       </c>
     </row>
   </sheetData>
@@ -14882,31 +14882,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.61602024245472</v>
+        <v>49.0332670230587</v>
       </c>
       <c r="C2" t="n">
-        <v>34.41781920733892</v>
+        <v>36.83943355123248</v>
       </c>
       <c r="D2" t="n">
-        <v>38.26201978972493</v>
+        <v>44.57812881197174</v>
       </c>
       <c r="E2" t="n">
-        <v>39.56034113548939</v>
+        <v>32.64699924889668</v>
       </c>
       <c r="F2" t="n">
-        <v>45.68043740290383</v>
+        <v>46.84083694067622</v>
       </c>
       <c r="G2" t="n">
-        <v>30.28655113994122</v>
+        <v>35.14807025566339</v>
       </c>
       <c r="H2" t="n">
-        <v>46.08052272788272</v>
+        <v>58.34942477074659</v>
       </c>
       <c r="I2" t="n">
-        <v>49.83502727183092</v>
+        <v>28.35346565673471</v>
       </c>
       <c r="J2" t="n">
-        <v>46.67939126094283</v>
+        <v>44.59160913532448</v>
       </c>
     </row>
   </sheetData>
@@ -14980,31 +14980,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.59546126696028</v>
+        <v>34.24198025088216</v>
       </c>
       <c r="C2" t="n">
-        <v>44.97897794584978</v>
+        <v>33.48957856137846</v>
       </c>
       <c r="D2" t="n">
-        <v>37.90331892690061</v>
+        <v>39.36620904010463</v>
       </c>
       <c r="E2" t="n">
-        <v>38.98014017151183</v>
+        <v>45.21083504610787</v>
       </c>
       <c r="F2" t="n">
-        <v>46.6744736380212</v>
+        <v>45.98309454916634</v>
       </c>
       <c r="G2" t="n">
-        <v>41.16733383123794</v>
+        <v>48.12371761177327</v>
       </c>
       <c r="H2" t="n">
-        <v>36.94988043631749</v>
+        <v>44.21025780815153</v>
       </c>
       <c r="I2" t="n">
-        <v>42.37109240066008</v>
+        <v>34.44011909820225</v>
       </c>
       <c r="J2" t="n">
-        <v>37.4309017469336</v>
+        <v>39.11704498455698</v>
       </c>
     </row>
   </sheetData>
@@ -15078,31 +15078,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.07655625951042</v>
+        <v>42.33021050575386</v>
       </c>
       <c r="C2" t="n">
-        <v>53.25920480358658</v>
+        <v>30.28599193080872</v>
       </c>
       <c r="D2" t="n">
-        <v>48.53599857156382</v>
+        <v>32.34443651564405</v>
       </c>
       <c r="E2" t="n">
-        <v>32.02999789662543</v>
+        <v>44.23647302260314</v>
       </c>
       <c r="F2" t="n">
-        <v>47.37657272087173</v>
+        <v>53.84336219815585</v>
       </c>
       <c r="G2" t="n">
-        <v>26.08601783342114</v>
+        <v>48.16103676319787</v>
       </c>
       <c r="H2" t="n">
-        <v>49.37339052224778</v>
+        <v>48.45599526280163</v>
       </c>
       <c r="I2" t="n">
-        <v>40.79932589892455</v>
+        <v>29.85153131789076</v>
       </c>
       <c r="J2" t="n">
-        <v>31.39350630521577</v>
+        <v>43.44847571241837</v>
       </c>
     </row>
   </sheetData>
@@ -15176,31 +15176,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.89734117612987</v>
+        <v>36.29180900908791</v>
       </c>
       <c r="C2" t="n">
-        <v>43.6441791808688</v>
+        <v>41.60073827632609</v>
       </c>
       <c r="D2" t="n">
-        <v>41.9578384419106</v>
+        <v>41.42199346590294</v>
       </c>
       <c r="E2" t="n">
-        <v>34.48531044943745</v>
+        <v>35.14512797807467</v>
       </c>
       <c r="F2" t="n">
-        <v>30.23561974979208</v>
+        <v>41.91417928033439</v>
       </c>
       <c r="G2" t="n">
-        <v>33.68449460628305</v>
+        <v>41.68000219139537</v>
       </c>
       <c r="H2" t="n">
-        <v>40.19445083593202</v>
+        <v>49.079968543611</v>
       </c>
       <c r="I2" t="n">
-        <v>51.74510054994481</v>
+        <v>28.91360600145639</v>
       </c>
       <c r="J2" t="n">
-        <v>40.42054576756018</v>
+        <v>39.80840778528977</v>
       </c>
     </row>
   </sheetData>
@@ -15274,31 +15274,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.43433515421437</v>
+        <v>48.56276966149338</v>
       </c>
       <c r="C2" t="n">
-        <v>49.8494716706434</v>
+        <v>47.29462159579583</v>
       </c>
       <c r="D2" t="n">
-        <v>57.59393664604734</v>
+        <v>38.92786553916059</v>
       </c>
       <c r="E2" t="n">
-        <v>36.9934971418753</v>
+        <v>41.77140228755363</v>
       </c>
       <c r="F2" t="n">
-        <v>32.23975143417558</v>
+        <v>42.19828536915092</v>
       </c>
       <c r="G2" t="n">
-        <v>39.21501922923268</v>
+        <v>31.56364103938173</v>
       </c>
       <c r="H2" t="n">
-        <v>52.41443536786407</v>
+        <v>32.91027136860689</v>
       </c>
       <c r="I2" t="n">
-        <v>36.78439589001038</v>
+        <v>52.87797381335798</v>
       </c>
       <c r="J2" t="n">
-        <v>46.82141709647832</v>
+        <v>40.91427462874055</v>
       </c>
     </row>
   </sheetData>
@@ -15372,31 +15372,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.74456527244342</v>
+        <v>31.41787255422294</v>
       </c>
       <c r="C2" t="n">
-        <v>39.56169624494289</v>
+        <v>32.64534173129194</v>
       </c>
       <c r="D2" t="n">
-        <v>25.98542518028848</v>
+        <v>39.12909301020914</v>
       </c>
       <c r="E2" t="n">
-        <v>36.23662170209816</v>
+        <v>33.32486074931521</v>
       </c>
       <c r="F2" t="n">
-        <v>43.52102290091437</v>
+        <v>40.50066216669461</v>
       </c>
       <c r="G2" t="n">
-        <v>46.31724361282311</v>
+        <v>34.48171338734261</v>
       </c>
       <c r="H2" t="n">
-        <v>36.04079996495726</v>
+        <v>43.19200375558621</v>
       </c>
       <c r="I2" t="n">
-        <v>42.04584654253522</v>
+        <v>41.78751719378145</v>
       </c>
       <c r="J2" t="n">
-        <v>34.16011564664326</v>
+        <v>34.21681858817341</v>
       </c>
     </row>
   </sheetData>
@@ -15470,31 +15470,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.513372376258</v>
+        <v>40.60652304513249</v>
       </c>
       <c r="C2" t="n">
-        <v>52.72543146368076</v>
+        <v>41.48662467232756</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84348554224034</v>
+        <v>39.5524325368131</v>
       </c>
       <c r="E2" t="n">
-        <v>32.01365937116081</v>
+        <v>39.77020820377987</v>
       </c>
       <c r="F2" t="n">
-        <v>38.48672152749512</v>
+        <v>32.03009597323974</v>
       </c>
       <c r="G2" t="n">
-        <v>39.99270817139762</v>
+        <v>32.2339802625383</v>
       </c>
       <c r="H2" t="n">
-        <v>45.6930315114278</v>
+        <v>41.69533483315205</v>
       </c>
       <c r="I2" t="n">
-        <v>41.98064176333175</v>
+        <v>22.28322964196594</v>
       </c>
       <c r="J2" t="n">
-        <v>35.73077438790346</v>
+        <v>42.11577291801813</v>
       </c>
     </row>
   </sheetData>
@@ -15568,31 +15568,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.69529485796871</v>
+        <v>42.90486577707401</v>
       </c>
       <c r="C2" t="n">
-        <v>47.2802629234153</v>
+        <v>39.61452029970889</v>
       </c>
       <c r="D2" t="n">
-        <v>44.96211830351428</v>
+        <v>37.85003430193899</v>
       </c>
       <c r="E2" t="n">
-        <v>28.26862757049929</v>
+        <v>37.17475131223172</v>
       </c>
       <c r="F2" t="n">
-        <v>28.86102473775417</v>
+        <v>37.62387168727261</v>
       </c>
       <c r="G2" t="n">
-        <v>43.91306599282976</v>
+        <v>40.86921855960195</v>
       </c>
       <c r="H2" t="n">
-        <v>28.94052714248324</v>
+        <v>32.94341261212193</v>
       </c>
       <c r="I2" t="n">
-        <v>38.16547082958817</v>
+        <v>35.04907862477208</v>
       </c>
       <c r="J2" t="n">
-        <v>41.98149408225944</v>
+        <v>42.64345431180391</v>
       </c>
     </row>
   </sheetData>
@@ -15666,31 +15666,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.92476796531155</v>
+        <v>49.45301422806931</v>
       </c>
       <c r="C2" t="n">
-        <v>36.63422186666423</v>
+        <v>39.3373317137799</v>
       </c>
       <c r="D2" t="n">
-        <v>40.88245830767441</v>
+        <v>28.8920439080805</v>
       </c>
       <c r="E2" t="n">
-        <v>45.48716440416095</v>
+        <v>39.45229547490474</v>
       </c>
       <c r="F2" t="n">
-        <v>40.25200144432439</v>
+        <v>29.07726026726201</v>
       </c>
       <c r="G2" t="n">
-        <v>45.66161437015262</v>
+        <v>44.24160183023477</v>
       </c>
       <c r="H2" t="n">
-        <v>45.82200442364118</v>
+        <v>33.42235888853546</v>
       </c>
       <c r="I2" t="n">
-        <v>30.10142803268492</v>
+        <v>44.07821297032017</v>
       </c>
       <c r="J2" t="n">
-        <v>19.83168573685139</v>
+        <v>38.07466131726711</v>
       </c>
     </row>
   </sheetData>
@@ -15764,31 +15764,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.14227904253332</v>
+        <v>34.83068024391009</v>
       </c>
       <c r="C2" t="n">
-        <v>47.81991012850276</v>
+        <v>35.73380594979719</v>
       </c>
       <c r="D2" t="n">
-        <v>54.06445879065677</v>
+        <v>42.76024085654991</v>
       </c>
       <c r="E2" t="n">
-        <v>36.58622184355838</v>
+        <v>32.91066191029631</v>
       </c>
       <c r="F2" t="n">
-        <v>43.65905622726666</v>
+        <v>42.407274306349</v>
       </c>
       <c r="G2" t="n">
-        <v>45.47263651900324</v>
+        <v>45.56832022019672</v>
       </c>
       <c r="H2" t="n">
-        <v>47.38959673391209</v>
+        <v>38.07396379827723</v>
       </c>
       <c r="I2" t="n">
-        <v>35.50064522386441</v>
+        <v>53.64758140057446</v>
       </c>
       <c r="J2" t="n">
-        <v>40.20531389764504</v>
+        <v>47.84641553133069</v>
       </c>
     </row>
   </sheetData>
@@ -15862,31 +15862,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.28517008350413</v>
+        <v>38.72739999705667</v>
       </c>
       <c r="C2" t="n">
-        <v>34.34168866744659</v>
+        <v>28.73493868758273</v>
       </c>
       <c r="D2" t="n">
-        <v>35.83025323245169</v>
+        <v>46.59994939334097</v>
       </c>
       <c r="E2" t="n">
-        <v>41.33403172920122</v>
+        <v>37.15306854419831</v>
       </c>
       <c r="F2" t="n">
-        <v>46.36604630467288</v>
+        <v>32.41220695049827</v>
       </c>
       <c r="G2" t="n">
-        <v>30.60473807198147</v>
+        <v>36.12162360336927</v>
       </c>
       <c r="H2" t="n">
-        <v>36.58121616033913</v>
+        <v>35.70057089991688</v>
       </c>
       <c r="I2" t="n">
-        <v>49.02101635819535</v>
+        <v>45.31595777270606</v>
       </c>
       <c r="J2" t="n">
-        <v>40.22333892713753</v>
+        <v>40.11751654811724</v>
       </c>
     </row>
   </sheetData>
@@ -15960,31 +15960,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>49.58507722500021</v>
+        <v>50.86500143391562</v>
       </c>
       <c r="C2" t="n">
-        <v>49.04565863570147</v>
+        <v>49.04656443445454</v>
       </c>
       <c r="D2" t="n">
-        <v>33.55988239106628</v>
+        <v>30.69110814755711</v>
       </c>
       <c r="E2" t="n">
-        <v>28.98121547349856</v>
+        <v>33.40403786135731</v>
       </c>
       <c r="F2" t="n">
-        <v>33.50729662452457</v>
+        <v>31.61081071703033</v>
       </c>
       <c r="G2" t="n">
-        <v>27.00209684184311</v>
+        <v>43.93993905762968</v>
       </c>
       <c r="H2" t="n">
-        <v>46.94192655207522</v>
+        <v>44.05767935123237</v>
       </c>
       <c r="I2" t="n">
-        <v>28.76767486255594</v>
+        <v>28.51516809472414</v>
       </c>
       <c r="J2" t="n">
-        <v>39.91937215224625</v>
+        <v>44.12413364806073</v>
       </c>
     </row>
   </sheetData>
@@ -16058,31 +16058,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.69064972588087</v>
+        <v>41.31962826372884</v>
       </c>
       <c r="C2" t="n">
-        <v>14.57201144096362</v>
+        <v>42.64774278494344</v>
       </c>
       <c r="D2" t="n">
-        <v>71.73090934787625</v>
+        <v>42.08877645104543</v>
       </c>
       <c r="E2" t="n">
-        <v>29.96438299833077</v>
+        <v>30.18339855843251</v>
       </c>
       <c r="F2" t="n">
-        <v>29.8969557814002</v>
+        <v>21.68200501125633</v>
       </c>
       <c r="G2" t="n">
-        <v>62.82542129675206</v>
+        <v>37.52834672053139</v>
       </c>
       <c r="H2" t="n">
-        <v>45.28675253415462</v>
+        <v>42.43517601097504</v>
       </c>
       <c r="I2" t="n">
-        <v>43.89255174995348</v>
+        <v>40.57638473703831</v>
       </c>
       <c r="J2" t="n">
-        <v>32.52667429212219</v>
+        <v>46.01466851924387</v>
       </c>
     </row>
   </sheetData>
@@ -16156,31 +16156,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.61449745479815</v>
+        <v>38.43116591474804</v>
       </c>
       <c r="C2" t="n">
-        <v>28.89105792925444</v>
+        <v>42.86488902238462</v>
       </c>
       <c r="D2" t="n">
-        <v>59.66463994255065</v>
+        <v>60.64039570452855</v>
       </c>
       <c r="E2" t="n">
-        <v>40.97017277335516</v>
+        <v>48.37980725051385</v>
       </c>
       <c r="F2" t="n">
-        <v>52.61686920396554</v>
+        <v>34.83187635785929</v>
       </c>
       <c r="G2" t="n">
-        <v>43.18444645386787</v>
+        <v>26.6626435219131</v>
       </c>
       <c r="H2" t="n">
-        <v>29.60169544355067</v>
+        <v>48.37507879489305</v>
       </c>
       <c r="I2" t="n">
-        <v>57.33854479332919</v>
+        <v>32.07320596162131</v>
       </c>
       <c r="J2" t="n">
-        <v>51.40176969618508</v>
+        <v>34.63111744563266</v>
       </c>
     </row>
   </sheetData>
@@ -16254,31 +16254,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.9393161415425</v>
+        <v>46.62467789175739</v>
       </c>
       <c r="C2" t="n">
-        <v>30.41509647292805</v>
+        <v>41.60515392867806</v>
       </c>
       <c r="D2" t="n">
-        <v>60.59605697007095</v>
+        <v>30.96301172638968</v>
       </c>
       <c r="E2" t="n">
-        <v>40.67873975487949</v>
+        <v>48.71537101839777</v>
       </c>
       <c r="F2" t="n">
-        <v>39.25931543860927</v>
+        <v>35.40508091630356</v>
       </c>
       <c r="G2" t="n">
-        <v>38.03015757761204</v>
+        <v>31.25794129537818</v>
       </c>
       <c r="H2" t="n">
-        <v>29.90249914877251</v>
+        <v>29.72471814605844</v>
       </c>
       <c r="I2" t="n">
-        <v>37.71200543594571</v>
+        <v>49.27716487999995</v>
       </c>
       <c r="J2" t="n">
-        <v>36.38866957239077</v>
+        <v>51.68356854163947</v>
       </c>
     </row>
   </sheetData>
@@ -16352,31 +16352,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.28573892891256</v>
+        <v>36.57415653819749</v>
       </c>
       <c r="C2" t="n">
-        <v>45.50057358521946</v>
+        <v>43.62581274790351</v>
       </c>
       <c r="D2" t="n">
-        <v>34.91616400165193</v>
+        <v>42.2713527389167</v>
       </c>
       <c r="E2" t="n">
-        <v>42.23276676694341</v>
+        <v>40.1332314547635</v>
       </c>
       <c r="F2" t="n">
-        <v>36.75725616148917</v>
+        <v>48.05320128883249</v>
       </c>
       <c r="G2" t="n">
-        <v>44.4266329845228</v>
+        <v>42.32234136696165</v>
       </c>
       <c r="H2" t="n">
-        <v>39.58614059151671</v>
+        <v>55.21047138828683</v>
       </c>
       <c r="I2" t="n">
-        <v>48.01651859497793</v>
+        <v>33.28314101857139</v>
       </c>
       <c r="J2" t="n">
-        <v>47.91080800425787</v>
+        <v>33.62672979670929</v>
       </c>
     </row>
   </sheetData>
@@ -16450,31 +16450,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.27181920690408</v>
+        <v>50.41098475441769</v>
       </c>
       <c r="C2" t="n">
-        <v>53.41810202405977</v>
+        <v>44.51642545951338</v>
       </c>
       <c r="D2" t="n">
-        <v>40.35048508118303</v>
+        <v>42.64233020432508</v>
       </c>
       <c r="E2" t="n">
-        <v>36.25374369058716</v>
+        <v>40.38679993382198</v>
       </c>
       <c r="F2" t="n">
-        <v>39.2212115515273</v>
+        <v>34.99912148204429</v>
       </c>
       <c r="G2" t="n">
-        <v>51.13867447341192</v>
+        <v>35.4617755792702</v>
       </c>
       <c r="H2" t="n">
-        <v>40.22152899483955</v>
+        <v>51.32914578106067</v>
       </c>
       <c r="I2" t="n">
-        <v>35.47418676126721</v>
+        <v>44.12440090731695</v>
       </c>
       <c r="J2" t="n">
-        <v>39.76575470478552</v>
+        <v>43.96309546006354</v>
       </c>
     </row>
   </sheetData>
@@ -16548,31 +16548,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.76615064722245</v>
+        <v>31.44660189328225</v>
       </c>
       <c r="C2" t="n">
-        <v>40.28168896502684</v>
+        <v>36.9773578396881</v>
       </c>
       <c r="D2" t="n">
-        <v>32.13280597401808</v>
+        <v>31.42782846311928</v>
       </c>
       <c r="E2" t="n">
-        <v>34.7378086399188</v>
+        <v>39.86296191749803</v>
       </c>
       <c r="F2" t="n">
-        <v>49.98174315641208</v>
+        <v>55.80851722671893</v>
       </c>
       <c r="G2" t="n">
-        <v>36.71833607621745</v>
+        <v>42.82201133693861</v>
       </c>
       <c r="H2" t="n">
-        <v>46.01013213657215</v>
+        <v>34.85234893762991</v>
       </c>
       <c r="I2" t="n">
-        <v>39.93037682036671</v>
+        <v>38.05835451644219</v>
       </c>
       <c r="J2" t="n">
-        <v>54.69933989723117</v>
+        <v>48.39823330898442</v>
       </c>
     </row>
   </sheetData>
@@ -16646,31 +16646,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.39427216745162</v>
+        <v>54.54331463564613</v>
       </c>
       <c r="C2" t="n">
-        <v>36.00419821328902</v>
+        <v>37.42331449633966</v>
       </c>
       <c r="D2" t="n">
-        <v>42.99363659910733</v>
+        <v>43.33825978537556</v>
       </c>
       <c r="E2" t="n">
-        <v>45.17700430428655</v>
+        <v>26.9011313417953</v>
       </c>
       <c r="F2" t="n">
-        <v>36.73188222944448</v>
+        <v>41.91535402047428</v>
       </c>
       <c r="G2" t="n">
-        <v>45.52933795077109</v>
+        <v>36.62890476384366</v>
       </c>
       <c r="H2" t="n">
-        <v>51.63636441761092</v>
+        <v>37.02924991358842</v>
       </c>
       <c r="I2" t="n">
-        <v>40.47526022915621</v>
+        <v>35.17368048468716</v>
       </c>
       <c r="J2" t="n">
-        <v>35.63607263350027</v>
+        <v>32.22365800386037</v>
       </c>
     </row>
   </sheetData>
@@ -16744,31 +16744,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>42.10348763835523</v>
+        <v>57.31278746507115</v>
       </c>
       <c r="C2" t="n">
-        <v>60.42204608448409</v>
+        <v>45.64692066001918</v>
       </c>
       <c r="D2" t="n">
-        <v>30.94191615980661</v>
+        <v>35.95247147706558</v>
       </c>
       <c r="E2" t="n">
-        <v>39.58984708997377</v>
+        <v>36.17292620755542</v>
       </c>
       <c r="F2" t="n">
-        <v>38.13253286805252</v>
+        <v>51.54436336059079</v>
       </c>
       <c r="G2" t="n">
-        <v>45.85052085270554</v>
+        <v>39.71553526817021</v>
       </c>
       <c r="H2" t="n">
-        <v>27.49916302380628</v>
+        <v>30.22795450624708</v>
       </c>
       <c r="I2" t="n">
-        <v>41.60770355355735</v>
+        <v>45.45417974154951</v>
       </c>
       <c r="J2" t="n">
-        <v>40.65036452128241</v>
+        <v>41.47600890462886</v>
       </c>
     </row>
   </sheetData>
@@ -16842,31 +16842,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29.95381914323065</v>
+        <v>37.69639432904938</v>
       </c>
       <c r="C2" t="n">
-        <v>32.95195889350581</v>
+        <v>33.39517581235567</v>
       </c>
       <c r="D2" t="n">
-        <v>30.38157713262926</v>
+        <v>42.84013315442455</v>
       </c>
       <c r="E2" t="n">
-        <v>44.0695104985378</v>
+        <v>38.87699468651439</v>
       </c>
       <c r="F2" t="n">
-        <v>32.36621105987221</v>
+        <v>28.81180851143479</v>
       </c>
       <c r="G2" t="n">
-        <v>31.10021117469375</v>
+        <v>41.70333906021214</v>
       </c>
       <c r="H2" t="n">
-        <v>28.2466472379758</v>
+        <v>34.18841786812421</v>
       </c>
       <c r="I2" t="n">
-        <v>49.57397139238705</v>
+        <v>39.16448671039299</v>
       </c>
       <c r="J2" t="n">
-        <v>40.5541469210009</v>
+        <v>34.58779021003814</v>
       </c>
     </row>
   </sheetData>
@@ -16940,31 +16940,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>50.22101836779273</v>
+        <v>47.3821320855831</v>
       </c>
       <c r="C2" t="n">
-        <v>39.99783431277967</v>
+        <v>38.18498693350718</v>
       </c>
       <c r="D2" t="n">
-        <v>45.01415542782202</v>
+        <v>32.0948767098327</v>
       </c>
       <c r="E2" t="n">
-        <v>39.117579646432</v>
+        <v>38.09297535780718</v>
       </c>
       <c r="F2" t="n">
-        <v>24.63606929205865</v>
+        <v>38.61851505234917</v>
       </c>
       <c r="G2" t="n">
-        <v>43.19015239883166</v>
+        <v>42.25726984204445</v>
       </c>
       <c r="H2" t="n">
-        <v>50.49961424004492</v>
+        <v>34.37989062351835</v>
       </c>
       <c r="I2" t="n">
-        <v>34.758967218929</v>
+        <v>31.07048947592136</v>
       </c>
       <c r="J2" t="n">
-        <v>42.8559323083746</v>
+        <v>31.28522565181036</v>
       </c>
     </row>
   </sheetData>
@@ -17038,31 +17038,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.00388866297027</v>
+        <v>45.661427705301</v>
       </c>
       <c r="C2" t="n">
-        <v>54.94163516294259</v>
+        <v>37.82628240302963</v>
       </c>
       <c r="D2" t="n">
-        <v>41.3390722177339</v>
+        <v>46.39345976179746</v>
       </c>
       <c r="E2" t="n">
-        <v>23.65209137504724</v>
+        <v>37.17202458339887</v>
       </c>
       <c r="F2" t="n">
-        <v>37.08047222301085</v>
+        <v>35.79707855951744</v>
       </c>
       <c r="G2" t="n">
-        <v>32.17838162507119</v>
+        <v>29.52684033190708</v>
       </c>
       <c r="H2" t="n">
-        <v>36.7428771769826</v>
+        <v>31.48623892918198</v>
       </c>
       <c r="I2" t="n">
-        <v>21.81867563031703</v>
+        <v>38.81287340717596</v>
       </c>
       <c r="J2" t="n">
-        <v>50.43152176290972</v>
+        <v>32.59786057480054</v>
       </c>
     </row>
   </sheetData>
@@ -17136,31 +17136,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>41.01021892704391</v>
+        <v>42.68082965053065</v>
       </c>
       <c r="C2" t="n">
-        <v>52.02488261232609</v>
+        <v>32.99018434365981</v>
       </c>
       <c r="D2" t="n">
-        <v>31.7880098592979</v>
+        <v>40.04919303164938</v>
       </c>
       <c r="E2" t="n">
-        <v>36.67901842781567</v>
+        <v>38.52249265650295</v>
       </c>
       <c r="F2" t="n">
-        <v>33.4103527937311</v>
+        <v>35.18388183270171</v>
       </c>
       <c r="G2" t="n">
-        <v>32.49182061057745</v>
+        <v>21.2635070957003</v>
       </c>
       <c r="H2" t="n">
-        <v>49.78102981238948</v>
+        <v>42.54667172761155</v>
       </c>
       <c r="I2" t="n">
-        <v>47.67904389350451</v>
+        <v>47.21303369423119</v>
       </c>
       <c r="J2" t="n">
-        <v>46.77697015631954</v>
+        <v>30.06199137959284</v>
       </c>
     </row>
   </sheetData>
@@ -17234,31 +17234,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.18210017465557</v>
+        <v>38.38524872509171</v>
       </c>
       <c r="C2" t="n">
-        <v>55.17987963365979</v>
+        <v>44.85494057825321</v>
       </c>
       <c r="D2" t="n">
-        <v>48.89143401561772</v>
+        <v>43.69049975872456</v>
       </c>
       <c r="E2" t="n">
-        <v>32.6425448556022</v>
+        <v>35.91339915141342</v>
       </c>
       <c r="F2" t="n">
-        <v>41.2184049068274</v>
+        <v>47.3266797640666</v>
       </c>
       <c r="G2" t="n">
-        <v>41.55594327241243</v>
+        <v>45.83948154367918</v>
       </c>
       <c r="H2" t="n">
-        <v>35.97641922258599</v>
+        <v>44.70784427736255</v>
       </c>
       <c r="I2" t="n">
-        <v>60.91796391422091</v>
+        <v>27.75223768383441</v>
       </c>
       <c r="J2" t="n">
-        <v>46.06010694905982</v>
+        <v>35.27972220423212</v>
       </c>
     </row>
   </sheetData>
@@ -17332,31 +17332,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.68827603214214</v>
+        <v>44.8966869966217</v>
       </c>
       <c r="C2" t="n">
-        <v>42.65798923590913</v>
+        <v>40.69284461821742</v>
       </c>
       <c r="D2" t="n">
-        <v>55.3897792788999</v>
+        <v>25.49584978095129</v>
       </c>
       <c r="E2" t="n">
-        <v>33.77623709734583</v>
+        <v>52.02601858161755</v>
       </c>
       <c r="F2" t="n">
-        <v>64.56926601861871</v>
+        <v>29.25776783512277</v>
       </c>
       <c r="G2" t="n">
-        <v>47.41668704245101</v>
+        <v>34.61401682900554</v>
       </c>
       <c r="H2" t="n">
-        <v>28.85922086580734</v>
+        <v>37.07512999677177</v>
       </c>
       <c r="I2" t="n">
-        <v>35.03569249399313</v>
+        <v>35.78726386567768</v>
       </c>
       <c r="J2" t="n">
-        <v>31.11045464653299</v>
+        <v>39.02713300337631</v>
       </c>
     </row>
   </sheetData>
@@ -17430,31 +17430,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.78240587071594</v>
+        <v>35.44704325662332</v>
       </c>
       <c r="C2" t="n">
-        <v>41.58563769071878</v>
+        <v>40.68119604159852</v>
       </c>
       <c r="D2" t="n">
-        <v>42.2189660195952</v>
+        <v>40.8948771524685</v>
       </c>
       <c r="E2" t="n">
-        <v>30.47910520816109</v>
+        <v>48.38777202993233</v>
       </c>
       <c r="F2" t="n">
-        <v>55.05590019963081</v>
+        <v>43.90707730501348</v>
       </c>
       <c r="G2" t="n">
-        <v>38.80722360038503</v>
+        <v>41.54583832350582</v>
       </c>
       <c r="H2" t="n">
-        <v>35.78841192757048</v>
+        <v>41.62251752795616</v>
       </c>
       <c r="I2" t="n">
-        <v>66.40390292262057</v>
+        <v>30.09832805795169</v>
       </c>
       <c r="J2" t="n">
-        <v>51.30111872709173</v>
+        <v>41.6968843719382</v>
       </c>
     </row>
   </sheetData>
@@ -17528,31 +17528,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.80935726738667</v>
+        <v>41.06395397105226</v>
       </c>
       <c r="C2" t="n">
-        <v>45.33980457528291</v>
+        <v>38.72197105988939</v>
       </c>
       <c r="D2" t="n">
-        <v>54.20683055373667</v>
+        <v>52.47227143644471</v>
       </c>
       <c r="E2" t="n">
-        <v>35.73211948478784</v>
+        <v>37.41187587250343</v>
       </c>
       <c r="F2" t="n">
-        <v>32.63515894125891</v>
+        <v>49.15309001129656</v>
       </c>
       <c r="G2" t="n">
-        <v>36.19298742425925</v>
+        <v>49.43317596892916</v>
       </c>
       <c r="H2" t="n">
-        <v>55.14114807102496</v>
+        <v>34.72254158663718</v>
       </c>
       <c r="I2" t="n">
-        <v>43.82821927097839</v>
+        <v>38.53684564882791</v>
       </c>
       <c r="J2" t="n">
-        <v>45.75778939871232</v>
+        <v>41.7617304613462</v>
       </c>
     </row>
   </sheetData>
@@ -17626,31 +17626,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.90357900332453</v>
+        <v>26.49159904076009</v>
       </c>
       <c r="C2" t="n">
-        <v>54.53984213547609</v>
+        <v>55.827797799183</v>
       </c>
       <c r="D2" t="n">
-        <v>51.73389216871408</v>
+        <v>37.79800904519379</v>
       </c>
       <c r="E2" t="n">
-        <v>39.43666153012668</v>
+        <v>46.91169153691019</v>
       </c>
       <c r="F2" t="n">
-        <v>48.07917632472507</v>
+        <v>36.5857923044067</v>
       </c>
       <c r="G2" t="n">
-        <v>40.97991861591773</v>
+        <v>55.52162708734929</v>
       </c>
       <c r="H2" t="n">
-        <v>52.76572244547724</v>
+        <v>37.47612040937223</v>
       </c>
       <c r="I2" t="n">
-        <v>38.84090056680666</v>
+        <v>45.77000509691559</v>
       </c>
       <c r="J2" t="n">
-        <v>43.26837582740055</v>
+        <v>36.7682750081206</v>
       </c>
     </row>
   </sheetData>
@@ -17724,31 +17724,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.06796002688398</v>
+        <v>44.68953291053008</v>
       </c>
       <c r="C2" t="n">
-        <v>51.68807542484186</v>
+        <v>39.65793440236372</v>
       </c>
       <c r="D2" t="n">
-        <v>34.73792049408568</v>
+        <v>38.97744931712685</v>
       </c>
       <c r="E2" t="n">
-        <v>35.29585785520825</v>
+        <v>34.07720041686551</v>
       </c>
       <c r="F2" t="n">
-        <v>37.35261603958124</v>
+        <v>32.94700888410496</v>
       </c>
       <c r="G2" t="n">
-        <v>30.97783144697967</v>
+        <v>44.34986013374118</v>
       </c>
       <c r="H2" t="n">
-        <v>36.12933572735412</v>
+        <v>37.97161559734365</v>
       </c>
       <c r="I2" t="n">
-        <v>33.11963779868262</v>
+        <v>40.43278845444802</v>
       </c>
       <c r="J2" t="n">
-        <v>34.58029554413309</v>
+        <v>37.26936702899223</v>
       </c>
     </row>
   </sheetData>
@@ -17822,31 +17822,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.07959381899208</v>
+        <v>30.67380612526143</v>
       </c>
       <c r="C2" t="n">
-        <v>43.5851658170934</v>
+        <v>38.5187993502743</v>
       </c>
       <c r="D2" t="n">
-        <v>36.73271015911169</v>
+        <v>31.29092470710257</v>
       </c>
       <c r="E2" t="n">
-        <v>26.37082033542575</v>
+        <v>24.43278851953307</v>
       </c>
       <c r="F2" t="n">
-        <v>46.23954397645982</v>
+        <v>45.36233673705142</v>
       </c>
       <c r="G2" t="n">
-        <v>29.1303642976455</v>
+        <v>26.71551180394596</v>
       </c>
       <c r="H2" t="n">
-        <v>50.06420873115688</v>
+        <v>37.15357208487318</v>
       </c>
       <c r="I2" t="n">
-        <v>31.50171642553045</v>
+        <v>37.96483439511049</v>
       </c>
       <c r="J2" t="n">
-        <v>36.73926337290575</v>
+        <v>60.62673419448252</v>
       </c>
     </row>
   </sheetData>
@@ -17920,31 +17920,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.64557917854667</v>
+        <v>35.5367507257136</v>
       </c>
       <c r="C2" t="n">
-        <v>52.79535983052093</v>
+        <v>40.03383584028467</v>
       </c>
       <c r="D2" t="n">
-        <v>43.08168448563917</v>
+        <v>56.29126498073215</v>
       </c>
       <c r="E2" t="n">
-        <v>44.94287768511288</v>
+        <v>39.38455397381479</v>
       </c>
       <c r="F2" t="n">
-        <v>33.44701978111944</v>
+        <v>58.4091195748589</v>
       </c>
       <c r="G2" t="n">
-        <v>36.74654916467194</v>
+        <v>32.52452527154289</v>
       </c>
       <c r="H2" t="n">
-        <v>43.79104676556146</v>
+        <v>40.11761919646955</v>
       </c>
       <c r="I2" t="n">
-        <v>34.73450963463016</v>
+        <v>37.53603484180459</v>
       </c>
       <c r="J2" t="n">
-        <v>44.82909123343011</v>
+        <v>38.26936261315415</v>
       </c>
     </row>
   </sheetData>
@@ -18018,31 +18018,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.96376206239983</v>
+        <v>44.9802215869966</v>
       </c>
       <c r="C2" t="n">
-        <v>41.30435558485154</v>
+        <v>43.06170345953875</v>
       </c>
       <c r="D2" t="n">
-        <v>23.92204173490612</v>
+        <v>35.77091593834886</v>
       </c>
       <c r="E2" t="n">
-        <v>36.20988878022398</v>
+        <v>50.09547700832459</v>
       </c>
       <c r="F2" t="n">
-        <v>27.50182451494792</v>
+        <v>42.41110898671249</v>
       </c>
       <c r="G2" t="n">
-        <v>39.45437742450078</v>
+        <v>28.92601726874167</v>
       </c>
       <c r="H2" t="n">
-        <v>44.76771167847027</v>
+        <v>56.19892554227707</v>
       </c>
       <c r="I2" t="n">
-        <v>45.1092357514806</v>
+        <v>34.7354744500961</v>
       </c>
       <c r="J2" t="n">
-        <v>33.44021188276987</v>
+        <v>30.18236769076483</v>
       </c>
     </row>
   </sheetData>
@@ -18116,31 +18116,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>43.62335698059099</v>
+        <v>48.76214299637886</v>
       </c>
       <c r="C2" t="n">
-        <v>41.35572421359129</v>
+        <v>45.06622661847747</v>
       </c>
       <c r="D2" t="n">
-        <v>47.98224120960816</v>
+        <v>40.23802833321466</v>
       </c>
       <c r="E2" t="n">
-        <v>35.43529956974584</v>
+        <v>42.63375959710111</v>
       </c>
       <c r="F2" t="n">
-        <v>36.71172690101233</v>
+        <v>31.59727665931825</v>
       </c>
       <c r="G2" t="n">
-        <v>38.44679583164853</v>
+        <v>46.21892475297668</v>
       </c>
       <c r="H2" t="n">
-        <v>53.69503370229364</v>
+        <v>44.92980020513011</v>
       </c>
       <c r="I2" t="n">
-        <v>40.97320218719373</v>
+        <v>57.31296651349286</v>
       </c>
       <c r="J2" t="n">
-        <v>42.36470825380742</v>
+        <v>45.93284446912479</v>
       </c>
     </row>
   </sheetData>
@@ -18214,31 +18214,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.63871305598763</v>
+        <v>39.43388658182559</v>
       </c>
       <c r="C2" t="n">
-        <v>47.04521987635943</v>
+        <v>41.47434827337627</v>
       </c>
       <c r="D2" t="n">
-        <v>43.61420601075396</v>
+        <v>37.19621359976801</v>
       </c>
       <c r="E2" t="n">
-        <v>37.24285806343745</v>
+        <v>33.0683195066058</v>
       </c>
       <c r="F2" t="n">
-        <v>41.38264501722431</v>
+        <v>47.10045066154216</v>
       </c>
       <c r="G2" t="n">
-        <v>41.54532590379063</v>
+        <v>33.22570809270808</v>
       </c>
       <c r="H2" t="n">
-        <v>32.79838170769828</v>
+        <v>35.91729979496161</v>
       </c>
       <c r="I2" t="n">
-        <v>41.06657022474525</v>
+        <v>37.76342911253332</v>
       </c>
       <c r="J2" t="n">
-        <v>55.65034306018288</v>
+        <v>49.68751763737677</v>
       </c>
     </row>
   </sheetData>
@@ -18312,31 +18312,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>31.51532884324046</v>
+        <v>32.87273262483006</v>
       </c>
       <c r="C2" t="n">
-        <v>35.88287701765589</v>
+        <v>44.87936015409353</v>
       </c>
       <c r="D2" t="n">
-        <v>47.7898779118234</v>
+        <v>37.39836485769539</v>
       </c>
       <c r="E2" t="n">
-        <v>25.26367129591984</v>
+        <v>38.79655308598581</v>
       </c>
       <c r="F2" t="n">
-        <v>41.55250744328867</v>
+        <v>52.0992861999176</v>
       </c>
       <c r="G2" t="n">
-        <v>41.11366564946215</v>
+        <v>23.8299334196183</v>
       </c>
       <c r="H2" t="n">
-        <v>47.02942536231267</v>
+        <v>43.74683440597273</v>
       </c>
       <c r="I2" t="n">
-        <v>39.98232496856214</v>
+        <v>31.35426379271318</v>
       </c>
       <c r="J2" t="n">
-        <v>24.01137706087258</v>
+        <v>28.41273896651228</v>
       </c>
     </row>
   </sheetData>
@@ -18410,31 +18410,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.74753667841571</v>
+        <v>35.46453749947597</v>
       </c>
       <c r="C2" t="n">
-        <v>29.1776620871608</v>
+        <v>35.52957422138014</v>
       </c>
       <c r="D2" t="n">
-        <v>50.7746780784603</v>
+        <v>42.60053357871679</v>
       </c>
       <c r="E2" t="n">
-        <v>31.93522899324089</v>
+        <v>50.34490819429198</v>
       </c>
       <c r="F2" t="n">
-        <v>40.67642151731997</v>
+        <v>37.31144889339846</v>
       </c>
       <c r="G2" t="n">
-        <v>34.56220331159557</v>
+        <v>37.21204897630584</v>
       </c>
       <c r="H2" t="n">
-        <v>31.96968732543535</v>
+        <v>37.25169357233924</v>
       </c>
       <c r="I2" t="n">
-        <v>44.6365740440401</v>
+        <v>35.65678530813878</v>
       </c>
       <c r="J2" t="n">
-        <v>38.50174107432957</v>
+        <v>38.48850311342682</v>
       </c>
     </row>
   </sheetData>
@@ -18508,31 +18508,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>35.11305744233974</v>
+        <v>38.07423538055821</v>
       </c>
       <c r="C2" t="n">
-        <v>36.4325857839947</v>
+        <v>41.35584128618976</v>
       </c>
       <c r="D2" t="n">
-        <v>45.47458298990649</v>
+        <v>32.15257530988045</v>
       </c>
       <c r="E2" t="n">
-        <v>31.74713444242166</v>
+        <v>46.84905581157245</v>
       </c>
       <c r="F2" t="n">
-        <v>35.43481646812431</v>
+        <v>34.75424183796918</v>
       </c>
       <c r="G2" t="n">
-        <v>32.94061056999787</v>
+        <v>41.51620144819982</v>
       </c>
       <c r="H2" t="n">
-        <v>37.49870602959881</v>
+        <v>34.29743772292824</v>
       </c>
       <c r="I2" t="n">
-        <v>48.22417643854237</v>
+        <v>34.37316865243848</v>
       </c>
       <c r="J2" t="n">
-        <v>47.37243600662708</v>
+        <v>49.80286892400342</v>
       </c>
     </row>
   </sheetData>
@@ -18606,31 +18606,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.47188717881112</v>
+        <v>30.32410291340917</v>
       </c>
       <c r="C2" t="n">
-        <v>46.78428580075001</v>
+        <v>45.97882045723728</v>
       </c>
       <c r="D2" t="n">
-        <v>65.01918884115648</v>
+        <v>46.42602137205819</v>
       </c>
       <c r="E2" t="n">
-        <v>44.20864386579453</v>
+        <v>46.12901356887243</v>
       </c>
       <c r="F2" t="n">
-        <v>31.92274680507654</v>
+        <v>40.94730540013972</v>
       </c>
       <c r="G2" t="n">
-        <v>34.5021666186233</v>
+        <v>50.18589080257227</v>
       </c>
       <c r="H2" t="n">
-        <v>35.28477908188891</v>
+        <v>40.14467458784357</v>
       </c>
       <c r="I2" t="n">
-        <v>38.71735155359821</v>
+        <v>29.30390396303119</v>
       </c>
       <c r="J2" t="n">
-        <v>44.66816843557823</v>
+        <v>45.65669077791014</v>
       </c>
     </row>
   </sheetData>
@@ -18704,31 +18704,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.8904756271515</v>
+        <v>40.67525094847487</v>
       </c>
       <c r="C2" t="n">
-        <v>36.78071379665249</v>
+        <v>44.05554190074779</v>
       </c>
       <c r="D2" t="n">
-        <v>24.80315912663258</v>
+        <v>34.01139160291282</v>
       </c>
       <c r="E2" t="n">
-        <v>28.87793004911451</v>
+        <v>38.17438209534176</v>
       </c>
       <c r="F2" t="n">
-        <v>35.75131929929319</v>
+        <v>36.03521363235164</v>
       </c>
       <c r="G2" t="n">
-        <v>51.59116892524449</v>
+        <v>48.36347596616573</v>
       </c>
       <c r="H2" t="n">
-        <v>29.86929722591045</v>
+        <v>33.85434931328529</v>
       </c>
       <c r="I2" t="n">
-        <v>48.77458226927895</v>
+        <v>36.44628044854085</v>
       </c>
       <c r="J2" t="n">
-        <v>57.74254958057938</v>
+        <v>51.53536881727909</v>
       </c>
     </row>
   </sheetData>
@@ -18802,31 +18802,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.0648335123449</v>
+        <v>41.11266400982369</v>
       </c>
       <c r="C2" t="n">
-        <v>38.48031615037979</v>
+        <v>45.04425533244735</v>
       </c>
       <c r="D2" t="n">
-        <v>42.32360312541466</v>
+        <v>36.62088541961283</v>
       </c>
       <c r="E2" t="n">
-        <v>44.64412540523097</v>
+        <v>38.37270089207568</v>
       </c>
       <c r="F2" t="n">
-        <v>37.09796904311075</v>
+        <v>35.62712610403984</v>
       </c>
       <c r="G2" t="n">
-        <v>36.77660561557634</v>
+        <v>42.56274789300586</v>
       </c>
       <c r="H2" t="n">
-        <v>49.54618378470361</v>
+        <v>46.11223739328554</v>
       </c>
       <c r="I2" t="n">
-        <v>27.3023363311768</v>
+        <v>51.71959364981462</v>
       </c>
       <c r="J2" t="n">
-        <v>60.7309002693973</v>
+        <v>30.09704733965649</v>
       </c>
     </row>
   </sheetData>
@@ -18900,31 +18900,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>24.99805471555504</v>
+        <v>22.16556711577879</v>
       </c>
       <c r="C2" t="n">
-        <v>33.64078213556085</v>
+        <v>45.2825894279329</v>
       </c>
       <c r="D2" t="n">
-        <v>46.9394744327583</v>
+        <v>42.22973955381563</v>
       </c>
       <c r="E2" t="n">
-        <v>38.08750754712739</v>
+        <v>28.76993454829239</v>
       </c>
       <c r="F2" t="n">
-        <v>32.51905473952898</v>
+        <v>43.09096639994555</v>
       </c>
       <c r="G2" t="n">
-        <v>39.82017348129609</v>
+        <v>37.17333403034525</v>
       </c>
       <c r="H2" t="n">
-        <v>44.46061721454399</v>
+        <v>47.17114134008428</v>
       </c>
       <c r="I2" t="n">
-        <v>49.39592609251421</v>
+        <v>47.36462564459426</v>
       </c>
       <c r="J2" t="n">
-        <v>39.56466572904429</v>
+        <v>38.47046496167429</v>
       </c>
     </row>
   </sheetData>
@@ -18998,31 +18998,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>32.67294028432151</v>
+        <v>51.5716467725929</v>
       </c>
       <c r="C2" t="n">
-        <v>36.70868640909769</v>
+        <v>49.55631974056174</v>
       </c>
       <c r="D2" t="n">
-        <v>40.53190010319025</v>
+        <v>37.46248642084526</v>
       </c>
       <c r="E2" t="n">
-        <v>28.48222765852147</v>
+        <v>40.59922695740919</v>
       </c>
       <c r="F2" t="n">
-        <v>44.33578246912824</v>
+        <v>32.35516897344029</v>
       </c>
       <c r="G2" t="n">
-        <v>49.42934079829266</v>
+        <v>43.9021927839341</v>
       </c>
       <c r="H2" t="n">
-        <v>59.74703512821277</v>
+        <v>31.74241986898813</v>
       </c>
       <c r="I2" t="n">
-        <v>42.56655843627355</v>
+        <v>31.97793345517943</v>
       </c>
       <c r="J2" t="n">
-        <v>34.27428696624344</v>
+        <v>35.50071598273018</v>
       </c>
     </row>
   </sheetData>
@@ -19096,31 +19096,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>45.36511575527986</v>
+        <v>40.34791616021108</v>
       </c>
       <c r="C2" t="n">
-        <v>52.97863277391285</v>
+        <v>29.68685136119412</v>
       </c>
       <c r="D2" t="n">
-        <v>34.17346664752257</v>
+        <v>34.55739672934062</v>
       </c>
       <c r="E2" t="n">
-        <v>36.26367528291618</v>
+        <v>41.22732031570952</v>
       </c>
       <c r="F2" t="n">
-        <v>46.68734746575895</v>
+        <v>34.33444041201648</v>
       </c>
       <c r="G2" t="n">
-        <v>30.09187543496311</v>
+        <v>36.63006226793075</v>
       </c>
       <c r="H2" t="n">
-        <v>42.27833617983637</v>
+        <v>38.84120777133765</v>
       </c>
       <c r="I2" t="n">
-        <v>45.44865845981867</v>
+        <v>44.67756096674555</v>
       </c>
       <c r="J2" t="n">
-        <v>41.13689880982395</v>
+        <v>57.97933614953308</v>
       </c>
     </row>
   </sheetData>
@@ -19194,31 +19194,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>30.14245597807811</v>
+        <v>36.03111875531197</v>
       </c>
       <c r="C2" t="n">
-        <v>34.19609389023198</v>
+        <v>32.00020747185298</v>
       </c>
       <c r="D2" t="n">
-        <v>46.97040572375074</v>
+        <v>28.91916003965493</v>
       </c>
       <c r="E2" t="n">
-        <v>41.4281427923183</v>
+        <v>41.09804610220194</v>
       </c>
       <c r="F2" t="n">
-        <v>39.78490633786926</v>
+        <v>29.88370895308377</v>
       </c>
       <c r="G2" t="n">
-        <v>34.69534835452774</v>
+        <v>64.67234966816484</v>
       </c>
       <c r="H2" t="n">
-        <v>40.41174867171957</v>
+        <v>38.34494294456369</v>
       </c>
       <c r="I2" t="n">
-        <v>46.36712508587729</v>
+        <v>45.18472201860695</v>
       </c>
       <c r="J2" t="n">
-        <v>45.01198706479607</v>
+        <v>44.09749449032366</v>
       </c>
     </row>
   </sheetData>
@@ -19292,31 +19292,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>38.18522628264267</v>
+        <v>34.59491533799621</v>
       </c>
       <c r="C2" t="n">
-        <v>37.2121713032919</v>
+        <v>37.54133563278547</v>
       </c>
       <c r="D2" t="n">
-        <v>38.94476262838484</v>
+        <v>49.4945081185239</v>
       </c>
       <c r="E2" t="n">
-        <v>32.97373437594345</v>
+        <v>36.66762902353388</v>
       </c>
       <c r="F2" t="n">
-        <v>43.84015958180407</v>
+        <v>50.36593800825083</v>
       </c>
       <c r="G2" t="n">
-        <v>45.31005966271477</v>
+        <v>51.95341329046595</v>
       </c>
       <c r="H2" t="n">
-        <v>31.08494348221395</v>
+        <v>26.859653110782</v>
       </c>
       <c r="I2" t="n">
-        <v>52.89714072796799</v>
+        <v>44.87897491181642</v>
       </c>
       <c r="J2" t="n">
-        <v>58.05694166668732</v>
+        <v>37.01922507118592</v>
       </c>
     </row>
   </sheetData>
@@ -19390,31 +19390,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>44.29031544138937</v>
+        <v>37.63744382640602</v>
       </c>
       <c r="C2" t="n">
-        <v>53.67595546127923</v>
+        <v>36.5991219386582</v>
       </c>
       <c r="D2" t="n">
-        <v>39.17801664239248</v>
+        <v>52.1546170056107</v>
       </c>
       <c r="E2" t="n">
-        <v>35.38048066742862</v>
+        <v>35.05714422398561</v>
       </c>
       <c r="F2" t="n">
-        <v>43.54783675799536</v>
+        <v>53.00854721100775</v>
       </c>
       <c r="G2" t="n">
-        <v>34.83926294806532</v>
+        <v>38.88684632471283</v>
       </c>
       <c r="H2" t="n">
-        <v>36.58638223115205</v>
+        <v>40.49900445904328</v>
       </c>
       <c r="I2" t="n">
-        <v>29.6491105070741</v>
+        <v>35.74480531169768</v>
       </c>
       <c r="J2" t="n">
-        <v>33.36767508830417</v>
+        <v>35.1401456513072</v>
       </c>
     </row>
   </sheetData>
@@ -19488,31 +19488,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>25.90629228751579</v>
+        <v>42.49975448263262</v>
       </c>
       <c r="C2" t="n">
-        <v>53.96349168795282</v>
+        <v>38.83622521761924</v>
       </c>
       <c r="D2" t="n">
-        <v>48.13953016783547</v>
+        <v>35.07614378526413</v>
       </c>
       <c r="E2" t="n">
-        <v>37.98678737934531</v>
+        <v>47.31706703172217</v>
       </c>
       <c r="F2" t="n">
-        <v>36.73187778306215</v>
+        <v>36.57178373465952</v>
       </c>
       <c r="G2" t="n">
-        <v>39.13795927402126</v>
+        <v>34.94987264940078</v>
       </c>
       <c r="H2" t="n">
-        <v>36.73193545541644</v>
+        <v>33.49541695310069</v>
       </c>
       <c r="I2" t="n">
-        <v>39.47123988494486</v>
+        <v>57.11922406808095</v>
       </c>
       <c r="J2" t="n">
-        <v>58.64974888975854</v>
+        <v>42.53814439246921</v>
       </c>
     </row>
   </sheetData>
@@ -19586,31 +19586,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.7075126941997</v>
+        <v>34.49338914508272</v>
       </c>
       <c r="C2" t="n">
-        <v>49.27579863384979</v>
+        <v>42.92163587369328</v>
       </c>
       <c r="D2" t="n">
-        <v>49.2996444591469</v>
+        <v>42.37588942469282</v>
       </c>
       <c r="E2" t="n">
-        <v>26.5229543409163</v>
+        <v>26.99149065994441</v>
       </c>
       <c r="F2" t="n">
-        <v>44.12630469973219</v>
+        <v>33.32811707146193</v>
       </c>
       <c r="G2" t="n">
-        <v>37.15773500623426</v>
+        <v>36.58901768601116</v>
       </c>
       <c r="H2" t="n">
-        <v>40.14326011189902</v>
+        <v>44.5779464295011</v>
       </c>
       <c r="I2" t="n">
-        <v>48.18002698375906</v>
+        <v>48.3920569684728</v>
       </c>
       <c r="J2" t="n">
-        <v>35.92870078821552</v>
+        <v>44.18085468041492</v>
       </c>
     </row>
   </sheetData>
@@ -19684,31 +19684,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33.61031821208294</v>
+        <v>28.25362608878917</v>
       </c>
       <c r="C2" t="n">
-        <v>33.81279436814992</v>
+        <v>38.37081206957288</v>
       </c>
       <c r="D2" t="n">
-        <v>50.59709216449473</v>
+        <v>33.48407376402437</v>
       </c>
       <c r="E2" t="n">
-        <v>33.22613131208878</v>
+        <v>43.98731528794617</v>
       </c>
       <c r="F2" t="n">
-        <v>44.64153409367033</v>
+        <v>39.30488089798271</v>
       </c>
       <c r="G2" t="n">
-        <v>31.42292620036391</v>
+        <v>41.51309470261354</v>
       </c>
       <c r="H2" t="n">
-        <v>41.87133890691444</v>
+        <v>38.27949916269577</v>
       </c>
       <c r="I2" t="n">
-        <v>44.44750240081876</v>
+        <v>41.11556055514975</v>
       </c>
       <c r="J2" t="n">
-        <v>37.78017845525903</v>
+        <v>46.38610791681764</v>
       </c>
     </row>
   </sheetData>
@@ -19782,31 +19782,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>26.21151140243977</v>
+        <v>34.64741823830332</v>
       </c>
       <c r="C2" t="n">
-        <v>30.29547297579052</v>
+        <v>34.79380369322114</v>
       </c>
       <c r="D2" t="n">
-        <v>37.88718292405875</v>
+        <v>31.65836012906341</v>
       </c>
       <c r="E2" t="n">
-        <v>34.21324981817822</v>
+        <v>32.13561021984331</v>
       </c>
       <c r="F2" t="n">
-        <v>34.69875578666876</v>
+        <v>42.19234309918828</v>
       </c>
       <c r="G2" t="n">
-        <v>32.1897067762531</v>
+        <v>51.93699969610208</v>
       </c>
       <c r="H2" t="n">
-        <v>38.7581948999607</v>
+        <v>35.86158576187493</v>
       </c>
       <c r="I2" t="n">
-        <v>36.81040928948204</v>
+        <v>39.58711494562075</v>
       </c>
       <c r="J2" t="n">
-        <v>57.43868188591547</v>
+        <v>37.36091714927969</v>
       </c>
     </row>
   </sheetData>
@@ -19880,31 +19880,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>34.19809047330111</v>
+        <v>53.43141114535656</v>
       </c>
       <c r="C2" t="n">
-        <v>47.59986948453645</v>
+        <v>45.17062001626989</v>
       </c>
       <c r="D2" t="n">
-        <v>43.49786567396309</v>
+        <v>36.44718243599755</v>
       </c>
       <c r="E2" t="n">
-        <v>37.79138945322824</v>
+        <v>35.61809120369284</v>
       </c>
       <c r="F2" t="n">
-        <v>33.99438594847332</v>
+        <v>51.74610500942807</v>
       </c>
       <c r="G2" t="n">
-        <v>35.12074559383224</v>
+        <v>33.69645534020412</v>
       </c>
       <c r="H2" t="n">
-        <v>35.01528387933192</v>
+        <v>36.54739931560607</v>
       </c>
       <c r="I2" t="n">
-        <v>39.36548848240278</v>
+        <v>36.00953720835437</v>
       </c>
       <c r="J2" t="n">
-        <v>47.79545732133307</v>
+        <v>36.47624474500878</v>
       </c>
     </row>
   </sheetData>
@@ -19978,31 +19978,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>28.92204091328061</v>
+        <v>42.35315435644004</v>
       </c>
       <c r="C2" t="n">
-        <v>37.60315550008447</v>
+        <v>38.1077621607802</v>
       </c>
       <c r="D2" t="n">
-        <v>34.15278457712056</v>
+        <v>23.72060458027827</v>
       </c>
       <c r="E2" t="n">
-        <v>33.47875081981989</v>
+        <v>38.18325517324664</v>
       </c>
       <c r="F2" t="n">
-        <v>43.50452245674105</v>
+        <v>52.64342168168005</v>
       </c>
       <c r="G2" t="n">
-        <v>38.0478255507736</v>
+        <v>37.5253243992188</v>
       </c>
       <c r="H2" t="n">
-        <v>36.42623640832333</v>
+        <v>41.73833683637208</v>
       </c>
       <c r="I2" t="n">
-        <v>45.31157372995483</v>
+        <v>39.01929580153227</v>
       </c>
       <c r="J2" t="n">
-        <v>45.85013917729479</v>
+        <v>42.83149680081426</v>
       </c>
     </row>
   </sheetData>
@@ -20076,31 +20076,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>37.20245733829628</v>
+        <v>44.62061907084041</v>
       </c>
       <c r="C2" t="n">
-        <v>47.23226654445961</v>
+        <v>36.47433964769736</v>
       </c>
       <c r="D2" t="n">
-        <v>55.11321597255743</v>
+        <v>55.6268128699599</v>
       </c>
       <c r="E2" t="n">
-        <v>27.57730817691092</v>
+        <v>48.15528779960916</v>
       </c>
       <c r="F2" t="n">
-        <v>33.25562634175053</v>
+        <v>64.51671454870659</v>
       </c>
       <c r="G2" t="n">
-        <v>49.98254519688508</v>
+        <v>34.68829075823968</v>
       </c>
       <c r="H2" t="n">
-        <v>43.60696647364723</v>
+        <v>35.48585812372198</v>
       </c>
       <c r="I2" t="n">
-        <v>39.86346228899683</v>
+        <v>43.97839045714403</v>
       </c>
       <c r="J2" t="n">
-        <v>59.65413094908577</v>
+        <v>27.98579583551572</v>
       </c>
     </row>
   </sheetData>
@@ -20174,31 +20174,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.71898025391983</v>
+        <v>43.96847704674179</v>
       </c>
       <c r="C2" t="n">
-        <v>48.01498839839373</v>
+        <v>38.59580486040014</v>
       </c>
       <c r="D2" t="n">
-        <v>37.52723534926417</v>
+        <v>27.69941988524574</v>
       </c>
       <c r="E2" t="n">
-        <v>44.30777864296009</v>
+        <v>39.93758249022621</v>
       </c>
       <c r="F2" t="n">
-        <v>41.97851341763848</v>
+        <v>39.74231254622646</v>
       </c>
       <c r="G2" t="n">
-        <v>34.44013307872686</v>
+        <v>40.26187161101468</v>
       </c>
       <c r="H2" t="n">
-        <v>50.84710432473318</v>
+        <v>35.73299251227037</v>
       </c>
       <c r="I2" t="n">
-        <v>38.05871415566288</v>
+        <v>35.46045971742623</v>
       </c>
       <c r="J2" t="n">
-        <v>30.92998073014765</v>
+        <v>37.18883752594846</v>
       </c>
     </row>
   </sheetData>
